--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAC0C05-1EEC-4F66-BCD3-07CFA8DA5BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303206BD-DA7C-4E1F-8897-49F8BA74D357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,7 +500,7 @@
     <numFmt numFmtId="174" formatCode="0.00_ ;\-0.00\ "/>
     <numFmt numFmtId="175" formatCode="[$-14409]dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,14 +644,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="14"/>
@@ -1754,19 +1746,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -1809,25 +1801,25 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="172" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1839,7 +1831,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1902,7 +1894,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1926,47 +1918,47 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1982,31 +1974,31 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2054,7 +2046,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyProtection="1">
@@ -2068,6 +2060,218 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="39" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2080,6 +2284,138 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2096,12 +2432,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2130,346 +2460,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="40" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="40" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="39" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2955,20 +2947,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="228" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
@@ -2976,26 +2968,26 @@
       <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="156"/>
-      <c r="Q2" s="156"/>
-      <c r="R2" s="156"/>
-      <c r="S2" s="156"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="228"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="N2" s="246"/>
+      <c r="O2" s="246"/>
+      <c r="P2" s="246"/>
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
@@ -3016,38 +3008,38 @@
       <c r="S3" s="10"/>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="240" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="179"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="179"/>
-      <c r="J4" s="179"/>
-      <c r="K4" s="179"/>
-      <c r="L4" s="179"/>
+      <c r="B4" s="240"/>
+      <c r="C4" s="240"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+      <c r="L4" s="240"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
     </row>
     <row r="5" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="180"/>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
+      <c r="A5" s="254"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="254"/>
+      <c r="J5" s="254"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="254"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
@@ -3056,20 +3048,20 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="241" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="181"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="181"/>
-      <c r="E6" s="181"/>
-      <c r="F6" s="181"/>
-      <c r="G6" s="181"/>
-      <c r="H6" s="181"/>
-      <c r="I6" s="181"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="181"/>
-      <c r="L6" s="181"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="241"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="241"/>
+      <c r="G6" s="241"/>
+      <c r="H6" s="241"/>
+      <c r="I6" s="241"/>
+      <c r="J6" s="241"/>
+      <c r="K6" s="241"/>
+      <c r="L6" s="241"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
@@ -3115,7 +3107,7 @@
       <c r="K8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="252"/>
+      <c r="L8" s="150"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
@@ -3124,9 +3116,9 @@
       <c r="B9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="251"/>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
+      <c r="C9" s="242"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="H9" s="20" t="s">
@@ -3137,7 +3129,7 @@
       <c r="K9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="253"/>
+      <c r="L9" s="151"/>
       <c r="N9" s="10" t="s">
         <v>39</v>
       </c>
@@ -3201,7 +3193,7 @@
       <c r="K11" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="254"/>
+      <c r="L11" s="152"/>
       <c r="N11" s="10" t="s">
         <v>59</v>
       </c>
@@ -3232,7 +3224,7 @@
       <c r="K12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="254"/>
+      <c r="L12" s="152"/>
       <c r="N12" s="17" t="s">
         <v>60</v>
       </c>
@@ -3275,41 +3267,41 @@
       <c r="A15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="167" t="s">
+      <c r="B15" s="229" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="167"/>
-      <c r="D15" s="169" t="s">
+      <c r="C15" s="229"/>
+      <c r="D15" s="231" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="170"/>
-      <c r="F15" s="170" t="s">
+      <c r="E15" s="232"/>
+      <c r="F15" s="232" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="175" t="s">
+      <c r="G15" s="237" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="175"/>
-      <c r="I15" s="175"/>
-      <c r="J15" s="175"/>
-      <c r="K15" s="176"/>
-      <c r="L15" s="159" t="s">
+      <c r="H15" s="237"/>
+      <c r="I15" s="237"/>
+      <c r="J15" s="237"/>
+      <c r="K15" s="238"/>
+      <c r="L15" s="247" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="150" t="s">
+      <c r="N15" s="206" t="s">
         <v>61</v>
       </c>
-      <c r="O15" s="162" t="s">
+      <c r="O15" s="250" t="s">
         <v>62</v>
       </c>
-      <c r="P15" s="163"/>
-      <c r="Q15" s="150" t="s">
+      <c r="P15" s="251"/>
+      <c r="Q15" s="206" t="s">
         <v>63</v>
       </c>
-      <c r="R15" s="153" t="s">
+      <c r="R15" s="243" t="s">
         <v>64</v>
       </c>
-      <c r="S15" s="150" t="s">
+      <c r="S15" s="206" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3317,23 +3309,23 @@
       <c r="A16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="168"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="172"/>
-      <c r="F16" s="173"/>
-      <c r="G16" s="177"/>
-      <c r="H16" s="177"/>
-      <c r="I16" s="177"/>
-      <c r="J16" s="177"/>
-      <c r="K16" s="178"/>
-      <c r="L16" s="160"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="164"/>
-      <c r="P16" s="165"/>
-      <c r="Q16" s="151"/>
-      <c r="R16" s="154"/>
-      <c r="S16" s="151"/>
+      <c r="B16" s="230"/>
+      <c r="C16" s="230"/>
+      <c r="D16" s="233"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="221"/>
+      <c r="H16" s="221"/>
+      <c r="I16" s="221"/>
+      <c r="J16" s="221"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="248"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="252"/>
+      <c r="P16" s="253"/>
+      <c r="Q16" s="207"/>
+      <c r="R16" s="244"/>
+      <c r="S16" s="207"/>
     </row>
     <row r="17" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
@@ -3351,7 +3343,7 @@
       <c r="E17" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="174"/>
+      <c r="F17" s="236"/>
       <c r="G17" s="36" t="s">
         <v>25</v>
       </c>
@@ -3367,33 +3359,36 @@
       <c r="K17" s="38">
         <v>2</v>
       </c>
-      <c r="L17" s="161"/>
-      <c r="N17" s="152"/>
+      <c r="L17" s="249"/>
+      <c r="N17" s="208"/>
       <c r="O17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="P17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="Q17" s="152"/>
-      <c r="R17" s="155"/>
-      <c r="S17" s="152"/>
+      <c r="Q17" s="208"/>
+      <c r="R17" s="245"/>
+      <c r="S17" s="208"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="193" t="s">
+      <c r="A18" s="220" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="177"/>
-      <c r="C18" s="177"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="194"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="157"/>
-      <c r="H18" s="157"/>
-      <c r="I18" s="157"/>
-      <c r="J18" s="157"/>
-      <c r="K18" s="184"/>
-      <c r="L18" s="186" t="s">
+      <c r="B18" s="221"/>
+      <c r="C18" s="221"/>
+      <c r="D18" s="221"/>
+      <c r="E18" s="222"/>
+      <c r="F18" s="226"/>
+      <c r="G18" s="209"/>
+      <c r="H18" s="209">
+        <f>F18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="209"/>
+      <c r="J18" s="209"/>
+      <c r="K18" s="211"/>
+      <c r="L18" s="213" t="s">
         <v>112</v>
       </c>
       <c r="N18" s="138" t="str">
@@ -3408,25 +3403,25 @@
         <f>IF(ISBLANK(E20),"",E20)</f>
         <v/>
       </c>
-      <c r="Q18" s="188" t="s">
+      <c r="Q18" s="215" t="s">
         <v>90</v>
       </c>
       <c r="R18" s="201"/>
       <c r="S18" s="40"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="195"/>
-      <c r="B19" s="196"/>
-      <c r="C19" s="196"/>
-      <c r="D19" s="196"/>
-      <c r="E19" s="197"/>
-      <c r="F19" s="199"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
-      <c r="J19" s="158"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="187"/>
+      <c r="A19" s="223"/>
+      <c r="B19" s="224"/>
+      <c r="C19" s="224"/>
+      <c r="D19" s="224"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="227"/>
+      <c r="G19" s="210"/>
+      <c r="H19" s="210"/>
+      <c r="I19" s="210"/>
+      <c r="J19" s="210"/>
+      <c r="K19" s="212"/>
+      <c r="L19" s="214"/>
       <c r="N19" s="141" t="str">
         <f>A21</f>
         <v/>
@@ -3439,7 +3434,7 @@
         <f>IF(ISBLANK(E21),"",E21)</f>
         <v/>
       </c>
-      <c r="Q19" s="189"/>
+      <c r="Q19" s="216"/>
       <c r="R19" s="202"/>
       <c r="S19" s="147"/>
       <c r="V19" t="s">
@@ -3484,8 +3479,8 @@
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="148"/>
-      <c r="B20" s="182"/>
-      <c r="C20" s="182"/>
+      <c r="B20" s="199"/>
+      <c r="C20" s="199"/>
       <c r="D20" s="144"/>
       <c r="E20" s="41"/>
       <c r="F20" s="134"/>
@@ -3494,7 +3489,7 @@
       <c r="I20" s="134"/>
       <c r="J20" s="134"/>
       <c r="K20" s="134"/>
-      <c r="L20" s="191" t="s">
+      <c r="L20" s="218" t="s">
         <v>89</v>
       </c>
       <c r="N20" s="138" t="str">
@@ -3509,7 +3504,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q20" s="189"/>
+      <c r="Q20" s="216"/>
       <c r="R20" s="202"/>
       <c r="S20" s="40"/>
       <c r="T20"/>
@@ -3685,8 +3680,8 @@
         <f t="shared" ref="A21" si="1">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B21" s="183"/>
-      <c r="C21" s="183"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="200"/>
       <c r="D21" s="145"/>
       <c r="E21" s="42"/>
       <c r="F21" s="132" t="str">
@@ -3698,7 +3693,7 @@
       <c r="I21" s="132"/>
       <c r="J21" s="132"/>
       <c r="K21" s="133"/>
-      <c r="L21" s="191"/>
+      <c r="L21" s="218"/>
       <c r="N21" s="141" t="str">
         <f>A23</f>
         <v/>
@@ -3711,7 +3706,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q21" s="189"/>
+      <c r="Q21" s="216"/>
       <c r="R21" s="202"/>
       <c r="S21" s="147"/>
       <c r="T21"/>
@@ -3881,8 +3876,8 @@
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="148"/>
-      <c r="B22" s="182"/>
-      <c r="C22" s="182"/>
+      <c r="B22" s="199"/>
+      <c r="C22" s="199"/>
       <c r="D22" s="144"/>
       <c r="E22" s="41"/>
       <c r="F22" s="134" t="str">
@@ -3894,7 +3889,7 @@
       <c r="I22" s="134"/>
       <c r="J22" s="134"/>
       <c r="K22" s="134"/>
-      <c r="L22" s="191"/>
+      <c r="L22" s="218"/>
       <c r="N22" s="138" t="str">
         <f t="shared" ref="N22" si="13">IF(ISBLANK(A24),"",A24)</f>
         <v/>
@@ -3907,7 +3902,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q22" s="189"/>
+      <c r="Q22" s="216"/>
       <c r="R22" s="202"/>
       <c r="S22" s="40"/>
       <c r="T22"/>
@@ -4029,8 +4024,8 @@
         <f t="shared" ref="A23:A25" si="14">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="183"/>
-      <c r="C23" s="183"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="200"/>
       <c r="D23" s="145"/>
       <c r="E23" s="42"/>
       <c r="F23" s="132" t="str">
@@ -4042,7 +4037,7 @@
       <c r="I23" s="132"/>
       <c r="J23" s="132"/>
       <c r="K23" s="133"/>
-      <c r="L23" s="191"/>
+      <c r="L23" s="218"/>
       <c r="N23" s="141" t="str">
         <f t="shared" ref="N23" si="15">A25</f>
         <v/>
@@ -4055,7 +4050,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q23" s="189"/>
+      <c r="Q23" s="216"/>
       <c r="R23" s="202"/>
       <c r="S23" s="147"/>
       <c r="T23"/>
@@ -4174,8 +4169,8 @@
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="148"/>
-      <c r="B24" s="182"/>
-      <c r="C24" s="182"/>
+      <c r="B24" s="199"/>
+      <c r="C24" s="199"/>
       <c r="D24" s="144"/>
       <c r="E24" s="41"/>
       <c r="F24" s="134" t="str">
@@ -4187,7 +4182,7 @@
       <c r="I24" s="134"/>
       <c r="J24" s="134"/>
       <c r="K24" s="134"/>
-      <c r="L24" s="191"/>
+      <c r="L24" s="218"/>
       <c r="N24" s="138" t="str">
         <f t="shared" ref="N24" si="16">IF(ISBLANK(A26),"",A26)</f>
         <v/>
@@ -4200,7 +4195,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q24" s="189"/>
+      <c r="Q24" s="216"/>
       <c r="R24" s="202"/>
       <c r="S24" s="40"/>
       <c r="T24"/>
@@ -4322,8 +4317,8 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="B25" s="183"/>
-      <c r="C25" s="183"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="200"/>
       <c r="D25" s="145"/>
       <c r="E25" s="42"/>
       <c r="F25" s="132" t="str">
@@ -4335,7 +4330,7 @@
       <c r="I25" s="132"/>
       <c r="J25" s="132"/>
       <c r="K25" s="133"/>
-      <c r="L25" s="191"/>
+      <c r="L25" s="218"/>
       <c r="N25" s="141" t="str">
         <f t="shared" ref="N25" si="17">A27</f>
         <v/>
@@ -4348,7 +4343,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q25" s="189"/>
+      <c r="Q25" s="216"/>
       <c r="R25" s="202"/>
       <c r="S25" s="147"/>
       <c r="T25"/>
@@ -4467,8 +4462,8 @@
     </row>
     <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="148"/>
-      <c r="B26" s="182"/>
-      <c r="C26" s="182"/>
+      <c r="B26" s="199"/>
+      <c r="C26" s="199"/>
       <c r="D26" s="144"/>
       <c r="E26" s="41"/>
       <c r="F26" s="134" t="str">
@@ -4480,7 +4475,7 @@
       <c r="I26" s="134"/>
       <c r="J26" s="134"/>
       <c r="K26" s="134"/>
-      <c r="L26" s="191"/>
+      <c r="L26" s="218"/>
       <c r="N26" s="138" t="str">
         <f t="shared" ref="N26" si="18">IF(ISBLANK(A28),"",A28)</f>
         <v/>
@@ -4493,7 +4488,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q26" s="189"/>
+      <c r="Q26" s="216"/>
       <c r="R26" s="202"/>
       <c r="S26" s="40"/>
       <c r="T26"/>
@@ -4615,8 +4610,8 @@
         <f t="shared" ref="A27" si="19">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="183"/>
-      <c r="C27" s="183"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="200"/>
       <c r="D27" s="145"/>
       <c r="E27" s="42"/>
       <c r="F27" s="132" t="str">
@@ -4628,7 +4623,7 @@
       <c r="I27" s="132"/>
       <c r="J27" s="132"/>
       <c r="K27" s="133"/>
-      <c r="L27" s="191"/>
+      <c r="L27" s="218"/>
       <c r="N27" s="141" t="str">
         <f t="shared" ref="N27" si="20">A29</f>
         <v/>
@@ -4641,7 +4636,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q27" s="189"/>
+      <c r="Q27" s="216"/>
       <c r="R27" s="202"/>
       <c r="S27" s="147"/>
       <c r="T27"/>
@@ -4760,8 +4755,8 @@
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="149"/>
-      <c r="B28" s="182"/>
-      <c r="C28" s="182"/>
+      <c r="B28" s="199"/>
+      <c r="C28" s="199"/>
       <c r="D28" s="144"/>
       <c r="E28" s="41"/>
       <c r="F28" s="134" t="str">
@@ -4773,7 +4768,7 @@
       <c r="I28" s="134"/>
       <c r="J28" s="134"/>
       <c r="K28" s="134"/>
-      <c r="L28" s="191"/>
+      <c r="L28" s="218"/>
       <c r="N28" s="138" t="str">
         <f t="shared" ref="N28" si="21">IF(ISBLANK(A30),"",A30)</f>
         <v/>
@@ -4786,7 +4781,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q28" s="189"/>
+      <c r="Q28" s="216"/>
       <c r="R28" s="202"/>
       <c r="S28" s="40"/>
       <c r="T28"/>
@@ -4908,8 +4903,8 @@
         <f t="shared" ref="A29" si="22">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="183"/>
-      <c r="C29" s="183"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="200"/>
       <c r="D29" s="145"/>
       <c r="E29" s="42"/>
       <c r="F29" s="132" t="str">
@@ -4921,7 +4916,7 @@
       <c r="I29" s="132"/>
       <c r="J29" s="132"/>
       <c r="K29" s="133"/>
-      <c r="L29" s="191"/>
+      <c r="L29" s="218"/>
       <c r="N29" s="141" t="str">
         <f t="shared" ref="N29" si="23">A31</f>
         <v/>
@@ -4934,7 +4929,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q29" s="189"/>
+      <c r="Q29" s="216"/>
       <c r="R29" s="202"/>
       <c r="S29" s="147"/>
       <c r="T29"/>
@@ -5053,8 +5048,8 @@
     </row>
     <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="148"/>
-      <c r="B30" s="182"/>
-      <c r="C30" s="182"/>
+      <c r="B30" s="199"/>
+      <c r="C30" s="199"/>
       <c r="D30" s="144"/>
       <c r="E30" s="41"/>
       <c r="F30" s="134" t="str">
@@ -5066,7 +5061,7 @@
       <c r="I30" s="134"/>
       <c r="J30" s="134"/>
       <c r="K30" s="134"/>
-      <c r="L30" s="191"/>
+      <c r="L30" s="218"/>
       <c r="N30" s="138" t="str">
         <f t="shared" ref="N30" si="24">IF(ISBLANK(A32),"",A32)</f>
         <v/>
@@ -5079,7 +5074,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q30" s="189"/>
+      <c r="Q30" s="216"/>
       <c r="R30" s="202"/>
       <c r="S30" s="40"/>
       <c r="T30"/>
@@ -5201,8 +5196,8 @@
         <f t="shared" ref="A31" si="25">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="183"/>
-      <c r="C31" s="183"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="200"/>
       <c r="D31" s="145"/>
       <c r="E31" s="42"/>
       <c r="F31" s="132" t="str">
@@ -5214,7 +5209,7 @@
       <c r="I31" s="132"/>
       <c r="J31" s="132"/>
       <c r="K31" s="133"/>
-      <c r="L31" s="191"/>
+      <c r="L31" s="218"/>
       <c r="N31" s="141" t="str">
         <f t="shared" ref="N31" si="26">A33</f>
         <v/>
@@ -5227,7 +5222,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q31" s="189"/>
+      <c r="Q31" s="216"/>
       <c r="R31" s="202"/>
       <c r="S31" s="147"/>
       <c r="T31"/>
@@ -5346,8 +5341,8 @@
     </row>
     <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="148"/>
-      <c r="B32" s="182"/>
-      <c r="C32" s="182"/>
+      <c r="B32" s="199"/>
+      <c r="C32" s="199"/>
       <c r="D32" s="144"/>
       <c r="E32" s="41"/>
       <c r="F32" s="134" t="str">
@@ -5359,7 +5354,7 @@
       <c r="I32" s="134"/>
       <c r="J32" s="134"/>
       <c r="K32" s="134"/>
-      <c r="L32" s="191"/>
+      <c r="L32" s="218"/>
       <c r="N32" s="138" t="str">
         <f t="shared" ref="N32" si="27">IF(ISBLANK(A34),"",A34)</f>
         <v/>
@@ -5372,7 +5367,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q32" s="189"/>
+      <c r="Q32" s="216"/>
       <c r="R32" s="202"/>
       <c r="S32" s="40"/>
       <c r="T32"/>
@@ -5494,8 +5489,8 @@
         <f t="shared" ref="A33" si="28">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="183"/>
-      <c r="C33" s="183"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="200"/>
       <c r="D33" s="145"/>
       <c r="E33" s="42"/>
       <c r="F33" s="132" t="str">
@@ -5507,7 +5502,7 @@
       <c r="I33" s="132"/>
       <c r="J33" s="132"/>
       <c r="K33" s="133"/>
-      <c r="L33" s="191"/>
+      <c r="L33" s="218"/>
       <c r="N33" s="141" t="str">
         <f t="shared" ref="N33" si="29">A35</f>
         <v/>
@@ -5520,7 +5515,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q33" s="189"/>
+      <c r="Q33" s="216"/>
       <c r="R33" s="202"/>
       <c r="S33" s="147"/>
       <c r="T33"/>
@@ -5639,8 +5634,8 @@
     </row>
     <row r="34" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="148"/>
-      <c r="B34" s="182"/>
-      <c r="C34" s="182"/>
+      <c r="B34" s="199"/>
+      <c r="C34" s="199"/>
       <c r="D34" s="144"/>
       <c r="E34" s="41"/>
       <c r="F34" s="134" t="str">
@@ -5652,7 +5647,7 @@
       <c r="I34" s="134"/>
       <c r="J34" s="134"/>
       <c r="K34" s="134"/>
-      <c r="L34" s="191"/>
+      <c r="L34" s="218"/>
       <c r="N34" s="138" t="str">
         <f t="shared" ref="N34" si="30">IF(ISBLANK(A36),"",A36)</f>
         <v/>
@@ -5665,7 +5660,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q34" s="189"/>
+      <c r="Q34" s="216"/>
       <c r="R34" s="202"/>
       <c r="S34" s="40"/>
       <c r="T34"/>
@@ -5787,8 +5782,8 @@
         <f t="shared" ref="A35" si="31">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="183"/>
-      <c r="C35" s="183"/>
+      <c r="B35" s="200"/>
+      <c r="C35" s="200"/>
       <c r="D35" s="145"/>
       <c r="E35" s="42"/>
       <c r="F35" s="132" t="str">
@@ -5800,7 +5795,7 @@
       <c r="I35" s="132"/>
       <c r="J35" s="132"/>
       <c r="K35" s="133"/>
-      <c r="L35" s="191"/>
+      <c r="L35" s="218"/>
       <c r="N35" s="141" t="str">
         <f t="shared" ref="N35" si="32">A37</f>
         <v/>
@@ -5813,7 +5808,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Q35" s="189"/>
+      <c r="Q35" s="216"/>
       <c r="R35" s="202"/>
       <c r="S35" s="147"/>
       <c r="T35"/>
@@ -5932,8 +5927,8 @@
     </row>
     <row r="36" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="148"/>
-      <c r="B36" s="182"/>
-      <c r="C36" s="182"/>
+      <c r="B36" s="199"/>
+      <c r="C36" s="199"/>
       <c r="D36" s="144"/>
       <c r="E36" s="41"/>
       <c r="F36" s="134" t="str">
@@ -5945,7 +5940,7 @@
       <c r="I36" s="134"/>
       <c r="J36" s="134"/>
       <c r="K36" s="134"/>
-      <c r="L36" s="191"/>
+      <c r="L36" s="218"/>
       <c r="N36" s="138" t="str">
         <f t="shared" ref="N36" si="33">IF(ISBLANK(A38),"",A38)</f>
         <v/>
@@ -5958,7 +5953,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q36" s="189"/>
+      <c r="Q36" s="216"/>
       <c r="R36" s="202"/>
       <c r="S36" s="40"/>
       <c r="T36"/>
@@ -6080,8 +6075,8 @@
         <f t="shared" ref="A37" si="35">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="183"/>
-      <c r="C37" s="183"/>
+      <c r="B37" s="200"/>
+      <c r="C37" s="200"/>
       <c r="D37" s="145"/>
       <c r="E37" s="42"/>
       <c r="F37" s="132" t="str">
@@ -6093,7 +6088,7 @@
       <c r="I37" s="132"/>
       <c r="J37" s="132"/>
       <c r="K37" s="133"/>
-      <c r="L37" s="191"/>
+      <c r="L37" s="218"/>
       <c r="N37" s="141" t="str">
         <f t="shared" ref="N37" si="36">A39</f>
         <v/>
@@ -6106,7 +6101,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q37" s="189"/>
+      <c r="Q37" s="216"/>
       <c r="R37" s="202"/>
       <c r="S37" s="147"/>
       <c r="T37"/>
@@ -6225,8 +6220,8 @@
     </row>
     <row r="38" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="148"/>
-      <c r="B38" s="182"/>
-      <c r="C38" s="182"/>
+      <c r="B38" s="199"/>
+      <c r="C38" s="199"/>
       <c r="D38" s="144"/>
       <c r="E38" s="41"/>
       <c r="F38" s="134" t="str">
@@ -6238,7 +6233,7 @@
       <c r="I38" s="134"/>
       <c r="J38" s="134"/>
       <c r="K38" s="134"/>
-      <c r="L38" s="191"/>
+      <c r="L38" s="218"/>
       <c r="N38" s="138" t="str">
         <f t="shared" ref="N38" si="37">IF(ISBLANK(A40),"",A40)</f>
         <v/>
@@ -6251,7 +6246,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q38" s="189"/>
+      <c r="Q38" s="216"/>
       <c r="R38" s="202"/>
       <c r="S38" s="40"/>
       <c r="T38"/>
@@ -6373,8 +6368,8 @@
         <f t="shared" ref="A39" si="38">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="183"/>
-      <c r="C39" s="183"/>
+      <c r="B39" s="200"/>
+      <c r="C39" s="200"/>
       <c r="D39" s="145"/>
       <c r="E39" s="42"/>
       <c r="F39" s="132" t="str">
@@ -6386,7 +6381,7 @@
       <c r="I39" s="132"/>
       <c r="J39" s="132"/>
       <c r="K39" s="133"/>
-      <c r="L39" s="191"/>
+      <c r="L39" s="218"/>
       <c r="N39" s="141" t="str">
         <f t="shared" ref="N39" si="39">A41</f>
         <v/>
@@ -6399,7 +6394,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q39" s="189"/>
+      <c r="Q39" s="216"/>
       <c r="R39" s="202"/>
       <c r="S39" s="147"/>
       <c r="T39"/>
@@ -6518,8 +6513,8 @@
     </row>
     <row r="40" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="148"/>
-      <c r="B40" s="182"/>
-      <c r="C40" s="182"/>
+      <c r="B40" s="199"/>
+      <c r="C40" s="199"/>
       <c r="D40" s="144"/>
       <c r="E40" s="41"/>
       <c r="F40" s="134" t="str">
@@ -6531,7 +6526,7 @@
       <c r="I40" s="134"/>
       <c r="J40" s="134"/>
       <c r="K40" s="134"/>
-      <c r="L40" s="191"/>
+      <c r="L40" s="218"/>
       <c r="N40" s="138" t="str">
         <f t="shared" ref="N40" si="40">IF(ISBLANK(A42),"",A42)</f>
         <v/>
@@ -6544,7 +6539,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q40" s="189"/>
+      <c r="Q40" s="216"/>
       <c r="R40" s="202"/>
       <c r="S40" s="40"/>
       <c r="T40"/>
@@ -6666,8 +6661,8 @@
         <f t="shared" ref="A41" si="41">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="183"/>
-      <c r="C41" s="183"/>
+      <c r="B41" s="200"/>
+      <c r="C41" s="200"/>
       <c r="D41" s="145"/>
       <c r="E41" s="42"/>
       <c r="F41" s="132" t="str">
@@ -6679,7 +6674,7 @@
       <c r="I41" s="132"/>
       <c r="J41" s="132"/>
       <c r="K41" s="133"/>
-      <c r="L41" s="191"/>
+      <c r="L41" s="218"/>
       <c r="N41" s="141" t="str">
         <f t="shared" ref="N41" si="42">A43</f>
         <v/>
@@ -6692,7 +6687,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q41" s="189"/>
+      <c r="Q41" s="216"/>
       <c r="R41" s="202"/>
       <c r="S41" s="147"/>
       <c r="T41"/>
@@ -6811,8 +6806,8 @@
     </row>
     <row r="42" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="148"/>
-      <c r="B42" s="182"/>
-      <c r="C42" s="182"/>
+      <c r="B42" s="199"/>
+      <c r="C42" s="199"/>
       <c r="D42" s="144"/>
       <c r="E42" s="41"/>
       <c r="F42" s="134" t="str">
@@ -6824,7 +6819,7 @@
       <c r="I42" s="134"/>
       <c r="J42" s="134"/>
       <c r="K42" s="134"/>
-      <c r="L42" s="191"/>
+      <c r="L42" s="218"/>
       <c r="N42" s="138" t="str">
         <f t="shared" ref="N42" si="43">IF(ISBLANK(A44),"",A44)</f>
         <v/>
@@ -6837,7 +6832,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q42" s="189"/>
+      <c r="Q42" s="216"/>
       <c r="R42" s="202"/>
       <c r="S42" s="40"/>
       <c r="T42"/>
@@ -6959,8 +6954,8 @@
         <f t="shared" ref="A43" si="44">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="183"/>
-      <c r="C43" s="183"/>
+      <c r="B43" s="200"/>
+      <c r="C43" s="200"/>
       <c r="D43" s="145"/>
       <c r="E43" s="42"/>
       <c r="F43" s="132" t="str">
@@ -6972,7 +6967,7 @@
       <c r="I43" s="132"/>
       <c r="J43" s="132"/>
       <c r="K43" s="133"/>
-      <c r="L43" s="191"/>
+      <c r="L43" s="218"/>
       <c r="N43" s="141" t="str">
         <f t="shared" ref="N43" si="45">A45</f>
         <v/>
@@ -6985,7 +6980,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q43" s="189"/>
+      <c r="Q43" s="216"/>
       <c r="R43" s="202"/>
       <c r="S43" s="147"/>
       <c r="T43"/>
@@ -7104,8 +7099,8 @@
     </row>
     <row r="44" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="148"/>
-      <c r="B44" s="182"/>
-      <c r="C44" s="182"/>
+      <c r="B44" s="199"/>
+      <c r="C44" s="199"/>
       <c r="D44" s="144"/>
       <c r="E44" s="41"/>
       <c r="F44" s="134" t="str">
@@ -7117,7 +7112,7 @@
       <c r="I44" s="134"/>
       <c r="J44" s="134"/>
       <c r="K44" s="134"/>
-      <c r="L44" s="191"/>
+      <c r="L44" s="218"/>
       <c r="N44" s="138" t="str">
         <f t="shared" ref="N44" si="46">IF(ISBLANK(A46),"",A46)</f>
         <v/>
@@ -7130,7 +7125,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q44" s="189"/>
+      <c r="Q44" s="216"/>
       <c r="R44" s="202"/>
       <c r="S44" s="40"/>
       <c r="T44"/>
@@ -7252,8 +7247,8 @@
         <f t="shared" ref="A45" si="47">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="183"/>
-      <c r="C45" s="183"/>
+      <c r="B45" s="200"/>
+      <c r="C45" s="200"/>
       <c r="D45" s="145"/>
       <c r="E45" s="42"/>
       <c r="F45" s="132" t="str">
@@ -7265,7 +7260,7 @@
       <c r="I45" s="132"/>
       <c r="J45" s="132"/>
       <c r="K45" s="133"/>
-      <c r="L45" s="191"/>
+      <c r="L45" s="218"/>
       <c r="N45" s="141" t="str">
         <f t="shared" ref="N45" si="48">A47</f>
         <v/>
@@ -7278,7 +7273,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q45" s="189"/>
+      <c r="Q45" s="216"/>
       <c r="R45" s="202"/>
       <c r="S45" s="147"/>
       <c r="T45"/>
@@ -7397,8 +7392,8 @@
     </row>
     <row r="46" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="148"/>
-      <c r="B46" s="182"/>
-      <c r="C46" s="182"/>
+      <c r="B46" s="199"/>
+      <c r="C46" s="199"/>
       <c r="D46" s="144"/>
       <c r="E46" s="41"/>
       <c r="F46" s="134" t="str">
@@ -7410,7 +7405,7 @@
       <c r="I46" s="134"/>
       <c r="J46" s="134"/>
       <c r="K46" s="134"/>
-      <c r="L46" s="191"/>
+      <c r="L46" s="218"/>
       <c r="N46" s="138" t="str">
         <f t="shared" ref="N46" si="49">IF(ISBLANK(A48),"",A48)</f>
         <v/>
@@ -7423,7 +7418,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q46" s="189"/>
+      <c r="Q46" s="216"/>
       <c r="R46" s="202"/>
       <c r="S46" s="40"/>
       <c r="T46"/>
@@ -7545,8 +7540,8 @@
         <f t="shared" ref="A47" si="50">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="183"/>
-      <c r="C47" s="183"/>
+      <c r="B47" s="200"/>
+      <c r="C47" s="200"/>
       <c r="D47" s="145"/>
       <c r="E47" s="42"/>
       <c r="F47" s="132" t="str">
@@ -7558,7 +7553,7 @@
       <c r="I47" s="132"/>
       <c r="J47" s="132"/>
       <c r="K47" s="133"/>
-      <c r="L47" s="191"/>
+      <c r="L47" s="218"/>
       <c r="N47" s="141" t="str">
         <f t="shared" ref="N47" si="51">A49</f>
         <v/>
@@ -7571,7 +7566,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q47" s="189"/>
+      <c r="Q47" s="216"/>
       <c r="R47" s="202"/>
       <c r="S47" s="147"/>
       <c r="T47"/>
@@ -7690,8 +7685,8 @@
     </row>
     <row r="48" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="148"/>
-      <c r="B48" s="182"/>
-      <c r="C48" s="182"/>
+      <c r="B48" s="199"/>
+      <c r="C48" s="199"/>
       <c r="D48" s="144"/>
       <c r="E48" s="41"/>
       <c r="F48" s="134" t="str">
@@ -7703,7 +7698,7 @@
       <c r="I48" s="134"/>
       <c r="J48" s="134"/>
       <c r="K48" s="134"/>
-      <c r="L48" s="191"/>
+      <c r="L48" s="218"/>
       <c r="N48" s="138" t="str">
         <f t="shared" ref="N48" si="52">IF(ISBLANK(A50),"",A50)</f>
         <v/>
@@ -7716,7 +7711,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q48" s="189"/>
+      <c r="Q48" s="216"/>
       <c r="R48" s="202"/>
       <c r="S48" s="40"/>
       <c r="T48"/>
@@ -7838,8 +7833,8 @@
         <f t="shared" ref="A49" si="53">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="183"/>
-      <c r="C49" s="183"/>
+      <c r="B49" s="200"/>
+      <c r="C49" s="200"/>
       <c r="D49" s="145"/>
       <c r="E49" s="42"/>
       <c r="F49" s="132" t="str">
@@ -7851,7 +7846,7 @@
       <c r="I49" s="132"/>
       <c r="J49" s="132"/>
       <c r="K49" s="133"/>
-      <c r="L49" s="191"/>
+      <c r="L49" s="218"/>
       <c r="N49" s="141" t="str">
         <f t="shared" ref="N49" si="54">A51</f>
         <v/>
@@ -7864,7 +7859,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q49" s="189"/>
+      <c r="Q49" s="216"/>
       <c r="R49" s="202"/>
       <c r="S49" s="147"/>
       <c r="T49"/>
@@ -7983,8 +7978,8 @@
     </row>
     <row r="50" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="148"/>
-      <c r="B50" s="182"/>
-      <c r="C50" s="182"/>
+      <c r="B50" s="199"/>
+      <c r="C50" s="199"/>
       <c r="D50" s="144"/>
       <c r="E50" s="41"/>
       <c r="F50" s="134" t="str">
@@ -7996,7 +7991,7 @@
       <c r="I50" s="134"/>
       <c r="J50" s="134"/>
       <c r="K50" s="134"/>
-      <c r="L50" s="191"/>
+      <c r="L50" s="218"/>
       <c r="N50" s="138" t="str">
         <f t="shared" ref="N50" si="55">IF(ISBLANK(A52),"",A52)</f>
         <v/>
@@ -8009,7 +8004,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q50" s="189"/>
+      <c r="Q50" s="216"/>
       <c r="R50" s="202"/>
       <c r="S50" s="40"/>
       <c r="T50"/>
@@ -8131,8 +8126,8 @@
         <f t="shared" ref="A51" si="56">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="183"/>
-      <c r="C51" s="183"/>
+      <c r="B51" s="200"/>
+      <c r="C51" s="200"/>
       <c r="D51" s="145"/>
       <c r="E51" s="42"/>
       <c r="F51" s="132" t="str">
@@ -8144,7 +8139,7 @@
       <c r="I51" s="132"/>
       <c r="J51" s="132"/>
       <c r="K51" s="133"/>
-      <c r="L51" s="191"/>
+      <c r="L51" s="218"/>
       <c r="N51" s="141" t="str">
         <f t="shared" ref="N51" si="57">A53</f>
         <v/>
@@ -8157,7 +8152,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="Q51" s="189"/>
+      <c r="Q51" s="216"/>
       <c r="R51" s="202"/>
       <c r="S51" s="147"/>
       <c r="T51"/>
@@ -8276,8 +8271,8 @@
     </row>
     <row r="52" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="148"/>
-      <c r="B52" s="182"/>
-      <c r="C52" s="182"/>
+      <c r="B52" s="199"/>
+      <c r="C52" s="199"/>
       <c r="D52" s="144"/>
       <c r="E52" s="41"/>
       <c r="F52" s="134" t="str">
@@ -8289,7 +8284,7 @@
       <c r="I52" s="134"/>
       <c r="J52" s="134"/>
       <c r="K52" s="134"/>
-      <c r="L52" s="191"/>
+      <c r="L52" s="218"/>
       <c r="N52" s="138"/>
       <c r="O52" s="139" t="str">
         <f t="shared" ref="O52:P53" si="58">IF(ISBLANK(D54),"",D54)</f>
@@ -8299,7 +8294,7 @@
         <f t="shared" si="58"/>
         <v/>
       </c>
-      <c r="Q52" s="189"/>
+      <c r="Q52" s="216"/>
       <c r="R52" s="202"/>
       <c r="S52" s="40"/>
       <c r="T52"/>
@@ -8421,8 +8416,8 @@
         <f t="shared" ref="A53" si="59">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B53" s="183"/>
-      <c r="C53" s="183"/>
+      <c r="B53" s="200"/>
+      <c r="C53" s="200"/>
       <c r="D53" s="145"/>
       <c r="E53" s="42"/>
       <c r="F53" s="132" t="str">
@@ -8434,7 +8429,7 @@
       <c r="I53" s="132"/>
       <c r="J53" s="132"/>
       <c r="K53" s="133"/>
-      <c r="L53" s="192"/>
+      <c r="L53" s="219"/>
       <c r="N53" s="141"/>
       <c r="O53" s="142" t="str">
         <f t="shared" si="58"/>
@@ -8444,7 +8439,7 @@
         <f t="shared" si="58"/>
         <v/>
       </c>
-      <c r="Q53" s="190"/>
+      <c r="Q53" s="217"/>
       <c r="R53" s="203"/>
       <c r="S53" s="147"/>
       <c r="T53"/>
@@ -8902,14 +8897,14 @@
       <c r="J71" s="64"/>
       <c r="K71" s="64"/>
       <c r="L71" s="3"/>
-      <c r="N71" s="200" t="s">
+      <c r="N71" s="198" t="s">
         <v>91</v>
       </c>
-      <c r="O71" s="200"/>
-      <c r="P71" s="200"/>
-      <c r="Q71" s="200"/>
-      <c r="R71" s="200"/>
-      <c r="S71" s="200"/>
+      <c r="O71" s="198"/>
+      <c r="P71" s="198"/>
+      <c r="Q71" s="198"/>
+      <c r="R71" s="198"/>
+      <c r="S71" s="198"/>
       <c r="T71" s="70"/>
       <c r="U71" s="70"/>
       <c r="V71" s="70"/>
@@ -8934,14 +8929,14 @@
       <c r="J72" s="64"/>
       <c r="K72" s="64"/>
       <c r="L72" s="3"/>
-      <c r="N72" s="200" t="s">
+      <c r="N72" s="198" t="s">
         <v>92</v>
       </c>
-      <c r="O72" s="200"/>
-      <c r="P72" s="200"/>
-      <c r="Q72" s="200"/>
-      <c r="R72" s="200"/>
-      <c r="S72" s="200"/>
+      <c r="O72" s="198"/>
+      <c r="P72" s="198"/>
+      <c r="Q72" s="198"/>
+      <c r="R72" s="198"/>
+      <c r="S72" s="198"/>
       <c r="T72" s="70"/>
       <c r="U72" s="70"/>
       <c r="V72" s="70"/>
@@ -8968,12 +8963,12 @@
       <c r="J73" s="64"/>
       <c r="K73" s="64"/>
       <c r="L73" s="3"/>
-      <c r="N73" s="207"/>
-      <c r="O73" s="207"/>
-      <c r="P73" s="207"/>
-      <c r="Q73" s="207"/>
-      <c r="R73" s="207"/>
-      <c r="S73" s="207"/>
+      <c r="N73" s="190"/>
+      <c r="O73" s="190"/>
+      <c r="P73" s="190"/>
+      <c r="Q73" s="190"/>
+      <c r="R73" s="190"/>
+      <c r="S73" s="190"/>
       <c r="T73" s="70"/>
       <c r="U73" s="70"/>
       <c r="V73" s="70"/>
@@ -9007,24 +9002,24 @@
       <c r="E75" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="208">
+      <c r="F75" s="191">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="208"/>
-      <c r="H75" s="208"/>
-      <c r="I75" s="208"/>
-      <c r="J75" s="208"/>
-      <c r="K75" s="208"/>
+      <c r="G75" s="191"/>
+      <c r="H75" s="191"/>
+      <c r="I75" s="191"/>
+      <c r="J75" s="191"/>
+      <c r="K75" s="191"/>
       <c r="L75" s="3"/>
-      <c r="N75" s="209" t="s">
+      <c r="N75" s="192" t="s">
         <v>93</v>
       </c>
-      <c r="O75" s="209"/>
-      <c r="P75" s="209"/>
-      <c r="Q75" s="209"/>
-      <c r="R75" s="209"/>
-      <c r="S75" s="209"/>
+      <c r="O75" s="192"/>
+      <c r="P75" s="192"/>
+      <c r="Q75" s="192"/>
+      <c r="R75" s="192"/>
+      <c r="S75" s="192"/>
     </row>
     <row r="76" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="54"/>
@@ -9056,14 +9051,14 @@
       <c r="E77" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="210">
+      <c r="F77" s="193">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="210"/>
-      <c r="H77" s="210"/>
-      <c r="I77" s="210"/>
-      <c r="J77" s="210"/>
+      <c r="G77" s="193"/>
+      <c r="H77" s="193"/>
+      <c r="I77" s="193"/>
+      <c r="J77" s="193"/>
       <c r="K77" s="44"/>
       <c r="L77" s="54"/>
       <c r="N77" s="80"/>
@@ -9088,13 +9083,13 @@
       <c r="L78" s="54"/>
       <c r="N78" s="146"/>
       <c r="O78" s="146"/>
-      <c r="P78" s="212" t="str">
+      <c r="P78" s="195" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="Q78" s="212"/>
-      <c r="R78" s="212"/>
-      <c r="S78" s="212"/>
+      <c r="Q78" s="195"/>
+      <c r="R78" s="195"/>
+      <c r="S78" s="195"/>
     </row>
     <row r="79" spans="1:29" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="72"/>
@@ -9116,11 +9111,11 @@
       <c r="N79" s="82"/>
       <c r="O79" s="82"/>
       <c r="P79" s="83"/>
-      <c r="Q79" s="211" t="str">
+      <c r="Q79" s="194" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="R79" s="211"/>
+      <c r="R79" s="194"/>
       <c r="S79" s="84"/>
       <c r="AC79" s="9" t="s">
         <v>30</v>
@@ -9161,13 +9156,13 @@
       <c r="L81" s="54"/>
       <c r="N81" s="83"/>
       <c r="O81" s="83"/>
-      <c r="P81" s="213" t="str">
+      <c r="P81" s="196" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="Q81" s="213"/>
-      <c r="R81" s="213"/>
-      <c r="S81" s="213"/>
+      <c r="Q81" s="196"/>
+      <c r="R81" s="196"/>
+      <c r="S81" s="196"/>
     </row>
     <row r="82" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="54"/>
@@ -9204,12 +9199,12 @@
       <c r="J83" s="54"/>
       <c r="K83" s="54"/>
       <c r="L83" s="54"/>
-      <c r="N83" s="214"/>
-      <c r="O83" s="214"/>
-      <c r="P83" s="214"/>
-      <c r="Q83" s="214"/>
-      <c r="R83" s="214"/>
-      <c r="S83" s="214"/>
+      <c r="N83" s="197"/>
+      <c r="O83" s="197"/>
+      <c r="P83" s="197"/>
+      <c r="Q83" s="197"/>
+      <c r="R83" s="197"/>
+      <c r="S83" s="197"/>
     </row>
     <row r="84" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="54"/>
@@ -9228,14 +9223,14 @@
       <c r="J84" s="79"/>
       <c r="K84" s="54"/>
       <c r="L84" s="54"/>
-      <c r="N84" s="206" t="s">
+      <c r="N84" s="176" t="s">
         <v>94</v>
       </c>
-      <c r="O84" s="206"/>
-      <c r="P84" s="206"/>
-      <c r="Q84" s="206"/>
-      <c r="R84" s="206"/>
-      <c r="S84" s="206"/>
+      <c r="O84" s="176"/>
+      <c r="P84" s="176"/>
+      <c r="Q84" s="176"/>
+      <c r="R84" s="176"/>
+      <c r="S84" s="176"/>
     </row>
     <row r="85" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="54"/>
@@ -9250,14 +9245,14 @@
       <c r="J85" s="54"/>
       <c r="K85" s="54"/>
       <c r="L85" s="54"/>
-      <c r="N85" s="206" t="s">
+      <c r="N85" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O85" s="206"/>
-      <c r="P85" s="206"/>
-      <c r="Q85" s="206"/>
-      <c r="R85" s="206"/>
-      <c r="S85" s="206"/>
+      <c r="O85" s="176"/>
+      <c r="P85" s="176"/>
+      <c r="Q85" s="176"/>
+      <c r="R85" s="176"/>
+      <c r="S85" s="176"/>
     </row>
     <row r="86" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="54"/>
@@ -9276,12 +9271,12 @@
       <c r="J86" s="54"/>
       <c r="K86" s="54"/>
       <c r="L86" s="54"/>
-      <c r="N86" s="215"/>
-      <c r="O86" s="215"/>
-      <c r="P86" s="215"/>
-      <c r="Q86" s="215"/>
-      <c r="R86" s="215"/>
-      <c r="S86" s="215"/>
+      <c r="N86" s="177"/>
+      <c r="O86" s="177"/>
+      <c r="P86" s="177"/>
+      <c r="Q86" s="177"/>
+      <c r="R86" s="177"/>
+      <c r="S86" s="177"/>
     </row>
     <row r="87" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="54"/>
@@ -9296,12 +9291,12 @@
       <c r="J87" s="54"/>
       <c r="K87" s="54"/>
       <c r="L87" s="54"/>
-      <c r="N87" s="206"/>
-      <c r="O87" s="206"/>
-      <c r="P87" s="206"/>
-      <c r="Q87" s="206"/>
-      <c r="R87" s="206"/>
-      <c r="S87" s="206"/>
+      <c r="N87" s="176"/>
+      <c r="O87" s="176"/>
+      <c r="P87" s="176"/>
+      <c r="Q87" s="176"/>
+      <c r="R87" s="176"/>
+      <c r="S87" s="176"/>
     </row>
     <row r="88" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="54"/>
@@ -9313,21 +9308,21 @@
       <c r="E88" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="226"/>
-      <c r="G88" s="226"/>
-      <c r="H88" s="226"/>
-      <c r="I88" s="226"/>
-      <c r="J88" s="226"/>
+      <c r="F88" s="175"/>
+      <c r="G88" s="175"/>
+      <c r="H88" s="175"/>
+      <c r="I88" s="175"/>
+      <c r="J88" s="175"/>
       <c r="K88" s="54"/>
       <c r="L88" s="54"/>
-      <c r="N88" s="206" t="s">
+      <c r="N88" s="176" t="s">
         <v>96</v>
       </c>
-      <c r="O88" s="206"/>
-      <c r="P88" s="206"/>
-      <c r="Q88" s="206"/>
-      <c r="R88" s="206"/>
-      <c r="S88" s="206"/>
+      <c r="O88" s="176"/>
+      <c r="P88" s="176"/>
+      <c r="Q88" s="176"/>
+      <c r="R88" s="176"/>
+      <c r="S88" s="176"/>
     </row>
     <row r="89" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="54"/>
@@ -9480,12 +9475,12 @@
       <c r="J95" s="91"/>
       <c r="K95" s="28"/>
       <c r="L95" s="18"/>
-      <c r="N95" s="215"/>
-      <c r="O95" s="215"/>
-      <c r="P95" s="215"/>
-      <c r="Q95" s="215"/>
-      <c r="R95" s="215"/>
-      <c r="S95" s="215"/>
+      <c r="N95" s="177"/>
+      <c r="O95" s="177"/>
+      <c r="P95" s="177"/>
+      <c r="Q95" s="177"/>
+      <c r="R95" s="177"/>
+      <c r="S95" s="177"/>
     </row>
     <row r="96" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="68"/>
@@ -9502,12 +9497,12 @@
       <c r="J96" s="91"/>
       <c r="K96" s="28"/>
       <c r="L96" s="18"/>
-      <c r="N96" s="215"/>
-      <c r="O96" s="215"/>
-      <c r="P96" s="215"/>
-      <c r="Q96" s="215"/>
-      <c r="R96" s="215"/>
-      <c r="S96" s="215"/>
+      <c r="N96" s="177"/>
+      <c r="O96" s="177"/>
+      <c r="P96" s="177"/>
+      <c r="Q96" s="177"/>
+      <c r="R96" s="177"/>
+      <c r="S96" s="177"/>
     </row>
     <row r="97" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="68"/>
@@ -9524,12 +9519,12 @@
       <c r="J97" s="91"/>
       <c r="K97" s="28"/>
       <c r="L97" s="18"/>
-      <c r="N97" s="215"/>
-      <c r="O97" s="215"/>
-      <c r="P97" s="215"/>
-      <c r="Q97" s="215"/>
-      <c r="R97" s="215"/>
-      <c r="S97" s="215"/>
+      <c r="N97" s="177"/>
+      <c r="O97" s="177"/>
+      <c r="P97" s="177"/>
+      <c r="Q97" s="177"/>
+      <c r="R97" s="177"/>
+      <c r="S97" s="177"/>
     </row>
     <row r="98" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="68"/>
@@ -9546,12 +9541,12 @@
       <c r="J98" s="91"/>
       <c r="K98" s="28"/>
       <c r="L98" s="18"/>
-      <c r="N98" s="215"/>
-      <c r="O98" s="215"/>
-      <c r="P98" s="215"/>
-      <c r="Q98" s="215"/>
-      <c r="R98" s="215"/>
-      <c r="S98" s="215"/>
+      <c r="N98" s="177"/>
+      <c r="O98" s="177"/>
+      <c r="P98" s="177"/>
+      <c r="Q98" s="177"/>
+      <c r="R98" s="177"/>
+      <c r="S98" s="177"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="68"/>
@@ -9568,12 +9563,12 @@
       <c r="J99" s="28"/>
       <c r="K99" s="28"/>
       <c r="L99" s="18"/>
-      <c r="N99" s="206"/>
-      <c r="O99" s="206"/>
-      <c r="P99" s="206"/>
-      <c r="Q99" s="206"/>
-      <c r="R99" s="206"/>
-      <c r="S99" s="206"/>
+      <c r="N99" s="176"/>
+      <c r="O99" s="176"/>
+      <c r="P99" s="176"/>
+      <c r="Q99" s="176"/>
+      <c r="R99" s="176"/>
+      <c r="S99" s="176"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="54"/>
@@ -9884,36 +9879,36 @@
     </row>
     <row r="119" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="227" t="s">
+      <c r="A124" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="B124" s="228"/>
-      <c r="C124" s="228"/>
-      <c r="D124" s="228"/>
-      <c r="E124" s="228"/>
-      <c r="F124" s="228"/>
-      <c r="G124" s="228"/>
-      <c r="H124" s="228"/>
-      <c r="I124" s="228"/>
-      <c r="J124" s="228"/>
-      <c r="K124" s="228"/>
-      <c r="L124" s="229"/>
+      <c r="B124" s="179"/>
+      <c r="C124" s="179"/>
+      <c r="D124" s="179"/>
+      <c r="E124" s="179"/>
+      <c r="F124" s="179"/>
+      <c r="G124" s="179"/>
+      <c r="H124" s="179"/>
+      <c r="I124" s="179"/>
+      <c r="J124" s="179"/>
+      <c r="K124" s="179"/>
+      <c r="L124" s="180"/>
     </row>
     <row r="125" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="230" t="s">
+      <c r="A125" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B125" s="231"/>
-      <c r="C125" s="231"/>
-      <c r="D125" s="231"/>
-      <c r="E125" s="231"/>
-      <c r="F125" s="231"/>
-      <c r="G125" s="231"/>
-      <c r="H125" s="231"/>
-      <c r="I125" s="231"/>
-      <c r="J125" s="231"/>
-      <c r="K125" s="231"/>
-      <c r="L125" s="232"/>
+      <c r="B125" s="182"/>
+      <c r="C125" s="182"/>
+      <c r="D125" s="182"/>
+      <c r="E125" s="182"/>
+      <c r="F125" s="182"/>
+      <c r="G125" s="182"/>
+      <c r="H125" s="182"/>
+      <c r="I125" s="182"/>
+      <c r="J125" s="182"/>
+      <c r="K125" s="182"/>
+      <c r="L125" s="183"/>
     </row>
     <row r="126" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="110" t="s">
@@ -9921,20 +9916,20 @@
       </c>
       <c r="B126" s="111"/>
       <c r="C126" s="111"/>
-      <c r="D126" s="233">
+      <c r="D126" s="184">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="234"/>
-      <c r="F126" s="234"/>
-      <c r="G126" s="234"/>
-      <c r="H126" s="234"/>
-      <c r="I126" s="235"/>
-      <c r="J126" s="236" t="s">
+      <c r="E126" s="185"/>
+      <c r="F126" s="185"/>
+      <c r="G126" s="185"/>
+      <c r="H126" s="185"/>
+      <c r="I126" s="186"/>
+      <c r="J126" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="K126" s="237"/>
-      <c r="L126" s="238"/>
+      <c r="K126" s="188"/>
+      <c r="L126" s="189"/>
     </row>
     <row r="127" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="112" t="s">
@@ -9970,23 +9965,23 @@
       <c r="A129" s="125" t="s">
         <v>72</v>
       </c>
-      <c r="B129" s="216" t="s">
+      <c r="B129" s="165" t="s">
         <v>73</v>
       </c>
-      <c r="C129" s="217"/>
-      <c r="D129" s="218" t="s">
+      <c r="C129" s="166"/>
+      <c r="D129" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="E129" s="219"/>
-      <c r="F129" s="219"/>
-      <c r="G129" s="219"/>
-      <c r="H129" s="219"/>
-      <c r="I129" s="219"/>
-      <c r="J129" s="220"/>
-      <c r="K129" s="218" t="s">
+      <c r="E129" s="168"/>
+      <c r="F129" s="168"/>
+      <c r="G129" s="168"/>
+      <c r="H129" s="168"/>
+      <c r="I129" s="168"/>
+      <c r="J129" s="169"/>
+      <c r="K129" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="L129" s="219"/>
+      <c r="L129" s="168"/>
     </row>
     <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="126"/>
@@ -9996,15 +9991,15 @@
       <c r="C130" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="D130" s="221"/>
-      <c r="E130" s="222"/>
-      <c r="F130" s="222"/>
-      <c r="G130" s="222"/>
-      <c r="H130" s="222"/>
-      <c r="I130" s="222"/>
-      <c r="J130" s="223"/>
-      <c r="K130" s="224"/>
-      <c r="L130" s="225"/>
+      <c r="D130" s="170"/>
+      <c r="E130" s="171"/>
+      <c r="F130" s="171"/>
+      <c r="G130" s="171"/>
+      <c r="H130" s="171"/>
+      <c r="I130" s="171"/>
+      <c r="J130" s="172"/>
+      <c r="K130" s="173"/>
+      <c r="L130" s="174"/>
     </row>
     <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="129">
@@ -10012,17 +10007,17 @@
       </c>
       <c r="B131" s="129"/>
       <c r="C131" s="130"/>
-      <c r="D131" s="239" t="s">
+      <c r="D131" s="160" t="s">
         <v>78</v>
       </c>
-      <c r="E131" s="240"/>
-      <c r="F131" s="240"/>
-      <c r="G131" s="240"/>
-      <c r="H131" s="240"/>
-      <c r="I131" s="240"/>
-      <c r="J131" s="241"/>
-      <c r="K131" s="242"/>
-      <c r="L131" s="242"/>
+      <c r="E131" s="161"/>
+      <c r="F131" s="161"/>
+      <c r="G131" s="161"/>
+      <c r="H131" s="161"/>
+      <c r="I131" s="161"/>
+      <c r="J131" s="162"/>
+      <c r="K131" s="156"/>
+      <c r="L131" s="156"/>
     </row>
     <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="129">
@@ -10030,17 +10025,17 @@
       </c>
       <c r="B132" s="129"/>
       <c r="C132" s="131"/>
-      <c r="D132" s="239" t="s">
+      <c r="D132" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="E132" s="240"/>
-      <c r="F132" s="240"/>
-      <c r="G132" s="240"/>
-      <c r="H132" s="240"/>
-      <c r="I132" s="240"/>
-      <c r="J132" s="241"/>
-      <c r="K132" s="242"/>
-      <c r="L132" s="242"/>
+      <c r="E132" s="161"/>
+      <c r="F132" s="161"/>
+      <c r="G132" s="161"/>
+      <c r="H132" s="161"/>
+      <c r="I132" s="161"/>
+      <c r="J132" s="162"/>
+      <c r="K132" s="156"/>
+      <c r="L132" s="156"/>
     </row>
     <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="129">
@@ -10048,17 +10043,17 @@
       </c>
       <c r="B133" s="129"/>
       <c r="C133" s="131"/>
-      <c r="D133" s="239" t="s">
+      <c r="D133" s="160" t="s">
         <v>80</v>
       </c>
-      <c r="E133" s="240"/>
-      <c r="F133" s="240"/>
-      <c r="G133" s="240"/>
-      <c r="H133" s="240"/>
-      <c r="I133" s="240"/>
-      <c r="J133" s="241"/>
-      <c r="K133" s="242"/>
-      <c r="L133" s="242"/>
+      <c r="E133" s="161"/>
+      <c r="F133" s="161"/>
+      <c r="G133" s="161"/>
+      <c r="H133" s="161"/>
+      <c r="I133" s="161"/>
+      <c r="J133" s="162"/>
+      <c r="K133" s="156"/>
+      <c r="L133" s="156"/>
     </row>
     <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="129">
@@ -10066,17 +10061,17 @@
       </c>
       <c r="B134" s="129"/>
       <c r="C134" s="131"/>
-      <c r="D134" s="239" t="s">
+      <c r="D134" s="160" t="s">
         <v>81</v>
       </c>
-      <c r="E134" s="240"/>
-      <c r="F134" s="240"/>
-      <c r="G134" s="240"/>
-      <c r="H134" s="240"/>
-      <c r="I134" s="240"/>
-      <c r="J134" s="241"/>
-      <c r="K134" s="242"/>
-      <c r="L134" s="242"/>
+      <c r="E134" s="161"/>
+      <c r="F134" s="161"/>
+      <c r="G134" s="161"/>
+      <c r="H134" s="161"/>
+      <c r="I134" s="161"/>
+      <c r="J134" s="162"/>
+      <c r="K134" s="156"/>
+      <c r="L134" s="156"/>
     </row>
     <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="129">
@@ -10084,17 +10079,17 @@
       </c>
       <c r="B135" s="129"/>
       <c r="C135" s="131"/>
-      <c r="D135" s="239" t="s">
+      <c r="D135" s="160" t="s">
         <v>82</v>
       </c>
-      <c r="E135" s="240"/>
-      <c r="F135" s="240"/>
-      <c r="G135" s="240"/>
-      <c r="H135" s="240"/>
-      <c r="I135" s="240"/>
-      <c r="J135" s="241"/>
-      <c r="K135" s="242"/>
-      <c r="L135" s="242"/>
+      <c r="E135" s="161"/>
+      <c r="F135" s="161"/>
+      <c r="G135" s="161"/>
+      <c r="H135" s="161"/>
+      <c r="I135" s="161"/>
+      <c r="J135" s="162"/>
+      <c r="K135" s="156"/>
+      <c r="L135" s="156"/>
     </row>
     <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="129">
@@ -10102,17 +10097,17 @@
       </c>
       <c r="B136" s="129"/>
       <c r="C136" s="131"/>
-      <c r="D136" s="239" t="s">
+      <c r="D136" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="E136" s="240"/>
-      <c r="F136" s="240"/>
-      <c r="G136" s="240"/>
-      <c r="H136" s="240"/>
-      <c r="I136" s="240"/>
-      <c r="J136" s="241"/>
-      <c r="K136" s="242"/>
-      <c r="L136" s="242"/>
+      <c r="E136" s="161"/>
+      <c r="F136" s="161"/>
+      <c r="G136" s="161"/>
+      <c r="H136" s="161"/>
+      <c r="I136" s="161"/>
+      <c r="J136" s="162"/>
+      <c r="K136" s="156"/>
+      <c r="L136" s="156"/>
     </row>
     <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="129">
@@ -10120,17 +10115,17 @@
       </c>
       <c r="B137" s="129"/>
       <c r="C137" s="131"/>
-      <c r="D137" s="239" t="s">
+      <c r="D137" s="160" t="s">
         <v>84</v>
       </c>
-      <c r="E137" s="240"/>
-      <c r="F137" s="240"/>
-      <c r="G137" s="240"/>
-      <c r="H137" s="240"/>
-      <c r="I137" s="240"/>
-      <c r="J137" s="241"/>
-      <c r="K137" s="242"/>
-      <c r="L137" s="242"/>
+      <c r="E137" s="161"/>
+      <c r="F137" s="161"/>
+      <c r="G137" s="161"/>
+      <c r="H137" s="161"/>
+      <c r="I137" s="161"/>
+      <c r="J137" s="162"/>
+      <c r="K137" s="156"/>
+      <c r="L137" s="156"/>
     </row>
     <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="129">
@@ -10138,17 +10133,17 @@
       </c>
       <c r="B138" s="129"/>
       <c r="C138" s="131"/>
-      <c r="D138" s="243" t="s">
+      <c r="D138" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="E138" s="244"/>
-      <c r="F138" s="244"/>
-      <c r="G138" s="244"/>
-      <c r="H138" s="244"/>
-      <c r="I138" s="244"/>
-      <c r="J138" s="245"/>
-      <c r="K138" s="249"/>
-      <c r="L138" s="250"/>
+      <c r="E138" s="154"/>
+      <c r="F138" s="154"/>
+      <c r="G138" s="154"/>
+      <c r="H138" s="154"/>
+      <c r="I138" s="154"/>
+      <c r="J138" s="155"/>
+      <c r="K138" s="163"/>
+      <c r="L138" s="164"/>
     </row>
     <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="129">
@@ -10156,17 +10151,17 @@
       </c>
       <c r="B139" s="129"/>
       <c r="C139" s="131"/>
-      <c r="D139" s="243" t="s">
+      <c r="D139" s="153" t="s">
         <v>85</v>
       </c>
-      <c r="E139" s="244"/>
-      <c r="F139" s="244"/>
-      <c r="G139" s="244"/>
-      <c r="H139" s="244"/>
-      <c r="I139" s="244"/>
-      <c r="J139" s="245"/>
-      <c r="K139" s="242"/>
-      <c r="L139" s="242"/>
+      <c r="E139" s="154"/>
+      <c r="F139" s="154"/>
+      <c r="G139" s="154"/>
+      <c r="H139" s="154"/>
+      <c r="I139" s="154"/>
+      <c r="J139" s="155"/>
+      <c r="K139" s="156"/>
+      <c r="L139" s="156"/>
     </row>
     <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="129">
@@ -10174,17 +10169,17 @@
       </c>
       <c r="B140" s="129"/>
       <c r="C140" s="131"/>
-      <c r="D140" s="243" t="s">
+      <c r="D140" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="E140" s="244"/>
-      <c r="F140" s="244"/>
-      <c r="G140" s="244"/>
-      <c r="H140" s="244"/>
-      <c r="I140" s="244"/>
-      <c r="J140" s="245"/>
-      <c r="K140" s="242"/>
-      <c r="L140" s="242"/>
+      <c r="E140" s="154"/>
+      <c r="F140" s="154"/>
+      <c r="G140" s="154"/>
+      <c r="H140" s="154"/>
+      <c r="I140" s="154"/>
+      <c r="J140" s="155"/>
+      <c r="K140" s="156"/>
+      <c r="L140" s="156"/>
     </row>
     <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="129">
@@ -10192,17 +10187,17 @@
       </c>
       <c r="B141" s="129"/>
       <c r="C141" s="131"/>
-      <c r="D141" s="246" t="s">
+      <c r="D141" s="157" t="s">
         <v>87</v>
       </c>
-      <c r="E141" s="247"/>
-      <c r="F141" s="247"/>
-      <c r="G141" s="247"/>
-      <c r="H141" s="247"/>
-      <c r="I141" s="247"/>
-      <c r="J141" s="248"/>
-      <c r="K141" s="242"/>
-      <c r="L141" s="242"/>
+      <c r="E141" s="158"/>
+      <c r="F141" s="158"/>
+      <c r="G141" s="158"/>
+      <c r="H141" s="158"/>
+      <c r="I141" s="158"/>
+      <c r="J141" s="159"/>
+      <c r="K141" s="156"/>
+      <c r="L141" s="156"/>
     </row>
     <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10214,54 +10209,40 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="98">
-    <mergeCell ref="D140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="D141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="D139:J139"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="D134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="D136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:J130"/>
-    <mergeCell ref="K129:L130"/>
-    <mergeCell ref="F88:J88"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N95:S95"/>
-    <mergeCell ref="N96:S96"/>
-    <mergeCell ref="N97:S97"/>
-    <mergeCell ref="N98:S98"/>
-    <mergeCell ref="N99:S99"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="F75:K75"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="Q79:R79"/>
-    <mergeCell ref="P78:S78"/>
-    <mergeCell ref="P81:S81"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="N15:N17"/>
+    <mergeCell ref="O15:P16"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:K16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="Q18:Q53"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="L20:L53"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
     <mergeCell ref="N72:S72"/>
     <mergeCell ref="B40:C41"/>
     <mergeCell ref="B42:C43"/>
@@ -10278,42 +10259,56 @@
     <mergeCell ref="B28:C29"/>
     <mergeCell ref="B30:C31"/>
     <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="Q18:Q53"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="L20:L53"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:K16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="N15:N17"/>
-    <mergeCell ref="O15:P16"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="F75:K75"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="Q79:R79"/>
+    <mergeCell ref="P78:S78"/>
+    <mergeCell ref="P81:S81"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:J130"/>
+    <mergeCell ref="K129:L130"/>
+    <mergeCell ref="F88:J88"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N95:S95"/>
+    <mergeCell ref="N96:S96"/>
+    <mergeCell ref="N97:S97"/>
+    <mergeCell ref="N98:S98"/>
+    <mergeCell ref="N99:S99"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="D126:I126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="D131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="D134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="D136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D140:J140"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="D141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="D139:J139"/>
+    <mergeCell ref="K139:L139"/>
   </mergeCells>
-  <phoneticPr fontId="41" type="noConversion"/>
+  <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" fitToWidth="2" fitToHeight="3" orientation="portrait" r:id="rId1"/>

--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2A1491-E4C4-45D9-8C8C-070E4B757254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FA7371-79C4-4341-A7D5-8808BC7EF150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim" sheetId="92" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Claim!$A$1:$S$143</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Claim!$A$1:$R$143</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2003,16 +2003,330 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2097,10 +2411,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2131,316 +2441,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2546,13 +2546,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>488950</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
@@ -2607,13 +2607,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>584210</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>95180</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>584570</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>95540</xdr:rowOff>
@@ -3022,7 +3022,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB524E58-DEC5-4CFF-AD7C-0D1451F04347}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S148"/>
+  <dimension ref="A1:R148"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="8" bestFit="1" customWidth="1"/>
@@ -3035,59 +3035,58 @@
     <col min="9" max="9" width="10" style="8" customWidth="1"/>
     <col min="10" max="11" width="9.26953125" style="8" customWidth="1"/>
     <col min="12" max="12" width="15.26953125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="9.1796875" style="8"/>
-    <col min="14" max="14" width="13.1796875" style="8" customWidth="1"/>
-    <col min="15" max="16" width="7.453125" style="8" customWidth="1"/>
-    <col min="17" max="17" width="28.26953125" style="8" customWidth="1"/>
-    <col min="18" max="18" width="30.54296875" style="8" customWidth="1"/>
-    <col min="19" max="19" width="31.81640625" style="8" customWidth="1"/>
-    <col min="20" max="16384" width="9.1796875" style="8"/>
+    <col min="13" max="13" width="13.1796875" style="8" customWidth="1"/>
+    <col min="14" max="15" width="7.453125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="28.26953125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="30.54296875" style="8" customWidth="1"/>
+    <col min="18" max="18" width="31.81640625" style="8" customWidth="1"/>
+    <col min="19" max="16384" width="9.1796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="157" t="s">
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="242" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="242"/>
+      <c r="J1" s="242"/>
+      <c r="K1" s="242"/>
+      <c r="L1" s="242"/>
+      <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="157" t="s">
+    </row>
+    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
-      <c r="R2" s="144"/>
-      <c r="S2" s="144"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="242"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="231"/>
+      <c r="Q2" s="231"/>
+      <c r="R2" s="231"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -3100,72 +3099,72 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
+      <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-    </row>
-    <row r="4" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="170" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="254" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="170"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="170"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="170"/>
-      <c r="J4" s="170"/>
-      <c r="K4" s="170"/>
-      <c r="L4" s="170"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="254"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-    </row>
-    <row r="5" spans="1:19" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="171"/>
-      <c r="B5" s="171"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="171"/>
+    </row>
+    <row r="5" spans="1:18" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="255"/>
+      <c r="B5" s="255"/>
+      <c r="C5" s="255"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="15" t="s">
+      <c r="R5" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="172" t="s">
+    <row r="6" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="256" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="172"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="172"/>
-      <c r="H6" s="172"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="172"/>
-      <c r="P6" s="16"/>
+      <c r="B6" s="256"/>
+      <c r="C6" s="256"/>
+      <c r="D6" s="256"/>
+      <c r="E6" s="256"/>
+      <c r="F6" s="256"/>
+      <c r="G6" s="256"/>
+      <c r="H6" s="256"/>
+      <c r="I6" s="256"/>
+      <c r="J6" s="256"/>
+      <c r="K6" s="256"/>
+      <c r="L6" s="256"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="17"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -3178,14 +3177,14 @@
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
+      <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-    </row>
-    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
@@ -3207,16 +3206,16 @@
       </c>
       <c r="L8" s="136"/>
     </row>
-    <row r="9" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="173"/>
+      <c r="C9" s="257"/>
+      <c r="D9" s="257"/>
+      <c r="E9" s="257"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="19" t="s">
@@ -3228,17 +3227,17 @@
         <v>5</v>
       </c>
       <c r="L9" s="137"/>
-      <c r="N9" s="250" t="s">
+      <c r="M9" s="144" t="s">
         <v>102</v>
       </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="252" t="str">
+      <c r="N9" s="9"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="146" t="str">
         <f>":   "&amp;C8</f>
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>8</v>
       </c>
@@ -3261,17 +3260,17 @@
       <c r="L10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="250" t="s">
+      <c r="M10" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="252" t="str">
+      <c r="N10" s="9"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="146" t="str">
         <f>":   "&amp;C10</f>
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>11</v>
       </c>
@@ -3292,17 +3291,17 @@
         <v>5</v>
       </c>
       <c r="L11" s="138"/>
-      <c r="N11" s="250" t="s">
+      <c r="M11" s="144" t="s">
         <v>112</v>
       </c>
-      <c r="O11" s="9"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="252" t="str">
+      <c r="N11" s="9"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="146" t="str">
         <f>":   "&amp;C11</f>
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
@@ -3323,17 +3322,17 @@
         <v>5</v>
       </c>
       <c r="L12" s="138"/>
-      <c r="N12" s="251" t="s">
+      <c r="M12" s="145" t="s">
         <v>113</v>
       </c>
-      <c r="O12" s="16"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="252" t="str">
+      <c r="N12" s="16"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="146" t="str">
         <f>":   "&amp;A5</f>
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="19"/>
       <c r="B13" s="21"/>
       <c r="C13" s="26"/>
@@ -3347,7 +3346,7 @@
       <c r="K13" s="20"/>
       <c r="L13" s="26"/>
     </row>
-    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -3361,71 +3360,71 @@
       <c r="K14" s="12"/>
       <c r="L14" s="26"/>
     </row>
-    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="158" t="s">
+      <c r="B15" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="158"/>
-      <c r="D15" s="160" t="s">
+      <c r="C15" s="243"/>
+      <c r="D15" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="161"/>
-      <c r="F15" s="161" t="s">
+      <c r="E15" s="246"/>
+      <c r="F15" s="246" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="166" t="s">
+      <c r="G15" s="251" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="166"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="167"/>
-      <c r="L15" s="147" t="s">
+      <c r="H15" s="251"/>
+      <c r="I15" s="251"/>
+      <c r="J15" s="251"/>
+      <c r="K15" s="252"/>
+      <c r="L15" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="150" t="s">
+      <c r="M15" s="235" t="s">
         <v>59</v>
       </c>
-      <c r="O15" s="153" t="s">
+      <c r="N15" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="P15" s="154"/>
-      <c r="Q15" s="150" t="s">
+      <c r="O15" s="239"/>
+      <c r="P15" s="235" t="s">
         <v>61</v>
       </c>
-      <c r="R15" s="174" t="s">
+      <c r="Q15" s="258" t="s">
         <v>62</v>
       </c>
-      <c r="S15" s="150" t="s">
+      <c r="R15" s="235" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="159"/>
-      <c r="C16" s="159"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="163"/>
-      <c r="F16" s="164"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="168"/>
-      <c r="J16" s="168"/>
-      <c r="K16" s="169"/>
-      <c r="L16" s="148"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="155"/>
-      <c r="P16" s="156"/>
-      <c r="Q16" s="151"/>
-      <c r="R16" s="175"/>
-      <c r="S16" s="151"/>
-    </row>
-    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="244"/>
+      <c r="C16" s="244"/>
+      <c r="D16" s="247"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="224"/>
+      <c r="H16" s="224"/>
+      <c r="I16" s="224"/>
+      <c r="J16" s="224"/>
+      <c r="K16" s="253"/>
+      <c r="L16" s="233"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="240"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="259"/>
+      <c r="R16" s="236"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="30" t="s">
         <v>22</v>
       </c>
@@ -3441,7 +3440,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="165"/>
+      <c r="F17" s="250"/>
       <c r="G17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3457,1011 +3456,1011 @@
       <c r="K17" s="37">
         <v>2</v>
       </c>
-      <c r="L17" s="149"/>
-      <c r="N17" s="152"/>
+      <c r="L17" s="234"/>
+      <c r="M17" s="237"/>
+      <c r="N17" s="38" t="s">
+        <v>23</v>
+      </c>
       <c r="O17" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="Q17" s="152"/>
-      <c r="R17" s="176"/>
-      <c r="S17" s="152"/>
-    </row>
-    <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="188" t="s">
+      <c r="P17" s="237"/>
+      <c r="Q17" s="260"/>
+      <c r="R17" s="237"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="223" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="168"/>
-      <c r="C18" s="168"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="193"/>
-      <c r="G18" s="145"/>
-      <c r="H18" s="145">
+      <c r="B18" s="224"/>
+      <c r="C18" s="224"/>
+      <c r="D18" s="224"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="229"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="145"/>
-      <c r="J18" s="145"/>
-      <c r="K18" s="179"/>
-      <c r="L18" s="181" t="s">
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="214"/>
+      <c r="L18" s="216" t="s">
         <v>110</v>
       </c>
-      <c r="N18" s="253" t="str">
+      <c r="M18" s="147" t="str">
         <f>IF(ISBLANK(A20),"",A20)</f>
         <v/>
       </c>
-      <c r="O18" s="254" t="str">
+      <c r="N18" s="153" t="str">
         <f>IF(ISBLANK(D20),"",D20)</f>
         <v/>
       </c>
-      <c r="P18" s="255"/>
-      <c r="Q18" s="183" t="s">
+      <c r="O18" s="154"/>
+      <c r="P18" s="218" t="s">
         <v>88</v>
       </c>
-      <c r="R18" s="200"/>
-      <c r="S18" s="259"/>
-    </row>
-    <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="190"/>
-      <c r="B19" s="191"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="192"/>
-      <c r="F19" s="194"/>
-      <c r="G19" s="146"/>
-      <c r="H19" s="146"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="146"/>
-      <c r="K19" s="180"/>
-      <c r="L19" s="182"/>
-      <c r="N19" s="256" t="str">
+      <c r="Q18" s="207"/>
+      <c r="R18" s="149"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="226"/>
+      <c r="B19" s="227"/>
+      <c r="C19" s="227"/>
+      <c r="D19" s="227"/>
+      <c r="E19" s="228"/>
+      <c r="F19" s="230"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="213"/>
+      <c r="J19" s="213"/>
+      <c r="K19" s="215"/>
+      <c r="L19" s="217"/>
+      <c r="M19" s="148" t="str">
         <f>A21</f>
         <v/>
       </c>
-      <c r="O19" s="257" t="str">
+      <c r="N19" s="151" t="str">
         <f>IF(ISBLANK(D21),"",D21)</f>
         <v/>
       </c>
-      <c r="P19" s="258"/>
-      <c r="Q19" s="184"/>
-      <c r="R19" s="201"/>
-      <c r="S19" s="260"/>
-    </row>
-    <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O19" s="152"/>
+      <c r="P19" s="219"/>
+      <c r="Q19" s="208"/>
+      <c r="R19" s="150"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="142"/>
-      <c r="B20" s="178"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="197"/>
-      <c r="E20" s="198"/>
+      <c r="B20" s="206"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="156"/>
       <c r="F20" s="139"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
       <c r="I20" s="129"/>
       <c r="J20" s="129"/>
       <c r="K20" s="129"/>
-      <c r="L20" s="186" t="s">
+      <c r="L20" s="221" t="s">
         <v>87</v>
       </c>
-      <c r="N20" s="253" t="str">
+      <c r="M20" s="147" t="str">
         <f>IF(ISBLANK(A22),"",A22)</f>
         <v/>
       </c>
-      <c r="O20" s="254" t="str">
-        <f t="shared" ref="O20:O53" si="0">IF(ISBLANK(D22),"",D22)</f>
-        <v/>
-      </c>
-      <c r="P20" s="255"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="201"/>
-      <c r="S20" s="259"/>
-    </row>
-    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N20" s="153" t="str">
+        <f t="shared" ref="N20:N53" si="0">IF(ISBLANK(D22),"",D22)</f>
+        <v/>
+      </c>
+      <c r="O20" s="154"/>
+      <c r="P20" s="219"/>
+      <c r="Q20" s="208"/>
+      <c r="R20" s="149"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="str">
         <f t="shared" ref="A21" si="1">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B21" s="178"/>
-      <c r="C21" s="178"/>
-      <c r="D21" s="195"/>
-      <c r="E21" s="196"/>
+      <c r="B21" s="206"/>
+      <c r="C21" s="206"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="158"/>
       <c r="F21" s="141"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
       <c r="I21" s="127"/>
       <c r="J21" s="127"/>
       <c r="K21" s="128"/>
-      <c r="L21" s="186"/>
-      <c r="N21" s="256" t="str">
+      <c r="L21" s="221"/>
+      <c r="M21" s="148" t="str">
         <f>A23</f>
         <v/>
       </c>
-      <c r="O21" s="257" t="str">
+      <c r="N21" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P21" s="258"/>
-      <c r="Q21" s="184"/>
-      <c r="R21" s="201"/>
-      <c r="S21" s="260"/>
-    </row>
-    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O21" s="152"/>
+      <c r="P21" s="219"/>
+      <c r="Q21" s="208"/>
+      <c r="R21" s="150"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="134"/>
-      <c r="B22" s="177"/>
-      <c r="C22" s="177"/>
-      <c r="D22" s="197"/>
-      <c r="E22" s="198"/>
+      <c r="B22" s="205"/>
+      <c r="C22" s="205"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="156"/>
       <c r="F22" s="139"/>
       <c r="G22" s="129"/>
       <c r="H22" s="129"/>
       <c r="I22" s="129"/>
       <c r="J22" s="129"/>
       <c r="K22" s="129"/>
-      <c r="L22" s="186"/>
-      <c r="N22" s="253" t="str">
-        <f t="shared" ref="N22" si="2">IF(ISBLANK(A24),"",A24)</f>
-        <v/>
-      </c>
-      <c r="O22" s="254" t="str">
+      <c r="L22" s="221"/>
+      <c r="M22" s="147" t="str">
+        <f t="shared" ref="M22" si="2">IF(ISBLANK(A24),"",A24)</f>
+        <v/>
+      </c>
+      <c r="N22" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P22" s="255"/>
-      <c r="Q22" s="184"/>
-      <c r="R22" s="201"/>
-      <c r="S22" s="259"/>
-    </row>
-    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O22" s="154"/>
+      <c r="P22" s="219"/>
+      <c r="Q22" s="208"/>
+      <c r="R22" s="149"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="str">
         <f t="shared" ref="A23:A25" si="3">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="178"/>
-      <c r="C23" s="178"/>
-      <c r="D23" s="195"/>
-      <c r="E23" s="196"/>
+      <c r="B23" s="206"/>
+      <c r="C23" s="206"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="158"/>
       <c r="F23" s="141"/>
       <c r="G23" s="127"/>
       <c r="H23" s="127"/>
       <c r="I23" s="127"/>
       <c r="J23" s="127"/>
       <c r="K23" s="128"/>
-      <c r="L23" s="186"/>
-      <c r="N23" s="256" t="str">
-        <f t="shared" ref="N23" si="4">A25</f>
-        <v/>
-      </c>
-      <c r="O23" s="257" t="str">
+      <c r="L23" s="221"/>
+      <c r="M23" s="148" t="str">
+        <f t="shared" ref="M23" si="4">A25</f>
+        <v/>
+      </c>
+      <c r="N23" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P23" s="258"/>
-      <c r="Q23" s="184"/>
-      <c r="R23" s="201"/>
-      <c r="S23" s="260"/>
-    </row>
-    <row r="24" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O23" s="152"/>
+      <c r="P23" s="219"/>
+      <c r="Q23" s="208"/>
+      <c r="R23" s="150"/>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="134"/>
-      <c r="B24" s="177"/>
-      <c r="C24" s="177"/>
-      <c r="D24" s="197"/>
-      <c r="E24" s="198"/>
+      <c r="B24" s="205"/>
+      <c r="C24" s="205"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="156"/>
       <c r="F24" s="139"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
       <c r="I24" s="129"/>
       <c r="J24" s="129"/>
       <c r="K24" s="129"/>
-      <c r="L24" s="186"/>
-      <c r="N24" s="253" t="str">
-        <f t="shared" ref="N24" si="5">IF(ISBLANK(A26),"",A26)</f>
-        <v/>
-      </c>
-      <c r="O24" s="254" t="str">
+      <c r="L24" s="221"/>
+      <c r="M24" s="147" t="str">
+        <f t="shared" ref="M24" si="5">IF(ISBLANK(A26),"",A26)</f>
+        <v/>
+      </c>
+      <c r="N24" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P24" s="255"/>
-      <c r="Q24" s="184"/>
-      <c r="R24" s="201"/>
-      <c r="S24" s="259"/>
-    </row>
-    <row r="25" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O24" s="154"/>
+      <c r="P24" s="219"/>
+      <c r="Q24" s="208"/>
+      <c r="R24" s="149"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B25" s="178"/>
-      <c r="C25" s="178"/>
-      <c r="D25" s="195"/>
-      <c r="E25" s="196"/>
+      <c r="B25" s="206"/>
+      <c r="C25" s="206"/>
+      <c r="D25" s="157"/>
+      <c r="E25" s="158"/>
       <c r="F25" s="141"/>
       <c r="G25" s="127"/>
       <c r="H25" s="127"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
       <c r="K25" s="128"/>
-      <c r="L25" s="186"/>
-      <c r="N25" s="256" t="str">
-        <f t="shared" ref="N25" si="6">A27</f>
-        <v/>
-      </c>
-      <c r="O25" s="257" t="str">
+      <c r="L25" s="221"/>
+      <c r="M25" s="148" t="str">
+        <f t="shared" ref="M25" si="6">A27</f>
+        <v/>
+      </c>
+      <c r="N25" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P25" s="258"/>
-      <c r="Q25" s="184"/>
-      <c r="R25" s="201"/>
-      <c r="S25" s="260"/>
-    </row>
-    <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O25" s="152"/>
+      <c r="P25" s="219"/>
+      <c r="Q25" s="208"/>
+      <c r="R25" s="150"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="134"/>
-      <c r="B26" s="177"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="197"/>
-      <c r="E26" s="198"/>
+      <c r="B26" s="205"/>
+      <c r="C26" s="205"/>
+      <c r="D26" s="155"/>
+      <c r="E26" s="156"/>
       <c r="F26" s="139"/>
       <c r="G26" s="129"/>
       <c r="H26" s="129"/>
       <c r="I26" s="129"/>
       <c r="J26" s="129"/>
       <c r="K26" s="129"/>
-      <c r="L26" s="186"/>
-      <c r="N26" s="253" t="str">
-        <f t="shared" ref="N26" si="7">IF(ISBLANK(A28),"",A28)</f>
-        <v/>
-      </c>
-      <c r="O26" s="254" t="str">
+      <c r="L26" s="221"/>
+      <c r="M26" s="147" t="str">
+        <f t="shared" ref="M26" si="7">IF(ISBLANK(A28),"",A28)</f>
+        <v/>
+      </c>
+      <c r="N26" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P26" s="255"/>
-      <c r="Q26" s="184"/>
-      <c r="R26" s="201"/>
-      <c r="S26" s="259"/>
-    </row>
-    <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O26" s="154"/>
+      <c r="P26" s="219"/>
+      <c r="Q26" s="208"/>
+      <c r="R26" s="149"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="str">
         <f t="shared" ref="A27" si="8">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="178"/>
-      <c r="C27" s="178"/>
-      <c r="D27" s="195"/>
-      <c r="E27" s="196"/>
+      <c r="B27" s="206"/>
+      <c r="C27" s="206"/>
+      <c r="D27" s="157"/>
+      <c r="E27" s="158"/>
       <c r="F27" s="141"/>
       <c r="G27" s="127"/>
       <c r="H27" s="127"/>
       <c r="I27" s="127"/>
       <c r="J27" s="127"/>
       <c r="K27" s="128"/>
-      <c r="L27" s="186"/>
-      <c r="N27" s="256" t="str">
-        <f t="shared" ref="N27" si="9">A29</f>
-        <v/>
-      </c>
-      <c r="O27" s="257" t="str">
+      <c r="L27" s="221"/>
+      <c r="M27" s="148" t="str">
+        <f t="shared" ref="M27" si="9">A29</f>
+        <v/>
+      </c>
+      <c r="N27" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P27" s="258"/>
-      <c r="Q27" s="184"/>
-      <c r="R27" s="201"/>
-      <c r="S27" s="260"/>
-    </row>
-    <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O27" s="152"/>
+      <c r="P27" s="219"/>
+      <c r="Q27" s="208"/>
+      <c r="R27" s="150"/>
+    </row>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="135"/>
-      <c r="B28" s="177"/>
-      <c r="C28" s="177"/>
-      <c r="D28" s="197"/>
-      <c r="E28" s="198"/>
+      <c r="B28" s="205"/>
+      <c r="C28" s="205"/>
+      <c r="D28" s="155"/>
+      <c r="E28" s="156"/>
       <c r="F28" s="139"/>
       <c r="G28" s="129"/>
       <c r="H28" s="129"/>
       <c r="I28" s="129"/>
       <c r="J28" s="129"/>
       <c r="K28" s="129"/>
-      <c r="L28" s="186"/>
-      <c r="N28" s="253" t="str">
-        <f t="shared" ref="N28" si="10">IF(ISBLANK(A30),"",A30)</f>
-        <v/>
-      </c>
-      <c r="O28" s="254" t="str">
+      <c r="L28" s="221"/>
+      <c r="M28" s="147" t="str">
+        <f t="shared" ref="M28" si="10">IF(ISBLANK(A30),"",A30)</f>
+        <v/>
+      </c>
+      <c r="N28" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P28" s="255"/>
-      <c r="Q28" s="184"/>
-      <c r="R28" s="201"/>
-      <c r="S28" s="259"/>
-    </row>
-    <row r="29" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O28" s="154"/>
+      <c r="P28" s="219"/>
+      <c r="Q28" s="208"/>
+      <c r="R28" s="149"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="str">
         <f t="shared" ref="A29" si="11">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="178"/>
-      <c r="C29" s="178"/>
-      <c r="D29" s="195"/>
-      <c r="E29" s="196"/>
+      <c r="B29" s="206"/>
+      <c r="C29" s="206"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="158"/>
       <c r="F29" s="141"/>
       <c r="G29" s="127"/>
       <c r="H29" s="127"/>
       <c r="I29" s="127"/>
       <c r="J29" s="129"/>
       <c r="K29" s="128"/>
-      <c r="L29" s="186"/>
-      <c r="N29" s="256" t="str">
-        <f t="shared" ref="N29" si="12">A31</f>
-        <v/>
-      </c>
-      <c r="O29" s="257" t="str">
+      <c r="L29" s="221"/>
+      <c r="M29" s="148" t="str">
+        <f t="shared" ref="M29" si="12">A31</f>
+        <v/>
+      </c>
+      <c r="N29" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P29" s="258"/>
-      <c r="Q29" s="184"/>
-      <c r="R29" s="201"/>
-      <c r="S29" s="260"/>
-    </row>
-    <row r="30" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O29" s="152"/>
+      <c r="P29" s="219"/>
+      <c r="Q29" s="208"/>
+      <c r="R29" s="150"/>
+    </row>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="134"/>
-      <c r="B30" s="177"/>
-      <c r="C30" s="177"/>
-      <c r="D30" s="197"/>
-      <c r="E30" s="198"/>
+      <c r="B30" s="205"/>
+      <c r="C30" s="205"/>
+      <c r="D30" s="155"/>
+      <c r="E30" s="156"/>
       <c r="F30" s="139"/>
       <c r="G30" s="129"/>
       <c r="H30" s="129"/>
       <c r="I30" s="140"/>
       <c r="J30" s="143"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="186"/>
-      <c r="N30" s="253" t="str">
-        <f t="shared" ref="N30" si="13">IF(ISBLANK(A32),"",A32)</f>
-        <v/>
-      </c>
-      <c r="O30" s="254" t="str">
+      <c r="L30" s="221"/>
+      <c r="M30" s="147" t="str">
+        <f t="shared" ref="M30" si="13">IF(ISBLANK(A32),"",A32)</f>
+        <v/>
+      </c>
+      <c r="N30" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P30" s="255"/>
-      <c r="Q30" s="184"/>
-      <c r="R30" s="201"/>
-      <c r="S30" s="259"/>
-    </row>
-    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O30" s="154"/>
+      <c r="P30" s="219"/>
+      <c r="Q30" s="208"/>
+      <c r="R30" s="149"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="str">
         <f t="shared" ref="A31" si="14">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="178"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="195"/>
-      <c r="E31" s="196"/>
+      <c r="B31" s="206"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="158"/>
       <c r="F31" s="141"/>
       <c r="G31" s="127"/>
       <c r="H31" s="127"/>
       <c r="I31" s="127"/>
       <c r="J31" s="127"/>
       <c r="K31" s="128"/>
-      <c r="L31" s="186"/>
-      <c r="N31" s="256" t="str">
-        <f t="shared" ref="N31" si="15">A33</f>
-        <v/>
-      </c>
-      <c r="O31" s="257" t="str">
+      <c r="L31" s="221"/>
+      <c r="M31" s="148" t="str">
+        <f t="shared" ref="M31" si="15">A33</f>
+        <v/>
+      </c>
+      <c r="N31" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P31" s="258"/>
-      <c r="Q31" s="184"/>
-      <c r="R31" s="201"/>
-      <c r="S31" s="260"/>
-    </row>
-    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O31" s="152"/>
+      <c r="P31" s="219"/>
+      <c r="Q31" s="208"/>
+      <c r="R31" s="150"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="134"/>
-      <c r="B32" s="177"/>
-      <c r="C32" s="177"/>
-      <c r="D32" s="197"/>
-      <c r="E32" s="198"/>
+      <c r="B32" s="205"/>
+      <c r="C32" s="205"/>
+      <c r="D32" s="155"/>
+      <c r="E32" s="156"/>
       <c r="F32" s="139"/>
       <c r="G32" s="129"/>
       <c r="H32" s="129"/>
       <c r="I32" s="129"/>
       <c r="J32" s="129"/>
       <c r="K32" s="129"/>
-      <c r="L32" s="186"/>
-      <c r="N32" s="253" t="str">
-        <f t="shared" ref="N32" si="16">IF(ISBLANK(A34),"",A34)</f>
-        <v/>
-      </c>
-      <c r="O32" s="254" t="str">
+      <c r="L32" s="221"/>
+      <c r="M32" s="147" t="str">
+        <f t="shared" ref="M32" si="16">IF(ISBLANK(A34),"",A34)</f>
+        <v/>
+      </c>
+      <c r="N32" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P32" s="255"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="201"/>
-      <c r="S32" s="259"/>
-    </row>
-    <row r="33" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O32" s="154"/>
+      <c r="P32" s="219"/>
+      <c r="Q32" s="208"/>
+      <c r="R32" s="149"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="str">
         <f t="shared" ref="A33" si="17">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="178"/>
-      <c r="C33" s="178"/>
-      <c r="D33" s="195"/>
-      <c r="E33" s="196"/>
+      <c r="B33" s="206"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="157"/>
+      <c r="E33" s="158"/>
       <c r="F33" s="141"/>
       <c r="G33" s="127"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
       <c r="J33" s="127"/>
       <c r="K33" s="128"/>
-      <c r="L33" s="186"/>
-      <c r="N33" s="256" t="str">
-        <f t="shared" ref="N33" si="18">A35</f>
-        <v/>
-      </c>
-      <c r="O33" s="257" t="str">
+      <c r="L33" s="221"/>
+      <c r="M33" s="148" t="str">
+        <f t="shared" ref="M33" si="18">A35</f>
+        <v/>
+      </c>
+      <c r="N33" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P33" s="258"/>
-      <c r="Q33" s="184"/>
-      <c r="R33" s="201"/>
-      <c r="S33" s="260"/>
-    </row>
-    <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O33" s="152"/>
+      <c r="P33" s="219"/>
+      <c r="Q33" s="208"/>
+      <c r="R33" s="150"/>
+    </row>
+    <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="134"/>
-      <c r="B34" s="177"/>
-      <c r="C34" s="177"/>
-      <c r="D34" s="197"/>
-      <c r="E34" s="198"/>
+      <c r="B34" s="205"/>
+      <c r="C34" s="205"/>
+      <c r="D34" s="155"/>
+      <c r="E34" s="156"/>
       <c r="F34" s="139"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
       <c r="I34" s="129"/>
       <c r="J34" s="129"/>
       <c r="K34" s="129"/>
-      <c r="L34" s="186"/>
-      <c r="N34" s="253" t="str">
-        <f t="shared" ref="N34" si="19">IF(ISBLANK(A36),"",A36)</f>
-        <v/>
-      </c>
-      <c r="O34" s="254" t="str">
+      <c r="L34" s="221"/>
+      <c r="M34" s="147" t="str">
+        <f t="shared" ref="M34" si="19">IF(ISBLANK(A36),"",A36)</f>
+        <v/>
+      </c>
+      <c r="N34" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P34" s="255"/>
-      <c r="Q34" s="184"/>
-      <c r="R34" s="201"/>
-      <c r="S34" s="259"/>
-    </row>
-    <row r="35" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O34" s="154"/>
+      <c r="P34" s="219"/>
+      <c r="Q34" s="208"/>
+      <c r="R34" s="149"/>
+    </row>
+    <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="str">
         <f t="shared" ref="A35" si="20">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="178"/>
-      <c r="C35" s="178"/>
-      <c r="D35" s="195"/>
-      <c r="E35" s="196"/>
+      <c r="B35" s="206"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="157"/>
+      <c r="E35" s="158"/>
       <c r="F35" s="141"/>
       <c r="G35" s="127"/>
       <c r="H35" s="127"/>
       <c r="I35" s="127"/>
       <c r="J35" s="127"/>
       <c r="K35" s="128"/>
-      <c r="L35" s="186"/>
-      <c r="N35" s="256" t="str">
-        <f t="shared" ref="N35" si="21">A37</f>
-        <v/>
-      </c>
-      <c r="O35" s="257" t="str">
+      <c r="L35" s="221"/>
+      <c r="M35" s="148" t="str">
+        <f t="shared" ref="M35" si="21">A37</f>
+        <v/>
+      </c>
+      <c r="N35" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P35" s="258"/>
-      <c r="Q35" s="184"/>
-      <c r="R35" s="201"/>
-      <c r="S35" s="260"/>
-    </row>
-    <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O35" s="152"/>
+      <c r="P35" s="219"/>
+      <c r="Q35" s="208"/>
+      <c r="R35" s="150"/>
+    </row>
+    <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="134"/>
-      <c r="B36" s="177"/>
-      <c r="C36" s="177"/>
-      <c r="D36" s="197"/>
-      <c r="E36" s="198"/>
+      <c r="B36" s="205"/>
+      <c r="C36" s="205"/>
+      <c r="D36" s="155"/>
+      <c r="E36" s="156"/>
       <c r="F36" s="139"/>
       <c r="G36" s="129"/>
       <c r="H36" s="129"/>
       <c r="I36" s="129"/>
       <c r="J36" s="129"/>
       <c r="K36" s="129"/>
-      <c r="L36" s="186"/>
-      <c r="N36" s="253" t="str">
-        <f t="shared" ref="N36" si="22">IF(ISBLANK(A38),"",A38)</f>
-        <v/>
-      </c>
-      <c r="O36" s="254" t="str">
+      <c r="L36" s="221"/>
+      <c r="M36" s="147" t="str">
+        <f t="shared" ref="M36" si="22">IF(ISBLANK(A38),"",A38)</f>
+        <v/>
+      </c>
+      <c r="N36" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P36" s="255"/>
-      <c r="Q36" s="184"/>
-      <c r="R36" s="201"/>
-      <c r="S36" s="259"/>
-    </row>
-    <row r="37" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O36" s="154"/>
+      <c r="P36" s="219"/>
+      <c r="Q36" s="208"/>
+      <c r="R36" s="149"/>
+    </row>
+    <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="str">
         <f t="shared" ref="A37" si="23">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="178"/>
-      <c r="C37" s="178"/>
-      <c r="D37" s="195"/>
-      <c r="E37" s="196"/>
+      <c r="B37" s="206"/>
+      <c r="C37" s="206"/>
+      <c r="D37" s="157"/>
+      <c r="E37" s="158"/>
       <c r="F37" s="141"/>
       <c r="G37" s="127"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
       <c r="J37" s="127"/>
       <c r="K37" s="128"/>
-      <c r="L37" s="186"/>
-      <c r="N37" s="256" t="str">
-        <f t="shared" ref="N37" si="24">A39</f>
-        <v/>
-      </c>
-      <c r="O37" s="257" t="str">
+      <c r="L37" s="221"/>
+      <c r="M37" s="148" t="str">
+        <f t="shared" ref="M37" si="24">A39</f>
+        <v/>
+      </c>
+      <c r="N37" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P37" s="258"/>
-      <c r="Q37" s="184"/>
-      <c r="R37" s="201"/>
-      <c r="S37" s="260"/>
-    </row>
-    <row r="38" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O37" s="152"/>
+      <c r="P37" s="219"/>
+      <c r="Q37" s="208"/>
+      <c r="R37" s="150"/>
+    </row>
+    <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="134"/>
-      <c r="B38" s="177"/>
-      <c r="C38" s="177"/>
-      <c r="D38" s="197"/>
-      <c r="E38" s="198"/>
+      <c r="B38" s="205"/>
+      <c r="C38" s="205"/>
+      <c r="D38" s="155"/>
+      <c r="E38" s="156"/>
       <c r="F38" s="139"/>
       <c r="G38" s="129"/>
       <c r="H38" s="129"/>
       <c r="I38" s="129"/>
       <c r="J38" s="129"/>
       <c r="K38" s="129"/>
-      <c r="L38" s="186"/>
-      <c r="N38" s="253" t="str">
-        <f t="shared" ref="N38" si="25">IF(ISBLANK(A40),"",A40)</f>
-        <v/>
-      </c>
-      <c r="O38" s="254" t="str">
+      <c r="L38" s="221"/>
+      <c r="M38" s="147" t="str">
+        <f t="shared" ref="M38" si="25">IF(ISBLANK(A40),"",A40)</f>
+        <v/>
+      </c>
+      <c r="N38" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P38" s="255"/>
-      <c r="Q38" s="184"/>
-      <c r="R38" s="201"/>
-      <c r="S38" s="259"/>
-    </row>
-    <row r="39" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O38" s="154"/>
+      <c r="P38" s="219"/>
+      <c r="Q38" s="208"/>
+      <c r="R38" s="149"/>
+    </row>
+    <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="str">
         <f t="shared" ref="A39" si="26">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="178"/>
-      <c r="C39" s="178"/>
-      <c r="D39" s="195"/>
-      <c r="E39" s="196"/>
+      <c r="B39" s="206"/>
+      <c r="C39" s="206"/>
+      <c r="D39" s="157"/>
+      <c r="E39" s="158"/>
       <c r="F39" s="141"/>
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
       <c r="K39" s="128"/>
-      <c r="L39" s="186"/>
-      <c r="N39" s="256" t="str">
-        <f t="shared" ref="N39" si="27">A41</f>
-        <v/>
-      </c>
-      <c r="O39" s="257" t="str">
+      <c r="L39" s="221"/>
+      <c r="M39" s="148" t="str">
+        <f t="shared" ref="M39" si="27">A41</f>
+        <v/>
+      </c>
+      <c r="N39" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P39" s="258"/>
-      <c r="Q39" s="184"/>
-      <c r="R39" s="201"/>
-      <c r="S39" s="260"/>
-    </row>
-    <row r="40" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O39" s="152"/>
+      <c r="P39" s="219"/>
+      <c r="Q39" s="208"/>
+      <c r="R39" s="150"/>
+    </row>
+    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="134"/>
-      <c r="B40" s="177"/>
-      <c r="C40" s="177"/>
-      <c r="D40" s="197"/>
-      <c r="E40" s="198"/>
+      <c r="B40" s="205"/>
+      <c r="C40" s="205"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="156"/>
       <c r="F40" s="139"/>
       <c r="G40" s="129"/>
       <c r="H40" s="129"/>
       <c r="I40" s="129"/>
       <c r="J40" s="129"/>
       <c r="K40" s="129"/>
-      <c r="L40" s="186"/>
-      <c r="N40" s="253" t="str">
-        <f t="shared" ref="N40" si="28">IF(ISBLANK(A42),"",A42)</f>
-        <v/>
-      </c>
-      <c r="O40" s="254" t="str">
+      <c r="L40" s="221"/>
+      <c r="M40" s="147" t="str">
+        <f t="shared" ref="M40" si="28">IF(ISBLANK(A42),"",A42)</f>
+        <v/>
+      </c>
+      <c r="N40" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P40" s="255"/>
-      <c r="Q40" s="184"/>
-      <c r="R40" s="201"/>
-      <c r="S40" s="259"/>
-    </row>
-    <row r="41" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O40" s="154"/>
+      <c r="P40" s="219"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="149"/>
+    </row>
+    <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="str">
         <f t="shared" ref="A41" si="29">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="178"/>
-      <c r="C41" s="178"/>
-      <c r="D41" s="195"/>
-      <c r="E41" s="196"/>
+      <c r="B41" s="206"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="157"/>
+      <c r="E41" s="158"/>
       <c r="F41" s="141"/>
       <c r="G41" s="127"/>
       <c r="H41" s="127"/>
       <c r="I41" s="127"/>
       <c r="J41" s="127"/>
       <c r="K41" s="128"/>
-      <c r="L41" s="186"/>
-      <c r="N41" s="256" t="str">
-        <f t="shared" ref="N41" si="30">A43</f>
-        <v/>
-      </c>
-      <c r="O41" s="257" t="str">
+      <c r="L41" s="221"/>
+      <c r="M41" s="148" t="str">
+        <f t="shared" ref="M41" si="30">A43</f>
+        <v/>
+      </c>
+      <c r="N41" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P41" s="258"/>
-      <c r="Q41" s="184"/>
-      <c r="R41" s="201"/>
-      <c r="S41" s="260"/>
-    </row>
-    <row r="42" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O41" s="152"/>
+      <c r="P41" s="219"/>
+      <c r="Q41" s="208"/>
+      <c r="R41" s="150"/>
+    </row>
+    <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="134"/>
-      <c r="B42" s="177"/>
-      <c r="C42" s="177"/>
-      <c r="D42" s="197"/>
-      <c r="E42" s="198"/>
+      <c r="B42" s="205"/>
+      <c r="C42" s="205"/>
+      <c r="D42" s="155"/>
+      <c r="E42" s="156"/>
       <c r="F42" s="139"/>
       <c r="G42" s="129"/>
       <c r="H42" s="129"/>
       <c r="I42" s="129"/>
       <c r="J42" s="129"/>
       <c r="K42" s="129"/>
-      <c r="L42" s="186"/>
-      <c r="N42" s="253" t="str">
-        <f t="shared" ref="N42" si="31">IF(ISBLANK(A44),"",A44)</f>
-        <v/>
-      </c>
-      <c r="O42" s="254" t="str">
+      <c r="L42" s="221"/>
+      <c r="M42" s="147" t="str">
+        <f t="shared" ref="M42" si="31">IF(ISBLANK(A44),"",A44)</f>
+        <v/>
+      </c>
+      <c r="N42" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P42" s="255"/>
-      <c r="Q42" s="184"/>
-      <c r="R42" s="201"/>
-      <c r="S42" s="259"/>
-    </row>
-    <row r="43" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O42" s="154"/>
+      <c r="P42" s="219"/>
+      <c r="Q42" s="208"/>
+      <c r="R42" s="149"/>
+    </row>
+    <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="str">
         <f t="shared" ref="A43" si="32">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="178"/>
-      <c r="C43" s="178"/>
-      <c r="D43" s="195"/>
-      <c r="E43" s="196"/>
+      <c r="B43" s="206"/>
+      <c r="C43" s="206"/>
+      <c r="D43" s="157"/>
+      <c r="E43" s="158"/>
       <c r="F43" s="141"/>
       <c r="G43" s="127"/>
       <c r="H43" s="127"/>
       <c r="I43" s="127"/>
       <c r="J43" s="127"/>
       <c r="K43" s="128"/>
-      <c r="L43" s="186"/>
-      <c r="N43" s="256" t="str">
-        <f t="shared" ref="N43" si="33">A45</f>
-        <v/>
-      </c>
-      <c r="O43" s="257" t="str">
+      <c r="L43" s="221"/>
+      <c r="M43" s="148" t="str">
+        <f t="shared" ref="M43" si="33">A45</f>
+        <v/>
+      </c>
+      <c r="N43" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P43" s="258"/>
-      <c r="Q43" s="184"/>
-      <c r="R43" s="201"/>
-      <c r="S43" s="260"/>
-    </row>
-    <row r="44" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O43" s="152"/>
+      <c r="P43" s="219"/>
+      <c r="Q43" s="208"/>
+      <c r="R43" s="150"/>
+    </row>
+    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="134"/>
-      <c r="B44" s="177"/>
-      <c r="C44" s="177"/>
-      <c r="D44" s="197"/>
-      <c r="E44" s="198"/>
+      <c r="B44" s="205"/>
+      <c r="C44" s="205"/>
+      <c r="D44" s="155"/>
+      <c r="E44" s="156"/>
       <c r="F44" s="139"/>
       <c r="G44" s="129"/>
       <c r="H44" s="129"/>
       <c r="I44" s="129"/>
       <c r="J44" s="129"/>
       <c r="K44" s="129"/>
-      <c r="L44" s="186"/>
-      <c r="N44" s="253" t="str">
-        <f t="shared" ref="N44" si="34">IF(ISBLANK(A46),"",A46)</f>
-        <v/>
-      </c>
-      <c r="O44" s="254" t="str">
+      <c r="L44" s="221"/>
+      <c r="M44" s="147" t="str">
+        <f t="shared" ref="M44" si="34">IF(ISBLANK(A46),"",A46)</f>
+        <v/>
+      </c>
+      <c r="N44" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P44" s="255"/>
-      <c r="Q44" s="184"/>
-      <c r="R44" s="201"/>
-      <c r="S44" s="259"/>
-    </row>
-    <row r="45" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O44" s="154"/>
+      <c r="P44" s="219"/>
+      <c r="Q44" s="208"/>
+      <c r="R44" s="149"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="str">
         <f t="shared" ref="A45" si="35">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="178"/>
-      <c r="C45" s="178"/>
-      <c r="D45" s="195"/>
-      <c r="E45" s="196"/>
+      <c r="B45" s="206"/>
+      <c r="C45" s="206"/>
+      <c r="D45" s="157"/>
+      <c r="E45" s="158"/>
       <c r="F45" s="141"/>
       <c r="G45" s="127"/>
       <c r="H45" s="127"/>
       <c r="I45" s="127"/>
       <c r="J45" s="127"/>
       <c r="K45" s="128"/>
-      <c r="L45" s="186"/>
-      <c r="N45" s="256" t="str">
-        <f t="shared" ref="N45" si="36">A47</f>
-        <v/>
-      </c>
-      <c r="O45" s="257" t="str">
+      <c r="L45" s="221"/>
+      <c r="M45" s="148" t="str">
+        <f t="shared" ref="M45" si="36">A47</f>
+        <v/>
+      </c>
+      <c r="N45" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P45" s="258"/>
-      <c r="Q45" s="184"/>
-      <c r="R45" s="201"/>
-      <c r="S45" s="260"/>
-    </row>
-    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O45" s="152"/>
+      <c r="P45" s="219"/>
+      <c r="Q45" s="208"/>
+      <c r="R45" s="150"/>
+    </row>
+    <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="134"/>
-      <c r="B46" s="177"/>
-      <c r="C46" s="177"/>
-      <c r="D46" s="197"/>
-      <c r="E46" s="198"/>
+      <c r="B46" s="205"/>
+      <c r="C46" s="205"/>
+      <c r="D46" s="155"/>
+      <c r="E46" s="156"/>
       <c r="F46" s="139"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
       <c r="I46" s="129"/>
       <c r="J46" s="129"/>
       <c r="K46" s="129"/>
-      <c r="L46" s="186"/>
-      <c r="N46" s="253" t="str">
-        <f t="shared" ref="N46" si="37">IF(ISBLANK(A48),"",A48)</f>
-        <v/>
-      </c>
-      <c r="O46" s="254" t="str">
+      <c r="L46" s="221"/>
+      <c r="M46" s="147" t="str">
+        <f t="shared" ref="M46" si="37">IF(ISBLANK(A48),"",A48)</f>
+        <v/>
+      </c>
+      <c r="N46" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P46" s="255"/>
-      <c r="Q46" s="184"/>
-      <c r="R46" s="201"/>
-      <c r="S46" s="259"/>
-    </row>
-    <row r="47" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O46" s="154"/>
+      <c r="P46" s="219"/>
+      <c r="Q46" s="208"/>
+      <c r="R46" s="149"/>
+    </row>
+    <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="str">
         <f t="shared" ref="A47" si="38">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="178"/>
-      <c r="C47" s="178"/>
-      <c r="D47" s="195"/>
-      <c r="E47" s="196"/>
+      <c r="B47" s="206"/>
+      <c r="C47" s="206"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="158"/>
       <c r="F47" s="141"/>
       <c r="G47" s="127"/>
       <c r="H47" s="127"/>
       <c r="I47" s="127"/>
       <c r="J47" s="127"/>
       <c r="K47" s="128"/>
-      <c r="L47" s="186"/>
-      <c r="N47" s="256" t="str">
-        <f t="shared" ref="N47" si="39">A49</f>
-        <v/>
-      </c>
-      <c r="O47" s="257" t="str">
+      <c r="L47" s="221"/>
+      <c r="M47" s="148" t="str">
+        <f t="shared" ref="M47" si="39">A49</f>
+        <v/>
+      </c>
+      <c r="N47" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P47" s="258"/>
-      <c r="Q47" s="184"/>
-      <c r="R47" s="201"/>
-      <c r="S47" s="260"/>
-    </row>
-    <row r="48" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O47" s="152"/>
+      <c r="P47" s="219"/>
+      <c r="Q47" s="208"/>
+      <c r="R47" s="150"/>
+    </row>
+    <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="134"/>
-      <c r="B48" s="177"/>
-      <c r="C48" s="177"/>
-      <c r="D48" s="197"/>
-      <c r="E48" s="198"/>
+      <c r="B48" s="205"/>
+      <c r="C48" s="205"/>
+      <c r="D48" s="155"/>
+      <c r="E48" s="156"/>
       <c r="F48" s="139"/>
       <c r="G48" s="129"/>
       <c r="H48" s="129"/>
       <c r="I48" s="129"/>
       <c r="J48" s="129"/>
       <c r="K48" s="129"/>
-      <c r="L48" s="186"/>
-      <c r="N48" s="253" t="str">
-        <f t="shared" ref="N48" si="40">IF(ISBLANK(A50),"",A50)</f>
-        <v/>
-      </c>
-      <c r="O48" s="254" t="str">
+      <c r="L48" s="221"/>
+      <c r="M48" s="147" t="str">
+        <f t="shared" ref="M48" si="40">IF(ISBLANK(A50),"",A50)</f>
+        <v/>
+      </c>
+      <c r="N48" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P48" s="255"/>
-      <c r="Q48" s="184"/>
-      <c r="R48" s="201"/>
-      <c r="S48" s="259"/>
-    </row>
-    <row r="49" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O48" s="154"/>
+      <c r="P48" s="219"/>
+      <c r="Q48" s="208"/>
+      <c r="R48" s="149"/>
+    </row>
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="str">
         <f t="shared" ref="A49" si="41">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="178"/>
-      <c r="C49" s="178"/>
-      <c r="D49" s="195"/>
-      <c r="E49" s="196"/>
+      <c r="B49" s="206"/>
+      <c r="C49" s="206"/>
+      <c r="D49" s="157"/>
+      <c r="E49" s="158"/>
       <c r="F49" s="141"/>
       <c r="G49" s="127"/>
       <c r="H49" s="127"/>
       <c r="I49" s="127"/>
       <c r="J49" s="127"/>
       <c r="K49" s="128"/>
-      <c r="L49" s="186"/>
-      <c r="N49" s="256" t="str">
-        <f t="shared" ref="N49" si="42">A51</f>
-        <v/>
-      </c>
-      <c r="O49" s="257" t="str">
+      <c r="L49" s="221"/>
+      <c r="M49" s="148" t="str">
+        <f t="shared" ref="M49" si="42">A51</f>
+        <v/>
+      </c>
+      <c r="N49" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P49" s="258"/>
-      <c r="Q49" s="184"/>
-      <c r="R49" s="201"/>
-      <c r="S49" s="260"/>
-    </row>
-    <row r="50" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O49" s="152"/>
+      <c r="P49" s="219"/>
+      <c r="Q49" s="208"/>
+      <c r="R49" s="150"/>
+    </row>
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="134"/>
-      <c r="B50" s="177"/>
-      <c r="C50" s="177"/>
-      <c r="D50" s="197"/>
-      <c r="E50" s="198"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
+      <c r="D50" s="155"/>
+      <c r="E50" s="156"/>
       <c r="F50" s="139"/>
       <c r="G50" s="129"/>
       <c r="H50" s="129"/>
       <c r="I50" s="129"/>
       <c r="J50" s="129"/>
       <c r="K50" s="129"/>
-      <c r="L50" s="186"/>
-      <c r="N50" s="253" t="str">
-        <f t="shared" ref="N50" si="43">IF(ISBLANK(A52),"",A52)</f>
-        <v/>
-      </c>
-      <c r="O50" s="254" t="str">
+      <c r="L50" s="221"/>
+      <c r="M50" s="147" t="str">
+        <f t="shared" ref="M50" si="43">IF(ISBLANK(A52),"",A52)</f>
+        <v/>
+      </c>
+      <c r="N50" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P50" s="255"/>
-      <c r="Q50" s="184"/>
-      <c r="R50" s="201"/>
-      <c r="S50" s="259"/>
-    </row>
-    <row r="51" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O50" s="154"/>
+      <c r="P50" s="219"/>
+      <c r="Q50" s="208"/>
+      <c r="R50" s="149"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="str">
         <f t="shared" ref="A51" si="44">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="178"/>
-      <c r="C51" s="178"/>
-      <c r="D51" s="195"/>
-      <c r="E51" s="196"/>
+      <c r="B51" s="206"/>
+      <c r="C51" s="206"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="158"/>
       <c r="F51" s="141"/>
       <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127"/>
       <c r="J51" s="127"/>
       <c r="K51" s="128"/>
-      <c r="L51" s="186"/>
-      <c r="N51" s="256" t="str">
-        <f t="shared" ref="N51" si="45">A53</f>
-        <v/>
-      </c>
-      <c r="O51" s="257" t="str">
+      <c r="L51" s="221"/>
+      <c r="M51" s="148" t="str">
+        <f t="shared" ref="M51" si="45">A53</f>
+        <v/>
+      </c>
+      <c r="N51" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P51" s="258"/>
-      <c r="Q51" s="184"/>
-      <c r="R51" s="201"/>
-      <c r="S51" s="260"/>
-    </row>
-    <row r="52" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O51" s="152"/>
+      <c r="P51" s="219"/>
+      <c r="Q51" s="208"/>
+      <c r="R51" s="150"/>
+    </row>
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="134"/>
-      <c r="B52" s="177"/>
-      <c r="C52" s="177"/>
-      <c r="D52" s="197"/>
-      <c r="E52" s="198"/>
+      <c r="B52" s="205"/>
+      <c r="C52" s="205"/>
+      <c r="D52" s="155"/>
+      <c r="E52" s="156"/>
       <c r="F52" s="139"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
       <c r="I52" s="129"/>
       <c r="J52" s="129"/>
       <c r="K52" s="129"/>
-      <c r="L52" s="186"/>
-      <c r="N52" s="253"/>
-      <c r="O52" s="254" t="str">
+      <c r="L52" s="221"/>
+      <c r="M52" s="147"/>
+      <c r="N52" s="153" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P52" s="255"/>
-      <c r="Q52" s="184"/>
-      <c r="R52" s="201"/>
-      <c r="S52" s="259"/>
-    </row>
-    <row r="53" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O52" s="154"/>
+      <c r="P52" s="219"/>
+      <c r="Q52" s="208"/>
+      <c r="R52" s="149"/>
+    </row>
+    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="str">
         <f t="shared" ref="A53" si="46">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B53" s="178"/>
-      <c r="C53" s="178"/>
-      <c r="D53" s="195"/>
-      <c r="E53" s="196"/>
+      <c r="B53" s="206"/>
+      <c r="C53" s="206"/>
+      <c r="D53" s="157"/>
+      <c r="E53" s="158"/>
       <c r="F53" s="141"/>
       <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127"/>
       <c r="J53" s="127"/>
       <c r="K53" s="128"/>
-      <c r="L53" s="187"/>
-      <c r="N53" s="256"/>
-      <c r="O53" s="257" t="str">
+      <c r="L53" s="222"/>
+      <c r="M53" s="148"/>
+      <c r="N53" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P53" s="258"/>
-      <c r="Q53" s="185"/>
-      <c r="R53" s="202"/>
-      <c r="S53" s="260"/>
-    </row>
-    <row r="54" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O53" s="152"/>
+      <c r="P53" s="220"/>
+      <c r="Q53" s="209"/>
+      <c r="R53" s="150"/>
+    </row>
+    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="39"/>
       <c r="B54" s="40"/>
       <c r="C54" s="40"/>
@@ -4492,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="L54" s="3"/>
+      <c r="M54" s="42"/>
       <c r="N54" s="42"/>
-      <c r="O54" s="42"/>
-      <c r="P54" s="43"/>
-      <c r="Q54" s="44"/>
-      <c r="S54" s="42"/>
-    </row>
-    <row r="55" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O54" s="43"/>
+      <c r="P54" s="44"/>
+      <c r="R54" s="42"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="45"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -4526,10 +4525,10 @@
         <v>0</v>
       </c>
       <c r="L55" s="3"/>
-      <c r="P55" s="47"/>
-      <c r="Q55" s="44"/>
-    </row>
-    <row r="56" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="O55" s="47"/>
+      <c r="P55" s="44"/>
+    </row>
+    <row r="56" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A56" s="45"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -4542,10 +4541,10 @@
       <c r="J56" s="46"/>
       <c r="K56" s="46"/>
       <c r="L56" s="3"/>
-      <c r="P56" s="47"/>
-      <c r="Q56" s="44"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="O56" s="47"/>
+      <c r="P56" s="44"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" s="45"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
@@ -4558,10 +4557,10 @@
       <c r="J57" s="48"/>
       <c r="K57" s="48"/>
       <c r="L57" s="3"/>
-      <c r="P57" s="47"/>
-      <c r="Q57" s="44"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="O57" s="47"/>
+      <c r="P57" s="44"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" s="45"/>
       <c r="B58" s="41" t="s">
         <v>28</v>
@@ -4573,8 +4572,8 @@
         <f>SUM(G55:K55)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="203"/>
-      <c r="H58" s="203"/>
+      <c r="G58" s="210"/>
+      <c r="H58" s="210"/>
       <c r="I58" s="49" t="s">
         <v>29</v>
       </c>
@@ -4583,10 +4582,10 @@
         <v>30</v>
       </c>
       <c r="L58" s="3"/>
-      <c r="P58" s="47"/>
-      <c r="Q58" s="44"/>
-    </row>
-    <row r="59" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O58" s="47"/>
+      <c r="P58" s="44"/>
+    </row>
+    <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="45"/>
       <c r="B59" s="41" t="s">
         <v>31</v>
@@ -4600,16 +4599,16 @@
         <f>L9</f>
         <v>0</v>
       </c>
-      <c r="G59" s="203"/>
-      <c r="H59" s="203"/>
+      <c r="G59" s="210"/>
+      <c r="H59" s="210"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
       <c r="L59" s="3"/>
-      <c r="P59" s="47"/>
-      <c r="Q59" s="44"/>
-    </row>
-    <row r="60" spans="1:19" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O59" s="47"/>
+      <c r="P59" s="44"/>
+    </row>
+    <row r="60" spans="1:18" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="50"/>
       <c r="B60" s="41" t="s">
         <v>33</v>
@@ -4629,10 +4628,10 @@
       <c r="J60" s="50"/>
       <c r="K60" s="53"/>
       <c r="L60" s="3"/>
-      <c r="P60" s="47"/>
-      <c r="Q60" s="44"/>
-    </row>
-    <row r="61" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="O60" s="47"/>
+      <c r="P60" s="44"/>
+    </row>
+    <row r="61" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A61" s="50"/>
       <c r="B61" s="40"/>
       <c r="C61" s="40"/>
@@ -4645,10 +4644,10 @@
       <c r="J61" s="50"/>
       <c r="K61" s="50"/>
       <c r="L61" s="3"/>
-      <c r="P61" s="47"/>
-      <c r="Q61" s="44"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="O61" s="47"/>
+      <c r="P61" s="44"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" s="56"/>
       <c r="B62" s="40" t="s">
         <v>34</v>
@@ -4664,37 +4663,37 @@
       <c r="K62" s="58"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" s="50"/>
       <c r="B63" s="57"/>
-      <c r="C63" s="204" t="s">
+      <c r="C63" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="D63" s="204"/>
-      <c r="E63" s="204"/>
-      <c r="F63" s="204"/>
-      <c r="G63" s="204"/>
-      <c r="H63" s="204"/>
-      <c r="I63" s="204"/>
-      <c r="J63" s="204"/>
-      <c r="K63" s="204"/>
+      <c r="D63" s="211"/>
+      <c r="E63" s="211"/>
+      <c r="F63" s="211"/>
+      <c r="G63" s="211"/>
+      <c r="H63" s="211"/>
+      <c r="I63" s="211"/>
+      <c r="J63" s="211"/>
+      <c r="K63" s="211"/>
       <c r="L63" s="3"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" s="50"/>
       <c r="B64" s="57"/>
-      <c r="C64" s="204"/>
-      <c r="D64" s="204"/>
-      <c r="E64" s="204"/>
-      <c r="F64" s="204"/>
-      <c r="G64" s="204"/>
-      <c r="H64" s="204"/>
-      <c r="I64" s="204"/>
-      <c r="J64" s="204"/>
-      <c r="K64" s="204"/>
+      <c r="C64" s="211"/>
+      <c r="D64" s="211"/>
+      <c r="E64" s="211"/>
+      <c r="F64" s="211"/>
+      <c r="G64" s="211"/>
+      <c r="H64" s="211"/>
+      <c r="I64" s="211"/>
+      <c r="J64" s="211"/>
+      <c r="K64" s="211"/>
       <c r="L64" s="3"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" s="50"/>
       <c r="B65" s="40"/>
       <c r="C65" s="61"/>
@@ -4708,7 +4707,7 @@
       <c r="K65" s="60"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -4721,11 +4720,11 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="3"/>
-      <c r="S66" s="62" t="s">
+      <c r="R66" s="62" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
@@ -4738,11 +4737,11 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="3"/>
-      <c r="S67" s="63" t="s">
+      <c r="R67" s="63" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A68" s="64" t="s">
         <v>36</v>
       </c>
@@ -4759,9 +4758,9 @@
       <c r="J68" s="40"/>
       <c r="K68" s="60"/>
       <c r="L68" s="3"/>
-      <c r="S68" s="65"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="R68" s="65"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" s="50"/>
       <c r="B69" s="40"/>
       <c r="C69" s="61"/>
@@ -4775,7 +4774,7 @@
       <c r="K69" s="60"/>
       <c r="L69" s="3"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" s="50"/>
       <c r="B70" s="40"/>
       <c r="C70" s="61"/>
@@ -4789,7 +4788,7 @@
       <c r="K70" s="60"/>
       <c r="L70" s="3"/>
     </row>
-    <row r="71" spans="1:19" ht="20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="20" x14ac:dyDescent="0.35">
       <c r="A71" s="50"/>
       <c r="B71" s="40"/>
       <c r="C71" s="61"/>
@@ -4802,16 +4801,16 @@
       <c r="J71" s="60"/>
       <c r="K71" s="60"/>
       <c r="L71" s="3"/>
-      <c r="N71" s="199" t="s">
+      <c r="M71" s="204" t="s">
         <v>89</v>
       </c>
-      <c r="O71" s="199"/>
-      <c r="P71" s="199"/>
-      <c r="Q71" s="199"/>
-      <c r="R71" s="199"/>
-      <c r="S71" s="199"/>
-    </row>
-    <row r="72" spans="1:19" ht="20" x14ac:dyDescent="0.35">
+      <c r="N71" s="204"/>
+      <c r="O71" s="204"/>
+      <c r="P71" s="204"/>
+      <c r="Q71" s="204"/>
+      <c r="R71" s="204"/>
+    </row>
+    <row r="72" spans="1:18" ht="20" x14ac:dyDescent="0.35">
       <c r="A72" s="50"/>
       <c r="B72" s="41"/>
       <c r="C72" s="41" t="s">
@@ -4826,16 +4825,16 @@
       <c r="J72" s="60"/>
       <c r="K72" s="60"/>
       <c r="L72" s="3"/>
-      <c r="N72" s="199" t="s">
+      <c r="M72" s="204" t="s">
         <v>90</v>
       </c>
-      <c r="O72" s="199"/>
-      <c r="P72" s="199"/>
-      <c r="Q72" s="199"/>
-      <c r="R72" s="199"/>
-      <c r="S72" s="199"/>
-    </row>
-    <row r="73" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N72" s="204"/>
+      <c r="O72" s="204"/>
+      <c r="P72" s="204"/>
+      <c r="Q72" s="204"/>
+      <c r="R72" s="204"/>
+    </row>
+    <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A73" s="50"/>
       <c r="B73" s="66"/>
       <c r="C73" s="66" t="s">
@@ -4852,14 +4851,14 @@
       <c r="J73" s="60"/>
       <c r="K73" s="60"/>
       <c r="L73" s="3"/>
-      <c r="N73" s="206"/>
-      <c r="O73" s="206"/>
-      <c r="P73" s="206"/>
-      <c r="Q73" s="206"/>
-      <c r="R73" s="206"/>
-      <c r="S73" s="206"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M73" s="196"/>
+      <c r="N73" s="196"/>
+      <c r="O73" s="196"/>
+      <c r="P73" s="196"/>
+      <c r="Q73" s="196"/>
+      <c r="R73" s="196"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="50"/>
       <c r="B74" s="40"/>
       <c r="C74" s="40"/>
@@ -4873,7 +4872,7 @@
       <c r="K74" s="60"/>
       <c r="L74" s="3"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" s="50"/>
       <c r="B75" s="41"/>
       <c r="C75" s="41" t="s">
@@ -4883,26 +4882,26 @@
       <c r="E75" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="207">
+      <c r="F75" s="197">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="207"/>
-      <c r="H75" s="207"/>
-      <c r="I75" s="207"/>
-      <c r="J75" s="207"/>
-      <c r="K75" s="207"/>
+      <c r="G75" s="197"/>
+      <c r="H75" s="197"/>
+      <c r="I75" s="197"/>
+      <c r="J75" s="197"/>
+      <c r="K75" s="197"/>
       <c r="L75" s="3"/>
-      <c r="N75" s="208" t="s">
+      <c r="M75" s="198" t="s">
         <v>91</v>
       </c>
-      <c r="O75" s="208"/>
-      <c r="P75" s="208"/>
-      <c r="Q75" s="208"/>
-      <c r="R75" s="208"/>
-      <c r="S75" s="208"/>
-    </row>
-    <row r="76" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="N75" s="198"/>
+      <c r="O75" s="198"/>
+      <c r="P75" s="198"/>
+      <c r="Q75" s="198"/>
+      <c r="R75" s="198"/>
+    </row>
+    <row r="76" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A76" s="50"/>
       <c r="B76" s="40"/>
       <c r="C76" s="40"/>
@@ -4915,14 +4914,14 @@
       <c r="J76" s="60"/>
       <c r="K76" s="60"/>
       <c r="L76" s="50"/>
+      <c r="M76" s="75"/>
       <c r="N76" s="75"/>
       <c r="O76" s="75"/>
       <c r="P76" s="75"/>
       <c r="Q76" s="75"/>
       <c r="R76" s="75"/>
-      <c r="S76" s="75"/>
-    </row>
-    <row r="77" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A77" s="64"/>
       <c r="B77" s="41"/>
       <c r="C77" s="41" t="s">
@@ -4932,24 +4931,24 @@
       <c r="E77" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="209">
+      <c r="F77" s="199">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="209"/>
-      <c r="H77" s="209"/>
-      <c r="I77" s="209"/>
-      <c r="J77" s="209"/>
+      <c r="G77" s="199"/>
+      <c r="H77" s="199"/>
+      <c r="I77" s="199"/>
+      <c r="J77" s="199"/>
       <c r="K77" s="40"/>
       <c r="L77" s="50"/>
+      <c r="M77" s="75"/>
       <c r="N77" s="75"/>
       <c r="O77" s="75"/>
       <c r="P77" s="75"/>
       <c r="Q77" s="75"/>
       <c r="R77" s="75"/>
-      <c r="S77" s="75"/>
-    </row>
-    <row r="78" spans="1:19" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:18" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="67"/>
       <c r="B78" s="40"/>
       <c r="C78" s="40"/>
@@ -4962,17 +4961,17 @@
       <c r="J78" s="67"/>
       <c r="K78" s="50"/>
       <c r="L78" s="50"/>
+      <c r="M78" s="133"/>
       <c r="N78" s="133"/>
-      <c r="O78" s="133"/>
-      <c r="P78" s="211" t="str">
+      <c r="O78" s="201" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="Q78" s="211"/>
-      <c r="R78" s="211"/>
-      <c r="S78" s="211"/>
-    </row>
-    <row r="79" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="P78" s="201"/>
+      <c r="Q78" s="201"/>
+      <c r="R78" s="201"/>
+    </row>
+    <row r="79" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A79" s="67"/>
       <c r="B79" s="40"/>
       <c r="C79" s="40" t="s">
@@ -4989,17 +4988,17 @@
       <c r="J79" s="67"/>
       <c r="K79" s="50"/>
       <c r="L79" s="10"/>
+      <c r="M79" s="77"/>
       <c r="N79" s="77"/>
-      <c r="O79" s="77"/>
-      <c r="P79" s="78"/>
-      <c r="Q79" s="210" t="str">
+      <c r="O79" s="78"/>
+      <c r="P79" s="200" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="R79" s="210"/>
-      <c r="S79" s="79"/>
-    </row>
-    <row r="80" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="Q79" s="200"/>
+      <c r="R79" s="79"/>
+    </row>
+    <row r="80" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A80" s="50"/>
       <c r="B80" s="67"/>
       <c r="C80" s="40"/>
@@ -5012,14 +5011,14 @@
       <c r="J80" s="50"/>
       <c r="K80" s="50"/>
       <c r="L80" s="10"/>
+      <c r="M80" s="77"/>
       <c r="N80" s="77"/>
-      <c r="O80" s="77"/>
+      <c r="O80" s="78"/>
       <c r="P80" s="78"/>
       <c r="Q80" s="78"/>
-      <c r="R80" s="78"/>
-      <c r="S80" s="80"/>
-    </row>
-    <row r="81" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R80" s="80"/>
+    </row>
+    <row r="81" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="50"/>
       <c r="B81" s="67"/>
       <c r="C81" s="41"/>
@@ -5032,17 +5031,17 @@
       <c r="J81" s="50"/>
       <c r="K81" s="50"/>
       <c r="L81" s="50"/>
+      <c r="M81" s="78"/>
       <c r="N81" s="78"/>
-      <c r="O81" s="78"/>
-      <c r="P81" s="212" t="str">
+      <c r="O81" s="202" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="Q81" s="212"/>
-      <c r="R81" s="212"/>
-      <c r="S81" s="212"/>
-    </row>
-    <row r="82" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="P81" s="202"/>
+      <c r="Q81" s="202"/>
+      <c r="R81" s="202"/>
+    </row>
+    <row r="82" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A82" s="50"/>
       <c r="B82" s="67"/>
       <c r="C82" s="66"/>
@@ -5055,14 +5054,14 @@
       <c r="J82" s="50"/>
       <c r="K82" s="50"/>
       <c r="L82" s="50"/>
+      <c r="M82" s="75"/>
       <c r="N82" s="75"/>
       <c r="O82" s="75"/>
       <c r="P82" s="75"/>
       <c r="Q82" s="75"/>
       <c r="R82" s="75"/>
-      <c r="S82" s="75"/>
-    </row>
-    <row r="83" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="83" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A83" s="50"/>
       <c r="B83" s="67"/>
       <c r="C83" s="41" t="s">
@@ -5077,14 +5076,14 @@
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="N83" s="213"/>
-      <c r="O83" s="213"/>
-      <c r="P83" s="213"/>
-      <c r="Q83" s="213"/>
-      <c r="R83" s="213"/>
-      <c r="S83" s="213"/>
-    </row>
-    <row r="84" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M83" s="203"/>
+      <c r="N83" s="203"/>
+      <c r="O83" s="203"/>
+      <c r="P83" s="203"/>
+      <c r="Q83" s="203"/>
+      <c r="R83" s="203"/>
+    </row>
+    <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="50"/>
       <c r="B84" s="67"/>
       <c r="C84" s="66" t="s">
@@ -5101,16 +5100,16 @@
       <c r="J84" s="74"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="N84" s="205" t="s">
+      <c r="M84" s="182" t="s">
         <v>92</v>
       </c>
-      <c r="O84" s="205"/>
-      <c r="P84" s="205"/>
-      <c r="Q84" s="205"/>
-      <c r="R84" s="205"/>
-      <c r="S84" s="205"/>
-    </row>
-    <row r="85" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N84" s="182"/>
+      <c r="O84" s="182"/>
+      <c r="P84" s="182"/>
+      <c r="Q84" s="182"/>
+      <c r="R84" s="182"/>
+    </row>
+    <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="50"/>
       <c r="B85" s="67"/>
       <c r="C85" s="40"/>
@@ -5123,16 +5122,16 @@
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="N85" s="205" t="s">
+      <c r="M85" s="182" t="s">
         <v>93</v>
       </c>
-      <c r="O85" s="205"/>
-      <c r="P85" s="205"/>
-      <c r="Q85" s="205"/>
-      <c r="R85" s="205"/>
-      <c r="S85" s="205"/>
-    </row>
-    <row r="86" spans="1:19" ht="18" x14ac:dyDescent="0.4">
+      <c r="N85" s="182"/>
+      <c r="O85" s="182"/>
+      <c r="P85" s="182"/>
+      <c r="Q85" s="182"/>
+      <c r="R85" s="182"/>
+    </row>
+    <row r="86" spans="1:18" ht="18" x14ac:dyDescent="0.4">
       <c r="A86" s="50"/>
       <c r="B86" s="67"/>
       <c r="C86" s="41" t="s">
@@ -5149,14 +5148,14 @@
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="N86" s="214"/>
-      <c r="O86" s="214"/>
-      <c r="P86" s="214"/>
-      <c r="Q86" s="214"/>
-      <c r="R86" s="214"/>
-      <c r="S86" s="214"/>
-    </row>
-    <row r="87" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M86" s="183"/>
+      <c r="N86" s="183"/>
+      <c r="O86" s="183"/>
+      <c r="P86" s="183"/>
+      <c r="Q86" s="183"/>
+      <c r="R86" s="183"/>
+    </row>
+    <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="50"/>
       <c r="B87" s="67"/>
       <c r="C87" s="40"/>
@@ -5169,14 +5168,14 @@
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="N87" s="205"/>
-      <c r="O87" s="205"/>
-      <c r="P87" s="205"/>
-      <c r="Q87" s="205"/>
-      <c r="R87" s="205"/>
-      <c r="S87" s="205"/>
-    </row>
-    <row r="88" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M87" s="182"/>
+      <c r="N87" s="182"/>
+      <c r="O87" s="182"/>
+      <c r="P87" s="182"/>
+      <c r="Q87" s="182"/>
+      <c r="R87" s="182"/>
+    </row>
+    <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="50"/>
       <c r="B88" s="67"/>
       <c r="C88" s="41" t="s">
@@ -5186,23 +5185,23 @@
       <c r="E88" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="229"/>
-      <c r="G88" s="229"/>
-      <c r="H88" s="229"/>
-      <c r="I88" s="229"/>
-      <c r="J88" s="229"/>
+      <c r="F88" s="181"/>
+      <c r="G88" s="181"/>
+      <c r="H88" s="181"/>
+      <c r="I88" s="181"/>
+      <c r="J88" s="181"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="N88" s="205" t="s">
+      <c r="M88" s="182" t="s">
         <v>94</v>
       </c>
-      <c r="O88" s="205"/>
-      <c r="P88" s="205"/>
-      <c r="Q88" s="205"/>
-      <c r="R88" s="205"/>
-      <c r="S88" s="205"/>
-    </row>
-    <row r="89" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N88" s="182"/>
+      <c r="O88" s="182"/>
+      <c r="P88" s="182"/>
+      <c r="Q88" s="182"/>
+      <c r="R88" s="182"/>
+    </row>
+    <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="50"/>
       <c r="B89" s="67"/>
       <c r="C89" s="40"/>
@@ -5215,16 +5214,16 @@
       <c r="J89" s="40"/>
       <c r="K89" s="50"/>
       <c r="L89" s="50"/>
-      <c r="N89" s="83" t="s">
+      <c r="M89" s="83" t="s">
         <v>95</v>
       </c>
+      <c r="N89" s="83"/>
       <c r="O89" s="83"/>
       <c r="P89" s="83"/>
       <c r="Q89" s="83"/>
       <c r="R89" s="83"/>
-      <c r="S89" s="83"/>
-    </row>
-    <row r="90" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="50"/>
       <c r="B90" s="67"/>
       <c r="C90" s="40" t="s">
@@ -5241,14 +5240,14 @@
       <c r="J90" s="41"/>
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
+      <c r="M90" s="83"/>
       <c r="N90" s="83"/>
       <c r="O90" s="83"/>
       <c r="P90" s="83"/>
       <c r="Q90" s="83"/>
       <c r="R90" s="83"/>
-      <c r="S90" s="83"/>
-    </row>
-    <row r="91" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="50"/>
       <c r="B91" s="67"/>
       <c r="C91" s="41"/>
@@ -5261,16 +5260,16 @@
       <c r="J91" s="50"/>
       <c r="K91" s="50"/>
       <c r="L91" s="50"/>
-      <c r="N91" s="83" t="s">
+      <c r="M91" s="83" t="s">
         <v>96</v>
       </c>
+      <c r="N91" s="83"/>
       <c r="O91" s="83"/>
       <c r="P91" s="83"/>
       <c r="Q91" s="83"/>
       <c r="R91" s="83"/>
-      <c r="S91" s="83"/>
-    </row>
-    <row r="92" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="50"/>
       <c r="B92" s="67"/>
       <c r="C92" s="40"/>
@@ -5283,14 +5282,14 @@
       <c r="J92" s="50"/>
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
+      <c r="M92" s="83"/>
       <c r="N92" s="83"/>
       <c r="O92" s="83"/>
       <c r="P92" s="83"/>
       <c r="Q92" s="83"/>
       <c r="R92" s="83"/>
-      <c r="S92" s="83"/>
-    </row>
-    <row r="93" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="50"/>
       <c r="B93" s="67"/>
       <c r="C93" s="40"/>
@@ -5303,16 +5302,16 @@
       <c r="J93" s="50"/>
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
-      <c r="N93" s="83" t="s">
+      <c r="M93" s="83" t="s">
         <v>97</v>
       </c>
+      <c r="N93" s="83"/>
       <c r="O93" s="83"/>
       <c r="P93" s="83"/>
       <c r="Q93" s="83"/>
       <c r="R93" s="83"/>
-      <c r="S93" s="83"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" s="64" t="s">
         <v>44</v>
       </c>
@@ -5329,16 +5328,16 @@
       <c r="J94" s="86"/>
       <c r="K94" s="27"/>
       <c r="L94" s="17"/>
-      <c r="N94" s="83" t="s">
+      <c r="M94" s="83" t="s">
         <v>106</v>
       </c>
+      <c r="N94" s="83"/>
       <c r="O94" s="83"/>
       <c r="P94" s="83"/>
       <c r="Q94" s="83"/>
       <c r="R94" s="83"/>
-      <c r="S94" s="83"/>
-    </row>
-    <row r="95" spans="1:19" ht="18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:18" ht="18" x14ac:dyDescent="0.4">
       <c r="A95" s="64"/>
       <c r="B95" s="86" t="s">
         <v>46</v>
@@ -5353,14 +5352,14 @@
       <c r="J95" s="86"/>
       <c r="K95" s="27"/>
       <c r="L95" s="17"/>
-      <c r="N95" s="214"/>
-      <c r="O95" s="214"/>
-      <c r="P95" s="214"/>
-      <c r="Q95" s="214"/>
-      <c r="R95" s="214"/>
-      <c r="S95" s="214"/>
-    </row>
-    <row r="96" spans="1:19" ht="18" x14ac:dyDescent="0.4">
+      <c r="M95" s="183"/>
+      <c r="N95" s="183"/>
+      <c r="O95" s="183"/>
+      <c r="P95" s="183"/>
+      <c r="Q95" s="183"/>
+      <c r="R95" s="183"/>
+    </row>
+    <row r="96" spans="1:18" ht="18" x14ac:dyDescent="0.4">
       <c r="A96" s="64"/>
       <c r="B96" s="86" t="s">
         <v>47</v>
@@ -5375,14 +5374,14 @@
       <c r="J96" s="86"/>
       <c r="K96" s="27"/>
       <c r="L96" s="17"/>
-      <c r="N96" s="214"/>
-      <c r="O96" s="214"/>
-      <c r="P96" s="214"/>
-      <c r="Q96" s="214"/>
-      <c r="R96" s="214"/>
-      <c r="S96" s="214"/>
-    </row>
-    <row r="97" spans="1:19" ht="18" x14ac:dyDescent="0.4">
+      <c r="M96" s="183"/>
+      <c r="N96" s="183"/>
+      <c r="O96" s="183"/>
+      <c r="P96" s="183"/>
+      <c r="Q96" s="183"/>
+      <c r="R96" s="183"/>
+    </row>
+    <row r="97" spans="1:18" ht="18" x14ac:dyDescent="0.4">
       <c r="A97" s="64"/>
       <c r="B97" s="86" t="s">
         <v>48</v>
@@ -5397,14 +5396,14 @@
       <c r="J97" s="86"/>
       <c r="K97" s="27"/>
       <c r="L97" s="17"/>
-      <c r="N97" s="214"/>
-      <c r="O97" s="214"/>
-      <c r="P97" s="214"/>
-      <c r="Q97" s="214"/>
-      <c r="R97" s="214"/>
-      <c r="S97" s="214"/>
-    </row>
-    <row r="98" spans="1:19" ht="18" x14ac:dyDescent="0.4">
+      <c r="M97" s="183"/>
+      <c r="N97" s="183"/>
+      <c r="O97" s="183"/>
+      <c r="P97" s="183"/>
+      <c r="Q97" s="183"/>
+      <c r="R97" s="183"/>
+    </row>
+    <row r="98" spans="1:18" ht="18" x14ac:dyDescent="0.4">
       <c r="A98" s="64"/>
       <c r="B98" s="86" t="s">
         <v>49</v>
@@ -5419,14 +5418,14 @@
       <c r="J98" s="86"/>
       <c r="K98" s="27"/>
       <c r="L98" s="17"/>
-      <c r="N98" s="214"/>
-      <c r="O98" s="214"/>
-      <c r="P98" s="214"/>
-      <c r="Q98" s="214"/>
-      <c r="R98" s="214"/>
-      <c r="S98" s="214"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M98" s="183"/>
+      <c r="N98" s="183"/>
+      <c r="O98" s="183"/>
+      <c r="P98" s="183"/>
+      <c r="Q98" s="183"/>
+      <c r="R98" s="183"/>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" s="64"/>
       <c r="B99" s="86" t="s">
         <v>50</v>
@@ -5441,14 +5440,14 @@
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
       <c r="L99" s="17"/>
-      <c r="N99" s="205"/>
-      <c r="O99" s="205"/>
-      <c r="P99" s="205"/>
-      <c r="Q99" s="205"/>
-      <c r="R99" s="205"/>
-      <c r="S99" s="205"/>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M99" s="182"/>
+      <c r="N99" s="182"/>
+      <c r="O99" s="182"/>
+      <c r="P99" s="182"/>
+      <c r="Q99" s="182"/>
+      <c r="R99" s="182"/>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A100" s="50"/>
       <c r="B100" s="86"/>
       <c r="C100" s="18"/>
@@ -5461,14 +5460,14 @@
       <c r="J100" s="17"/>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
+      <c r="M100" s="83"/>
       <c r="N100" s="83"/>
       <c r="O100" s="83"/>
       <c r="P100" s="83"/>
       <c r="Q100" s="83"/>
       <c r="R100" s="83"/>
-      <c r="S100" s="83"/>
-    </row>
-    <row r="101" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A101" s="64" t="s">
         <v>51</v>
       </c>
@@ -5485,9 +5484,9 @@
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
-      <c r="P101" s="79"/>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="O101" s="79"/>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A102" s="64"/>
       <c r="B102" s="18" t="s">
         <v>53</v>
@@ -5503,7 +5502,7 @@
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A103" s="64"/>
       <c r="B103" s="18" t="s">
         <v>54</v>
@@ -5518,11 +5517,11 @@
       <c r="J103" s="17"/>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
-      <c r="P103" s="77" t="s">
+      <c r="O103" s="77" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A104" s="64"/>
       <c r="B104" s="41"/>
       <c r="C104" s="92"/>
@@ -5535,11 +5534,11 @@
       <c r="J104" s="41"/>
       <c r="K104" s="93"/>
       <c r="L104" s="50"/>
+      <c r="P104" s="94"/>
       <c r="Q104" s="94"/>
       <c r="R104" s="94"/>
-      <c r="S104" s="94"/>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A105" s="64"/>
       <c r="B105" s="40" t="s">
         <v>55</v>
@@ -5555,7 +5554,7 @@
       <c r="K105" s="50"/>
       <c r="L105" s="50"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A106" s="64"/>
       <c r="B106" s="40"/>
       <c r="C106" s="95"/>
@@ -5569,7 +5568,7 @@
       <c r="K106" s="50"/>
       <c r="L106" s="50"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A107" s="64"/>
       <c r="B107" s="40"/>
       <c r="C107" s="95"/>
@@ -5582,14 +5581,14 @@
       <c r="J107" s="50"/>
       <c r="K107" s="50"/>
       <c r="L107" s="50"/>
-      <c r="P107" s="94" t="s">
+      <c r="O107" s="94" t="s">
         <v>104</v>
       </c>
+      <c r="P107" s="94"/>
       <c r="Q107" s="94"/>
       <c r="R107" s="94"/>
-      <c r="S107" s="94"/>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A108" s="64" t="s">
         <v>56</v>
       </c>
@@ -5608,11 +5607,11 @@
       <c r="J108" s="50"/>
       <c r="K108" s="50"/>
       <c r="L108" s="50"/>
+      <c r="P108" s="94"/>
       <c r="Q108" s="94"/>
       <c r="R108" s="94"/>
-      <c r="S108" s="94"/>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A109" s="55"/>
       <c r="B109" s="95"/>
       <c r="C109" s="40"/>
@@ -5625,14 +5624,14 @@
       <c r="J109" s="50"/>
       <c r="K109" s="50"/>
       <c r="L109" s="50"/>
-      <c r="P109" s="83" t="s">
+      <c r="O109" s="83" t="s">
         <v>98</v>
       </c>
+      <c r="P109" s="94"/>
       <c r="Q109" s="94"/>
       <c r="R109" s="94"/>
-      <c r="S109" s="94"/>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A110" s="50"/>
       <c r="B110" s="95"/>
       <c r="C110" s="41" t="s">
@@ -5649,11 +5648,11 @@
       <c r="J110" s="50"/>
       <c r="K110" s="50"/>
       <c r="L110" s="50"/>
-      <c r="P110" s="99" t="s">
+      <c r="O110" s="99" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A111" s="50"/>
       <c r="B111" s="95"/>
       <c r="C111" s="66"/>
@@ -5666,14 +5665,14 @@
       <c r="J111" s="50"/>
       <c r="K111" s="50"/>
       <c r="L111" s="50"/>
-      <c r="P111" s="99" t="s">
+      <c r="O111" s="99" t="s">
         <v>100</v>
       </c>
+      <c r="P111" s="94"/>
       <c r="Q111" s="94"/>
       <c r="R111" s="94"/>
-      <c r="S111" s="94"/>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A112" s="50"/>
       <c r="B112" s="95"/>
       <c r="C112" s="41" t="s">
@@ -5690,13 +5689,13 @@
       <c r="J112" s="50"/>
       <c r="K112" s="50"/>
       <c r="L112" s="50"/>
-      <c r="P112" s="99" t="s">
+      <c r="O112" s="99" t="s">
         <v>101</v>
       </c>
+      <c r="Q112" s="100"/>
       <c r="R112" s="100"/>
-      <c r="S112" s="100"/>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A113" s="50"/>
       <c r="B113" s="95"/>
       <c r="C113" s="40"/>
@@ -5709,12 +5708,12 @@
       <c r="J113" s="50"/>
       <c r="K113" s="50"/>
       <c r="L113" s="50"/>
-      <c r="P113" s="83"/>
+      <c r="O113" s="83"/>
+      <c r="P113" s="94"/>
       <c r="Q113" s="94"/>
       <c r="R113" s="94"/>
-      <c r="S113" s="94"/>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A114" s="17"/>
       <c r="B114" s="91"/>
       <c r="C114" s="86" t="s">
@@ -5731,79 +5730,79 @@
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="50"/>
-      <c r="P114" s="99" t="s">
+      <c r="O114" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="Q114" s="8" t="s">
+      <c r="P114" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="P115" s="83"/>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="P116" s="99" t="s">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="O115" s="83"/>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="O116" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="Q116" s="8" t="s">
+      <c r="P116" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="60" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A124" s="230" t="s">
+    <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="124" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A124" s="184" t="s">
         <v>65</v>
       </c>
-      <c r="B124" s="231"/>
-      <c r="C124" s="231"/>
-      <c r="D124" s="231"/>
-      <c r="E124" s="231"/>
-      <c r="F124" s="231"/>
-      <c r="G124" s="231"/>
-      <c r="H124" s="231"/>
-      <c r="I124" s="231"/>
-      <c r="J124" s="231"/>
-      <c r="K124" s="231"/>
-      <c r="L124" s="232"/>
-    </row>
-    <row r="125" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="233" t="s">
+      <c r="B124" s="185"/>
+      <c r="C124" s="185"/>
+      <c r="D124" s="185"/>
+      <c r="E124" s="185"/>
+      <c r="F124" s="185"/>
+      <c r="G124" s="185"/>
+      <c r="H124" s="185"/>
+      <c r="I124" s="185"/>
+      <c r="J124" s="185"/>
+      <c r="K124" s="185"/>
+      <c r="L124" s="186"/>
+    </row>
+    <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="187" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="234"/>
-      <c r="C125" s="234"/>
-      <c r="D125" s="234"/>
-      <c r="E125" s="234"/>
-      <c r="F125" s="234"/>
-      <c r="G125" s="234"/>
-      <c r="H125" s="234"/>
-      <c r="I125" s="234"/>
-      <c r="J125" s="234"/>
-      <c r="K125" s="234"/>
-      <c r="L125" s="235"/>
-    </row>
-    <row r="126" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="188"/>
+      <c r="C125" s="188"/>
+      <c r="D125" s="188"/>
+      <c r="E125" s="188"/>
+      <c r="F125" s="188"/>
+      <c r="G125" s="188"/>
+      <c r="H125" s="188"/>
+      <c r="I125" s="188"/>
+      <c r="J125" s="188"/>
+      <c r="K125" s="188"/>
+      <c r="L125" s="189"/>
+    </row>
+    <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="105" t="s">
         <v>67</v>
       </c>
       <c r="B126" s="106"/>
       <c r="C126" s="106"/>
-      <c r="D126" s="236">
+      <c r="D126" s="190">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="237"/>
-      <c r="F126" s="237"/>
-      <c r="G126" s="237"/>
-      <c r="H126" s="237"/>
-      <c r="I126" s="238"/>
-      <c r="J126" s="239" t="s">
+      <c r="E126" s="191"/>
+      <c r="F126" s="191"/>
+      <c r="G126" s="191"/>
+      <c r="H126" s="191"/>
+      <c r="I126" s="192"/>
+      <c r="J126" s="193" t="s">
         <v>68</v>
       </c>
-      <c r="K126" s="240"/>
-      <c r="L126" s="241"/>
-    </row>
-    <row r="127" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K126" s="194"/>
+      <c r="L126" s="195"/>
+    </row>
+    <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="107" t="s">
         <v>69</v>
       </c>
@@ -5819,7 +5818,7 @@
       <c r="K127" s="112"/>
       <c r="L127" s="113"/>
     </row>
-    <row r="128" spans="1:19" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="114"/>
       <c r="B128" s="115"/>
       <c r="C128" s="115"/>
@@ -5837,23 +5836,23 @@
       <c r="A129" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B129" s="219" t="s">
+      <c r="B129" s="171" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="220"/>
-      <c r="D129" s="221" t="s">
+      <c r="C129" s="172"/>
+      <c r="D129" s="173" t="s">
         <v>72</v>
       </c>
-      <c r="E129" s="222"/>
-      <c r="F129" s="222"/>
-      <c r="G129" s="222"/>
-      <c r="H129" s="222"/>
-      <c r="I129" s="222"/>
-      <c r="J129" s="223"/>
-      <c r="K129" s="221" t="s">
+      <c r="E129" s="174"/>
+      <c r="F129" s="174"/>
+      <c r="G129" s="174"/>
+      <c r="H129" s="174"/>
+      <c r="I129" s="174"/>
+      <c r="J129" s="175"/>
+      <c r="K129" s="173" t="s">
         <v>73</v>
       </c>
-      <c r="L129" s="222"/>
+      <c r="L129" s="174"/>
     </row>
     <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="121"/>
@@ -5863,15 +5862,15 @@
       <c r="C130" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="D130" s="224"/>
-      <c r="E130" s="225"/>
-      <c r="F130" s="225"/>
-      <c r="G130" s="225"/>
-      <c r="H130" s="225"/>
-      <c r="I130" s="225"/>
-      <c r="J130" s="226"/>
-      <c r="K130" s="227"/>
-      <c r="L130" s="228"/>
+      <c r="D130" s="176"/>
+      <c r="E130" s="177"/>
+      <c r="F130" s="177"/>
+      <c r="G130" s="177"/>
+      <c r="H130" s="177"/>
+      <c r="I130" s="177"/>
+      <c r="J130" s="178"/>
+      <c r="K130" s="179"/>
+      <c r="L130" s="180"/>
     </row>
     <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="124">
@@ -5879,17 +5878,17 @@
       </c>
       <c r="B131" s="124"/>
       <c r="C131" s="125"/>
-      <c r="D131" s="216" t="s">
+      <c r="D131" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="217"/>
-      <c r="F131" s="217"/>
-      <c r="G131" s="217"/>
-      <c r="H131" s="217"/>
-      <c r="I131" s="217"/>
-      <c r="J131" s="218"/>
-      <c r="K131" s="215"/>
-      <c r="L131" s="215"/>
+      <c r="E131" s="167"/>
+      <c r="F131" s="167"/>
+      <c r="G131" s="167"/>
+      <c r="H131" s="167"/>
+      <c r="I131" s="167"/>
+      <c r="J131" s="168"/>
+      <c r="K131" s="162"/>
+      <c r="L131" s="162"/>
     </row>
     <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="124">
@@ -5897,17 +5896,17 @@
       </c>
       <c r="B132" s="124"/>
       <c r="C132" s="126"/>
-      <c r="D132" s="216" t="s">
+      <c r="D132" s="166" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="217"/>
-      <c r="F132" s="217"/>
-      <c r="G132" s="217"/>
-      <c r="H132" s="217"/>
-      <c r="I132" s="217"/>
-      <c r="J132" s="218"/>
-      <c r="K132" s="215"/>
-      <c r="L132" s="215"/>
+      <c r="E132" s="167"/>
+      <c r="F132" s="167"/>
+      <c r="G132" s="167"/>
+      <c r="H132" s="167"/>
+      <c r="I132" s="167"/>
+      <c r="J132" s="168"/>
+      <c r="K132" s="162"/>
+      <c r="L132" s="162"/>
     </row>
     <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="124">
@@ -5915,17 +5914,17 @@
       </c>
       <c r="B133" s="124"/>
       <c r="C133" s="126"/>
-      <c r="D133" s="216" t="s">
+      <c r="D133" s="166" t="s">
         <v>78</v>
       </c>
-      <c r="E133" s="217"/>
-      <c r="F133" s="217"/>
-      <c r="G133" s="217"/>
-      <c r="H133" s="217"/>
-      <c r="I133" s="217"/>
-      <c r="J133" s="218"/>
-      <c r="K133" s="215"/>
-      <c r="L133" s="215"/>
+      <c r="E133" s="167"/>
+      <c r="F133" s="167"/>
+      <c r="G133" s="167"/>
+      <c r="H133" s="167"/>
+      <c r="I133" s="167"/>
+      <c r="J133" s="168"/>
+      <c r="K133" s="162"/>
+      <c r="L133" s="162"/>
     </row>
     <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="124">
@@ -5933,17 +5932,17 @@
       </c>
       <c r="B134" s="124"/>
       <c r="C134" s="126"/>
-      <c r="D134" s="216" t="s">
+      <c r="D134" s="166" t="s">
         <v>79</v>
       </c>
-      <c r="E134" s="217"/>
-      <c r="F134" s="217"/>
-      <c r="G134" s="217"/>
-      <c r="H134" s="217"/>
-      <c r="I134" s="217"/>
-      <c r="J134" s="218"/>
-      <c r="K134" s="215"/>
-      <c r="L134" s="215"/>
+      <c r="E134" s="167"/>
+      <c r="F134" s="167"/>
+      <c r="G134" s="167"/>
+      <c r="H134" s="167"/>
+      <c r="I134" s="167"/>
+      <c r="J134" s="168"/>
+      <c r="K134" s="162"/>
+      <c r="L134" s="162"/>
     </row>
     <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="124">
@@ -5951,17 +5950,17 @@
       </c>
       <c r="B135" s="124"/>
       <c r="C135" s="126"/>
-      <c r="D135" s="216" t="s">
+      <c r="D135" s="166" t="s">
         <v>80</v>
       </c>
-      <c r="E135" s="217"/>
-      <c r="F135" s="217"/>
-      <c r="G135" s="217"/>
-      <c r="H135" s="217"/>
-      <c r="I135" s="217"/>
-      <c r="J135" s="218"/>
-      <c r="K135" s="215"/>
-      <c r="L135" s="215"/>
+      <c r="E135" s="167"/>
+      <c r="F135" s="167"/>
+      <c r="G135" s="167"/>
+      <c r="H135" s="167"/>
+      <c r="I135" s="167"/>
+      <c r="J135" s="168"/>
+      <c r="K135" s="162"/>
+      <c r="L135" s="162"/>
     </row>
     <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="124">
@@ -5969,17 +5968,17 @@
       </c>
       <c r="B136" s="124"/>
       <c r="C136" s="126"/>
-      <c r="D136" s="216" t="s">
+      <c r="D136" s="166" t="s">
         <v>81</v>
       </c>
-      <c r="E136" s="217"/>
-      <c r="F136" s="217"/>
-      <c r="G136" s="217"/>
-      <c r="H136" s="217"/>
-      <c r="I136" s="217"/>
-      <c r="J136" s="218"/>
-      <c r="K136" s="215"/>
-      <c r="L136" s="215"/>
+      <c r="E136" s="167"/>
+      <c r="F136" s="167"/>
+      <c r="G136" s="167"/>
+      <c r="H136" s="167"/>
+      <c r="I136" s="167"/>
+      <c r="J136" s="168"/>
+      <c r="K136" s="162"/>
+      <c r="L136" s="162"/>
     </row>
     <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="124">
@@ -5987,17 +5986,17 @@
       </c>
       <c r="B137" s="124"/>
       <c r="C137" s="126"/>
-      <c r="D137" s="216" t="s">
+      <c r="D137" s="166" t="s">
         <v>82</v>
       </c>
-      <c r="E137" s="217"/>
-      <c r="F137" s="217"/>
-      <c r="G137" s="217"/>
-      <c r="H137" s="217"/>
-      <c r="I137" s="217"/>
-      <c r="J137" s="218"/>
-      <c r="K137" s="215"/>
-      <c r="L137" s="215"/>
+      <c r="E137" s="167"/>
+      <c r="F137" s="167"/>
+      <c r="G137" s="167"/>
+      <c r="H137" s="167"/>
+      <c r="I137" s="167"/>
+      <c r="J137" s="168"/>
+      <c r="K137" s="162"/>
+      <c r="L137" s="162"/>
     </row>
     <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="124">
@@ -6005,17 +6004,17 @@
       </c>
       <c r="B138" s="124"/>
       <c r="C138" s="126"/>
-      <c r="D138" s="242" t="s">
+      <c r="D138" s="159" t="s">
         <v>111</v>
       </c>
-      <c r="E138" s="243"/>
-      <c r="F138" s="243"/>
-      <c r="G138" s="243"/>
-      <c r="H138" s="243"/>
-      <c r="I138" s="243"/>
-      <c r="J138" s="244"/>
-      <c r="K138" s="248"/>
-      <c r="L138" s="249"/>
+      <c r="E138" s="160"/>
+      <c r="F138" s="160"/>
+      <c r="G138" s="160"/>
+      <c r="H138" s="160"/>
+      <c r="I138" s="160"/>
+      <c r="J138" s="161"/>
+      <c r="K138" s="169"/>
+      <c r="L138" s="170"/>
     </row>
     <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="124">
@@ -6023,17 +6022,17 @@
       </c>
       <c r="B139" s="124"/>
       <c r="C139" s="126"/>
-      <c r="D139" s="242" t="s">
+      <c r="D139" s="159" t="s">
         <v>83</v>
       </c>
-      <c r="E139" s="243"/>
-      <c r="F139" s="243"/>
-      <c r="G139" s="243"/>
-      <c r="H139" s="243"/>
-      <c r="I139" s="243"/>
-      <c r="J139" s="244"/>
-      <c r="K139" s="215"/>
-      <c r="L139" s="215"/>
+      <c r="E139" s="160"/>
+      <c r="F139" s="160"/>
+      <c r="G139" s="160"/>
+      <c r="H139" s="160"/>
+      <c r="I139" s="160"/>
+      <c r="J139" s="161"/>
+      <c r="K139" s="162"/>
+      <c r="L139" s="162"/>
     </row>
     <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="124">
@@ -6041,17 +6040,17 @@
       </c>
       <c r="B140" s="124"/>
       <c r="C140" s="126"/>
-      <c r="D140" s="242" t="s">
+      <c r="D140" s="159" t="s">
         <v>84</v>
       </c>
-      <c r="E140" s="243"/>
-      <c r="F140" s="243"/>
-      <c r="G140" s="243"/>
-      <c r="H140" s="243"/>
-      <c r="I140" s="243"/>
-      <c r="J140" s="244"/>
-      <c r="K140" s="215"/>
-      <c r="L140" s="215"/>
+      <c r="E140" s="160"/>
+      <c r="F140" s="160"/>
+      <c r="G140" s="160"/>
+      <c r="H140" s="160"/>
+      <c r="I140" s="160"/>
+      <c r="J140" s="161"/>
+      <c r="K140" s="162"/>
+      <c r="L140" s="162"/>
     </row>
     <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="124">
@@ -6059,17 +6058,17 @@
       </c>
       <c r="B141" s="124"/>
       <c r="C141" s="126"/>
-      <c r="D141" s="245" t="s">
+      <c r="D141" s="163" t="s">
         <v>85</v>
       </c>
-      <c r="E141" s="246"/>
-      <c r="F141" s="246"/>
-      <c r="G141" s="246"/>
-      <c r="H141" s="246"/>
-      <c r="I141" s="246"/>
-      <c r="J141" s="247"/>
-      <c r="K141" s="215"/>
-      <c r="L141" s="215"/>
+      <c r="E141" s="164"/>
+      <c r="F141" s="164"/>
+      <c r="G141" s="164"/>
+      <c r="H141" s="164"/>
+      <c r="I141" s="164"/>
+      <c r="J141" s="165"/>
+      <c r="K141" s="162"/>
+      <c r="L141" s="162"/>
     </row>
     <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -6081,54 +6080,102 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="168">
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="O51:P51"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="O45:P45"/>
-    <mergeCell ref="O46:P46"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:K16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="P18:P53"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="L20:L53"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="M72:R72"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="Q18:Q53"/>
+    <mergeCell ref="B52:C53"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C63:K64"/>
+    <mergeCell ref="M71:R71"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M87:R87"/>
+    <mergeCell ref="M73:R73"/>
+    <mergeCell ref="F75:K75"/>
+    <mergeCell ref="M75:R75"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="O78:R78"/>
+    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="M83:R83"/>
+    <mergeCell ref="M84:R84"/>
+    <mergeCell ref="M85:R85"/>
+    <mergeCell ref="M86:R86"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:J130"/>
+    <mergeCell ref="K129:L130"/>
+    <mergeCell ref="F88:J88"/>
+    <mergeCell ref="M88:R88"/>
+    <mergeCell ref="M95:R95"/>
+    <mergeCell ref="M96:R96"/>
+    <mergeCell ref="M97:R97"/>
+    <mergeCell ref="M98:R98"/>
+    <mergeCell ref="M99:R99"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="D126:I126"/>
+    <mergeCell ref="J126:L126"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D37:E37"/>
@@ -6153,102 +6200,54 @@
     <mergeCell ref="D131:J131"/>
     <mergeCell ref="K131:L131"/>
     <mergeCell ref="D132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:J130"/>
-    <mergeCell ref="K129:L130"/>
-    <mergeCell ref="F88:J88"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N95:S95"/>
-    <mergeCell ref="N96:S96"/>
-    <mergeCell ref="N97:S97"/>
-    <mergeCell ref="N98:S98"/>
-    <mergeCell ref="N99:S99"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="F75:K75"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="Q79:R79"/>
-    <mergeCell ref="P78:S78"/>
-    <mergeCell ref="P81:S81"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="R18:R53"/>
-    <mergeCell ref="B52:C53"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="C63:K64"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="Q18:Q53"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="L20:L53"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="N15:N17"/>
-    <mergeCell ref="O15:P16"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:K16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="N49:O49"/>
   </mergeCells>
   <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FA7371-79C4-4341-A7D5-8808BC7EF150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A87795-5ADA-44A3-9E43-EDC74F72EE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="1020" windowWidth="22500" windowHeight="11790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim" sheetId="92" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
   <si>
     <t>JABATAN KASTAM DIRAJA MALAYSIA</t>
   </si>
@@ -338,12 +338,6 @@
   </si>
   <si>
     <t xml:space="preserve">NO. KP   </t>
-  </si>
-  <si>
-    <t>MENYEMAK IMEJ/ MENAHAN KONTENA</t>
-  </si>
-  <si>
-    <t>Menyemak sistem SMK dan GCS, Menganalisa imej dagangan kontena dan menahan kontena</t>
   </si>
   <si>
     <t>SIJIL TUNTUTAN LEBIHMASA MENGIKUT SURAT</t>
@@ -2022,17 +2016,213 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2042,11 +2232,176 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2062,10 +2417,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2078,369 +2429,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2701,9 +2695,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2741,9 +2735,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2776,26 +2770,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2828,26 +2805,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3023,70 +2983,70 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB524E58-DEC5-4CFF-AD7C-0D1451F04347}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:R148"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="8"/>
-    <col min="5" max="5" width="8.54296875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="8"/>
+    <col min="5" max="5" width="8.5703125" style="8" customWidth="1"/>
     <col min="6" max="6" width="12" style="8" customWidth="1"/>
-    <col min="7" max="8" width="9.26953125" style="8" customWidth="1"/>
+    <col min="7" max="8" width="9.28515625" style="8" customWidth="1"/>
     <col min="9" max="9" width="10" style="8" customWidth="1"/>
-    <col min="10" max="11" width="9.26953125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="15.26953125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="13.1796875" style="8" customWidth="1"/>
-    <col min="14" max="15" width="7.453125" style="8" customWidth="1"/>
-    <col min="16" max="16" width="28.26953125" style="8" customWidth="1"/>
-    <col min="17" max="17" width="30.54296875" style="8" customWidth="1"/>
-    <col min="18" max="18" width="31.81640625" style="8" customWidth="1"/>
-    <col min="19" max="16384" width="9.1796875" style="8"/>
+    <col min="10" max="11" width="9.28515625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="8" customWidth="1"/>
+    <col min="14" max="15" width="7.42578125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="28.28515625" style="8" customWidth="1"/>
+    <col min="17" max="17" width="30.5703125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="31.85546875" style="8" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="242" t="s">
+    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1" s="9"/>
     </row>
-    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="242" t="s">
+    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="242"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="M2" s="231"/>
-      <c r="N2" s="231"/>
-      <c r="O2" s="231"/>
-      <c r="P2" s="231"/>
-      <c r="Q2" s="231"/>
-      <c r="R2" s="231"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="164"/>
+      <c r="L2" s="164"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="151"/>
+      <c r="R2" s="151"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -3104,39 +3064,39 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="254" t="s">
+    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="254"/>
-      <c r="C4" s="254"/>
-      <c r="D4" s="254"/>
-      <c r="E4" s="254"/>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="254"/>
-      <c r="I4" s="254"/>
-      <c r="J4" s="254"/>
-      <c r="K4" s="254"/>
-      <c r="L4" s="254"/>
+      <c r="B4" s="177"/>
+      <c r="C4" s="177"/>
+      <c r="D4" s="177"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="177"/>
+      <c r="G4" s="177"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="177"/>
+      <c r="K4" s="177"/>
+      <c r="L4" s="177"/>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:18" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="255"/>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="255"/>
-      <c r="J5" s="255"/>
-      <c r="K5" s="255"/>
-      <c r="L5" s="255"/>
+    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="178"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="178"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="178"/>
+      <c r="L5" s="178"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3144,27 +3104,27 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="256" t="s">
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="179" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="256"/>
-      <c r="C6" s="256"/>
-      <c r="D6" s="256"/>
-      <c r="E6" s="256"/>
-      <c r="F6" s="256"/>
-      <c r="G6" s="256"/>
-      <c r="H6" s="256"/>
-      <c r="I6" s="256"/>
-      <c r="J6" s="256"/>
-      <c r="K6" s="256"/>
-      <c r="L6" s="256"/>
+      <c r="B6" s="179"/>
+      <c r="C6" s="179"/>
+      <c r="D6" s="179"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="179"/>
+      <c r="H6" s="179"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="179"/>
+      <c r="L6" s="179"/>
       <c r="O6" s="16"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -3184,7 +3144,7 @@
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
     </row>
-    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
@@ -3206,16 +3166,16 @@
       </c>
       <c r="L8" s="136"/>
     </row>
-    <row r="9" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="257"/>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
+      <c r="C9" s="180"/>
+      <c r="D9" s="180"/>
+      <c r="E9" s="180"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="19" t="s">
@@ -3228,7 +3188,7 @@
       </c>
       <c r="L9" s="137"/>
       <c r="M9" s="144" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="24"/>
@@ -3237,7 +3197,7 @@
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>8</v>
       </c>
@@ -3261,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="M10" s="144" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="24"/>
@@ -3270,7 +3230,7 @@
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>11</v>
       </c>
@@ -3292,7 +3252,7 @@
       </c>
       <c r="L11" s="138"/>
       <c r="M11" s="144" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="24"/>
@@ -3301,7 +3261,7 @@
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
@@ -3323,7 +3283,7 @@
       </c>
       <c r="L12" s="138"/>
       <c r="M12" s="145" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="24"/>
@@ -3332,7 +3292,7 @@
         <v xml:space="preserve">:   </v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="19"/>
       <c r="B13" s="21"/>
       <c r="C13" s="26"/>
@@ -3346,7 +3306,7 @@
       <c r="K13" s="20"/>
       <c r="L13" s="26"/>
     </row>
-    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -3360,71 +3320,71 @@
       <c r="K14" s="12"/>
       <c r="L14" s="26"/>
     </row>
-    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="165" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="D15" s="245" t="s">
+      <c r="C15" s="165"/>
+      <c r="D15" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="246"/>
-      <c r="F15" s="246" t="s">
+      <c r="E15" s="168"/>
+      <c r="F15" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="251" t="s">
+      <c r="G15" s="173" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="251"/>
-      <c r="I15" s="251"/>
-      <c r="J15" s="251"/>
-      <c r="K15" s="252"/>
-      <c r="L15" s="232" t="s">
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="173"/>
+      <c r="K15" s="174"/>
+      <c r="L15" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="235" t="s">
+      <c r="M15" s="157" t="s">
         <v>59</v>
       </c>
-      <c r="N15" s="238" t="s">
+      <c r="N15" s="160" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="239"/>
-      <c r="P15" s="235" t="s">
+      <c r="O15" s="161"/>
+      <c r="P15" s="157" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" s="258" t="s">
+      <c r="Q15" s="181" t="s">
         <v>62</v>
       </c>
-      <c r="R15" s="235" t="s">
+      <c r="R15" s="157" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="244"/>
-      <c r="C16" s="244"/>
-      <c r="D16" s="247"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="249"/>
-      <c r="G16" s="224"/>
-      <c r="H16" s="224"/>
-      <c r="I16" s="224"/>
-      <c r="J16" s="224"/>
-      <c r="K16" s="253"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="240"/>
-      <c r="O16" s="241"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="259"/>
-      <c r="R16" s="236"/>
-    </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="166"/>
+      <c r="C16" s="166"/>
+      <c r="D16" s="169"/>
+      <c r="E16" s="170"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="175"/>
+      <c r="I16" s="175"/>
+      <c r="J16" s="175"/>
+      <c r="K16" s="176"/>
+      <c r="L16" s="155"/>
+      <c r="M16" s="158"/>
+      <c r="N16" s="162"/>
+      <c r="O16" s="163"/>
+      <c r="P16" s="158"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="158"/>
+    </row>
+    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>22</v>
       </c>
@@ -3440,7 +3400,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="250"/>
+      <c r="F17" s="172"/>
       <c r="G17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3456,1011 +3416,1007 @@
       <c r="K17" s="37">
         <v>2</v>
       </c>
-      <c r="L17" s="234"/>
-      <c r="M17" s="237"/>
+      <c r="L17" s="156"/>
+      <c r="M17" s="159"/>
       <c r="N17" s="38" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="237"/>
-      <c r="Q17" s="260"/>
-      <c r="R17" s="237"/>
-    </row>
-    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="223" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="224"/>
-      <c r="C18" s="224"/>
-      <c r="D18" s="224"/>
-      <c r="E18" s="225"/>
-      <c r="F18" s="229"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212">
+      <c r="P17" s="159"/>
+      <c r="Q17" s="183"/>
+      <c r="R17" s="159"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="195" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="175"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="196"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="152"/>
+      <c r="H18" s="152">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="214"/>
-      <c r="L18" s="216" t="s">
-        <v>110</v>
+      <c r="I18" s="152"/>
+      <c r="J18" s="152"/>
+      <c r="K18" s="186"/>
+      <c r="L18" s="188" t="s">
+        <v>108</v>
       </c>
       <c r="M18" s="147" t="str">
         <f>IF(ISBLANK(A20),"",A20)</f>
         <v/>
       </c>
-      <c r="N18" s="153" t="str">
+      <c r="N18" s="208" t="str">
         <f>IF(ISBLANK(D20),"",D20)</f>
         <v/>
       </c>
-      <c r="O18" s="154"/>
-      <c r="P18" s="218" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" s="207"/>
+      <c r="O18" s="209"/>
+      <c r="P18" s="190"/>
+      <c r="Q18" s="211"/>
       <c r="R18" s="149"/>
     </row>
-    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="226"/>
-      <c r="B19" s="227"/>
-      <c r="C19" s="227"/>
-      <c r="D19" s="227"/>
-      <c r="E19" s="228"/>
-      <c r="F19" s="230"/>
-      <c r="G19" s="213"/>
-      <c r="H19" s="213"/>
-      <c r="I19" s="213"/>
-      <c r="J19" s="213"/>
-      <c r="K19" s="215"/>
-      <c r="L19" s="217"/>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="197"/>
+      <c r="B19" s="198"/>
+      <c r="C19" s="198"/>
+      <c r="D19" s="198"/>
+      <c r="E19" s="199"/>
+      <c r="F19" s="201"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="153"/>
+      <c r="K19" s="187"/>
+      <c r="L19" s="189"/>
       <c r="M19" s="148" t="str">
         <f>A21</f>
         <v/>
       </c>
-      <c r="N19" s="151" t="str">
+      <c r="N19" s="206" t="str">
         <f>IF(ISBLANK(D21),"",D21)</f>
         <v/>
       </c>
-      <c r="O19" s="152"/>
-      <c r="P19" s="219"/>
-      <c r="Q19" s="208"/>
+      <c r="O19" s="207"/>
+      <c r="P19" s="191"/>
+      <c r="Q19" s="212"/>
       <c r="R19" s="150"/>
     </row>
-    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="142"/>
-      <c r="B20" s="206"/>
-      <c r="C20" s="206"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="156"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="204"/>
+      <c r="E20" s="205"/>
       <c r="F20" s="139"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
       <c r="I20" s="129"/>
       <c r="J20" s="129"/>
       <c r="K20" s="129"/>
-      <c r="L20" s="221" t="s">
-        <v>87</v>
-      </c>
+      <c r="L20" s="193"/>
       <c r="M20" s="147" t="str">
         <f>IF(ISBLANK(A22),"",A22)</f>
         <v/>
       </c>
-      <c r="N20" s="153" t="str">
+      <c r="N20" s="208" t="str">
         <f t="shared" ref="N20:N53" si="0">IF(ISBLANK(D22),"",D22)</f>
         <v/>
       </c>
-      <c r="O20" s="154"/>
-      <c r="P20" s="219"/>
-      <c r="Q20" s="208"/>
+      <c r="O20" s="209"/>
+      <c r="P20" s="191"/>
+      <c r="Q20" s="212"/>
       <c r="R20" s="149"/>
     </row>
-    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f t="shared" ref="A21" si="1">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B21" s="206"/>
-      <c r="C21" s="206"/>
-      <c r="D21" s="157"/>
-      <c r="E21" s="158"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203"/>
       <c r="F21" s="141"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
       <c r="I21" s="127"/>
       <c r="J21" s="127"/>
       <c r="K21" s="128"/>
-      <c r="L21" s="221"/>
+      <c r="L21" s="193"/>
       <c r="M21" s="148" t="str">
         <f>A23</f>
         <v/>
       </c>
-      <c r="N21" s="151" t="str">
+      <c r="N21" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O21" s="152"/>
-      <c r="P21" s="219"/>
-      <c r="Q21" s="208"/>
+      <c r="O21" s="207"/>
+      <c r="P21" s="191"/>
+      <c r="Q21" s="212"/>
       <c r="R21" s="150"/>
     </row>
-    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="134"/>
-      <c r="B22" s="205"/>
-      <c r="C22" s="205"/>
-      <c r="D22" s="155"/>
-      <c r="E22" s="156"/>
+      <c r="B22" s="184"/>
+      <c r="C22" s="184"/>
+      <c r="D22" s="204"/>
+      <c r="E22" s="205"/>
       <c r="F22" s="139"/>
       <c r="G22" s="129"/>
       <c r="H22" s="129"/>
       <c r="I22" s="129"/>
       <c r="J22" s="129"/>
       <c r="K22" s="129"/>
-      <c r="L22" s="221"/>
+      <c r="L22" s="193"/>
       <c r="M22" s="147" t="str">
         <f t="shared" ref="M22" si="2">IF(ISBLANK(A24),"",A24)</f>
         <v/>
       </c>
-      <c r="N22" s="153" t="str">
+      <c r="N22" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O22" s="154"/>
-      <c r="P22" s="219"/>
-      <c r="Q22" s="208"/>
+      <c r="O22" s="209"/>
+      <c r="P22" s="191"/>
+      <c r="Q22" s="212"/>
       <c r="R22" s="149"/>
     </row>
-    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f t="shared" ref="A23:A25" si="3">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="206"/>
-      <c r="C23" s="206"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="158"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="185"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="203"/>
       <c r="F23" s="141"/>
       <c r="G23" s="127"/>
       <c r="H23" s="127"/>
       <c r="I23" s="127"/>
       <c r="J23" s="127"/>
       <c r="K23" s="128"/>
-      <c r="L23" s="221"/>
+      <c r="L23" s="193"/>
       <c r="M23" s="148" t="str">
         <f t="shared" ref="M23" si="4">A25</f>
         <v/>
       </c>
-      <c r="N23" s="151" t="str">
+      <c r="N23" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O23" s="152"/>
-      <c r="P23" s="219"/>
-      <c r="Q23" s="208"/>
+      <c r="O23" s="207"/>
+      <c r="P23" s="191"/>
+      <c r="Q23" s="212"/>
       <c r="R23" s="150"/>
     </row>
-    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="134"/>
-      <c r="B24" s="205"/>
-      <c r="C24" s="205"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="156"/>
+      <c r="B24" s="184"/>
+      <c r="C24" s="184"/>
+      <c r="D24" s="204"/>
+      <c r="E24" s="205"/>
       <c r="F24" s="139"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
       <c r="I24" s="129"/>
       <c r="J24" s="129"/>
       <c r="K24" s="129"/>
-      <c r="L24" s="221"/>
+      <c r="L24" s="193"/>
       <c r="M24" s="147" t="str">
         <f t="shared" ref="M24" si="5">IF(ISBLANK(A26),"",A26)</f>
         <v/>
       </c>
-      <c r="N24" s="153" t="str">
+      <c r="N24" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O24" s="154"/>
-      <c r="P24" s="219"/>
-      <c r="Q24" s="208"/>
+      <c r="O24" s="209"/>
+      <c r="P24" s="191"/>
+      <c r="Q24" s="212"/>
       <c r="R24" s="149"/>
     </row>
-    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B25" s="206"/>
-      <c r="C25" s="206"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="158"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="185"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="203"/>
       <c r="F25" s="141"/>
       <c r="G25" s="127"/>
       <c r="H25" s="127"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
       <c r="K25" s="128"/>
-      <c r="L25" s="221"/>
+      <c r="L25" s="193"/>
       <c r="M25" s="148" t="str">
         <f t="shared" ref="M25" si="6">A27</f>
         <v/>
       </c>
-      <c r="N25" s="151" t="str">
+      <c r="N25" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O25" s="152"/>
-      <c r="P25" s="219"/>
-      <c r="Q25" s="208"/>
+      <c r="O25" s="207"/>
+      <c r="P25" s="191"/>
+      <c r="Q25" s="212"/>
       <c r="R25" s="150"/>
     </row>
-    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="134"/>
-      <c r="B26" s="205"/>
-      <c r="C26" s="205"/>
-      <c r="D26" s="155"/>
-      <c r="E26" s="156"/>
+      <c r="B26" s="184"/>
+      <c r="C26" s="184"/>
+      <c r="D26" s="204"/>
+      <c r="E26" s="205"/>
       <c r="F26" s="139"/>
       <c r="G26" s="129"/>
       <c r="H26" s="129"/>
       <c r="I26" s="129"/>
       <c r="J26" s="129"/>
       <c r="K26" s="129"/>
-      <c r="L26" s="221"/>
+      <c r="L26" s="193"/>
       <c r="M26" s="147" t="str">
         <f t="shared" ref="M26" si="7">IF(ISBLANK(A28),"",A28)</f>
         <v/>
       </c>
-      <c r="N26" s="153" t="str">
+      <c r="N26" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O26" s="154"/>
-      <c r="P26" s="219"/>
-      <c r="Q26" s="208"/>
+      <c r="O26" s="209"/>
+      <c r="P26" s="191"/>
+      <c r="Q26" s="212"/>
       <c r="R26" s="149"/>
     </row>
-    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f t="shared" ref="A27" si="8">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="157"/>
-      <c r="E27" s="158"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="203"/>
       <c r="F27" s="141"/>
       <c r="G27" s="127"/>
       <c r="H27" s="127"/>
       <c r="I27" s="127"/>
       <c r="J27" s="127"/>
       <c r="K27" s="128"/>
-      <c r="L27" s="221"/>
+      <c r="L27" s="193"/>
       <c r="M27" s="148" t="str">
         <f t="shared" ref="M27" si="9">A29</f>
         <v/>
       </c>
-      <c r="N27" s="151" t="str">
+      <c r="N27" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O27" s="152"/>
-      <c r="P27" s="219"/>
-      <c r="Q27" s="208"/>
+      <c r="O27" s="207"/>
+      <c r="P27" s="191"/>
+      <c r="Q27" s="212"/>
       <c r="R27" s="150"/>
     </row>
-    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="135"/>
-      <c r="B28" s="205"/>
-      <c r="C28" s="205"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="156"/>
+      <c r="B28" s="184"/>
+      <c r="C28" s="184"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="205"/>
       <c r="F28" s="139"/>
       <c r="G28" s="129"/>
       <c r="H28" s="129"/>
       <c r="I28" s="129"/>
       <c r="J28" s="129"/>
       <c r="K28" s="129"/>
-      <c r="L28" s="221"/>
+      <c r="L28" s="193"/>
       <c r="M28" s="147" t="str">
         <f t="shared" ref="M28" si="10">IF(ISBLANK(A30),"",A30)</f>
         <v/>
       </c>
-      <c r="N28" s="153" t="str">
+      <c r="N28" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O28" s="154"/>
-      <c r="P28" s="219"/>
-      <c r="Q28" s="208"/>
+      <c r="O28" s="209"/>
+      <c r="P28" s="191"/>
+      <c r="Q28" s="212"/>
       <c r="R28" s="149"/>
     </row>
-    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="str">
         <f t="shared" ref="A29" si="11">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="206"/>
-      <c r="C29" s="206"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="158"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="185"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="203"/>
       <c r="F29" s="141"/>
       <c r="G29" s="127"/>
       <c r="H29" s="127"/>
       <c r="I29" s="127"/>
       <c r="J29" s="129"/>
       <c r="K29" s="128"/>
-      <c r="L29" s="221"/>
+      <c r="L29" s="193"/>
       <c r="M29" s="148" t="str">
         <f t="shared" ref="M29" si="12">A31</f>
         <v/>
       </c>
-      <c r="N29" s="151" t="str">
+      <c r="N29" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O29" s="152"/>
-      <c r="P29" s="219"/>
-      <c r="Q29" s="208"/>
+      <c r="O29" s="207"/>
+      <c r="P29" s="191"/>
+      <c r="Q29" s="212"/>
       <c r="R29" s="150"/>
     </row>
-    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="134"/>
-      <c r="B30" s="205"/>
-      <c r="C30" s="205"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="156"/>
+      <c r="B30" s="184"/>
+      <c r="C30" s="184"/>
+      <c r="D30" s="204"/>
+      <c r="E30" s="205"/>
       <c r="F30" s="139"/>
       <c r="G30" s="129"/>
       <c r="H30" s="129"/>
       <c r="I30" s="140"/>
       <c r="J30" s="143"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="221"/>
+      <c r="L30" s="193"/>
       <c r="M30" s="147" t="str">
         <f t="shared" ref="M30" si="13">IF(ISBLANK(A32),"",A32)</f>
         <v/>
       </c>
-      <c r="N30" s="153" t="str">
+      <c r="N30" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O30" s="154"/>
-      <c r="P30" s="219"/>
-      <c r="Q30" s="208"/>
+      <c r="O30" s="209"/>
+      <c r="P30" s="191"/>
+      <c r="Q30" s="212"/>
       <c r="R30" s="149"/>
     </row>
-    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f t="shared" ref="A31" si="14">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="206"/>
-      <c r="C31" s="206"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="158"/>
+      <c r="B31" s="185"/>
+      <c r="C31" s="185"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="203"/>
       <c r="F31" s="141"/>
       <c r="G31" s="127"/>
       <c r="H31" s="127"/>
       <c r="I31" s="127"/>
       <c r="J31" s="127"/>
       <c r="K31" s="128"/>
-      <c r="L31" s="221"/>
+      <c r="L31" s="193"/>
       <c r="M31" s="148" t="str">
         <f t="shared" ref="M31" si="15">A33</f>
         <v/>
       </c>
-      <c r="N31" s="151" t="str">
+      <c r="N31" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O31" s="152"/>
-      <c r="P31" s="219"/>
-      <c r="Q31" s="208"/>
+      <c r="O31" s="207"/>
+      <c r="P31" s="191"/>
+      <c r="Q31" s="212"/>
       <c r="R31" s="150"/>
     </row>
-    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="134"/>
-      <c r="B32" s="205"/>
-      <c r="C32" s="205"/>
-      <c r="D32" s="155"/>
-      <c r="E32" s="156"/>
+      <c r="B32" s="184"/>
+      <c r="C32" s="184"/>
+      <c r="D32" s="204"/>
+      <c r="E32" s="205"/>
       <c r="F32" s="139"/>
       <c r="G32" s="129"/>
       <c r="H32" s="129"/>
       <c r="I32" s="129"/>
       <c r="J32" s="129"/>
       <c r="K32" s="129"/>
-      <c r="L32" s="221"/>
+      <c r="L32" s="193"/>
       <c r="M32" s="147" t="str">
         <f t="shared" ref="M32" si="16">IF(ISBLANK(A34),"",A34)</f>
         <v/>
       </c>
-      <c r="N32" s="153" t="str">
+      <c r="N32" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O32" s="154"/>
-      <c r="P32" s="219"/>
-      <c r="Q32" s="208"/>
+      <c r="O32" s="209"/>
+      <c r="P32" s="191"/>
+      <c r="Q32" s="212"/>
       <c r="R32" s="149"/>
     </row>
-    <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f t="shared" ref="A33" si="17">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="206"/>
-      <c r="C33" s="206"/>
-      <c r="D33" s="157"/>
-      <c r="E33" s="158"/>
+      <c r="B33" s="185"/>
+      <c r="C33" s="185"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="203"/>
       <c r="F33" s="141"/>
       <c r="G33" s="127"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
       <c r="J33" s="127"/>
       <c r="K33" s="128"/>
-      <c r="L33" s="221"/>
+      <c r="L33" s="193"/>
       <c r="M33" s="148" t="str">
         <f t="shared" ref="M33" si="18">A35</f>
         <v/>
       </c>
-      <c r="N33" s="151" t="str">
+      <c r="N33" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O33" s="152"/>
-      <c r="P33" s="219"/>
-      <c r="Q33" s="208"/>
+      <c r="O33" s="207"/>
+      <c r="P33" s="191"/>
+      <c r="Q33" s="212"/>
       <c r="R33" s="150"/>
     </row>
-    <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="134"/>
-      <c r="B34" s="205"/>
-      <c r="C34" s="205"/>
-      <c r="D34" s="155"/>
-      <c r="E34" s="156"/>
+      <c r="B34" s="184"/>
+      <c r="C34" s="184"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="205"/>
       <c r="F34" s="139"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
       <c r="I34" s="129"/>
       <c r="J34" s="129"/>
       <c r="K34" s="129"/>
-      <c r="L34" s="221"/>
+      <c r="L34" s="193"/>
       <c r="M34" s="147" t="str">
         <f t="shared" ref="M34" si="19">IF(ISBLANK(A36),"",A36)</f>
         <v/>
       </c>
-      <c r="N34" s="153" t="str">
+      <c r="N34" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O34" s="154"/>
-      <c r="P34" s="219"/>
-      <c r="Q34" s="208"/>
+      <c r="O34" s="209"/>
+      <c r="P34" s="191"/>
+      <c r="Q34" s="212"/>
       <c r="R34" s="149"/>
     </row>
-    <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f t="shared" ref="A35" si="20">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="206"/>
-      <c r="C35" s="206"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="158"/>
+      <c r="B35" s="185"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="203"/>
       <c r="F35" s="141"/>
       <c r="G35" s="127"/>
       <c r="H35" s="127"/>
       <c r="I35" s="127"/>
       <c r="J35" s="127"/>
       <c r="K35" s="128"/>
-      <c r="L35" s="221"/>
+      <c r="L35" s="193"/>
       <c r="M35" s="148" t="str">
         <f t="shared" ref="M35" si="21">A37</f>
         <v/>
       </c>
-      <c r="N35" s="151" t="str">
+      <c r="N35" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O35" s="152"/>
-      <c r="P35" s="219"/>
-      <c r="Q35" s="208"/>
+      <c r="O35" s="207"/>
+      <c r="P35" s="191"/>
+      <c r="Q35" s="212"/>
       <c r="R35" s="150"/>
     </row>
-    <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134"/>
-      <c r="B36" s="205"/>
-      <c r="C36" s="205"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="156"/>
+      <c r="B36" s="184"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="204"/>
+      <c r="E36" s="205"/>
       <c r="F36" s="139"/>
       <c r="G36" s="129"/>
       <c r="H36" s="129"/>
       <c r="I36" s="129"/>
       <c r="J36" s="129"/>
       <c r="K36" s="129"/>
-      <c r="L36" s="221"/>
+      <c r="L36" s="193"/>
       <c r="M36" s="147" t="str">
         <f t="shared" ref="M36" si="22">IF(ISBLANK(A38),"",A38)</f>
         <v/>
       </c>
-      <c r="N36" s="153" t="str">
+      <c r="N36" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O36" s="154"/>
-      <c r="P36" s="219"/>
-      <c r="Q36" s="208"/>
+      <c r="O36" s="209"/>
+      <c r="P36" s="191"/>
+      <c r="Q36" s="212"/>
       <c r="R36" s="149"/>
     </row>
-    <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f t="shared" ref="A37" si="23">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="206"/>
-      <c r="C37" s="206"/>
-      <c r="D37" s="157"/>
-      <c r="E37" s="158"/>
+      <c r="B37" s="185"/>
+      <c r="C37" s="185"/>
+      <c r="D37" s="202"/>
+      <c r="E37" s="203"/>
       <c r="F37" s="141"/>
       <c r="G37" s="127"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
       <c r="J37" s="127"/>
       <c r="K37" s="128"/>
-      <c r="L37" s="221"/>
+      <c r="L37" s="193"/>
       <c r="M37" s="148" t="str">
         <f t="shared" ref="M37" si="24">A39</f>
         <v/>
       </c>
-      <c r="N37" s="151" t="str">
+      <c r="N37" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O37" s="152"/>
-      <c r="P37" s="219"/>
-      <c r="Q37" s="208"/>
+      <c r="O37" s="207"/>
+      <c r="P37" s="191"/>
+      <c r="Q37" s="212"/>
       <c r="R37" s="150"/>
     </row>
-    <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="134"/>
-      <c r="B38" s="205"/>
-      <c r="C38" s="205"/>
-      <c r="D38" s="155"/>
-      <c r="E38" s="156"/>
+      <c r="B38" s="184"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="204"/>
+      <c r="E38" s="205"/>
       <c r="F38" s="139"/>
       <c r="G38" s="129"/>
       <c r="H38" s="129"/>
       <c r="I38" s="129"/>
       <c r="J38" s="129"/>
       <c r="K38" s="129"/>
-      <c r="L38" s="221"/>
+      <c r="L38" s="193"/>
       <c r="M38" s="147" t="str">
         <f t="shared" ref="M38" si="25">IF(ISBLANK(A40),"",A40)</f>
         <v/>
       </c>
-      <c r="N38" s="153" t="str">
+      <c r="N38" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O38" s="154"/>
-      <c r="P38" s="219"/>
-      <c r="Q38" s="208"/>
+      <c r="O38" s="209"/>
+      <c r="P38" s="191"/>
+      <c r="Q38" s="212"/>
       <c r="R38" s="149"/>
     </row>
-    <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f t="shared" ref="A39" si="26">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="206"/>
-      <c r="C39" s="206"/>
-      <c r="D39" s="157"/>
-      <c r="E39" s="158"/>
+      <c r="B39" s="185"/>
+      <c r="C39" s="185"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="203"/>
       <c r="F39" s="141"/>
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
       <c r="K39" s="128"/>
-      <c r="L39" s="221"/>
+      <c r="L39" s="193"/>
       <c r="M39" s="148" t="str">
         <f t="shared" ref="M39" si="27">A41</f>
         <v/>
       </c>
-      <c r="N39" s="151" t="str">
+      <c r="N39" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O39" s="152"/>
-      <c r="P39" s="219"/>
-      <c r="Q39" s="208"/>
+      <c r="O39" s="207"/>
+      <c r="P39" s="191"/>
+      <c r="Q39" s="212"/>
       <c r="R39" s="150"/>
     </row>
-    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="134"/>
-      <c r="B40" s="205"/>
-      <c r="C40" s="205"/>
-      <c r="D40" s="155"/>
-      <c r="E40" s="156"/>
+      <c r="B40" s="184"/>
+      <c r="C40" s="184"/>
+      <c r="D40" s="204"/>
+      <c r="E40" s="205"/>
       <c r="F40" s="139"/>
       <c r="G40" s="129"/>
       <c r="H40" s="129"/>
       <c r="I40" s="129"/>
       <c r="J40" s="129"/>
       <c r="K40" s="129"/>
-      <c r="L40" s="221"/>
+      <c r="L40" s="193"/>
       <c r="M40" s="147" t="str">
         <f t="shared" ref="M40" si="28">IF(ISBLANK(A42),"",A42)</f>
         <v/>
       </c>
-      <c r="N40" s="153" t="str">
+      <c r="N40" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O40" s="154"/>
-      <c r="P40" s="219"/>
-      <c r="Q40" s="208"/>
+      <c r="O40" s="209"/>
+      <c r="P40" s="191"/>
+      <c r="Q40" s="212"/>
       <c r="R40" s="149"/>
     </row>
-    <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f t="shared" ref="A41" si="29">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="206"/>
-      <c r="C41" s="206"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="158"/>
+      <c r="B41" s="185"/>
+      <c r="C41" s="185"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="203"/>
       <c r="F41" s="141"/>
       <c r="G41" s="127"/>
       <c r="H41" s="127"/>
       <c r="I41" s="127"/>
       <c r="J41" s="127"/>
       <c r="K41" s="128"/>
-      <c r="L41" s="221"/>
+      <c r="L41" s="193"/>
       <c r="M41" s="148" t="str">
         <f t="shared" ref="M41" si="30">A43</f>
         <v/>
       </c>
-      <c r="N41" s="151" t="str">
+      <c r="N41" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O41" s="152"/>
-      <c r="P41" s="219"/>
-      <c r="Q41" s="208"/>
+      <c r="O41" s="207"/>
+      <c r="P41" s="191"/>
+      <c r="Q41" s="212"/>
       <c r="R41" s="150"/>
     </row>
-    <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="134"/>
-      <c r="B42" s="205"/>
-      <c r="C42" s="205"/>
-      <c r="D42" s="155"/>
-      <c r="E42" s="156"/>
+      <c r="B42" s="184"/>
+      <c r="C42" s="184"/>
+      <c r="D42" s="204"/>
+      <c r="E42" s="205"/>
       <c r="F42" s="139"/>
       <c r="G42" s="129"/>
       <c r="H42" s="129"/>
       <c r="I42" s="129"/>
       <c r="J42" s="129"/>
       <c r="K42" s="129"/>
-      <c r="L42" s="221"/>
+      <c r="L42" s="193"/>
       <c r="M42" s="147" t="str">
         <f t="shared" ref="M42" si="31">IF(ISBLANK(A44),"",A44)</f>
         <v/>
       </c>
-      <c r="N42" s="153" t="str">
+      <c r="N42" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O42" s="154"/>
-      <c r="P42" s="219"/>
-      <c r="Q42" s="208"/>
+      <c r="O42" s="209"/>
+      <c r="P42" s="191"/>
+      <c r="Q42" s="212"/>
       <c r="R42" s="149"/>
     </row>
-    <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f t="shared" ref="A43" si="32">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="206"/>
-      <c r="C43" s="206"/>
-      <c r="D43" s="157"/>
-      <c r="E43" s="158"/>
+      <c r="B43" s="185"/>
+      <c r="C43" s="185"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="203"/>
       <c r="F43" s="141"/>
       <c r="G43" s="127"/>
       <c r="H43" s="127"/>
       <c r="I43" s="127"/>
       <c r="J43" s="127"/>
       <c r="K43" s="128"/>
-      <c r="L43" s="221"/>
+      <c r="L43" s="193"/>
       <c r="M43" s="148" t="str">
         <f t="shared" ref="M43" si="33">A45</f>
         <v/>
       </c>
-      <c r="N43" s="151" t="str">
+      <c r="N43" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O43" s="152"/>
-      <c r="P43" s="219"/>
-      <c r="Q43" s="208"/>
+      <c r="O43" s="207"/>
+      <c r="P43" s="191"/>
+      <c r="Q43" s="212"/>
       <c r="R43" s="150"/>
     </row>
-    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="134"/>
-      <c r="B44" s="205"/>
-      <c r="C44" s="205"/>
-      <c r="D44" s="155"/>
-      <c r="E44" s="156"/>
+      <c r="B44" s="184"/>
+      <c r="C44" s="184"/>
+      <c r="D44" s="204"/>
+      <c r="E44" s="205"/>
       <c r="F44" s="139"/>
       <c r="G44" s="129"/>
       <c r="H44" s="129"/>
       <c r="I44" s="129"/>
       <c r="J44" s="129"/>
       <c r="K44" s="129"/>
-      <c r="L44" s="221"/>
+      <c r="L44" s="193"/>
       <c r="M44" s="147" t="str">
         <f t="shared" ref="M44" si="34">IF(ISBLANK(A46),"",A46)</f>
         <v/>
       </c>
-      <c r="N44" s="153" t="str">
+      <c r="N44" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O44" s="154"/>
-      <c r="P44" s="219"/>
-      <c r="Q44" s="208"/>
+      <c r="O44" s="209"/>
+      <c r="P44" s="191"/>
+      <c r="Q44" s="212"/>
       <c r="R44" s="149"/>
     </row>
-    <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f t="shared" ref="A45" si="35">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="206"/>
-      <c r="C45" s="206"/>
-      <c r="D45" s="157"/>
-      <c r="E45" s="158"/>
+      <c r="B45" s="185"/>
+      <c r="C45" s="185"/>
+      <c r="D45" s="202"/>
+      <c r="E45" s="203"/>
       <c r="F45" s="141"/>
       <c r="G45" s="127"/>
       <c r="H45" s="127"/>
       <c r="I45" s="127"/>
       <c r="J45" s="127"/>
       <c r="K45" s="128"/>
-      <c r="L45" s="221"/>
+      <c r="L45" s="193"/>
       <c r="M45" s="148" t="str">
         <f t="shared" ref="M45" si="36">A47</f>
         <v/>
       </c>
-      <c r="N45" s="151" t="str">
+      <c r="N45" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O45" s="152"/>
-      <c r="P45" s="219"/>
-      <c r="Q45" s="208"/>
+      <c r="O45" s="207"/>
+      <c r="P45" s="191"/>
+      <c r="Q45" s="212"/>
       <c r="R45" s="150"/>
     </row>
-    <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="134"/>
-      <c r="B46" s="205"/>
-      <c r="C46" s="205"/>
-      <c r="D46" s="155"/>
-      <c r="E46" s="156"/>
+      <c r="B46" s="184"/>
+      <c r="C46" s="184"/>
+      <c r="D46" s="204"/>
+      <c r="E46" s="205"/>
       <c r="F46" s="139"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
       <c r="I46" s="129"/>
       <c r="J46" s="129"/>
       <c r="K46" s="129"/>
-      <c r="L46" s="221"/>
+      <c r="L46" s="193"/>
       <c r="M46" s="147" t="str">
         <f t="shared" ref="M46" si="37">IF(ISBLANK(A48),"",A48)</f>
         <v/>
       </c>
-      <c r="N46" s="153" t="str">
+      <c r="N46" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O46" s="154"/>
-      <c r="P46" s="219"/>
-      <c r="Q46" s="208"/>
+      <c r="O46" s="209"/>
+      <c r="P46" s="191"/>
+      <c r="Q46" s="212"/>
       <c r="R46" s="149"/>
     </row>
-    <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f t="shared" ref="A47" si="38">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="206"/>
-      <c r="C47" s="206"/>
-      <c r="D47" s="157"/>
-      <c r="E47" s="158"/>
+      <c r="B47" s="185"/>
+      <c r="C47" s="185"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="203"/>
       <c r="F47" s="141"/>
       <c r="G47" s="127"/>
       <c r="H47" s="127"/>
       <c r="I47" s="127"/>
       <c r="J47" s="127"/>
       <c r="K47" s="128"/>
-      <c r="L47" s="221"/>
+      <c r="L47" s="193"/>
       <c r="M47" s="148" t="str">
         <f t="shared" ref="M47" si="39">A49</f>
         <v/>
       </c>
-      <c r="N47" s="151" t="str">
+      <c r="N47" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O47" s="152"/>
-      <c r="P47" s="219"/>
-      <c r="Q47" s="208"/>
+      <c r="O47" s="207"/>
+      <c r="P47" s="191"/>
+      <c r="Q47" s="212"/>
       <c r="R47" s="150"/>
     </row>
-    <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="134"/>
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
-      <c r="D48" s="155"/>
-      <c r="E48" s="156"/>
+      <c r="B48" s="184"/>
+      <c r="C48" s="184"/>
+      <c r="D48" s="204"/>
+      <c r="E48" s="205"/>
       <c r="F48" s="139"/>
       <c r="G48" s="129"/>
       <c r="H48" s="129"/>
       <c r="I48" s="129"/>
       <c r="J48" s="129"/>
       <c r="K48" s="129"/>
-      <c r="L48" s="221"/>
+      <c r="L48" s="193"/>
       <c r="M48" s="147" t="str">
         <f t="shared" ref="M48" si="40">IF(ISBLANK(A50),"",A50)</f>
         <v/>
       </c>
-      <c r="N48" s="153" t="str">
+      <c r="N48" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O48" s="154"/>
-      <c r="P48" s="219"/>
-      <c r="Q48" s="208"/>
+      <c r="O48" s="209"/>
+      <c r="P48" s="191"/>
+      <c r="Q48" s="212"/>
       <c r="R48" s="149"/>
     </row>
-    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f t="shared" ref="A49" si="41">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="206"/>
-      <c r="C49" s="206"/>
-      <c r="D49" s="157"/>
-      <c r="E49" s="158"/>
+      <c r="B49" s="185"/>
+      <c r="C49" s="185"/>
+      <c r="D49" s="202"/>
+      <c r="E49" s="203"/>
       <c r="F49" s="141"/>
       <c r="G49" s="127"/>
       <c r="H49" s="127"/>
       <c r="I49" s="127"/>
       <c r="J49" s="127"/>
       <c r="K49" s="128"/>
-      <c r="L49" s="221"/>
+      <c r="L49" s="193"/>
       <c r="M49" s="148" t="str">
         <f t="shared" ref="M49" si="42">A51</f>
         <v/>
       </c>
-      <c r="N49" s="151" t="str">
+      <c r="N49" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O49" s="152"/>
-      <c r="P49" s="219"/>
-      <c r="Q49" s="208"/>
+      <c r="O49" s="207"/>
+      <c r="P49" s="191"/>
+      <c r="Q49" s="212"/>
       <c r="R49" s="150"/>
     </row>
-    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134"/>
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
-      <c r="D50" s="155"/>
-      <c r="E50" s="156"/>
+      <c r="B50" s="184"/>
+      <c r="C50" s="184"/>
+      <c r="D50" s="204"/>
+      <c r="E50" s="205"/>
       <c r="F50" s="139"/>
       <c r="G50" s="129"/>
       <c r="H50" s="129"/>
       <c r="I50" s="129"/>
       <c r="J50" s="129"/>
       <c r="K50" s="129"/>
-      <c r="L50" s="221"/>
+      <c r="L50" s="193"/>
       <c r="M50" s="147" t="str">
         <f t="shared" ref="M50" si="43">IF(ISBLANK(A52),"",A52)</f>
         <v/>
       </c>
-      <c r="N50" s="153" t="str">
+      <c r="N50" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O50" s="154"/>
-      <c r="P50" s="219"/>
-      <c r="Q50" s="208"/>
+      <c r="O50" s="209"/>
+      <c r="P50" s="191"/>
+      <c r="Q50" s="212"/>
       <c r="R50" s="149"/>
     </row>
-    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f t="shared" ref="A51" si="44">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="206"/>
-      <c r="C51" s="206"/>
-      <c r="D51" s="157"/>
-      <c r="E51" s="158"/>
+      <c r="B51" s="185"/>
+      <c r="C51" s="185"/>
+      <c r="D51" s="202"/>
+      <c r="E51" s="203"/>
       <c r="F51" s="141"/>
       <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127"/>
       <c r="J51" s="127"/>
       <c r="K51" s="128"/>
-      <c r="L51" s="221"/>
+      <c r="L51" s="193"/>
       <c r="M51" s="148" t="str">
         <f t="shared" ref="M51" si="45">A53</f>
         <v/>
       </c>
-      <c r="N51" s="151" t="str">
+      <c r="N51" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O51" s="152"/>
-      <c r="P51" s="219"/>
-      <c r="Q51" s="208"/>
+      <c r="O51" s="207"/>
+      <c r="P51" s="191"/>
+      <c r="Q51" s="212"/>
       <c r="R51" s="150"/>
     </row>
-    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="134"/>
-      <c r="B52" s="205"/>
-      <c r="C52" s="205"/>
-      <c r="D52" s="155"/>
-      <c r="E52" s="156"/>
+      <c r="B52" s="184"/>
+      <c r="C52" s="184"/>
+      <c r="D52" s="204"/>
+      <c r="E52" s="205"/>
       <c r="F52" s="139"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
       <c r="I52" s="129"/>
       <c r="J52" s="129"/>
       <c r="K52" s="129"/>
-      <c r="L52" s="221"/>
+      <c r="L52" s="193"/>
       <c r="M52" s="147"/>
-      <c r="N52" s="153" t="str">
+      <c r="N52" s="208" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O52" s="154"/>
-      <c r="P52" s="219"/>
-      <c r="Q52" s="208"/>
+      <c r="O52" s="209"/>
+      <c r="P52" s="191"/>
+      <c r="Q52" s="212"/>
       <c r="R52" s="149"/>
     </row>
-    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
         <f t="shared" ref="A53" si="46">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B53" s="206"/>
-      <c r="C53" s="206"/>
-      <c r="D53" s="157"/>
-      <c r="E53" s="158"/>
+      <c r="B53" s="185"/>
+      <c r="C53" s="185"/>
+      <c r="D53" s="202"/>
+      <c r="E53" s="203"/>
       <c r="F53" s="141"/>
       <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127"/>
       <c r="J53" s="127"/>
       <c r="K53" s="128"/>
-      <c r="L53" s="222"/>
+      <c r="L53" s="194"/>
       <c r="M53" s="148"/>
-      <c r="N53" s="151" t="str">
+      <c r="N53" s="206" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O53" s="152"/>
-      <c r="P53" s="220"/>
-      <c r="Q53" s="209"/>
+      <c r="O53" s="207"/>
+      <c r="P53" s="192"/>
+      <c r="Q53" s="213"/>
       <c r="R53" s="150"/>
     </row>
-    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="39"/>
       <c r="B54" s="40"/>
       <c r="C54" s="40"/>
@@ -4497,7 +4453,7 @@
       <c r="P54" s="44"/>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="45"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -4528,7 +4484,7 @@
       <c r="O55" s="47"/>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A56" s="45"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -4544,7 +4500,7 @@
       <c r="O56" s="47"/>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="45"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
@@ -4560,7 +4516,7 @@
       <c r="O57" s="47"/>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="45"/>
       <c r="B58" s="41" t="s">
         <v>28</v>
@@ -4572,8 +4528,8 @@
         <f>SUM(G55:K55)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="210"/>
-      <c r="H58" s="210"/>
+      <c r="G58" s="214"/>
+      <c r="H58" s="214"/>
       <c r="I58" s="49" t="s">
         <v>29</v>
       </c>
@@ -4585,7 +4541,7 @@
       <c r="O58" s="47"/>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="45"/>
       <c r="B59" s="41" t="s">
         <v>31</v>
@@ -4599,8 +4555,8 @@
         <f>L9</f>
         <v>0</v>
       </c>
-      <c r="G59" s="210"/>
-      <c r="H59" s="210"/>
+      <c r="G59" s="214"/>
+      <c r="H59" s="214"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
@@ -4608,7 +4564,7 @@
       <c r="O59" s="47"/>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="1:18" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:18" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="50"/>
       <c r="B60" s="41" t="s">
         <v>33</v>
@@ -4631,7 +4587,7 @@
       <c r="O60" s="47"/>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A61" s="50"/>
       <c r="B61" s="40"/>
       <c r="C61" s="40"/>
@@ -4647,7 +4603,7 @@
       <c r="O61" s="47"/>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="56"/>
       <c r="B62" s="40" t="s">
         <v>34</v>
@@ -4663,37 +4619,37 @@
       <c r="K62" s="58"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
       <c r="B63" s="57"/>
-      <c r="C63" s="211" t="s">
+      <c r="C63" s="215" t="s">
         <v>35</v>
       </c>
-      <c r="D63" s="211"/>
-      <c r="E63" s="211"/>
-      <c r="F63" s="211"/>
-      <c r="G63" s="211"/>
-      <c r="H63" s="211"/>
-      <c r="I63" s="211"/>
-      <c r="J63" s="211"/>
-      <c r="K63" s="211"/>
+      <c r="D63" s="215"/>
+      <c r="E63" s="215"/>
+      <c r="F63" s="215"/>
+      <c r="G63" s="215"/>
+      <c r="H63" s="215"/>
+      <c r="I63" s="215"/>
+      <c r="J63" s="215"/>
+      <c r="K63" s="215"/>
       <c r="L63" s="3"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
       <c r="B64" s="57"/>
-      <c r="C64" s="211"/>
-      <c r="D64" s="211"/>
-      <c r="E64" s="211"/>
-      <c r="F64" s="211"/>
-      <c r="G64" s="211"/>
-      <c r="H64" s="211"/>
-      <c r="I64" s="211"/>
-      <c r="J64" s="211"/>
-      <c r="K64" s="211"/>
+      <c r="C64" s="215"/>
+      <c r="D64" s="215"/>
+      <c r="E64" s="215"/>
+      <c r="F64" s="215"/>
+      <c r="G64" s="215"/>
+      <c r="H64" s="215"/>
+      <c r="I64" s="215"/>
+      <c r="J64" s="215"/>
+      <c r="K64" s="215"/>
       <c r="L64" s="3"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="50"/>
       <c r="B65" s="40"/>
       <c r="C65" s="61"/>
@@ -4707,7 +4663,7 @@
       <c r="K65" s="60"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -4724,7 +4680,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
@@ -4741,7 +4697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
         <v>36</v>
       </c>
@@ -4760,7 +4716,7 @@
       <c r="L68" s="3"/>
       <c r="R68" s="65"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="50"/>
       <c r="B69" s="40"/>
       <c r="C69" s="61"/>
@@ -4774,7 +4730,7 @@
       <c r="K69" s="60"/>
       <c r="L69" s="3"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="50"/>
       <c r="B70" s="40"/>
       <c r="C70" s="61"/>
@@ -4788,7 +4744,7 @@
       <c r="K70" s="60"/>
       <c r="L70" s="3"/>
     </row>
-    <row r="71" spans="1:18" ht="20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="50"/>
       <c r="B71" s="40"/>
       <c r="C71" s="61"/>
@@ -4801,16 +4757,16 @@
       <c r="J71" s="60"/>
       <c r="K71" s="60"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="204" t="s">
-        <v>89</v>
-      </c>
-      <c r="N71" s="204"/>
-      <c r="O71" s="204"/>
-      <c r="P71" s="204"/>
-      <c r="Q71" s="204"/>
-      <c r="R71" s="204"/>
-    </row>
-    <row r="72" spans="1:18" ht="20" x14ac:dyDescent="0.35">
+      <c r="M71" s="210" t="s">
+        <v>87</v>
+      </c>
+      <c r="N71" s="210"/>
+      <c r="O71" s="210"/>
+      <c r="P71" s="210"/>
+      <c r="Q71" s="210"/>
+      <c r="R71" s="210"/>
+    </row>
+    <row r="72" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="50"/>
       <c r="B72" s="41"/>
       <c r="C72" s="41" t="s">
@@ -4825,20 +4781,20 @@
       <c r="J72" s="60"/>
       <c r="K72" s="60"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="204" t="s">
-        <v>90</v>
-      </c>
-      <c r="N72" s="204"/>
-      <c r="O72" s="204"/>
-      <c r="P72" s="204"/>
-      <c r="Q72" s="204"/>
-      <c r="R72" s="204"/>
-    </row>
-    <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="M72" s="210" t="s">
+        <v>88</v>
+      </c>
+      <c r="N72" s="210"/>
+      <c r="O72" s="210"/>
+      <c r="P72" s="210"/>
+      <c r="Q72" s="210"/>
+      <c r="R72" s="210"/>
+    </row>
+    <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
       <c r="B73" s="66"/>
       <c r="C73" s="66" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D73" s="67"/>
       <c r="E73" s="68" t="s">
@@ -4851,14 +4807,14 @@
       <c r="J73" s="60"/>
       <c r="K73" s="60"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="196"/>
-      <c r="N73" s="196"/>
-      <c r="O73" s="196"/>
-      <c r="P73" s="196"/>
-      <c r="Q73" s="196"/>
-      <c r="R73" s="196"/>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="M73" s="217"/>
+      <c r="N73" s="217"/>
+      <c r="O73" s="217"/>
+      <c r="P73" s="217"/>
+      <c r="Q73" s="217"/>
+      <c r="R73" s="217"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="50"/>
       <c r="B74" s="40"/>
       <c r="C74" s="40"/>
@@ -4872,7 +4828,7 @@
       <c r="K74" s="60"/>
       <c r="L74" s="3"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="50"/>
       <c r="B75" s="41"/>
       <c r="C75" s="41" t="s">
@@ -4882,26 +4838,26 @@
       <c r="E75" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="197">
+      <c r="F75" s="218">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="197"/>
-      <c r="H75" s="197"/>
-      <c r="I75" s="197"/>
-      <c r="J75" s="197"/>
-      <c r="K75" s="197"/>
+      <c r="G75" s="218"/>
+      <c r="H75" s="218"/>
+      <c r="I75" s="218"/>
+      <c r="J75" s="218"/>
+      <c r="K75" s="218"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="198" t="s">
-        <v>91</v>
-      </c>
-      <c r="N75" s="198"/>
-      <c r="O75" s="198"/>
-      <c r="P75" s="198"/>
-      <c r="Q75" s="198"/>
-      <c r="R75" s="198"/>
-    </row>
-    <row r="76" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="M75" s="219" t="s">
+        <v>89</v>
+      </c>
+      <c r="N75" s="219"/>
+      <c r="O75" s="219"/>
+      <c r="P75" s="219"/>
+      <c r="Q75" s="219"/>
+      <c r="R75" s="219"/>
+    </row>
+    <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="50"/>
       <c r="B76" s="40"/>
       <c r="C76" s="40"/>
@@ -4921,7 +4877,7 @@
       <c r="Q76" s="75"/>
       <c r="R76" s="75"/>
     </row>
-    <row r="77" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A77" s="64"/>
       <c r="B77" s="41"/>
       <c r="C77" s="41" t="s">
@@ -4931,14 +4887,14 @@
       <c r="E77" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="199">
+      <c r="F77" s="220">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="199"/>
-      <c r="H77" s="199"/>
-      <c r="I77" s="199"/>
-      <c r="J77" s="199"/>
+      <c r="G77" s="220"/>
+      <c r="H77" s="220"/>
+      <c r="I77" s="220"/>
+      <c r="J77" s="220"/>
       <c r="K77" s="40"/>
       <c r="L77" s="50"/>
       <c r="M77" s="75"/>
@@ -4948,7 +4904,7 @@
       <c r="Q77" s="75"/>
       <c r="R77" s="75"/>
     </row>
-    <row r="78" spans="1:18" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="67"/>
       <c r="B78" s="40"/>
       <c r="C78" s="40"/>
@@ -4963,15 +4919,15 @@
       <c r="L78" s="50"/>
       <c r="M78" s="133"/>
       <c r="N78" s="133"/>
-      <c r="O78" s="201" t="str">
+      <c r="O78" s="222" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="P78" s="201"/>
-      <c r="Q78" s="201"/>
-      <c r="R78" s="201"/>
-    </row>
-    <row r="79" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="P78" s="222"/>
+      <c r="Q78" s="222"/>
+      <c r="R78" s="222"/>
+    </row>
+    <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="67"/>
       <c r="B79" s="40"/>
       <c r="C79" s="40" t="s">
@@ -4991,14 +4947,14 @@
       <c r="M79" s="77"/>
       <c r="N79" s="77"/>
       <c r="O79" s="78"/>
-      <c r="P79" s="200" t="str">
+      <c r="P79" s="221" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="Q79" s="200"/>
+      <c r="Q79" s="221"/>
       <c r="R79" s="79"/>
     </row>
-    <row r="80" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A80" s="50"/>
       <c r="B80" s="67"/>
       <c r="C80" s="40"/>
@@ -5018,7 +4974,7 @@
       <c r="Q80" s="78"/>
       <c r="R80" s="80"/>
     </row>
-    <row r="81" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="50"/>
       <c r="B81" s="67"/>
       <c r="C81" s="41"/>
@@ -5033,15 +4989,15 @@
       <c r="L81" s="50"/>
       <c r="M81" s="78"/>
       <c r="N81" s="78"/>
-      <c r="O81" s="202" t="str">
+      <c r="O81" s="223" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="P81" s="202"/>
-      <c r="Q81" s="202"/>
-      <c r="R81" s="202"/>
-    </row>
-    <row r="82" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="P81" s="223"/>
+      <c r="Q81" s="223"/>
+      <c r="R81" s="223"/>
+    </row>
+    <row r="82" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="50"/>
       <c r="B82" s="67"/>
       <c r="C82" s="66"/>
@@ -5061,7 +5017,7 @@
       <c r="Q82" s="75"/>
       <c r="R82" s="75"/>
     </row>
-    <row r="83" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A83" s="50"/>
       <c r="B83" s="67"/>
       <c r="C83" s="41" t="s">
@@ -5076,18 +5032,18 @@
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="203"/>
-      <c r="N83" s="203"/>
-      <c r="O83" s="203"/>
-      <c r="P83" s="203"/>
-      <c r="Q83" s="203"/>
-      <c r="R83" s="203"/>
-    </row>
-    <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M83" s="224"/>
+      <c r="N83" s="224"/>
+      <c r="O83" s="224"/>
+      <c r="P83" s="224"/>
+      <c r="Q83" s="224"/>
+      <c r="R83" s="224"/>
+    </row>
+    <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="50"/>
       <c r="B84" s="67"/>
       <c r="C84" s="66" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D84" s="50"/>
       <c r="E84" s="68" t="s">
@@ -5100,16 +5056,16 @@
       <c r="J84" s="74"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="182" t="s">
-        <v>92</v>
-      </c>
-      <c r="N84" s="182"/>
-      <c r="O84" s="182"/>
-      <c r="P84" s="182"/>
-      <c r="Q84" s="182"/>
-      <c r="R84" s="182"/>
-    </row>
-    <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M84" s="216" t="s">
+        <v>90</v>
+      </c>
+      <c r="N84" s="216"/>
+      <c r="O84" s="216"/>
+      <c r="P84" s="216"/>
+      <c r="Q84" s="216"/>
+      <c r="R84" s="216"/>
+    </row>
+    <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="50"/>
       <c r="B85" s="67"/>
       <c r="C85" s="40"/>
@@ -5122,16 +5078,16 @@
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="N85" s="182"/>
-      <c r="O85" s="182"/>
-      <c r="P85" s="182"/>
-      <c r="Q85" s="182"/>
-      <c r="R85" s="182"/>
-    </row>
-    <row r="86" spans="1:18" ht="18" x14ac:dyDescent="0.4">
+      <c r="M85" s="216" t="s">
+        <v>91</v>
+      </c>
+      <c r="N85" s="216"/>
+      <c r="O85" s="216"/>
+      <c r="P85" s="216"/>
+      <c r="Q85" s="216"/>
+      <c r="R85" s="216"/>
+    </row>
+    <row r="86" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="50"/>
       <c r="B86" s="67"/>
       <c r="C86" s="41" t="s">
@@ -5148,14 +5104,14 @@
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="183"/>
-      <c r="N86" s="183"/>
-      <c r="O86" s="183"/>
-      <c r="P86" s="183"/>
-      <c r="Q86" s="183"/>
-      <c r="R86" s="183"/>
-    </row>
-    <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M86" s="225"/>
+      <c r="N86" s="225"/>
+      <c r="O86" s="225"/>
+      <c r="P86" s="225"/>
+      <c r="Q86" s="225"/>
+      <c r="R86" s="225"/>
+    </row>
+    <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="50"/>
       <c r="B87" s="67"/>
       <c r="C87" s="40"/>
@@ -5168,14 +5124,14 @@
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="182"/>
-      <c r="N87" s="182"/>
-      <c r="O87" s="182"/>
-      <c r="P87" s="182"/>
-      <c r="Q87" s="182"/>
-      <c r="R87" s="182"/>
-    </row>
-    <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M87" s="216"/>
+      <c r="N87" s="216"/>
+      <c r="O87" s="216"/>
+      <c r="P87" s="216"/>
+      <c r="Q87" s="216"/>
+      <c r="R87" s="216"/>
+    </row>
+    <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50"/>
       <c r="B88" s="67"/>
       <c r="C88" s="41" t="s">
@@ -5185,23 +5141,23 @@
       <c r="E88" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="181"/>
-      <c r="G88" s="181"/>
-      <c r="H88" s="181"/>
-      <c r="I88" s="181"/>
-      <c r="J88" s="181"/>
+      <c r="F88" s="240"/>
+      <c r="G88" s="240"/>
+      <c r="H88" s="240"/>
+      <c r="I88" s="240"/>
+      <c r="J88" s="240"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="182" t="s">
-        <v>94</v>
-      </c>
-      <c r="N88" s="182"/>
-      <c r="O88" s="182"/>
-      <c r="P88" s="182"/>
-      <c r="Q88" s="182"/>
-      <c r="R88" s="182"/>
-    </row>
-    <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M88" s="216" t="s">
+        <v>92</v>
+      </c>
+      <c r="N88" s="216"/>
+      <c r="O88" s="216"/>
+      <c r="P88" s="216"/>
+      <c r="Q88" s="216"/>
+      <c r="R88" s="216"/>
+    </row>
+    <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="50"/>
       <c r="B89" s="67"/>
       <c r="C89" s="40"/>
@@ -5215,7 +5171,7 @@
       <c r="K89" s="50"/>
       <c r="L89" s="50"/>
       <c r="M89" s="83" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N89" s="83"/>
       <c r="O89" s="83"/>
@@ -5223,7 +5179,7 @@
       <c r="Q89" s="83"/>
       <c r="R89" s="83"/>
     </row>
-    <row r="90" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="50"/>
       <c r="B90" s="67"/>
       <c r="C90" s="40" t="s">
@@ -5247,7 +5203,7 @@
       <c r="Q90" s="83"/>
       <c r="R90" s="83"/>
     </row>
-    <row r="91" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="50"/>
       <c r="B91" s="67"/>
       <c r="C91" s="41"/>
@@ -5261,7 +5217,7 @@
       <c r="K91" s="50"/>
       <c r="L91" s="50"/>
       <c r="M91" s="83" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N91" s="83"/>
       <c r="O91" s="83"/>
@@ -5269,7 +5225,7 @@
       <c r="Q91" s="83"/>
       <c r="R91" s="83"/>
     </row>
-    <row r="92" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="50"/>
       <c r="B92" s="67"/>
       <c r="C92" s="40"/>
@@ -5289,7 +5245,7 @@
       <c r="Q92" s="83"/>
       <c r="R92" s="83"/>
     </row>
-    <row r="93" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="50"/>
       <c r="B93" s="67"/>
       <c r="C93" s="40"/>
@@ -5303,7 +5259,7 @@
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
       <c r="M93" s="83" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N93" s="83"/>
       <c r="O93" s="83"/>
@@ -5311,7 +5267,7 @@
       <c r="Q93" s="83"/>
       <c r="R93" s="83"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="64" t="s">
         <v>44</v>
       </c>
@@ -5329,7 +5285,7 @@
       <c r="K94" s="27"/>
       <c r="L94" s="17"/>
       <c r="M94" s="83" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N94" s="83"/>
       <c r="O94" s="83"/>
@@ -5337,7 +5293,7 @@
       <c r="Q94" s="83"/>
       <c r="R94" s="83"/>
     </row>
-    <row r="95" spans="1:18" ht="18" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A95" s="64"/>
       <c r="B95" s="86" t="s">
         <v>46</v>
@@ -5352,14 +5308,14 @@
       <c r="J95" s="86"/>
       <c r="K95" s="27"/>
       <c r="L95" s="17"/>
-      <c r="M95" s="183"/>
-      <c r="N95" s="183"/>
-      <c r="O95" s="183"/>
-      <c r="P95" s="183"/>
-      <c r="Q95" s="183"/>
-      <c r="R95" s="183"/>
-    </row>
-    <row r="96" spans="1:18" ht="18" x14ac:dyDescent="0.4">
+      <c r="M95" s="225"/>
+      <c r="N95" s="225"/>
+      <c r="O95" s="225"/>
+      <c r="P95" s="225"/>
+      <c r="Q95" s="225"/>
+      <c r="R95" s="225"/>
+    </row>
+    <row r="96" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
       <c r="B96" s="86" t="s">
         <v>47</v>
@@ -5374,14 +5330,14 @@
       <c r="J96" s="86"/>
       <c r="K96" s="27"/>
       <c r="L96" s="17"/>
-      <c r="M96" s="183"/>
-      <c r="N96" s="183"/>
-      <c r="O96" s="183"/>
-      <c r="P96" s="183"/>
-      <c r="Q96" s="183"/>
-      <c r="R96" s="183"/>
-    </row>
-    <row r="97" spans="1:18" ht="18" x14ac:dyDescent="0.4">
+      <c r="M96" s="225"/>
+      <c r="N96" s="225"/>
+      <c r="O96" s="225"/>
+      <c r="P96" s="225"/>
+      <c r="Q96" s="225"/>
+      <c r="R96" s="225"/>
+    </row>
+    <row r="97" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
       <c r="B97" s="86" t="s">
         <v>48</v>
@@ -5396,14 +5352,14 @@
       <c r="J97" s="86"/>
       <c r="K97" s="27"/>
       <c r="L97" s="17"/>
-      <c r="M97" s="183"/>
-      <c r="N97" s="183"/>
-      <c r="O97" s="183"/>
-      <c r="P97" s="183"/>
-      <c r="Q97" s="183"/>
-      <c r="R97" s="183"/>
-    </row>
-    <row r="98" spans="1:18" ht="18" x14ac:dyDescent="0.4">
+      <c r="M97" s="225"/>
+      <c r="N97" s="225"/>
+      <c r="O97" s="225"/>
+      <c r="P97" s="225"/>
+      <c r="Q97" s="225"/>
+      <c r="R97" s="225"/>
+    </row>
+    <row r="98" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
       <c r="B98" s="86" t="s">
         <v>49</v>
@@ -5418,14 +5374,14 @@
       <c r="J98" s="86"/>
       <c r="K98" s="27"/>
       <c r="L98" s="17"/>
-      <c r="M98" s="183"/>
-      <c r="N98" s="183"/>
-      <c r="O98" s="183"/>
-      <c r="P98" s="183"/>
-      <c r="Q98" s="183"/>
-      <c r="R98" s="183"/>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="M98" s="225"/>
+      <c r="N98" s="225"/>
+      <c r="O98" s="225"/>
+      <c r="P98" s="225"/>
+      <c r="Q98" s="225"/>
+      <c r="R98" s="225"/>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="64"/>
       <c r="B99" s="86" t="s">
         <v>50</v>
@@ -5440,14 +5396,14 @@
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
       <c r="L99" s="17"/>
-      <c r="M99" s="182"/>
-      <c r="N99" s="182"/>
-      <c r="O99" s="182"/>
-      <c r="P99" s="182"/>
-      <c r="Q99" s="182"/>
-      <c r="R99" s="182"/>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="M99" s="216"/>
+      <c r="N99" s="216"/>
+      <c r="O99" s="216"/>
+      <c r="P99" s="216"/>
+      <c r="Q99" s="216"/>
+      <c r="R99" s="216"/>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="50"/>
       <c r="B100" s="86"/>
       <c r="C100" s="18"/>
@@ -5467,7 +5423,7 @@
       <c r="Q100" s="83"/>
       <c r="R100" s="83"/>
     </row>
-    <row r="101" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A101" s="64" t="s">
         <v>51</v>
       </c>
@@ -5486,7 +5442,7 @@
       <c r="L101" s="17"/>
       <c r="O101" s="79"/>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="64"/>
       <c r="B102" s="18" t="s">
         <v>53</v>
@@ -5502,7 +5458,7 @@
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="64"/>
       <c r="B103" s="18" t="s">
         <v>54</v>
@@ -5518,10 +5474,10 @@
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="O103" s="77" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="64"/>
       <c r="B104" s="41"/>
       <c r="C104" s="92"/>
@@ -5538,7 +5494,7 @@
       <c r="Q104" s="94"/>
       <c r="R104" s="94"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="64"/>
       <c r="B105" s="40" t="s">
         <v>55</v>
@@ -5554,7 +5510,7 @@
       <c r="K105" s="50"/>
       <c r="L105" s="50"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="64"/>
       <c r="B106" s="40"/>
       <c r="C106" s="95"/>
@@ -5568,7 +5524,7 @@
       <c r="K106" s="50"/>
       <c r="L106" s="50"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="64"/>
       <c r="B107" s="40"/>
       <c r="C107" s="95"/>
@@ -5582,19 +5538,19 @@
       <c r="K107" s="50"/>
       <c r="L107" s="50"/>
       <c r="O107" s="94" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P107" s="94"/>
       <c r="Q107" s="94"/>
       <c r="R107" s="94"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="64" t="s">
         <v>56</v>
       </c>
       <c r="B108" s="95"/>
       <c r="C108" s="40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D108" s="40"/>
       <c r="E108" s="68" t="s">
@@ -5611,7 +5567,7 @@
       <c r="Q108" s="94"/>
       <c r="R108" s="94"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="55"/>
       <c r="B109" s="95"/>
       <c r="C109" s="40"/>
@@ -5625,13 +5581,13 @@
       <c r="K109" s="50"/>
       <c r="L109" s="50"/>
       <c r="O109" s="83" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P109" s="94"/>
       <c r="Q109" s="94"/>
       <c r="R109" s="94"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="50"/>
       <c r="B110" s="95"/>
       <c r="C110" s="41" t="s">
@@ -5649,10 +5605,10 @@
       <c r="K110" s="50"/>
       <c r="L110" s="50"/>
       <c r="O110" s="99" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="50"/>
       <c r="B111" s="95"/>
       <c r="C111" s="66"/>
@@ -5666,13 +5622,13 @@
       <c r="K111" s="50"/>
       <c r="L111" s="50"/>
       <c r="O111" s="99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P111" s="94"/>
       <c r="Q111" s="94"/>
       <c r="R111" s="94"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="50"/>
       <c r="B112" s="95"/>
       <c r="C112" s="41" t="s">
@@ -5690,12 +5646,12 @@
       <c r="K112" s="50"/>
       <c r="L112" s="50"/>
       <c r="O112" s="99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q112" s="100"/>
       <c r="R112" s="100"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="50"/>
       <c r="B113" s="95"/>
       <c r="C113" s="40"/>
@@ -5713,7 +5669,7 @@
       <c r="Q113" s="94"/>
       <c r="R113" s="94"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="17"/>
       <c r="B114" s="91"/>
       <c r="C114" s="86" t="s">
@@ -5731,78 +5687,78 @@
       <c r="K114" s="17"/>
       <c r="L114" s="50"/>
       <c r="O114" s="99" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P114" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O115" s="83"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O116" s="99" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P116" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A124" s="184" t="s">
+    <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="241" t="s">
         <v>65</v>
       </c>
-      <c r="B124" s="185"/>
-      <c r="C124" s="185"/>
-      <c r="D124" s="185"/>
-      <c r="E124" s="185"/>
-      <c r="F124" s="185"/>
-      <c r="G124" s="185"/>
-      <c r="H124" s="185"/>
-      <c r="I124" s="185"/>
-      <c r="J124" s="185"/>
-      <c r="K124" s="185"/>
-      <c r="L124" s="186"/>
-    </row>
-    <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="187" t="s">
+      <c r="B124" s="242"/>
+      <c r="C124" s="242"/>
+      <c r="D124" s="242"/>
+      <c r="E124" s="242"/>
+      <c r="F124" s="242"/>
+      <c r="G124" s="242"/>
+      <c r="H124" s="242"/>
+      <c r="I124" s="242"/>
+      <c r="J124" s="242"/>
+      <c r="K124" s="242"/>
+      <c r="L124" s="243"/>
+    </row>
+    <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="244" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="188"/>
-      <c r="C125" s="188"/>
-      <c r="D125" s="188"/>
-      <c r="E125" s="188"/>
-      <c r="F125" s="188"/>
-      <c r="G125" s="188"/>
-      <c r="H125" s="188"/>
-      <c r="I125" s="188"/>
-      <c r="J125" s="188"/>
-      <c r="K125" s="188"/>
-      <c r="L125" s="189"/>
-    </row>
-    <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="245"/>
+      <c r="C125" s="245"/>
+      <c r="D125" s="245"/>
+      <c r="E125" s="245"/>
+      <c r="F125" s="245"/>
+      <c r="G125" s="245"/>
+      <c r="H125" s="245"/>
+      <c r="I125" s="245"/>
+      <c r="J125" s="245"/>
+      <c r="K125" s="245"/>
+      <c r="L125" s="246"/>
+    </row>
+    <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="105" t="s">
         <v>67</v>
       </c>
       <c r="B126" s="106"/>
       <c r="C126" s="106"/>
-      <c r="D126" s="190">
+      <c r="D126" s="247">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="191"/>
-      <c r="F126" s="191"/>
-      <c r="G126" s="191"/>
-      <c r="H126" s="191"/>
-      <c r="I126" s="192"/>
-      <c r="J126" s="193" t="s">
+      <c r="E126" s="248"/>
+      <c r="F126" s="248"/>
+      <c r="G126" s="248"/>
+      <c r="H126" s="248"/>
+      <c r="I126" s="249"/>
+      <c r="J126" s="250" t="s">
         <v>68</v>
       </c>
-      <c r="K126" s="194"/>
-      <c r="L126" s="195"/>
-    </row>
-    <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K126" s="251"/>
+      <c r="L126" s="252"/>
+    </row>
+    <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="107" t="s">
         <v>69</v>
       </c>
@@ -5818,7 +5774,7 @@
       <c r="K127" s="112"/>
       <c r="L127" s="113"/>
     </row>
-    <row r="128" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="114"/>
       <c r="B128" s="115"/>
       <c r="C128" s="115"/>
@@ -5832,29 +5788,29 @@
       <c r="K128" s="118"/>
       <c r="L128" s="119"/>
     </row>
-    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B129" s="171" t="s">
+      <c r="B129" s="230" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="172"/>
-      <c r="D129" s="173" t="s">
+      <c r="C129" s="231"/>
+      <c r="D129" s="232" t="s">
         <v>72</v>
       </c>
-      <c r="E129" s="174"/>
-      <c r="F129" s="174"/>
-      <c r="G129" s="174"/>
-      <c r="H129" s="174"/>
-      <c r="I129" s="174"/>
-      <c r="J129" s="175"/>
-      <c r="K129" s="173" t="s">
+      <c r="E129" s="233"/>
+      <c r="F129" s="233"/>
+      <c r="G129" s="233"/>
+      <c r="H129" s="233"/>
+      <c r="I129" s="233"/>
+      <c r="J129" s="234"/>
+      <c r="K129" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="L129" s="174"/>
-    </row>
-    <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L129" s="233"/>
+    </row>
+    <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="121"/>
       <c r="B130" s="122" t="s">
         <v>74</v>
@@ -5862,243 +5818,349 @@
       <c r="C130" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="D130" s="176"/>
-      <c r="E130" s="177"/>
-      <c r="F130" s="177"/>
-      <c r="G130" s="177"/>
-      <c r="H130" s="177"/>
-      <c r="I130" s="177"/>
-      <c r="J130" s="178"/>
-      <c r="K130" s="179"/>
-      <c r="L130" s="180"/>
-    </row>
-    <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D130" s="235"/>
+      <c r="E130" s="236"/>
+      <c r="F130" s="236"/>
+      <c r="G130" s="236"/>
+      <c r="H130" s="236"/>
+      <c r="I130" s="236"/>
+      <c r="J130" s="237"/>
+      <c r="K130" s="238"/>
+      <c r="L130" s="239"/>
+    </row>
+    <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="124">
         <v>1</v>
       </c>
       <c r="B131" s="124"/>
       <c r="C131" s="125"/>
-      <c r="D131" s="166" t="s">
+      <c r="D131" s="227" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="167"/>
-      <c r="F131" s="167"/>
-      <c r="G131" s="167"/>
-      <c r="H131" s="167"/>
-      <c r="I131" s="167"/>
-      <c r="J131" s="168"/>
-      <c r="K131" s="162"/>
-      <c r="L131" s="162"/>
-    </row>
-    <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E131" s="228"/>
+      <c r="F131" s="228"/>
+      <c r="G131" s="228"/>
+      <c r="H131" s="228"/>
+      <c r="I131" s="228"/>
+      <c r="J131" s="229"/>
+      <c r="K131" s="226"/>
+      <c r="L131" s="226"/>
+    </row>
+    <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="124">
         <v>2</v>
       </c>
       <c r="B132" s="124"/>
       <c r="C132" s="126"/>
-      <c r="D132" s="166" t="s">
+      <c r="D132" s="227" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="167"/>
-      <c r="F132" s="167"/>
-      <c r="G132" s="167"/>
-      <c r="H132" s="167"/>
-      <c r="I132" s="167"/>
-      <c r="J132" s="168"/>
-      <c r="K132" s="162"/>
-      <c r="L132" s="162"/>
-    </row>
-    <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E132" s="228"/>
+      <c r="F132" s="228"/>
+      <c r="G132" s="228"/>
+      <c r="H132" s="228"/>
+      <c r="I132" s="228"/>
+      <c r="J132" s="229"/>
+      <c r="K132" s="226"/>
+      <c r="L132" s="226"/>
+    </row>
+    <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="124">
         <v>3</v>
       </c>
       <c r="B133" s="124"/>
       <c r="C133" s="126"/>
-      <c r="D133" s="166" t="s">
+      <c r="D133" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="E133" s="167"/>
-      <c r="F133" s="167"/>
-      <c r="G133" s="167"/>
-      <c r="H133" s="167"/>
-      <c r="I133" s="167"/>
-      <c r="J133" s="168"/>
-      <c r="K133" s="162"/>
-      <c r="L133" s="162"/>
-    </row>
-    <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E133" s="228"/>
+      <c r="F133" s="228"/>
+      <c r="G133" s="228"/>
+      <c r="H133" s="228"/>
+      <c r="I133" s="228"/>
+      <c r="J133" s="229"/>
+      <c r="K133" s="226"/>
+      <c r="L133" s="226"/>
+    </row>
+    <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="124">
         <v>4</v>
       </c>
       <c r="B134" s="124"/>
       <c r="C134" s="126"/>
-      <c r="D134" s="166" t="s">
+      <c r="D134" s="227" t="s">
         <v>79</v>
       </c>
-      <c r="E134" s="167"/>
-      <c r="F134" s="167"/>
-      <c r="G134" s="167"/>
-      <c r="H134" s="167"/>
-      <c r="I134" s="167"/>
-      <c r="J134" s="168"/>
-      <c r="K134" s="162"/>
-      <c r="L134" s="162"/>
-    </row>
-    <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E134" s="228"/>
+      <c r="F134" s="228"/>
+      <c r="G134" s="228"/>
+      <c r="H134" s="228"/>
+      <c r="I134" s="228"/>
+      <c r="J134" s="229"/>
+      <c r="K134" s="226"/>
+      <c r="L134" s="226"/>
+    </row>
+    <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="124">
         <v>5</v>
       </c>
       <c r="B135" s="124"/>
       <c r="C135" s="126"/>
-      <c r="D135" s="166" t="s">
+      <c r="D135" s="227" t="s">
         <v>80</v>
       </c>
-      <c r="E135" s="167"/>
-      <c r="F135" s="167"/>
-      <c r="G135" s="167"/>
-      <c r="H135" s="167"/>
-      <c r="I135" s="167"/>
-      <c r="J135" s="168"/>
-      <c r="K135" s="162"/>
-      <c r="L135" s="162"/>
-    </row>
-    <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E135" s="228"/>
+      <c r="F135" s="228"/>
+      <c r="G135" s="228"/>
+      <c r="H135" s="228"/>
+      <c r="I135" s="228"/>
+      <c r="J135" s="229"/>
+      <c r="K135" s="226"/>
+      <c r="L135" s="226"/>
+    </row>
+    <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="124">
         <v>6</v>
       </c>
       <c r="B136" s="124"/>
       <c r="C136" s="126"/>
-      <c r="D136" s="166" t="s">
+      <c r="D136" s="227" t="s">
         <v>81</v>
       </c>
-      <c r="E136" s="167"/>
-      <c r="F136" s="167"/>
-      <c r="G136" s="167"/>
-      <c r="H136" s="167"/>
-      <c r="I136" s="167"/>
-      <c r="J136" s="168"/>
-      <c r="K136" s="162"/>
-      <c r="L136" s="162"/>
-    </row>
-    <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E136" s="228"/>
+      <c r="F136" s="228"/>
+      <c r="G136" s="228"/>
+      <c r="H136" s="228"/>
+      <c r="I136" s="228"/>
+      <c r="J136" s="229"/>
+      <c r="K136" s="226"/>
+      <c r="L136" s="226"/>
+    </row>
+    <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="124">
         <v>7</v>
       </c>
       <c r="B137" s="124"/>
       <c r="C137" s="126"/>
-      <c r="D137" s="166" t="s">
+      <c r="D137" s="227" t="s">
         <v>82</v>
       </c>
-      <c r="E137" s="167"/>
-      <c r="F137" s="167"/>
-      <c r="G137" s="167"/>
-      <c r="H137" s="167"/>
-      <c r="I137" s="167"/>
-      <c r="J137" s="168"/>
-      <c r="K137" s="162"/>
-      <c r="L137" s="162"/>
-    </row>
-    <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E137" s="228"/>
+      <c r="F137" s="228"/>
+      <c r="G137" s="228"/>
+      <c r="H137" s="228"/>
+      <c r="I137" s="228"/>
+      <c r="J137" s="229"/>
+      <c r="K137" s="226"/>
+      <c r="L137" s="226"/>
+    </row>
+    <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="124">
         <v>8</v>
       </c>
       <c r="B138" s="124"/>
       <c r="C138" s="126"/>
-      <c r="D138" s="159" t="s">
-        <v>111</v>
-      </c>
-      <c r="E138" s="160"/>
-      <c r="F138" s="160"/>
-      <c r="G138" s="160"/>
-      <c r="H138" s="160"/>
-      <c r="I138" s="160"/>
-      <c r="J138" s="161"/>
-      <c r="K138" s="169"/>
-      <c r="L138" s="170"/>
-    </row>
-    <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D138" s="253" t="s">
+        <v>109</v>
+      </c>
+      <c r="E138" s="254"/>
+      <c r="F138" s="254"/>
+      <c r="G138" s="254"/>
+      <c r="H138" s="254"/>
+      <c r="I138" s="254"/>
+      <c r="J138" s="255"/>
+      <c r="K138" s="259"/>
+      <c r="L138" s="260"/>
+    </row>
+    <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="124">
         <v>9</v>
       </c>
       <c r="B139" s="124"/>
       <c r="C139" s="126"/>
-      <c r="D139" s="159" t="s">
+      <c r="D139" s="253" t="s">
         <v>83</v>
       </c>
-      <c r="E139" s="160"/>
-      <c r="F139" s="160"/>
-      <c r="G139" s="160"/>
-      <c r="H139" s="160"/>
-      <c r="I139" s="160"/>
-      <c r="J139" s="161"/>
-      <c r="K139" s="162"/>
-      <c r="L139" s="162"/>
-    </row>
-    <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E139" s="254"/>
+      <c r="F139" s="254"/>
+      <c r="G139" s="254"/>
+      <c r="H139" s="254"/>
+      <c r="I139" s="254"/>
+      <c r="J139" s="255"/>
+      <c r="K139" s="226"/>
+      <c r="L139" s="226"/>
+    </row>
+    <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="124">
         <v>10</v>
       </c>
       <c r="B140" s="124"/>
       <c r="C140" s="126"/>
-      <c r="D140" s="159" t="s">
+      <c r="D140" s="253" t="s">
         <v>84</v>
       </c>
-      <c r="E140" s="160"/>
-      <c r="F140" s="160"/>
-      <c r="G140" s="160"/>
-      <c r="H140" s="160"/>
-      <c r="I140" s="160"/>
-      <c r="J140" s="161"/>
-      <c r="K140" s="162"/>
-      <c r="L140" s="162"/>
-    </row>
-    <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E140" s="254"/>
+      <c r="F140" s="254"/>
+      <c r="G140" s="254"/>
+      <c r="H140" s="254"/>
+      <c r="I140" s="254"/>
+      <c r="J140" s="255"/>
+      <c r="K140" s="226"/>
+      <c r="L140" s="226"/>
+    </row>
+    <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="124">
         <v>11</v>
       </c>
       <c r="B141" s="124"/>
       <c r="C141" s="126"/>
-      <c r="D141" s="163" t="s">
+      <c r="D141" s="256" t="s">
         <v>85</v>
       </c>
-      <c r="E141" s="164"/>
-      <c r="F141" s="164"/>
-      <c r="G141" s="164"/>
-      <c r="H141" s="164"/>
-      <c r="I141" s="164"/>
-      <c r="J141" s="165"/>
-      <c r="K141" s="162"/>
-      <c r="L141" s="162"/>
-    </row>
-    <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="61.5" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="E141" s="257"/>
+      <c r="F141" s="257"/>
+      <c r="G141" s="257"/>
+      <c r="H141" s="257"/>
+      <c r="I141" s="257"/>
+      <c r="J141" s="258"/>
+      <c r="K141" s="226"/>
+      <c r="L141" s="226"/>
+    </row>
+    <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="168">
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:K16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D140:J140"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="D141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="D139:J139"/>
+    <mergeCell ref="K139:L139"/>
+    <mergeCell ref="D134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="D136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:J130"/>
+    <mergeCell ref="K129:L130"/>
+    <mergeCell ref="F88:J88"/>
+    <mergeCell ref="M88:R88"/>
+    <mergeCell ref="M95:R95"/>
+    <mergeCell ref="M96:R96"/>
+    <mergeCell ref="M97:R97"/>
+    <mergeCell ref="M98:R98"/>
+    <mergeCell ref="M99:R99"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="D126:I126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="M87:R87"/>
+    <mergeCell ref="M73:R73"/>
+    <mergeCell ref="F75:K75"/>
+    <mergeCell ref="M75:R75"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="O78:R78"/>
+    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="M83:R83"/>
+    <mergeCell ref="M84:R84"/>
+    <mergeCell ref="M85:R85"/>
+    <mergeCell ref="M86:R86"/>
+    <mergeCell ref="M72:R72"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="Q18:Q53"/>
+    <mergeCell ref="B52:C53"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C63:K64"/>
+    <mergeCell ref="M71:R71"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="B38:C39"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="K18:K19"/>
@@ -6123,131 +6185,25 @@
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D48:E48"/>
-    <mergeCell ref="M72:R72"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="Q18:Q53"/>
-    <mergeCell ref="B52:C53"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="C63:K64"/>
-    <mergeCell ref="M71:R71"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M87:R87"/>
-    <mergeCell ref="M73:R73"/>
-    <mergeCell ref="F75:K75"/>
-    <mergeCell ref="M75:R75"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="O78:R78"/>
-    <mergeCell ref="O81:R81"/>
-    <mergeCell ref="M83:R83"/>
-    <mergeCell ref="M84:R84"/>
-    <mergeCell ref="M85:R85"/>
-    <mergeCell ref="M86:R86"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:J130"/>
-    <mergeCell ref="K129:L130"/>
-    <mergeCell ref="F88:J88"/>
-    <mergeCell ref="M88:R88"/>
-    <mergeCell ref="M95:R95"/>
-    <mergeCell ref="M96:R96"/>
-    <mergeCell ref="M97:R97"/>
-    <mergeCell ref="M98:R98"/>
-    <mergeCell ref="M99:R99"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="D141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="D139:J139"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="D134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="D136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:K16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
   </mergeCells>
   <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A87795-5ADA-44A3-9E43-EDC74F72EE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE93C46-1321-4174-9BAA-D7D7EF81F9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5550" yWindow="1020" windowWidth="22500" windowHeight="11790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim" sheetId="92" r:id="rId1"/>
@@ -400,9 +400,6 @@
     <t xml:space="preserve">(TANDATANGAN )   </t>
   </si>
   <si>
-    <t>LEBIHAN JAM BERTUGAS KUMPULAN</t>
-  </si>
-  <si>
     <t>RUJUK JADUAL DI LAMPIRAN</t>
   </si>
   <si>
@@ -413,6 +410,9 @@
   </si>
   <si>
     <t>BULAN</t>
+  </si>
+  <si>
+    <t>LEBIHAN JAM BERTUGAS</t>
   </si>
 </sst>
 </file>
@@ -433,7 +433,7 @@
     <numFmt numFmtId="174" formatCode="0.00_ ;\-0.00\ "/>
     <numFmt numFmtId="175" formatCode="[$-14409]dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,6 +707,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1455,7 +1462,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2016,6 +2023,44 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2168,18 +2213,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2246,18 +2279,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -2541,13 +2562,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>488950</xdr:colOff>
+      <xdr:colOff>469900</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
@@ -2564,8 +2585,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13074650" y="3403600"/>
-          <a:ext cx="463550" cy="6724650"/>
+          <a:off x="11845925" y="3743325"/>
+          <a:ext cx="463550" cy="6451600"/>
         </a:xfrm>
         <a:prstGeom prst="rightBrace">
           <a:avLst>
@@ -3004,20 +3025,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
-      <c r="L1" s="164"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
@@ -3025,26 +3046,26 @@
       <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
-      <c r="L2" s="164"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="151"/>
-      <c r="R2" s="151"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
@@ -3065,38 +3086,38 @@
       <c r="R3" s="9"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="177" t="s">
+      <c r="A4" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="177"/>
-      <c r="C4" s="177"/>
-      <c r="D4" s="177"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="177"/>
-      <c r="H4" s="177"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="177"/>
-      <c r="K4" s="177"/>
-      <c r="L4" s="177"/>
+      <c r="B4" s="187"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="187"/>
+      <c r="L4" s="187"/>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="178"/>
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="178"/>
-      <c r="G5" s="178"/>
-      <c r="H5" s="178"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="178"/>
-      <c r="L5" s="178"/>
+      <c r="A5" s="188"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="188"/>
+      <c r="L5" s="188"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3105,20 +3126,20 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="179" t="s">
+      <c r="A6" s="189" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="179"/>
-      <c r="C6" s="179"/>
-      <c r="D6" s="179"/>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="179"/>
-      <c r="H6" s="179"/>
-      <c r="I6" s="179"/>
-      <c r="J6" s="179"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="179"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
       <c r="O6" s="16"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -3173,9 +3194,9 @@
       <c r="B9" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="180"/>
-      <c r="D9" s="180"/>
-      <c r="E9" s="180"/>
+      <c r="C9" s="190"/>
+      <c r="D9" s="190"/>
+      <c r="E9" s="190"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="19" t="s">
@@ -3252,7 +3273,7 @@
       </c>
       <c r="L11" s="138"/>
       <c r="M11" s="144" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="24"/>
@@ -3283,7 +3304,7 @@
       </c>
       <c r="L12" s="138"/>
       <c r="M12" s="145" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="24"/>
@@ -3324,41 +3345,41 @@
       <c r="A15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="165" t="s">
+      <c r="B15" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="165"/>
-      <c r="D15" s="167" t="s">
+      <c r="C15" s="175"/>
+      <c r="D15" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="168"/>
-      <c r="F15" s="168" t="s">
+      <c r="E15" s="178"/>
+      <c r="F15" s="178" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="173" t="s">
+      <c r="G15" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="173"/>
-      <c r="I15" s="173"/>
-      <c r="J15" s="173"/>
-      <c r="K15" s="174"/>
-      <c r="L15" s="154" t="s">
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="184"/>
+      <c r="L15" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="157" t="s">
+      <c r="M15" s="167" t="s">
         <v>59</v>
       </c>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="161"/>
-      <c r="P15" s="157" t="s">
+      <c r="O15" s="171"/>
+      <c r="P15" s="167" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" s="181" t="s">
+      <c r="Q15" s="191" t="s">
         <v>62</v>
       </c>
-      <c r="R15" s="157" t="s">
+      <c r="R15" s="167" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3366,23 +3387,23 @@
       <c r="A16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="166"/>
-      <c r="C16" s="166"/>
-      <c r="D16" s="169"/>
-      <c r="E16" s="170"/>
-      <c r="F16" s="171"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="175"/>
-      <c r="I16" s="175"/>
-      <c r="J16" s="175"/>
-      <c r="K16" s="176"/>
-      <c r="L16" s="155"/>
-      <c r="M16" s="158"/>
-      <c r="N16" s="162"/>
-      <c r="O16" s="163"/>
-      <c r="P16" s="158"/>
-      <c r="Q16" s="182"/>
-      <c r="R16" s="158"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="186"/>
+      <c r="L16" s="165"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="173"/>
+      <c r="P16" s="168"/>
+      <c r="Q16" s="192"/>
+      <c r="R16" s="168"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
@@ -3400,7 +3421,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="172"/>
+      <c r="F17" s="182"/>
       <c r="G17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3416,156 +3437,144 @@
       <c r="K17" s="37">
         <v>2</v>
       </c>
-      <c r="L17" s="156"/>
-      <c r="M17" s="159"/>
+      <c r="L17" s="166"/>
+      <c r="M17" s="169"/>
       <c r="N17" s="38" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="159"/>
-      <c r="Q17" s="183"/>
-      <c r="R17" s="159"/>
+      <c r="P17" s="169"/>
+      <c r="Q17" s="193"/>
+      <c r="R17" s="169"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="195" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="175"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="196"/>
-      <c r="F18" s="200"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152">
+      <c r="A18" s="202"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="207"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="162">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="152"/>
-      <c r="J18" s="152"/>
-      <c r="K18" s="186"/>
-      <c r="L18" s="188" t="s">
-        <v>108</v>
-      </c>
-      <c r="M18" s="147" t="str">
-        <f>IF(ISBLANK(A20),"",A20)</f>
-        <v/>
-      </c>
-      <c r="N18" s="208" t="str">
-        <f>IF(ISBLANK(D20),"",D20)</f>
-        <v/>
-      </c>
-      <c r="O18" s="209"/>
-      <c r="P18" s="190"/>
-      <c r="Q18" s="211"/>
-      <c r="R18" s="149"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="162"/>
+      <c r="K18" s="196"/>
+      <c r="L18" s="198" t="s">
+        <v>107</v>
+      </c>
+      <c r="M18" s="147"/>
+      <c r="N18" s="215"/>
+      <c r="O18" s="216"/>
+      <c r="P18" s="151"/>
+      <c r="Q18" s="153"/>
+      <c r="R18" s="155" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="197"/>
-      <c r="B19" s="198"/>
-      <c r="C19" s="198"/>
-      <c r="D19" s="198"/>
-      <c r="E19" s="199"/>
-      <c r="F19" s="201"/>
-      <c r="G19" s="153"/>
-      <c r="H19" s="153"/>
-      <c r="I19" s="153"/>
-      <c r="J19" s="153"/>
-      <c r="K19" s="187"/>
-      <c r="L19" s="189"/>
-      <c r="M19" s="148" t="str">
-        <f>A21</f>
-        <v/>
-      </c>
-      <c r="N19" s="206" t="str">
-        <f>IF(ISBLANK(D21),"",D21)</f>
-        <v/>
-      </c>
-      <c r="O19" s="207"/>
-      <c r="P19" s="191"/>
-      <c r="Q19" s="212"/>
-      <c r="R19" s="150"/>
+      <c r="A19" s="204"/>
+      <c r="B19" s="205"/>
+      <c r="C19" s="205"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="163"/>
+      <c r="I19" s="163"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="197"/>
+      <c r="L19" s="199"/>
+      <c r="M19" s="148"/>
+      <c r="N19" s="213"/>
+      <c r="O19" s="214"/>
+      <c r="P19" s="152"/>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="156"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="142"/>
-      <c r="B20" s="185"/>
-      <c r="C20" s="185"/>
-      <c r="D20" s="204"/>
-      <c r="E20" s="205"/>
+      <c r="B20" s="195"/>
+      <c r="C20" s="195"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="212"/>
       <c r="F20" s="139"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
       <c r="I20" s="129"/>
       <c r="J20" s="129"/>
       <c r="K20" s="129"/>
-      <c r="L20" s="193"/>
+      <c r="L20" s="200"/>
       <c r="M20" s="147" t="str">
-        <f>IF(ISBLANK(A22),"",A22)</f>
-        <v/>
-      </c>
-      <c r="N20" s="208" t="str">
-        <f t="shared" ref="N20:N53" si="0">IF(ISBLANK(D22),"",D22)</f>
-        <v/>
-      </c>
-      <c r="O20" s="209"/>
-      <c r="P20" s="191"/>
-      <c r="Q20" s="212"/>
+        <f>IF(ISBLANK(A20),"",A20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="215" t="str">
+        <f>IF(ISBLANK(D20),"",D20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="216"/>
+      <c r="P20" s="157"/>
+      <c r="Q20" s="159"/>
       <c r="R20" s="149"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
-        <f t="shared" ref="A21" si="1">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
-        <v/>
-      </c>
-      <c r="B21" s="185"/>
-      <c r="C21" s="185"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="203"/>
+        <f t="shared" ref="A21" si="0">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
+        <v/>
+      </c>
+      <c r="B21" s="195"/>
+      <c r="C21" s="195"/>
+      <c r="D21" s="209"/>
+      <c r="E21" s="210"/>
       <c r="F21" s="141"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
       <c r="I21" s="127"/>
       <c r="J21" s="127"/>
       <c r="K21" s="128"/>
-      <c r="L21" s="193"/>
+      <c r="L21" s="200"/>
       <c r="M21" s="148" t="str">
-        <f>A23</f>
-        <v/>
-      </c>
-      <c r="N21" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O21" s="207"/>
-      <c r="P21" s="191"/>
-      <c r="Q21" s="212"/>
+        <f>A21</f>
+        <v/>
+      </c>
+      <c r="N21" s="213" t="str">
+        <f>IF(ISBLANK(D21),"",D21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="214"/>
+      <c r="P21" s="157"/>
+      <c r="Q21" s="159"/>
       <c r="R21" s="150"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="134"/>
-      <c r="B22" s="184"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="204"/>
-      <c r="E22" s="205"/>
+      <c r="B22" s="194"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="211"/>
+      <c r="E22" s="212"/>
       <c r="F22" s="139"/>
       <c r="G22" s="129"/>
       <c r="H22" s="129"/>
       <c r="I22" s="129"/>
       <c r="J22" s="129"/>
       <c r="K22" s="129"/>
-      <c r="L22" s="193"/>
+      <c r="L22" s="200"/>
       <c r="M22" s="147" t="str">
-        <f t="shared" ref="M22" si="2">IF(ISBLANK(A24),"",A24)</f>
-        <v/>
-      </c>
-      <c r="N22" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O22" s="209"/>
-      <c r="P22" s="191"/>
-      <c r="Q22" s="212"/>
+        <f t="shared" ref="M22" si="1">IF(ISBLANK(A22),"",A22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="215" t="str">
+        <f t="shared" ref="N22:N53" si="2">IF(ISBLANK(D22),"",D22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="216"/>
+      <c r="P22" s="157"/>
+      <c r="Q22" s="159"/>
       <c r="R22" s="149"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3573,54 +3582,54 @@
         <f t="shared" ref="A23:A25" si="3">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="185"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="203"/>
+      <c r="B23" s="195"/>
+      <c r="C23" s="195"/>
+      <c r="D23" s="209"/>
+      <c r="E23" s="210"/>
       <c r="F23" s="141"/>
       <c r="G23" s="127"/>
       <c r="H23" s="127"/>
       <c r="I23" s="127"/>
       <c r="J23" s="127"/>
       <c r="K23" s="128"/>
-      <c r="L23" s="193"/>
+      <c r="L23" s="200"/>
       <c r="M23" s="148" t="str">
-        <f t="shared" ref="M23" si="4">A25</f>
-        <v/>
-      </c>
-      <c r="N23" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O23" s="207"/>
-      <c r="P23" s="191"/>
-      <c r="Q23" s="212"/>
+        <f t="shared" ref="M23" si="4">A23</f>
+        <v/>
+      </c>
+      <c r="N23" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O23" s="214"/>
+      <c r="P23" s="157"/>
+      <c r="Q23" s="159"/>
       <c r="R23" s="150"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="134"/>
-      <c r="B24" s="184"/>
-      <c r="C24" s="184"/>
-      <c r="D24" s="204"/>
-      <c r="E24" s="205"/>
+      <c r="B24" s="194"/>
+      <c r="C24" s="194"/>
+      <c r="D24" s="211"/>
+      <c r="E24" s="212"/>
       <c r="F24" s="139"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
       <c r="I24" s="129"/>
       <c r="J24" s="129"/>
       <c r="K24" s="129"/>
-      <c r="L24" s="193"/>
+      <c r="L24" s="200"/>
       <c r="M24" s="147" t="str">
-        <f t="shared" ref="M24" si="5">IF(ISBLANK(A26),"",A26)</f>
-        <v/>
-      </c>
-      <c r="N24" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O24" s="209"/>
-      <c r="P24" s="191"/>
-      <c r="Q24" s="212"/>
+        <f t="shared" ref="M24" si="5">IF(ISBLANK(A24),"",A24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O24" s="216"/>
+      <c r="P24" s="157"/>
+      <c r="Q24" s="159"/>
       <c r="R24" s="149"/>
     </row>
     <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3628,54 +3637,54 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B25" s="185"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="203"/>
+      <c r="B25" s="195"/>
+      <c r="C25" s="195"/>
+      <c r="D25" s="209"/>
+      <c r="E25" s="210"/>
       <c r="F25" s="141"/>
       <c r="G25" s="127"/>
       <c r="H25" s="127"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
       <c r="K25" s="128"/>
-      <c r="L25" s="193"/>
+      <c r="L25" s="200"/>
       <c r="M25" s="148" t="str">
-        <f t="shared" ref="M25" si="6">A27</f>
-        <v/>
-      </c>
-      <c r="N25" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O25" s="207"/>
-      <c r="P25" s="191"/>
-      <c r="Q25" s="212"/>
+        <f t="shared" ref="M25" si="6">A25</f>
+        <v/>
+      </c>
+      <c r="N25" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O25" s="214"/>
+      <c r="P25" s="157"/>
+      <c r="Q25" s="159"/>
       <c r="R25" s="150"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="134"/>
-      <c r="B26" s="184"/>
-      <c r="C26" s="184"/>
-      <c r="D26" s="204"/>
-      <c r="E26" s="205"/>
+      <c r="B26" s="194"/>
+      <c r="C26" s="194"/>
+      <c r="D26" s="211"/>
+      <c r="E26" s="212"/>
       <c r="F26" s="139"/>
       <c r="G26" s="129"/>
       <c r="H26" s="129"/>
       <c r="I26" s="129"/>
       <c r="J26" s="129"/>
       <c r="K26" s="129"/>
-      <c r="L26" s="193"/>
+      <c r="L26" s="200"/>
       <c r="M26" s="147" t="str">
-        <f t="shared" ref="M26" si="7">IF(ISBLANK(A28),"",A28)</f>
-        <v/>
-      </c>
-      <c r="N26" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O26" s="209"/>
-      <c r="P26" s="191"/>
-      <c r="Q26" s="212"/>
+        <f t="shared" ref="M26" si="7">IF(ISBLANK(A26),"",A26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O26" s="216"/>
+      <c r="P26" s="157"/>
+      <c r="Q26" s="159"/>
       <c r="R26" s="149"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3683,54 +3692,54 @@
         <f t="shared" ref="A27" si="8">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="185"/>
-      <c r="C27" s="185"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="203"/>
+      <c r="B27" s="195"/>
+      <c r="C27" s="195"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="210"/>
       <c r="F27" s="141"/>
       <c r="G27" s="127"/>
       <c r="H27" s="127"/>
       <c r="I27" s="127"/>
       <c r="J27" s="127"/>
       <c r="K27" s="128"/>
-      <c r="L27" s="193"/>
+      <c r="L27" s="200"/>
       <c r="M27" s="148" t="str">
-        <f t="shared" ref="M27" si="9">A29</f>
-        <v/>
-      </c>
-      <c r="N27" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O27" s="207"/>
-      <c r="P27" s="191"/>
-      <c r="Q27" s="212"/>
+        <f t="shared" ref="M27" si="9">A27</f>
+        <v/>
+      </c>
+      <c r="N27" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O27" s="214"/>
+      <c r="P27" s="157"/>
+      <c r="Q27" s="159"/>
       <c r="R27" s="150"/>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="135"/>
-      <c r="B28" s="184"/>
-      <c r="C28" s="184"/>
-      <c r="D28" s="204"/>
-      <c r="E28" s="205"/>
+      <c r="B28" s="194"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="211"/>
+      <c r="E28" s="212"/>
       <c r="F28" s="139"/>
       <c r="G28" s="129"/>
       <c r="H28" s="129"/>
       <c r="I28" s="129"/>
       <c r="J28" s="129"/>
       <c r="K28" s="129"/>
-      <c r="L28" s="193"/>
+      <c r="L28" s="200"/>
       <c r="M28" s="147" t="str">
-        <f t="shared" ref="M28" si="10">IF(ISBLANK(A30),"",A30)</f>
-        <v/>
-      </c>
-      <c r="N28" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O28" s="209"/>
-      <c r="P28" s="191"/>
-      <c r="Q28" s="212"/>
+        <f t="shared" ref="M28" si="10">IF(ISBLANK(A28),"",A28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O28" s="216"/>
+      <c r="P28" s="157"/>
+      <c r="Q28" s="159"/>
       <c r="R28" s="149"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3738,54 +3747,54 @@
         <f t="shared" ref="A29" si="11">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="185"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="203"/>
+      <c r="B29" s="195"/>
+      <c r="C29" s="195"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="210"/>
       <c r="F29" s="141"/>
       <c r="G29" s="127"/>
       <c r="H29" s="127"/>
       <c r="I29" s="127"/>
       <c r="J29" s="129"/>
       <c r="K29" s="128"/>
-      <c r="L29" s="193"/>
+      <c r="L29" s="200"/>
       <c r="M29" s="148" t="str">
-        <f t="shared" ref="M29" si="12">A31</f>
-        <v/>
-      </c>
-      <c r="N29" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O29" s="207"/>
-      <c r="P29" s="191"/>
-      <c r="Q29" s="212"/>
+        <f t="shared" ref="M29" si="12">A29</f>
+        <v/>
+      </c>
+      <c r="N29" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O29" s="214"/>
+      <c r="P29" s="157"/>
+      <c r="Q29" s="159"/>
       <c r="R29" s="150"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="134"/>
-      <c r="B30" s="184"/>
-      <c r="C30" s="184"/>
-      <c r="D30" s="204"/>
-      <c r="E30" s="205"/>
+      <c r="B30" s="194"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="211"/>
+      <c r="E30" s="212"/>
       <c r="F30" s="139"/>
       <c r="G30" s="129"/>
       <c r="H30" s="129"/>
       <c r="I30" s="140"/>
       <c r="J30" s="143"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="193"/>
+      <c r="L30" s="200"/>
       <c r="M30" s="147" t="str">
-        <f t="shared" ref="M30" si="13">IF(ISBLANK(A32),"",A32)</f>
-        <v/>
-      </c>
-      <c r="N30" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O30" s="209"/>
-      <c r="P30" s="191"/>
-      <c r="Q30" s="212"/>
+        <f t="shared" ref="M30" si="13">IF(ISBLANK(A30),"",A30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O30" s="216"/>
+      <c r="P30" s="157"/>
+      <c r="Q30" s="159"/>
       <c r="R30" s="149"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3793,54 +3802,54 @@
         <f t="shared" ref="A31" si="14">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="185"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="203"/>
+      <c r="B31" s="195"/>
+      <c r="C31" s="195"/>
+      <c r="D31" s="209"/>
+      <c r="E31" s="210"/>
       <c r="F31" s="141"/>
       <c r="G31" s="127"/>
       <c r="H31" s="127"/>
       <c r="I31" s="127"/>
       <c r="J31" s="127"/>
       <c r="K31" s="128"/>
-      <c r="L31" s="193"/>
+      <c r="L31" s="200"/>
       <c r="M31" s="148" t="str">
-        <f t="shared" ref="M31" si="15">A33</f>
-        <v/>
-      </c>
-      <c r="N31" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O31" s="207"/>
-      <c r="P31" s="191"/>
-      <c r="Q31" s="212"/>
+        <f t="shared" ref="M31" si="15">A31</f>
+        <v/>
+      </c>
+      <c r="N31" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O31" s="214"/>
+      <c r="P31" s="157"/>
+      <c r="Q31" s="159"/>
       <c r="R31" s="150"/>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="134"/>
-      <c r="B32" s="184"/>
-      <c r="C32" s="184"/>
-      <c r="D32" s="204"/>
-      <c r="E32" s="205"/>
+      <c r="B32" s="194"/>
+      <c r="C32" s="194"/>
+      <c r="D32" s="211"/>
+      <c r="E32" s="212"/>
       <c r="F32" s="139"/>
       <c r="G32" s="129"/>
       <c r="H32" s="129"/>
       <c r="I32" s="129"/>
       <c r="J32" s="129"/>
       <c r="K32" s="129"/>
-      <c r="L32" s="193"/>
+      <c r="L32" s="200"/>
       <c r="M32" s="147" t="str">
-        <f t="shared" ref="M32" si="16">IF(ISBLANK(A34),"",A34)</f>
-        <v/>
-      </c>
-      <c r="N32" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O32" s="209"/>
-      <c r="P32" s="191"/>
-      <c r="Q32" s="212"/>
+        <f t="shared" ref="M32" si="16">IF(ISBLANK(A32),"",A32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O32" s="216"/>
+      <c r="P32" s="157"/>
+      <c r="Q32" s="159"/>
       <c r="R32" s="149"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3848,54 +3857,54 @@
         <f t="shared" ref="A33" si="17">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="185"/>
-      <c r="C33" s="185"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="203"/>
+      <c r="B33" s="195"/>
+      <c r="C33" s="195"/>
+      <c r="D33" s="209"/>
+      <c r="E33" s="210"/>
       <c r="F33" s="141"/>
       <c r="G33" s="127"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
       <c r="J33" s="127"/>
       <c r="K33" s="128"/>
-      <c r="L33" s="193"/>
+      <c r="L33" s="200"/>
       <c r="M33" s="148" t="str">
-        <f t="shared" ref="M33" si="18">A35</f>
-        <v/>
-      </c>
-      <c r="N33" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O33" s="207"/>
-      <c r="P33" s="191"/>
-      <c r="Q33" s="212"/>
+        <f t="shared" ref="M33" si="18">A33</f>
+        <v/>
+      </c>
+      <c r="N33" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O33" s="214"/>
+      <c r="P33" s="157"/>
+      <c r="Q33" s="159"/>
       <c r="R33" s="150"/>
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="134"/>
-      <c r="B34" s="184"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="205"/>
+      <c r="B34" s="194"/>
+      <c r="C34" s="194"/>
+      <c r="D34" s="211"/>
+      <c r="E34" s="212"/>
       <c r="F34" s="139"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
       <c r="I34" s="129"/>
       <c r="J34" s="129"/>
       <c r="K34" s="129"/>
-      <c r="L34" s="193"/>
+      <c r="L34" s="200"/>
       <c r="M34" s="147" t="str">
-        <f t="shared" ref="M34" si="19">IF(ISBLANK(A36),"",A36)</f>
-        <v/>
-      </c>
-      <c r="N34" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O34" s="209"/>
-      <c r="P34" s="191"/>
-      <c r="Q34" s="212"/>
+        <f t="shared" ref="M34" si="19">IF(ISBLANK(A34),"",A34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O34" s="216"/>
+      <c r="P34" s="157"/>
+      <c r="Q34" s="159"/>
       <c r="R34" s="149"/>
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3903,54 +3912,54 @@
         <f t="shared" ref="A35" si="20">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="185"/>
-      <c r="C35" s="185"/>
-      <c r="D35" s="202"/>
-      <c r="E35" s="203"/>
+      <c r="B35" s="195"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="209"/>
+      <c r="E35" s="210"/>
       <c r="F35" s="141"/>
       <c r="G35" s="127"/>
       <c r="H35" s="127"/>
       <c r="I35" s="127"/>
       <c r="J35" s="127"/>
       <c r="K35" s="128"/>
-      <c r="L35" s="193"/>
+      <c r="L35" s="200"/>
       <c r="M35" s="148" t="str">
-        <f t="shared" ref="M35" si="21">A37</f>
-        <v/>
-      </c>
-      <c r="N35" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O35" s="207"/>
-      <c r="P35" s="191"/>
-      <c r="Q35" s="212"/>
+        <f t="shared" ref="M35" si="21">A35</f>
+        <v/>
+      </c>
+      <c r="N35" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O35" s="214"/>
+      <c r="P35" s="157"/>
+      <c r="Q35" s="159"/>
       <c r="R35" s="150"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134"/>
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="204"/>
-      <c r="E36" s="205"/>
+      <c r="B36" s="194"/>
+      <c r="C36" s="194"/>
+      <c r="D36" s="211"/>
+      <c r="E36" s="212"/>
       <c r="F36" s="139"/>
       <c r="G36" s="129"/>
       <c r="H36" s="129"/>
       <c r="I36" s="129"/>
       <c r="J36" s="129"/>
       <c r="K36" s="129"/>
-      <c r="L36" s="193"/>
+      <c r="L36" s="200"/>
       <c r="M36" s="147" t="str">
-        <f t="shared" ref="M36" si="22">IF(ISBLANK(A38),"",A38)</f>
-        <v/>
-      </c>
-      <c r="N36" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O36" s="209"/>
-      <c r="P36" s="191"/>
-      <c r="Q36" s="212"/>
+        <f t="shared" ref="M36" si="22">IF(ISBLANK(A36),"",A36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O36" s="216"/>
+      <c r="P36" s="157"/>
+      <c r="Q36" s="159"/>
       <c r="R36" s="149"/>
     </row>
     <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,54 +3967,54 @@
         <f t="shared" ref="A37" si="23">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="185"/>
-      <c r="C37" s="185"/>
-      <c r="D37" s="202"/>
-      <c r="E37" s="203"/>
+      <c r="B37" s="195"/>
+      <c r="C37" s="195"/>
+      <c r="D37" s="209"/>
+      <c r="E37" s="210"/>
       <c r="F37" s="141"/>
       <c r="G37" s="127"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
       <c r="J37" s="127"/>
       <c r="K37" s="128"/>
-      <c r="L37" s="193"/>
+      <c r="L37" s="200"/>
       <c r="M37" s="148" t="str">
-        <f t="shared" ref="M37" si="24">A39</f>
-        <v/>
-      </c>
-      <c r="N37" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O37" s="207"/>
-      <c r="P37" s="191"/>
-      <c r="Q37" s="212"/>
+        <f t="shared" ref="M37" si="24">A37</f>
+        <v/>
+      </c>
+      <c r="N37" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O37" s="214"/>
+      <c r="P37" s="157"/>
+      <c r="Q37" s="159"/>
       <c r="R37" s="150"/>
     </row>
     <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="134"/>
-      <c r="B38" s="184"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="204"/>
-      <c r="E38" s="205"/>
+      <c r="B38" s="194"/>
+      <c r="C38" s="194"/>
+      <c r="D38" s="211"/>
+      <c r="E38" s="212"/>
       <c r="F38" s="139"/>
       <c r="G38" s="129"/>
       <c r="H38" s="129"/>
       <c r="I38" s="129"/>
       <c r="J38" s="129"/>
       <c r="K38" s="129"/>
-      <c r="L38" s="193"/>
+      <c r="L38" s="200"/>
       <c r="M38" s="147" t="str">
-        <f t="shared" ref="M38" si="25">IF(ISBLANK(A40),"",A40)</f>
-        <v/>
-      </c>
-      <c r="N38" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O38" s="209"/>
-      <c r="P38" s="191"/>
-      <c r="Q38" s="212"/>
+        <f t="shared" ref="M38" si="25">IF(ISBLANK(A38),"",A38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O38" s="216"/>
+      <c r="P38" s="157"/>
+      <c r="Q38" s="159"/>
       <c r="R38" s="149"/>
     </row>
     <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4013,54 +4022,54 @@
         <f t="shared" ref="A39" si="26">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="185"/>
-      <c r="C39" s="185"/>
-      <c r="D39" s="202"/>
-      <c r="E39" s="203"/>
+      <c r="B39" s="195"/>
+      <c r="C39" s="195"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="210"/>
       <c r="F39" s="141"/>
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
       <c r="K39" s="128"/>
-      <c r="L39" s="193"/>
+      <c r="L39" s="200"/>
       <c r="M39" s="148" t="str">
-        <f t="shared" ref="M39" si="27">A41</f>
-        <v/>
-      </c>
-      <c r="N39" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O39" s="207"/>
-      <c r="P39" s="191"/>
-      <c r="Q39" s="212"/>
+        <f t="shared" ref="M39" si="27">A39</f>
+        <v/>
+      </c>
+      <c r="N39" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O39" s="214"/>
+      <c r="P39" s="157"/>
+      <c r="Q39" s="159"/>
       <c r="R39" s="150"/>
     </row>
     <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="134"/>
-      <c r="B40" s="184"/>
-      <c r="C40" s="184"/>
-      <c r="D40" s="204"/>
-      <c r="E40" s="205"/>
+      <c r="B40" s="194"/>
+      <c r="C40" s="194"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="212"/>
       <c r="F40" s="139"/>
       <c r="G40" s="129"/>
       <c r="H40" s="129"/>
       <c r="I40" s="129"/>
       <c r="J40" s="129"/>
       <c r="K40" s="129"/>
-      <c r="L40" s="193"/>
+      <c r="L40" s="200"/>
       <c r="M40" s="147" t="str">
-        <f t="shared" ref="M40" si="28">IF(ISBLANK(A42),"",A42)</f>
-        <v/>
-      </c>
-      <c r="N40" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O40" s="209"/>
-      <c r="P40" s="191"/>
-      <c r="Q40" s="212"/>
+        <f t="shared" ref="M40" si="28">IF(ISBLANK(A40),"",A40)</f>
+        <v/>
+      </c>
+      <c r="N40" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O40" s="216"/>
+      <c r="P40" s="157"/>
+      <c r="Q40" s="159"/>
       <c r="R40" s="149"/>
     </row>
     <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4068,54 +4077,54 @@
         <f t="shared" ref="A41" si="29">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="185"/>
-      <c r="C41" s="185"/>
-      <c r="D41" s="202"/>
-      <c r="E41" s="203"/>
+      <c r="B41" s="195"/>
+      <c r="C41" s="195"/>
+      <c r="D41" s="209"/>
+      <c r="E41" s="210"/>
       <c r="F41" s="141"/>
       <c r="G41" s="127"/>
       <c r="H41" s="127"/>
       <c r="I41" s="127"/>
       <c r="J41" s="127"/>
       <c r="K41" s="128"/>
-      <c r="L41" s="193"/>
+      <c r="L41" s="200"/>
       <c r="M41" s="148" t="str">
-        <f t="shared" ref="M41" si="30">A43</f>
-        <v/>
-      </c>
-      <c r="N41" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O41" s="207"/>
-      <c r="P41" s="191"/>
-      <c r="Q41" s="212"/>
+        <f t="shared" ref="M41" si="30">A41</f>
+        <v/>
+      </c>
+      <c r="N41" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O41" s="214"/>
+      <c r="P41" s="157"/>
+      <c r="Q41" s="159"/>
       <c r="R41" s="150"/>
     </row>
     <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="134"/>
-      <c r="B42" s="184"/>
-      <c r="C42" s="184"/>
-      <c r="D42" s="204"/>
-      <c r="E42" s="205"/>
+      <c r="B42" s="194"/>
+      <c r="C42" s="194"/>
+      <c r="D42" s="211"/>
+      <c r="E42" s="212"/>
       <c r="F42" s="139"/>
       <c r="G42" s="129"/>
       <c r="H42" s="129"/>
       <c r="I42" s="129"/>
       <c r="J42" s="129"/>
       <c r="K42" s="129"/>
-      <c r="L42" s="193"/>
+      <c r="L42" s="200"/>
       <c r="M42" s="147" t="str">
-        <f t="shared" ref="M42" si="31">IF(ISBLANK(A44),"",A44)</f>
-        <v/>
-      </c>
-      <c r="N42" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O42" s="209"/>
-      <c r="P42" s="191"/>
-      <c r="Q42" s="212"/>
+        <f t="shared" ref="M42" si="31">IF(ISBLANK(A42),"",A42)</f>
+        <v/>
+      </c>
+      <c r="N42" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O42" s="216"/>
+      <c r="P42" s="157"/>
+      <c r="Q42" s="159"/>
       <c r="R42" s="149"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4123,54 +4132,54 @@
         <f t="shared" ref="A43" si="32">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="185"/>
-      <c r="C43" s="185"/>
-      <c r="D43" s="202"/>
-      <c r="E43" s="203"/>
+      <c r="B43" s="195"/>
+      <c r="C43" s="195"/>
+      <c r="D43" s="209"/>
+      <c r="E43" s="210"/>
       <c r="F43" s="141"/>
       <c r="G43" s="127"/>
       <c r="H43" s="127"/>
       <c r="I43" s="127"/>
       <c r="J43" s="127"/>
       <c r="K43" s="128"/>
-      <c r="L43" s="193"/>
+      <c r="L43" s="200"/>
       <c r="M43" s="148" t="str">
-        <f t="shared" ref="M43" si="33">A45</f>
-        <v/>
-      </c>
-      <c r="N43" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O43" s="207"/>
-      <c r="P43" s="191"/>
-      <c r="Q43" s="212"/>
+        <f t="shared" ref="M43" si="33">A43</f>
+        <v/>
+      </c>
+      <c r="N43" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O43" s="214"/>
+      <c r="P43" s="157"/>
+      <c r="Q43" s="159"/>
       <c r="R43" s="150"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="134"/>
-      <c r="B44" s="184"/>
-      <c r="C44" s="184"/>
-      <c r="D44" s="204"/>
-      <c r="E44" s="205"/>
+      <c r="B44" s="194"/>
+      <c r="C44" s="194"/>
+      <c r="D44" s="211"/>
+      <c r="E44" s="212"/>
       <c r="F44" s="139"/>
       <c r="G44" s="129"/>
       <c r="H44" s="129"/>
       <c r="I44" s="129"/>
       <c r="J44" s="129"/>
       <c r="K44" s="129"/>
-      <c r="L44" s="193"/>
+      <c r="L44" s="200"/>
       <c r="M44" s="147" t="str">
-        <f t="shared" ref="M44" si="34">IF(ISBLANK(A46),"",A46)</f>
-        <v/>
-      </c>
-      <c r="N44" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O44" s="209"/>
-      <c r="P44" s="191"/>
-      <c r="Q44" s="212"/>
+        <f t="shared" ref="M44" si="34">IF(ISBLANK(A44),"",A44)</f>
+        <v/>
+      </c>
+      <c r="N44" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O44" s="216"/>
+      <c r="P44" s="157"/>
+      <c r="Q44" s="159"/>
       <c r="R44" s="149"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4178,54 +4187,54 @@
         <f t="shared" ref="A45" si="35">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="185"/>
-      <c r="C45" s="185"/>
-      <c r="D45" s="202"/>
-      <c r="E45" s="203"/>
+      <c r="B45" s="195"/>
+      <c r="C45" s="195"/>
+      <c r="D45" s="209"/>
+      <c r="E45" s="210"/>
       <c r="F45" s="141"/>
       <c r="G45" s="127"/>
       <c r="H45" s="127"/>
       <c r="I45" s="127"/>
       <c r="J45" s="127"/>
       <c r="K45" s="128"/>
-      <c r="L45" s="193"/>
+      <c r="L45" s="200"/>
       <c r="M45" s="148" t="str">
-        <f t="shared" ref="M45" si="36">A47</f>
-        <v/>
-      </c>
-      <c r="N45" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O45" s="207"/>
-      <c r="P45" s="191"/>
-      <c r="Q45" s="212"/>
+        <f t="shared" ref="M45" si="36">A45</f>
+        <v/>
+      </c>
+      <c r="N45" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O45" s="214"/>
+      <c r="P45" s="157"/>
+      <c r="Q45" s="159"/>
       <c r="R45" s="150"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="134"/>
-      <c r="B46" s="184"/>
-      <c r="C46" s="184"/>
-      <c r="D46" s="204"/>
-      <c r="E46" s="205"/>
+      <c r="B46" s="194"/>
+      <c r="C46" s="194"/>
+      <c r="D46" s="211"/>
+      <c r="E46" s="212"/>
       <c r="F46" s="139"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
       <c r="I46" s="129"/>
       <c r="J46" s="129"/>
       <c r="K46" s="129"/>
-      <c r="L46" s="193"/>
+      <c r="L46" s="200"/>
       <c r="M46" s="147" t="str">
-        <f t="shared" ref="M46" si="37">IF(ISBLANK(A48),"",A48)</f>
-        <v/>
-      </c>
-      <c r="N46" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O46" s="209"/>
-      <c r="P46" s="191"/>
-      <c r="Q46" s="212"/>
+        <f t="shared" ref="M46" si="37">IF(ISBLANK(A46),"",A46)</f>
+        <v/>
+      </c>
+      <c r="N46" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O46" s="216"/>
+      <c r="P46" s="157"/>
+      <c r="Q46" s="159"/>
       <c r="R46" s="149"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4233,54 +4242,54 @@
         <f t="shared" ref="A47" si="38">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="185"/>
-      <c r="C47" s="185"/>
-      <c r="D47" s="202"/>
-      <c r="E47" s="203"/>
+      <c r="B47" s="195"/>
+      <c r="C47" s="195"/>
+      <c r="D47" s="209"/>
+      <c r="E47" s="210"/>
       <c r="F47" s="141"/>
       <c r="G47" s="127"/>
       <c r="H47" s="127"/>
       <c r="I47" s="127"/>
       <c r="J47" s="127"/>
       <c r="K47" s="128"/>
-      <c r="L47" s="193"/>
+      <c r="L47" s="200"/>
       <c r="M47" s="148" t="str">
-        <f t="shared" ref="M47" si="39">A49</f>
-        <v/>
-      </c>
-      <c r="N47" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O47" s="207"/>
-      <c r="P47" s="191"/>
-      <c r="Q47" s="212"/>
+        <f t="shared" ref="M47" si="39">A47</f>
+        <v/>
+      </c>
+      <c r="N47" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O47" s="214"/>
+      <c r="P47" s="157"/>
+      <c r="Q47" s="159"/>
       <c r="R47" s="150"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="134"/>
-      <c r="B48" s="184"/>
-      <c r="C48" s="184"/>
-      <c r="D48" s="204"/>
-      <c r="E48" s="205"/>
+      <c r="B48" s="194"/>
+      <c r="C48" s="194"/>
+      <c r="D48" s="211"/>
+      <c r="E48" s="212"/>
       <c r="F48" s="139"/>
       <c r="G48" s="129"/>
       <c r="H48" s="129"/>
       <c r="I48" s="129"/>
       <c r="J48" s="129"/>
       <c r="K48" s="129"/>
-      <c r="L48" s="193"/>
+      <c r="L48" s="200"/>
       <c r="M48" s="147" t="str">
-        <f t="shared" ref="M48" si="40">IF(ISBLANK(A50),"",A50)</f>
-        <v/>
-      </c>
-      <c r="N48" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O48" s="209"/>
-      <c r="P48" s="191"/>
-      <c r="Q48" s="212"/>
+        <f t="shared" ref="M48" si="40">IF(ISBLANK(A48),"",A48)</f>
+        <v/>
+      </c>
+      <c r="N48" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O48" s="216"/>
+      <c r="P48" s="157"/>
+      <c r="Q48" s="159"/>
       <c r="R48" s="149"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4288,54 +4297,54 @@
         <f t="shared" ref="A49" si="41">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="185"/>
-      <c r="C49" s="185"/>
-      <c r="D49" s="202"/>
-      <c r="E49" s="203"/>
+      <c r="B49" s="195"/>
+      <c r="C49" s="195"/>
+      <c r="D49" s="209"/>
+      <c r="E49" s="210"/>
       <c r="F49" s="141"/>
       <c r="G49" s="127"/>
       <c r="H49" s="127"/>
       <c r="I49" s="127"/>
       <c r="J49" s="127"/>
       <c r="K49" s="128"/>
-      <c r="L49" s="193"/>
+      <c r="L49" s="200"/>
       <c r="M49" s="148" t="str">
-        <f t="shared" ref="M49" si="42">A51</f>
-        <v/>
-      </c>
-      <c r="N49" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O49" s="207"/>
-      <c r="P49" s="191"/>
-      <c r="Q49" s="212"/>
+        <f t="shared" ref="M49" si="42">A49</f>
+        <v/>
+      </c>
+      <c r="N49" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O49" s="214"/>
+      <c r="P49" s="157"/>
+      <c r="Q49" s="159"/>
       <c r="R49" s="150"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134"/>
-      <c r="B50" s="184"/>
-      <c r="C50" s="184"/>
-      <c r="D50" s="204"/>
-      <c r="E50" s="205"/>
+      <c r="B50" s="194"/>
+      <c r="C50" s="194"/>
+      <c r="D50" s="211"/>
+      <c r="E50" s="212"/>
       <c r="F50" s="139"/>
       <c r="G50" s="129"/>
       <c r="H50" s="129"/>
       <c r="I50" s="129"/>
       <c r="J50" s="129"/>
       <c r="K50" s="129"/>
-      <c r="L50" s="193"/>
+      <c r="L50" s="200"/>
       <c r="M50" s="147" t="str">
-        <f t="shared" ref="M50" si="43">IF(ISBLANK(A52),"",A52)</f>
-        <v/>
-      </c>
-      <c r="N50" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O50" s="209"/>
-      <c r="P50" s="191"/>
-      <c r="Q50" s="212"/>
+        <f t="shared" ref="M50" si="43">IF(ISBLANK(A50),"",A50)</f>
+        <v/>
+      </c>
+      <c r="N50" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O50" s="216"/>
+      <c r="P50" s="157"/>
+      <c r="Q50" s="159"/>
       <c r="R50" s="149"/>
     </row>
     <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4343,77 +4352,83 @@
         <f t="shared" ref="A51" si="44">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="185"/>
-      <c r="C51" s="185"/>
-      <c r="D51" s="202"/>
-      <c r="E51" s="203"/>
+      <c r="B51" s="195"/>
+      <c r="C51" s="195"/>
+      <c r="D51" s="209"/>
+      <c r="E51" s="210"/>
       <c r="F51" s="141"/>
       <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127"/>
       <c r="J51" s="127"/>
       <c r="K51" s="128"/>
-      <c r="L51" s="193"/>
+      <c r="L51" s="200"/>
       <c r="M51" s="148" t="str">
-        <f t="shared" ref="M51" si="45">A53</f>
-        <v/>
-      </c>
-      <c r="N51" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O51" s="207"/>
-      <c r="P51" s="191"/>
-      <c r="Q51" s="212"/>
+        <f t="shared" ref="M51" si="45">A51</f>
+        <v/>
+      </c>
+      <c r="N51" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O51" s="214"/>
+      <c r="P51" s="157"/>
+      <c r="Q51" s="159"/>
       <c r="R51" s="150"/>
     </row>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="134"/>
-      <c r="B52" s="184"/>
-      <c r="C52" s="184"/>
-      <c r="D52" s="204"/>
-      <c r="E52" s="205"/>
+      <c r="B52" s="194"/>
+      <c r="C52" s="194"/>
+      <c r="D52" s="211"/>
+      <c r="E52" s="212"/>
       <c r="F52" s="139"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
       <c r="I52" s="129"/>
       <c r="J52" s="129"/>
       <c r="K52" s="129"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="147"/>
-      <c r="N52" s="208" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O52" s="209"/>
-      <c r="P52" s="191"/>
-      <c r="Q52" s="212"/>
+      <c r="L52" s="200"/>
+      <c r="M52" s="147" t="str">
+        <f t="shared" ref="M52" si="46">IF(ISBLANK(A52),"",A52)</f>
+        <v/>
+      </c>
+      <c r="N52" s="215" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O52" s="216"/>
+      <c r="P52" s="157"/>
+      <c r="Q52" s="159"/>
       <c r="R52" s="149"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
-        <f t="shared" ref="A53" si="46">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
-        <v/>
-      </c>
-      <c r="B53" s="185"/>
-      <c r="C53" s="185"/>
-      <c r="D53" s="202"/>
-      <c r="E53" s="203"/>
+        <f t="shared" ref="A53" si="47">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
+        <v/>
+      </c>
+      <c r="B53" s="195"/>
+      <c r="C53" s="195"/>
+      <c r="D53" s="209"/>
+      <c r="E53" s="210"/>
       <c r="F53" s="141"/>
       <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127"/>
       <c r="J53" s="127"/>
       <c r="K53" s="128"/>
-      <c r="L53" s="194"/>
-      <c r="M53" s="148"/>
-      <c r="N53" s="206" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O53" s="207"/>
-      <c r="P53" s="192"/>
-      <c r="Q53" s="213"/>
+      <c r="L53" s="201"/>
+      <c r="M53" s="148" t="str">
+        <f t="shared" ref="M53" si="48">A53</f>
+        <v/>
+      </c>
+      <c r="N53" s="213" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O53" s="214"/>
+      <c r="P53" s="158"/>
+      <c r="Q53" s="160"/>
       <c r="R53" s="150"/>
     </row>
     <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4427,23 +4442,23 @@
         <v>0</v>
       </c>
       <c r="G54" s="2">
-        <f t="shared" ref="G54:K54" si="47">SUM(G18:G53)</f>
+        <f t="shared" ref="G54:K54" si="49">SUM(G18:G53)</f>
         <v>0</v>
       </c>
       <c r="H54" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="K54" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L54" s="3"/>
@@ -4528,8 +4543,8 @@
         <f>SUM(G55:K55)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="214"/>
-      <c r="H58" s="214"/>
+      <c r="G58" s="218"/>
+      <c r="H58" s="218"/>
       <c r="I58" s="49" t="s">
         <v>29</v>
       </c>
@@ -4555,8 +4570,8 @@
         <f>L9</f>
         <v>0</v>
       </c>
-      <c r="G59" s="214"/>
-      <c r="H59" s="214"/>
+      <c r="G59" s="218"/>
+      <c r="H59" s="218"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
@@ -4622,31 +4637,31 @@
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
       <c r="B63" s="57"/>
-      <c r="C63" s="215" t="s">
+      <c r="C63" s="219" t="s">
         <v>35</v>
       </c>
-      <c r="D63" s="215"/>
-      <c r="E63" s="215"/>
-      <c r="F63" s="215"/>
-      <c r="G63" s="215"/>
-      <c r="H63" s="215"/>
-      <c r="I63" s="215"/>
-      <c r="J63" s="215"/>
-      <c r="K63" s="215"/>
+      <c r="D63" s="219"/>
+      <c r="E63" s="219"/>
+      <c r="F63" s="219"/>
+      <c r="G63" s="219"/>
+      <c r="H63" s="219"/>
+      <c r="I63" s="219"/>
+      <c r="J63" s="219"/>
+      <c r="K63" s="219"/>
       <c r="L63" s="3"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
       <c r="B64" s="57"/>
-      <c r="C64" s="215"/>
-      <c r="D64" s="215"/>
-      <c r="E64" s="215"/>
-      <c r="F64" s="215"/>
-      <c r="G64" s="215"/>
-      <c r="H64" s="215"/>
-      <c r="I64" s="215"/>
-      <c r="J64" s="215"/>
-      <c r="K64" s="215"/>
+      <c r="C64" s="219"/>
+      <c r="D64" s="219"/>
+      <c r="E64" s="219"/>
+      <c r="F64" s="219"/>
+      <c r="G64" s="219"/>
+      <c r="H64" s="219"/>
+      <c r="I64" s="219"/>
+      <c r="J64" s="219"/>
+      <c r="K64" s="219"/>
       <c r="L64" s="3"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -4757,14 +4772,14 @@
       <c r="J71" s="60"/>
       <c r="K71" s="60"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="210" t="s">
+      <c r="M71" s="217" t="s">
         <v>87</v>
       </c>
-      <c r="N71" s="210"/>
-      <c r="O71" s="210"/>
-      <c r="P71" s="210"/>
-      <c r="Q71" s="210"/>
-      <c r="R71" s="210"/>
+      <c r="N71" s="217"/>
+      <c r="O71" s="217"/>
+      <c r="P71" s="217"/>
+      <c r="Q71" s="217"/>
+      <c r="R71" s="217"/>
     </row>
     <row r="72" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="50"/>
@@ -4781,14 +4796,14 @@
       <c r="J72" s="60"/>
       <c r="K72" s="60"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="210" t="s">
+      <c r="M72" s="217" t="s">
         <v>88</v>
       </c>
-      <c r="N72" s="210"/>
-      <c r="O72" s="210"/>
-      <c r="P72" s="210"/>
-      <c r="Q72" s="210"/>
-      <c r="R72" s="210"/>
+      <c r="N72" s="217"/>
+      <c r="O72" s="217"/>
+      <c r="P72" s="217"/>
+      <c r="Q72" s="217"/>
+      <c r="R72" s="217"/>
     </row>
     <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
@@ -4807,12 +4822,12 @@
       <c r="J73" s="60"/>
       <c r="K73" s="60"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="217"/>
-      <c r="N73" s="217"/>
-      <c r="O73" s="217"/>
-      <c r="P73" s="217"/>
-      <c r="Q73" s="217"/>
-      <c r="R73" s="217"/>
+      <c r="M73" s="221"/>
+      <c r="N73" s="221"/>
+      <c r="O73" s="221"/>
+      <c r="P73" s="221"/>
+      <c r="Q73" s="221"/>
+      <c r="R73" s="221"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="50"/>
@@ -4838,24 +4853,24 @@
       <c r="E75" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="218">
+      <c r="F75" s="222">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="218"/>
-      <c r="H75" s="218"/>
-      <c r="I75" s="218"/>
-      <c r="J75" s="218"/>
-      <c r="K75" s="218"/>
+      <c r="G75" s="222"/>
+      <c r="H75" s="222"/>
+      <c r="I75" s="222"/>
+      <c r="J75" s="222"/>
+      <c r="K75" s="222"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="219" t="s">
+      <c r="M75" s="223" t="s">
         <v>89</v>
       </c>
-      <c r="N75" s="219"/>
-      <c r="O75" s="219"/>
-      <c r="P75" s="219"/>
-      <c r="Q75" s="219"/>
-      <c r="R75" s="219"/>
+      <c r="N75" s="223"/>
+      <c r="O75" s="223"/>
+      <c r="P75" s="223"/>
+      <c r="Q75" s="223"/>
+      <c r="R75" s="223"/>
     </row>
     <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="50"/>
@@ -4887,14 +4902,14 @@
       <c r="E77" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="220">
+      <c r="F77" s="224">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="220"/>
-      <c r="H77" s="220"/>
-      <c r="I77" s="220"/>
-      <c r="J77" s="220"/>
+      <c r="G77" s="224"/>
+      <c r="H77" s="224"/>
+      <c r="I77" s="224"/>
+      <c r="J77" s="224"/>
       <c r="K77" s="40"/>
       <c r="L77" s="50"/>
       <c r="M77" s="75"/>
@@ -4919,13 +4934,13 @@
       <c r="L78" s="50"/>
       <c r="M78" s="133"/>
       <c r="N78" s="133"/>
-      <c r="O78" s="222" t="str">
+      <c r="O78" s="226" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="P78" s="222"/>
-      <c r="Q78" s="222"/>
-      <c r="R78" s="222"/>
+      <c r="P78" s="226"/>
+      <c r="Q78" s="226"/>
+      <c r="R78" s="226"/>
     </row>
     <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="67"/>
@@ -4947,11 +4962,11 @@
       <c r="M79" s="77"/>
       <c r="N79" s="77"/>
       <c r="O79" s="78"/>
-      <c r="P79" s="221" t="str">
+      <c r="P79" s="225" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="Q79" s="221"/>
+      <c r="Q79" s="225"/>
       <c r="R79" s="79"/>
     </row>
     <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
@@ -4989,13 +5004,13 @@
       <c r="L81" s="50"/>
       <c r="M81" s="78"/>
       <c r="N81" s="78"/>
-      <c r="O81" s="223" t="str">
+      <c r="O81" s="227" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="P81" s="223"/>
-      <c r="Q81" s="223"/>
-      <c r="R81" s="223"/>
+      <c r="P81" s="227"/>
+      <c r="Q81" s="227"/>
+      <c r="R81" s="227"/>
     </row>
     <row r="82" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="50"/>
@@ -5032,12 +5047,12 @@
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="224"/>
-      <c r="N83" s="224"/>
-      <c r="O83" s="224"/>
-      <c r="P83" s="224"/>
-      <c r="Q83" s="224"/>
-      <c r="R83" s="224"/>
+      <c r="M83" s="228"/>
+      <c r="N83" s="228"/>
+      <c r="O83" s="228"/>
+      <c r="P83" s="228"/>
+      <c r="Q83" s="228"/>
+      <c r="R83" s="228"/>
     </row>
     <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="50"/>
@@ -5056,14 +5071,14 @@
       <c r="J84" s="74"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="216" t="s">
+      <c r="M84" s="220" t="s">
         <v>90</v>
       </c>
-      <c r="N84" s="216"/>
-      <c r="O84" s="216"/>
-      <c r="P84" s="216"/>
-      <c r="Q84" s="216"/>
-      <c r="R84" s="216"/>
+      <c r="N84" s="220"/>
+      <c r="O84" s="220"/>
+      <c r="P84" s="220"/>
+      <c r="Q84" s="220"/>
+      <c r="R84" s="220"/>
     </row>
     <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="50"/>
@@ -5078,14 +5093,14 @@
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="216" t="s">
+      <c r="M85" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="N85" s="216"/>
-      <c r="O85" s="216"/>
-      <c r="P85" s="216"/>
-      <c r="Q85" s="216"/>
-      <c r="R85" s="216"/>
+      <c r="N85" s="220"/>
+      <c r="O85" s="220"/>
+      <c r="P85" s="220"/>
+      <c r="Q85" s="220"/>
+      <c r="R85" s="220"/>
     </row>
     <row r="86" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="50"/>
@@ -5104,12 +5119,12 @@
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="225"/>
-      <c r="N86" s="225"/>
-      <c r="O86" s="225"/>
-      <c r="P86" s="225"/>
-      <c r="Q86" s="225"/>
-      <c r="R86" s="225"/>
+      <c r="M86" s="229"/>
+      <c r="N86" s="229"/>
+      <c r="O86" s="229"/>
+      <c r="P86" s="229"/>
+      <c r="Q86" s="229"/>
+      <c r="R86" s="229"/>
     </row>
     <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="50"/>
@@ -5124,12 +5139,12 @@
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="216"/>
-      <c r="N87" s="216"/>
-      <c r="O87" s="216"/>
-      <c r="P87" s="216"/>
-      <c r="Q87" s="216"/>
-      <c r="R87" s="216"/>
+      <c r="M87" s="220"/>
+      <c r="N87" s="220"/>
+      <c r="O87" s="220"/>
+      <c r="P87" s="220"/>
+      <c r="Q87" s="220"/>
+      <c r="R87" s="220"/>
     </row>
     <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50"/>
@@ -5141,21 +5156,21 @@
       <c r="E88" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="240"/>
-      <c r="G88" s="240"/>
-      <c r="H88" s="240"/>
-      <c r="I88" s="240"/>
-      <c r="J88" s="240"/>
+      <c r="F88" s="244"/>
+      <c r="G88" s="244"/>
+      <c r="H88" s="244"/>
+      <c r="I88" s="244"/>
+      <c r="J88" s="244"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="216" t="s">
+      <c r="M88" s="220" t="s">
         <v>92</v>
       </c>
-      <c r="N88" s="216"/>
-      <c r="O88" s="216"/>
-      <c r="P88" s="216"/>
-      <c r="Q88" s="216"/>
-      <c r="R88" s="216"/>
+      <c r="N88" s="220"/>
+      <c r="O88" s="220"/>
+      <c r="P88" s="220"/>
+      <c r="Q88" s="220"/>
+      <c r="R88" s="220"/>
     </row>
     <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="50"/>
@@ -5308,12 +5323,12 @@
       <c r="J95" s="86"/>
       <c r="K95" s="27"/>
       <c r="L95" s="17"/>
-      <c r="M95" s="225"/>
-      <c r="N95" s="225"/>
-      <c r="O95" s="225"/>
-      <c r="P95" s="225"/>
-      <c r="Q95" s="225"/>
-      <c r="R95" s="225"/>
+      <c r="M95" s="229"/>
+      <c r="N95" s="229"/>
+      <c r="O95" s="229"/>
+      <c r="P95" s="229"/>
+      <c r="Q95" s="229"/>
+      <c r="R95" s="229"/>
     </row>
     <row r="96" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
@@ -5330,12 +5345,12 @@
       <c r="J96" s="86"/>
       <c r="K96" s="27"/>
       <c r="L96" s="17"/>
-      <c r="M96" s="225"/>
-      <c r="N96" s="225"/>
-      <c r="O96" s="225"/>
-      <c r="P96" s="225"/>
-      <c r="Q96" s="225"/>
-      <c r="R96" s="225"/>
+      <c r="M96" s="229"/>
+      <c r="N96" s="229"/>
+      <c r="O96" s="229"/>
+      <c r="P96" s="229"/>
+      <c r="Q96" s="229"/>
+      <c r="R96" s="229"/>
     </row>
     <row r="97" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
@@ -5352,12 +5367,12 @@
       <c r="J97" s="86"/>
       <c r="K97" s="27"/>
       <c r="L97" s="17"/>
-      <c r="M97" s="225"/>
-      <c r="N97" s="225"/>
-      <c r="O97" s="225"/>
-      <c r="P97" s="225"/>
-      <c r="Q97" s="225"/>
-      <c r="R97" s="225"/>
+      <c r="M97" s="229"/>
+      <c r="N97" s="229"/>
+      <c r="O97" s="229"/>
+      <c r="P97" s="229"/>
+      <c r="Q97" s="229"/>
+      <c r="R97" s="229"/>
     </row>
     <row r="98" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
@@ -5374,12 +5389,12 @@
       <c r="J98" s="86"/>
       <c r="K98" s="27"/>
       <c r="L98" s="17"/>
-      <c r="M98" s="225"/>
-      <c r="N98" s="225"/>
-      <c r="O98" s="225"/>
-      <c r="P98" s="225"/>
-      <c r="Q98" s="225"/>
-      <c r="R98" s="225"/>
+      <c r="M98" s="229"/>
+      <c r="N98" s="229"/>
+      <c r="O98" s="229"/>
+      <c r="P98" s="229"/>
+      <c r="Q98" s="229"/>
+      <c r="R98" s="229"/>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="64"/>
@@ -5396,12 +5411,12 @@
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
       <c r="L99" s="17"/>
-      <c r="M99" s="216"/>
-      <c r="N99" s="216"/>
-      <c r="O99" s="216"/>
-      <c r="P99" s="216"/>
-      <c r="Q99" s="216"/>
-      <c r="R99" s="216"/>
+      <c r="M99" s="220"/>
+      <c r="N99" s="220"/>
+      <c r="O99" s="220"/>
+      <c r="P99" s="220"/>
+      <c r="Q99" s="220"/>
+      <c r="R99" s="220"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="50"/>
@@ -5706,36 +5721,36 @@
     </row>
     <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="241" t="s">
+      <c r="A124" s="245" t="s">
         <v>65</v>
       </c>
-      <c r="B124" s="242"/>
-      <c r="C124" s="242"/>
-      <c r="D124" s="242"/>
-      <c r="E124" s="242"/>
-      <c r="F124" s="242"/>
-      <c r="G124" s="242"/>
-      <c r="H124" s="242"/>
-      <c r="I124" s="242"/>
-      <c r="J124" s="242"/>
-      <c r="K124" s="242"/>
-      <c r="L124" s="243"/>
+      <c r="B124" s="246"/>
+      <c r="C124" s="246"/>
+      <c r="D124" s="246"/>
+      <c r="E124" s="246"/>
+      <c r="F124" s="246"/>
+      <c r="G124" s="246"/>
+      <c r="H124" s="246"/>
+      <c r="I124" s="246"/>
+      <c r="J124" s="246"/>
+      <c r="K124" s="246"/>
+      <c r="L124" s="247"/>
     </row>
     <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="244" t="s">
+      <c r="A125" s="248" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="245"/>
-      <c r="C125" s="245"/>
-      <c r="D125" s="245"/>
-      <c r="E125" s="245"/>
-      <c r="F125" s="245"/>
-      <c r="G125" s="245"/>
-      <c r="H125" s="245"/>
-      <c r="I125" s="245"/>
-      <c r="J125" s="245"/>
-      <c r="K125" s="245"/>
-      <c r="L125" s="246"/>
+      <c r="B125" s="249"/>
+      <c r="C125" s="249"/>
+      <c r="D125" s="249"/>
+      <c r="E125" s="249"/>
+      <c r="F125" s="249"/>
+      <c r="G125" s="249"/>
+      <c r="H125" s="249"/>
+      <c r="I125" s="249"/>
+      <c r="J125" s="249"/>
+      <c r="K125" s="249"/>
+      <c r="L125" s="250"/>
     </row>
     <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="105" t="s">
@@ -5743,20 +5758,20 @@
       </c>
       <c r="B126" s="106"/>
       <c r="C126" s="106"/>
-      <c r="D126" s="247">
+      <c r="D126" s="251">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="248"/>
-      <c r="F126" s="248"/>
-      <c r="G126" s="248"/>
-      <c r="H126" s="248"/>
-      <c r="I126" s="249"/>
-      <c r="J126" s="250" t="s">
+      <c r="E126" s="252"/>
+      <c r="F126" s="252"/>
+      <c r="G126" s="252"/>
+      <c r="H126" s="252"/>
+      <c r="I126" s="253"/>
+      <c r="J126" s="254" t="s">
         <v>68</v>
       </c>
-      <c r="K126" s="251"/>
-      <c r="L126" s="252"/>
+      <c r="K126" s="255"/>
+      <c r="L126" s="256"/>
     </row>
     <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="107" t="s">
@@ -5792,23 +5807,23 @@
       <c r="A129" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B129" s="230" t="s">
+      <c r="B129" s="234" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="231"/>
-      <c r="D129" s="232" t="s">
+      <c r="C129" s="235"/>
+      <c r="D129" s="236" t="s">
         <v>72</v>
       </c>
-      <c r="E129" s="233"/>
-      <c r="F129" s="233"/>
-      <c r="G129" s="233"/>
-      <c r="H129" s="233"/>
-      <c r="I129" s="233"/>
-      <c r="J129" s="234"/>
-      <c r="K129" s="232" t="s">
+      <c r="E129" s="237"/>
+      <c r="F129" s="237"/>
+      <c r="G129" s="237"/>
+      <c r="H129" s="237"/>
+      <c r="I129" s="237"/>
+      <c r="J129" s="238"/>
+      <c r="K129" s="236" t="s">
         <v>73</v>
       </c>
-      <c r="L129" s="233"/>
+      <c r="L129" s="237"/>
     </row>
     <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="121"/>
@@ -5818,15 +5833,15 @@
       <c r="C130" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="D130" s="235"/>
-      <c r="E130" s="236"/>
-      <c r="F130" s="236"/>
-      <c r="G130" s="236"/>
-      <c r="H130" s="236"/>
-      <c r="I130" s="236"/>
-      <c r="J130" s="237"/>
-      <c r="K130" s="238"/>
-      <c r="L130" s="239"/>
+      <c r="D130" s="239"/>
+      <c r="E130" s="240"/>
+      <c r="F130" s="240"/>
+      <c r="G130" s="240"/>
+      <c r="H130" s="240"/>
+      <c r="I130" s="240"/>
+      <c r="J130" s="241"/>
+      <c r="K130" s="242"/>
+      <c r="L130" s="243"/>
     </row>
     <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="124">
@@ -5834,17 +5849,17 @@
       </c>
       <c r="B131" s="124"/>
       <c r="C131" s="125"/>
-      <c r="D131" s="227" t="s">
+      <c r="D131" s="231" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="228"/>
-      <c r="F131" s="228"/>
-      <c r="G131" s="228"/>
-      <c r="H131" s="228"/>
-      <c r="I131" s="228"/>
-      <c r="J131" s="229"/>
-      <c r="K131" s="226"/>
-      <c r="L131" s="226"/>
+      <c r="E131" s="232"/>
+      <c r="F131" s="232"/>
+      <c r="G131" s="232"/>
+      <c r="H131" s="232"/>
+      <c r="I131" s="232"/>
+      <c r="J131" s="233"/>
+      <c r="K131" s="230"/>
+      <c r="L131" s="230"/>
     </row>
     <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="124">
@@ -5852,17 +5867,17 @@
       </c>
       <c r="B132" s="124"/>
       <c r="C132" s="126"/>
-      <c r="D132" s="227" t="s">
+      <c r="D132" s="231" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="228"/>
-      <c r="F132" s="228"/>
-      <c r="G132" s="228"/>
-      <c r="H132" s="228"/>
-      <c r="I132" s="228"/>
-      <c r="J132" s="229"/>
-      <c r="K132" s="226"/>
-      <c r="L132" s="226"/>
+      <c r="E132" s="232"/>
+      <c r="F132" s="232"/>
+      <c r="G132" s="232"/>
+      <c r="H132" s="232"/>
+      <c r="I132" s="232"/>
+      <c r="J132" s="233"/>
+      <c r="K132" s="230"/>
+      <c r="L132" s="230"/>
     </row>
     <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="124">
@@ -5870,17 +5885,17 @@
       </c>
       <c r="B133" s="124"/>
       <c r="C133" s="126"/>
-      <c r="D133" s="227" t="s">
+      <c r="D133" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="E133" s="228"/>
-      <c r="F133" s="228"/>
-      <c r="G133" s="228"/>
-      <c r="H133" s="228"/>
-      <c r="I133" s="228"/>
-      <c r="J133" s="229"/>
-      <c r="K133" s="226"/>
-      <c r="L133" s="226"/>
+      <c r="E133" s="232"/>
+      <c r="F133" s="232"/>
+      <c r="G133" s="232"/>
+      <c r="H133" s="232"/>
+      <c r="I133" s="232"/>
+      <c r="J133" s="233"/>
+      <c r="K133" s="230"/>
+      <c r="L133" s="230"/>
     </row>
     <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="124">
@@ -5888,17 +5903,17 @@
       </c>
       <c r="B134" s="124"/>
       <c r="C134" s="126"/>
-      <c r="D134" s="227" t="s">
+      <c r="D134" s="231" t="s">
         <v>79</v>
       </c>
-      <c r="E134" s="228"/>
-      <c r="F134" s="228"/>
-      <c r="G134" s="228"/>
-      <c r="H134" s="228"/>
-      <c r="I134" s="228"/>
-      <c r="J134" s="229"/>
-      <c r="K134" s="226"/>
-      <c r="L134" s="226"/>
+      <c r="E134" s="232"/>
+      <c r="F134" s="232"/>
+      <c r="G134" s="232"/>
+      <c r="H134" s="232"/>
+      <c r="I134" s="232"/>
+      <c r="J134" s="233"/>
+      <c r="K134" s="230"/>
+      <c r="L134" s="230"/>
     </row>
     <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="124">
@@ -5906,17 +5921,17 @@
       </c>
       <c r="B135" s="124"/>
       <c r="C135" s="126"/>
-      <c r="D135" s="227" t="s">
+      <c r="D135" s="231" t="s">
         <v>80</v>
       </c>
-      <c r="E135" s="228"/>
-      <c r="F135" s="228"/>
-      <c r="G135" s="228"/>
-      <c r="H135" s="228"/>
-      <c r="I135" s="228"/>
-      <c r="J135" s="229"/>
-      <c r="K135" s="226"/>
-      <c r="L135" s="226"/>
+      <c r="E135" s="232"/>
+      <c r="F135" s="232"/>
+      <c r="G135" s="232"/>
+      <c r="H135" s="232"/>
+      <c r="I135" s="232"/>
+      <c r="J135" s="233"/>
+      <c r="K135" s="230"/>
+      <c r="L135" s="230"/>
     </row>
     <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="124">
@@ -5924,17 +5939,17 @@
       </c>
       <c r="B136" s="124"/>
       <c r="C136" s="126"/>
-      <c r="D136" s="227" t="s">
+      <c r="D136" s="231" t="s">
         <v>81</v>
       </c>
-      <c r="E136" s="228"/>
-      <c r="F136" s="228"/>
-      <c r="G136" s="228"/>
-      <c r="H136" s="228"/>
-      <c r="I136" s="228"/>
-      <c r="J136" s="229"/>
-      <c r="K136" s="226"/>
-      <c r="L136" s="226"/>
+      <c r="E136" s="232"/>
+      <c r="F136" s="232"/>
+      <c r="G136" s="232"/>
+      <c r="H136" s="232"/>
+      <c r="I136" s="232"/>
+      <c r="J136" s="233"/>
+      <c r="K136" s="230"/>
+      <c r="L136" s="230"/>
     </row>
     <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="124">
@@ -5942,17 +5957,17 @@
       </c>
       <c r="B137" s="124"/>
       <c r="C137" s="126"/>
-      <c r="D137" s="227" t="s">
+      <c r="D137" s="231" t="s">
         <v>82</v>
       </c>
-      <c r="E137" s="228"/>
-      <c r="F137" s="228"/>
-      <c r="G137" s="228"/>
-      <c r="H137" s="228"/>
-      <c r="I137" s="228"/>
-      <c r="J137" s="229"/>
-      <c r="K137" s="226"/>
-      <c r="L137" s="226"/>
+      <c r="E137" s="232"/>
+      <c r="F137" s="232"/>
+      <c r="G137" s="232"/>
+      <c r="H137" s="232"/>
+      <c r="I137" s="232"/>
+      <c r="J137" s="233"/>
+      <c r="K137" s="230"/>
+      <c r="L137" s="230"/>
     </row>
     <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="124">
@@ -5960,17 +5975,17 @@
       </c>
       <c r="B138" s="124"/>
       <c r="C138" s="126"/>
-      <c r="D138" s="253" t="s">
-        <v>109</v>
-      </c>
-      <c r="E138" s="254"/>
-      <c r="F138" s="254"/>
-      <c r="G138" s="254"/>
-      <c r="H138" s="254"/>
-      <c r="I138" s="254"/>
-      <c r="J138" s="255"/>
-      <c r="K138" s="259"/>
-      <c r="L138" s="260"/>
+      <c r="D138" s="257" t="s">
+        <v>108</v>
+      </c>
+      <c r="E138" s="258"/>
+      <c r="F138" s="258"/>
+      <c r="G138" s="258"/>
+      <c r="H138" s="258"/>
+      <c r="I138" s="258"/>
+      <c r="J138" s="259"/>
+      <c r="K138" s="263"/>
+      <c r="L138" s="264"/>
     </row>
     <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="124">
@@ -5978,17 +5993,17 @@
       </c>
       <c r="B139" s="124"/>
       <c r="C139" s="126"/>
-      <c r="D139" s="253" t="s">
+      <c r="D139" s="257" t="s">
         <v>83</v>
       </c>
-      <c r="E139" s="254"/>
-      <c r="F139" s="254"/>
-      <c r="G139" s="254"/>
-      <c r="H139" s="254"/>
-      <c r="I139" s="254"/>
-      <c r="J139" s="255"/>
-      <c r="K139" s="226"/>
-      <c r="L139" s="226"/>
+      <c r="E139" s="258"/>
+      <c r="F139" s="258"/>
+      <c r="G139" s="258"/>
+      <c r="H139" s="258"/>
+      <c r="I139" s="258"/>
+      <c r="J139" s="259"/>
+      <c r="K139" s="230"/>
+      <c r="L139" s="230"/>
     </row>
     <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="124">
@@ -5996,17 +6011,17 @@
       </c>
       <c r="B140" s="124"/>
       <c r="C140" s="126"/>
-      <c r="D140" s="253" t="s">
+      <c r="D140" s="257" t="s">
         <v>84</v>
       </c>
-      <c r="E140" s="254"/>
-      <c r="F140" s="254"/>
-      <c r="G140" s="254"/>
-      <c r="H140" s="254"/>
-      <c r="I140" s="254"/>
-      <c r="J140" s="255"/>
-      <c r="K140" s="226"/>
-      <c r="L140" s="226"/>
+      <c r="E140" s="258"/>
+      <c r="F140" s="258"/>
+      <c r="G140" s="258"/>
+      <c r="H140" s="258"/>
+      <c r="I140" s="258"/>
+      <c r="J140" s="259"/>
+      <c r="K140" s="230"/>
+      <c r="L140" s="230"/>
     </row>
     <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="124">
@@ -6014,17 +6029,17 @@
       </c>
       <c r="B141" s="124"/>
       <c r="C141" s="126"/>
-      <c r="D141" s="256" t="s">
+      <c r="D141" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="E141" s="257"/>
-      <c r="F141" s="257"/>
-      <c r="G141" s="257"/>
-      <c r="H141" s="257"/>
-      <c r="I141" s="257"/>
-      <c r="J141" s="258"/>
-      <c r="K141" s="226"/>
-      <c r="L141" s="226"/>
+      <c r="E141" s="261"/>
+      <c r="F141" s="261"/>
+      <c r="G141" s="261"/>
+      <c r="H141" s="261"/>
+      <c r="I141" s="261"/>
+      <c r="J141" s="262"/>
+      <c r="K141" s="230"/>
+      <c r="L141" s="230"/>
     </row>
     <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6084,11 +6099,15 @@
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="N33:O33"/>
     <mergeCell ref="N34:O34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="D136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="D132:J132"/>
     <mergeCell ref="D140:J140"/>
     <mergeCell ref="K140:L140"/>
     <mergeCell ref="D141:J141"/>
@@ -6099,15 +6118,6 @@
     <mergeCell ref="K138:L138"/>
     <mergeCell ref="D139:J139"/>
     <mergeCell ref="K139:L139"/>
-    <mergeCell ref="D134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="D136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="D132:J132"/>
     <mergeCell ref="K132:L132"/>
     <mergeCell ref="D133:J133"/>
     <mergeCell ref="K133:L133"/>
@@ -6137,6 +6147,13 @@
     <mergeCell ref="M84:R84"/>
     <mergeCell ref="M85:R85"/>
     <mergeCell ref="M86:R86"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
     <mergeCell ref="M72:R72"/>
     <mergeCell ref="B40:C41"/>
     <mergeCell ref="B42:C43"/>
@@ -6144,7 +6161,6 @@
     <mergeCell ref="B46:C47"/>
     <mergeCell ref="B48:C49"/>
     <mergeCell ref="B50:C51"/>
-    <mergeCell ref="Q18:Q53"/>
     <mergeCell ref="B52:C53"/>
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="G59:H59"/>
@@ -6155,17 +6171,7 @@
     <mergeCell ref="B32:C33"/>
     <mergeCell ref="B34:C35"/>
     <mergeCell ref="B36:C37"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
     <mergeCell ref="L18:L19"/>
-    <mergeCell ref="P18:P53"/>
     <mergeCell ref="B20:C21"/>
     <mergeCell ref="L20:L53"/>
     <mergeCell ref="B22:C23"/>
@@ -6178,13 +6184,19 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="P20:P53"/>
+    <mergeCell ref="Q20:Q53"/>
     <mergeCell ref="M2:R2"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="I18:I19"/>
@@ -6204,6 +6216,9 @@
     <mergeCell ref="R15:R17"/>
     <mergeCell ref="P15:P17"/>
     <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
   </mergeCells>
   <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE93C46-1321-4174-9BAA-D7D7EF81F9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868F5EF8-9904-40A0-859E-3626D39367A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2045,6 +2045,110 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2065,12 +2169,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2111,74 +2209,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2191,20 +2221,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2249,34 +2265,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2321,22 +2309,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2438,6 +2410,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2450,6 +2426,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2457,6 +2445,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2683,6 +2683,56 @@
         </xdr:pic>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>432543</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>470925</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325D5F6B-6E8E-5C88-EDA5-61650BDD43EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8528793" y="3531439"/>
+          <a:ext cx="38382" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3025,20 +3075,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
+      <c r="L1" s="163"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
@@ -3046,26 +3096,26 @@
       <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
-      <c r="L2" s="174"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="161"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="188"/>
+      <c r="N2" s="188"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="188"/>
+      <c r="Q2" s="188"/>
+      <c r="R2" s="188"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
@@ -3086,38 +3136,38 @@
       <c r="R3" s="9"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="187" t="s">
+      <c r="A4" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="187"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="187"/>
-      <c r="L4" s="187"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="188"/>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="188"/>
+      <c r="A5" s="177"/>
+      <c r="B5" s="177"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="177"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3126,20 +3176,20 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="189"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="189"/>
-      <c r="E6" s="189"/>
-      <c r="F6" s="189"/>
-      <c r="G6" s="189"/>
-      <c r="H6" s="189"/>
-      <c r="I6" s="189"/>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="B6" s="178"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="178"/>
+      <c r="L6" s="178"/>
       <c r="O6" s="16"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -3194,9 +3244,9 @@
       <c r="B9" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="190"/>
-      <c r="D9" s="190"/>
-      <c r="E9" s="190"/>
+      <c r="C9" s="179"/>
+      <c r="D9" s="179"/>
+      <c r="E9" s="179"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="19" t="s">
@@ -3345,41 +3395,41 @@
       <c r="A15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="175" t="s">
+      <c r="B15" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="175"/>
-      <c r="D15" s="177" t="s">
+      <c r="C15" s="164"/>
+      <c r="D15" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178" t="s">
+      <c r="E15" s="167"/>
+      <c r="F15" s="167" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="183" t="s">
+      <c r="G15" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="183"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="183"/>
-      <c r="K15" s="184"/>
-      <c r="L15" s="164" t="s">
+      <c r="H15" s="172"/>
+      <c r="I15" s="172"/>
+      <c r="J15" s="172"/>
+      <c r="K15" s="173"/>
+      <c r="L15" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="167" t="s">
+      <c r="M15" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="N15" s="170" t="s">
+      <c r="N15" s="195" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="171"/>
-      <c r="P15" s="167" t="s">
+      <c r="O15" s="196"/>
+      <c r="P15" s="192" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" s="191" t="s">
+      <c r="Q15" s="199" t="s">
         <v>62</v>
       </c>
-      <c r="R15" s="167" t="s">
+      <c r="R15" s="192" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3387,23 +3437,23 @@
       <c r="A16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="176"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="179"/>
-      <c r="E16" s="180"/>
-      <c r="F16" s="181"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="186"/>
-      <c r="L16" s="165"/>
-      <c r="M16" s="168"/>
-      <c r="N16" s="172"/>
-      <c r="O16" s="173"/>
-      <c r="P16" s="168"/>
-      <c r="Q16" s="192"/>
-      <c r="R16" s="168"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="170"/>
+      <c r="G16" s="174"/>
+      <c r="H16" s="174"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="174"/>
+      <c r="K16" s="175"/>
+      <c r="L16" s="190"/>
+      <c r="M16" s="193"/>
+      <c r="N16" s="197"/>
+      <c r="O16" s="198"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="200"/>
+      <c r="R16" s="193"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
@@ -3421,7 +3471,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="182"/>
+      <c r="F17" s="171"/>
       <c r="G17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3437,39 +3487,39 @@
       <c r="K17" s="37">
         <v>2</v>
       </c>
-      <c r="L17" s="166"/>
-      <c r="M17" s="169"/>
+      <c r="L17" s="191"/>
+      <c r="M17" s="194"/>
       <c r="N17" s="38" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="169"/>
-      <c r="Q17" s="193"/>
-      <c r="R17" s="169"/>
+      <c r="P17" s="194"/>
+      <c r="Q17" s="201"/>
+      <c r="R17" s="194"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="202"/>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="207"/>
-      <c r="G18" s="162"/>
-      <c r="H18" s="162">
+      <c r="A18" s="206"/>
+      <c r="B18" s="174"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="174"/>
+      <c r="E18" s="207"/>
+      <c r="F18" s="211"/>
+      <c r="G18" s="159"/>
+      <c r="H18" s="159">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="162"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="196"/>
-      <c r="L18" s="198" t="s">
+      <c r="I18" s="159"/>
+      <c r="J18" s="159"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="202" t="s">
         <v>107</v>
       </c>
       <c r="M18" s="147"/>
-      <c r="N18" s="215"/>
-      <c r="O18" s="216"/>
+      <c r="N18" s="261"/>
+      <c r="O18" s="262"/>
       <c r="P18" s="151"/>
       <c r="Q18" s="153"/>
       <c r="R18" s="155" t="s">
@@ -3477,49 +3527,49 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="204"/>
-      <c r="B19" s="205"/>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="208"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="163"/>
-      <c r="I19" s="163"/>
-      <c r="J19" s="163"/>
-      <c r="K19" s="197"/>
-      <c r="L19" s="199"/>
+      <c r="A19" s="208"/>
+      <c r="B19" s="209"/>
+      <c r="C19" s="209"/>
+      <c r="D19" s="209"/>
+      <c r="E19" s="210"/>
+      <c r="F19" s="212"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
+      <c r="J19" s="160"/>
+      <c r="K19" s="162"/>
+      <c r="L19" s="203"/>
       <c r="M19" s="148"/>
-      <c r="N19" s="213"/>
-      <c r="O19" s="214"/>
+      <c r="N19" s="263"/>
+      <c r="O19" s="264"/>
       <c r="P19" s="152"/>
       <c r="Q19" s="154"/>
       <c r="R19" s="156"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="142"/>
-      <c r="B20" s="195"/>
-      <c r="C20" s="195"/>
-      <c r="D20" s="211"/>
-      <c r="E20" s="212"/>
+      <c r="B20" s="158"/>
+      <c r="C20" s="158"/>
+      <c r="D20" s="182"/>
+      <c r="E20" s="183"/>
       <c r="F20" s="139"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
       <c r="I20" s="129"/>
       <c r="J20" s="129"/>
       <c r="K20" s="129"/>
-      <c r="L20" s="200"/>
+      <c r="L20" s="204"/>
       <c r="M20" s="147" t="str">
         <f>IF(ISBLANK(A20),"",A20)</f>
         <v/>
       </c>
-      <c r="N20" s="215" t="str">
+      <c r="N20" s="261" t="str">
         <f>IF(ISBLANK(D20),"",D20)</f>
         <v/>
       </c>
-      <c r="O20" s="216"/>
-      <c r="P20" s="157"/>
-      <c r="Q20" s="159"/>
+      <c r="O20" s="262"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="186"/>
       <c r="R20" s="149"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3527,54 +3577,54 @@
         <f t="shared" ref="A21" si="0">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B21" s="195"/>
-      <c r="C21" s="195"/>
-      <c r="D21" s="209"/>
-      <c r="E21" s="210"/>
+      <c r="B21" s="158"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="180"/>
+      <c r="E21" s="181"/>
       <c r="F21" s="141"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
       <c r="I21" s="127"/>
       <c r="J21" s="127"/>
       <c r="K21" s="128"/>
-      <c r="L21" s="200"/>
+      <c r="L21" s="204"/>
       <c r="M21" s="148" t="str">
         <f>A21</f>
         <v/>
       </c>
-      <c r="N21" s="213" t="str">
+      <c r="N21" s="263" t="str">
         <f>IF(ISBLANK(D21),"",D21)</f>
         <v/>
       </c>
-      <c r="O21" s="214"/>
-      <c r="P21" s="157"/>
-      <c r="Q21" s="159"/>
+      <c r="O21" s="264"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="186"/>
       <c r="R21" s="150"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="134"/>
-      <c r="B22" s="194"/>
-      <c r="C22" s="194"/>
-      <c r="D22" s="211"/>
-      <c r="E22" s="212"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="183"/>
       <c r="F22" s="139"/>
       <c r="G22" s="129"/>
       <c r="H22" s="129"/>
       <c r="I22" s="129"/>
       <c r="J22" s="129"/>
       <c r="K22" s="129"/>
-      <c r="L22" s="200"/>
+      <c r="L22" s="204"/>
       <c r="M22" s="147" t="str">
         <f t="shared" ref="M22" si="1">IF(ISBLANK(A22),"",A22)</f>
         <v/>
       </c>
-      <c r="N22" s="215" t="str">
+      <c r="N22" s="261" t="str">
         <f t="shared" ref="N22:N53" si="2">IF(ISBLANK(D22),"",D22)</f>
         <v/>
       </c>
-      <c r="O22" s="216"/>
-      <c r="P22" s="157"/>
-      <c r="Q22" s="159"/>
+      <c r="O22" s="262"/>
+      <c r="P22" s="184"/>
+      <c r="Q22" s="186"/>
       <c r="R22" s="149"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3582,54 +3632,54 @@
         <f t="shared" ref="A23:A25" si="3">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="195"/>
-      <c r="C23" s="195"/>
-      <c r="D23" s="209"/>
-      <c r="E23" s="210"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="180"/>
+      <c r="E23" s="181"/>
       <c r="F23" s="141"/>
       <c r="G23" s="127"/>
       <c r="H23" s="127"/>
       <c r="I23" s="127"/>
       <c r="J23" s="127"/>
       <c r="K23" s="128"/>
-      <c r="L23" s="200"/>
+      <c r="L23" s="204"/>
       <c r="M23" s="148" t="str">
         <f t="shared" ref="M23" si="4">A23</f>
         <v/>
       </c>
-      <c r="N23" s="213" t="str">
+      <c r="N23" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O23" s="214"/>
-      <c r="P23" s="157"/>
-      <c r="Q23" s="159"/>
+      <c r="O23" s="264"/>
+      <c r="P23" s="184"/>
+      <c r="Q23" s="186"/>
       <c r="R23" s="150"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="134"/>
-      <c r="B24" s="194"/>
-      <c r="C24" s="194"/>
-      <c r="D24" s="211"/>
-      <c r="E24" s="212"/>
+      <c r="B24" s="157"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="183"/>
       <c r="F24" s="139"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
       <c r="I24" s="129"/>
       <c r="J24" s="129"/>
       <c r="K24" s="129"/>
-      <c r="L24" s="200"/>
+      <c r="L24" s="204"/>
       <c r="M24" s="147" t="str">
         <f t="shared" ref="M24" si="5">IF(ISBLANK(A24),"",A24)</f>
         <v/>
       </c>
-      <c r="N24" s="215" t="str">
+      <c r="N24" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O24" s="216"/>
-      <c r="P24" s="157"/>
-      <c r="Q24" s="159"/>
+      <c r="O24" s="262"/>
+      <c r="P24" s="184"/>
+      <c r="Q24" s="186"/>
       <c r="R24" s="149"/>
     </row>
     <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3637,54 +3687,54 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B25" s="195"/>
-      <c r="C25" s="195"/>
-      <c r="D25" s="209"/>
-      <c r="E25" s="210"/>
+      <c r="B25" s="158"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="180"/>
+      <c r="E25" s="181"/>
       <c r="F25" s="141"/>
       <c r="G25" s="127"/>
       <c r="H25" s="127"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
       <c r="K25" s="128"/>
-      <c r="L25" s="200"/>
+      <c r="L25" s="204"/>
       <c r="M25" s="148" t="str">
         <f t="shared" ref="M25" si="6">A25</f>
         <v/>
       </c>
-      <c r="N25" s="213" t="str">
+      <c r="N25" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O25" s="214"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="159"/>
+      <c r="O25" s="264"/>
+      <c r="P25" s="184"/>
+      <c r="Q25" s="186"/>
       <c r="R25" s="150"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="134"/>
-      <c r="B26" s="194"/>
-      <c r="C26" s="194"/>
-      <c r="D26" s="211"/>
-      <c r="E26" s="212"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="157"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="183"/>
       <c r="F26" s="139"/>
       <c r="G26" s="129"/>
       <c r="H26" s="129"/>
       <c r="I26" s="129"/>
       <c r="J26" s="129"/>
       <c r="K26" s="129"/>
-      <c r="L26" s="200"/>
+      <c r="L26" s="204"/>
       <c r="M26" s="147" t="str">
         <f t="shared" ref="M26" si="7">IF(ISBLANK(A26),"",A26)</f>
         <v/>
       </c>
-      <c r="N26" s="215" t="str">
+      <c r="N26" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O26" s="216"/>
-      <c r="P26" s="157"/>
-      <c r="Q26" s="159"/>
+      <c r="O26" s="262"/>
+      <c r="P26" s="184"/>
+      <c r="Q26" s="186"/>
       <c r="R26" s="149"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3692,54 +3742,54 @@
         <f t="shared" ref="A27" si="8">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="195"/>
-      <c r="C27" s="195"/>
-      <c r="D27" s="209"/>
-      <c r="E27" s="210"/>
+      <c r="B27" s="158"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="180"/>
+      <c r="E27" s="181"/>
       <c r="F27" s="141"/>
       <c r="G27" s="127"/>
       <c r="H27" s="127"/>
       <c r="I27" s="127"/>
       <c r="J27" s="127"/>
       <c r="K27" s="128"/>
-      <c r="L27" s="200"/>
+      <c r="L27" s="204"/>
       <c r="M27" s="148" t="str">
         <f t="shared" ref="M27" si="9">A27</f>
         <v/>
       </c>
-      <c r="N27" s="213" t="str">
+      <c r="N27" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O27" s="214"/>
-      <c r="P27" s="157"/>
-      <c r="Q27" s="159"/>
+      <c r="O27" s="264"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="186"/>
       <c r="R27" s="150"/>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="135"/>
-      <c r="B28" s="194"/>
-      <c r="C28" s="194"/>
-      <c r="D28" s="211"/>
-      <c r="E28" s="212"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="182"/>
+      <c r="E28" s="183"/>
       <c r="F28" s="139"/>
       <c r="G28" s="129"/>
       <c r="H28" s="129"/>
       <c r="I28" s="129"/>
       <c r="J28" s="129"/>
       <c r="K28" s="129"/>
-      <c r="L28" s="200"/>
+      <c r="L28" s="204"/>
       <c r="M28" s="147" t="str">
         <f t="shared" ref="M28" si="10">IF(ISBLANK(A28),"",A28)</f>
         <v/>
       </c>
-      <c r="N28" s="215" t="str">
+      <c r="N28" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O28" s="216"/>
-      <c r="P28" s="157"/>
-      <c r="Q28" s="159"/>
+      <c r="O28" s="262"/>
+      <c r="P28" s="184"/>
+      <c r="Q28" s="186"/>
       <c r="R28" s="149"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3747,54 +3797,54 @@
         <f t="shared" ref="A29" si="11">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="195"/>
-      <c r="C29" s="195"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="210"/>
+      <c r="B29" s="158"/>
+      <c r="C29" s="158"/>
+      <c r="D29" s="180"/>
+      <c r="E29" s="181"/>
       <c r="F29" s="141"/>
       <c r="G29" s="127"/>
       <c r="H29" s="127"/>
       <c r="I29" s="127"/>
       <c r="J29" s="129"/>
       <c r="K29" s="128"/>
-      <c r="L29" s="200"/>
+      <c r="L29" s="204"/>
       <c r="M29" s="148" t="str">
         <f t="shared" ref="M29" si="12">A29</f>
         <v/>
       </c>
-      <c r="N29" s="213" t="str">
+      <c r="N29" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O29" s="214"/>
-      <c r="P29" s="157"/>
-      <c r="Q29" s="159"/>
+      <c r="O29" s="264"/>
+      <c r="P29" s="184"/>
+      <c r="Q29" s="186"/>
       <c r="R29" s="150"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="134"/>
-      <c r="B30" s="194"/>
-      <c r="C30" s="194"/>
-      <c r="D30" s="211"/>
-      <c r="E30" s="212"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="182"/>
+      <c r="E30" s="183"/>
       <c r="F30" s="139"/>
       <c r="G30" s="129"/>
       <c r="H30" s="129"/>
       <c r="I30" s="140"/>
       <c r="J30" s="143"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="200"/>
+      <c r="L30" s="204"/>
       <c r="M30" s="147" t="str">
         <f t="shared" ref="M30" si="13">IF(ISBLANK(A30),"",A30)</f>
         <v/>
       </c>
-      <c r="N30" s="215" t="str">
+      <c r="N30" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O30" s="216"/>
-      <c r="P30" s="157"/>
-      <c r="Q30" s="159"/>
+      <c r="O30" s="262"/>
+      <c r="P30" s="184"/>
+      <c r="Q30" s="186"/>
       <c r="R30" s="149"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3802,54 +3852,54 @@
         <f t="shared" ref="A31" si="14">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="195"/>
-      <c r="C31" s="195"/>
-      <c r="D31" s="209"/>
-      <c r="E31" s="210"/>
+      <c r="B31" s="158"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="180"/>
+      <c r="E31" s="181"/>
       <c r="F31" s="141"/>
       <c r="G31" s="127"/>
       <c r="H31" s="127"/>
       <c r="I31" s="127"/>
       <c r="J31" s="127"/>
       <c r="K31" s="128"/>
-      <c r="L31" s="200"/>
+      <c r="L31" s="204"/>
       <c r="M31" s="148" t="str">
         <f t="shared" ref="M31" si="15">A31</f>
         <v/>
       </c>
-      <c r="N31" s="213" t="str">
+      <c r="N31" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O31" s="214"/>
-      <c r="P31" s="157"/>
-      <c r="Q31" s="159"/>
+      <c r="O31" s="264"/>
+      <c r="P31" s="184"/>
+      <c r="Q31" s="186"/>
       <c r="R31" s="150"/>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="134"/>
-      <c r="B32" s="194"/>
-      <c r="C32" s="194"/>
-      <c r="D32" s="211"/>
-      <c r="E32" s="212"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="157"/>
+      <c r="D32" s="182"/>
+      <c r="E32" s="183"/>
       <c r="F32" s="139"/>
       <c r="G32" s="129"/>
       <c r="H32" s="129"/>
       <c r="I32" s="129"/>
       <c r="J32" s="129"/>
       <c r="K32" s="129"/>
-      <c r="L32" s="200"/>
+      <c r="L32" s="204"/>
       <c r="M32" s="147" t="str">
         <f t="shared" ref="M32" si="16">IF(ISBLANK(A32),"",A32)</f>
         <v/>
       </c>
-      <c r="N32" s="215" t="str">
+      <c r="N32" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O32" s="216"/>
-      <c r="P32" s="157"/>
-      <c r="Q32" s="159"/>
+      <c r="O32" s="262"/>
+      <c r="P32" s="184"/>
+      <c r="Q32" s="186"/>
       <c r="R32" s="149"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3857,54 +3907,54 @@
         <f t="shared" ref="A33" si="17">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
-      <c r="D33" s="209"/>
-      <c r="E33" s="210"/>
+      <c r="B33" s="158"/>
+      <c r="C33" s="158"/>
+      <c r="D33" s="180"/>
+      <c r="E33" s="181"/>
       <c r="F33" s="141"/>
       <c r="G33" s="127"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
       <c r="J33" s="127"/>
       <c r="K33" s="128"/>
-      <c r="L33" s="200"/>
+      <c r="L33" s="204"/>
       <c r="M33" s="148" t="str">
         <f t="shared" ref="M33" si="18">A33</f>
         <v/>
       </c>
-      <c r="N33" s="213" t="str">
+      <c r="N33" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O33" s="214"/>
-      <c r="P33" s="157"/>
-      <c r="Q33" s="159"/>
+      <c r="O33" s="264"/>
+      <c r="P33" s="184"/>
+      <c r="Q33" s="186"/>
       <c r="R33" s="150"/>
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="134"/>
-      <c r="B34" s="194"/>
-      <c r="C34" s="194"/>
-      <c r="D34" s="211"/>
-      <c r="E34" s="212"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="183"/>
       <c r="F34" s="139"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
       <c r="I34" s="129"/>
       <c r="J34" s="129"/>
       <c r="K34" s="129"/>
-      <c r="L34" s="200"/>
+      <c r="L34" s="204"/>
       <c r="M34" s="147" t="str">
         <f t="shared" ref="M34" si="19">IF(ISBLANK(A34),"",A34)</f>
         <v/>
       </c>
-      <c r="N34" s="215" t="str">
+      <c r="N34" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O34" s="216"/>
-      <c r="P34" s="157"/>
-      <c r="Q34" s="159"/>
+      <c r="O34" s="262"/>
+      <c r="P34" s="184"/>
+      <c r="Q34" s="186"/>
       <c r="R34" s="149"/>
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3912,54 +3962,54 @@
         <f t="shared" ref="A35" si="20">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="195"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="209"/>
-      <c r="E35" s="210"/>
+      <c r="B35" s="158"/>
+      <c r="C35" s="158"/>
+      <c r="D35" s="180"/>
+      <c r="E35" s="181"/>
       <c r="F35" s="141"/>
       <c r="G35" s="127"/>
       <c r="H35" s="127"/>
       <c r="I35" s="127"/>
       <c r="J35" s="127"/>
       <c r="K35" s="128"/>
-      <c r="L35" s="200"/>
+      <c r="L35" s="204"/>
       <c r="M35" s="148" t="str">
         <f t="shared" ref="M35" si="21">A35</f>
         <v/>
       </c>
-      <c r="N35" s="213" t="str">
+      <c r="N35" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O35" s="214"/>
-      <c r="P35" s="157"/>
-      <c r="Q35" s="159"/>
+      <c r="O35" s="264"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="186"/>
       <c r="R35" s="150"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134"/>
-      <c r="B36" s="194"/>
-      <c r="C36" s="194"/>
-      <c r="D36" s="211"/>
-      <c r="E36" s="212"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="157"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="183"/>
       <c r="F36" s="139"/>
       <c r="G36" s="129"/>
       <c r="H36" s="129"/>
       <c r="I36" s="129"/>
       <c r="J36" s="129"/>
       <c r="K36" s="129"/>
-      <c r="L36" s="200"/>
+      <c r="L36" s="204"/>
       <c r="M36" s="147" t="str">
         <f t="shared" ref="M36" si="22">IF(ISBLANK(A36),"",A36)</f>
         <v/>
       </c>
-      <c r="N36" s="215" t="str">
+      <c r="N36" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O36" s="216"/>
-      <c r="P36" s="157"/>
-      <c r="Q36" s="159"/>
+      <c r="O36" s="262"/>
+      <c r="P36" s="184"/>
+      <c r="Q36" s="186"/>
       <c r="R36" s="149"/>
     </row>
     <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3967,54 +4017,54 @@
         <f t="shared" ref="A37" si="23">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="195"/>
-      <c r="C37" s="195"/>
-      <c r="D37" s="209"/>
-      <c r="E37" s="210"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="158"/>
+      <c r="D37" s="180"/>
+      <c r="E37" s="181"/>
       <c r="F37" s="141"/>
       <c r="G37" s="127"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
       <c r="J37" s="127"/>
       <c r="K37" s="128"/>
-      <c r="L37" s="200"/>
+      <c r="L37" s="204"/>
       <c r="M37" s="148" t="str">
         <f t="shared" ref="M37" si="24">A37</f>
         <v/>
       </c>
-      <c r="N37" s="213" t="str">
+      <c r="N37" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O37" s="214"/>
-      <c r="P37" s="157"/>
-      <c r="Q37" s="159"/>
+      <c r="O37" s="264"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="186"/>
       <c r="R37" s="150"/>
     </row>
     <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="134"/>
-      <c r="B38" s="194"/>
-      <c r="C38" s="194"/>
-      <c r="D38" s="211"/>
-      <c r="E38" s="212"/>
+      <c r="B38" s="157"/>
+      <c r="C38" s="157"/>
+      <c r="D38" s="182"/>
+      <c r="E38" s="183"/>
       <c r="F38" s="139"/>
       <c r="G38" s="129"/>
       <c r="H38" s="129"/>
       <c r="I38" s="129"/>
       <c r="J38" s="129"/>
       <c r="K38" s="129"/>
-      <c r="L38" s="200"/>
+      <c r="L38" s="204"/>
       <c r="M38" s="147" t="str">
         <f t="shared" ref="M38" si="25">IF(ISBLANK(A38),"",A38)</f>
         <v/>
       </c>
-      <c r="N38" s="215" t="str">
+      <c r="N38" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O38" s="216"/>
-      <c r="P38" s="157"/>
-      <c r="Q38" s="159"/>
+      <c r="O38" s="262"/>
+      <c r="P38" s="184"/>
+      <c r="Q38" s="186"/>
       <c r="R38" s="149"/>
     </row>
     <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,54 +4072,54 @@
         <f t="shared" ref="A39" si="26">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="195"/>
-      <c r="C39" s="195"/>
-      <c r="D39" s="209"/>
-      <c r="E39" s="210"/>
+      <c r="B39" s="158"/>
+      <c r="C39" s="158"/>
+      <c r="D39" s="180"/>
+      <c r="E39" s="181"/>
       <c r="F39" s="141"/>
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
       <c r="K39" s="128"/>
-      <c r="L39" s="200"/>
+      <c r="L39" s="204"/>
       <c r="M39" s="148" t="str">
         <f t="shared" ref="M39" si="27">A39</f>
         <v/>
       </c>
-      <c r="N39" s="213" t="str">
+      <c r="N39" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O39" s="214"/>
-      <c r="P39" s="157"/>
-      <c r="Q39" s="159"/>
+      <c r="O39" s="264"/>
+      <c r="P39" s="184"/>
+      <c r="Q39" s="186"/>
       <c r="R39" s="150"/>
     </row>
     <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="134"/>
-      <c r="B40" s="194"/>
-      <c r="C40" s="194"/>
-      <c r="D40" s="211"/>
-      <c r="E40" s="212"/>
+      <c r="B40" s="157"/>
+      <c r="C40" s="157"/>
+      <c r="D40" s="182"/>
+      <c r="E40" s="183"/>
       <c r="F40" s="139"/>
       <c r="G40" s="129"/>
       <c r="H40" s="129"/>
       <c r="I40" s="129"/>
       <c r="J40" s="129"/>
       <c r="K40" s="129"/>
-      <c r="L40" s="200"/>
+      <c r="L40" s="204"/>
       <c r="M40" s="147" t="str">
         <f t="shared" ref="M40" si="28">IF(ISBLANK(A40),"",A40)</f>
         <v/>
       </c>
-      <c r="N40" s="215" t="str">
+      <c r="N40" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O40" s="216"/>
-      <c r="P40" s="157"/>
-      <c r="Q40" s="159"/>
+      <c r="O40" s="262"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="186"/>
       <c r="R40" s="149"/>
     </row>
     <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4077,54 +4127,54 @@
         <f t="shared" ref="A41" si="29">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="195"/>
-      <c r="C41" s="195"/>
-      <c r="D41" s="209"/>
-      <c r="E41" s="210"/>
+      <c r="B41" s="158"/>
+      <c r="C41" s="158"/>
+      <c r="D41" s="180"/>
+      <c r="E41" s="181"/>
       <c r="F41" s="141"/>
       <c r="G41" s="127"/>
       <c r="H41" s="127"/>
       <c r="I41" s="127"/>
       <c r="J41" s="127"/>
       <c r="K41" s="128"/>
-      <c r="L41" s="200"/>
+      <c r="L41" s="204"/>
       <c r="M41" s="148" t="str">
         <f t="shared" ref="M41" si="30">A41</f>
         <v/>
       </c>
-      <c r="N41" s="213" t="str">
+      <c r="N41" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O41" s="214"/>
-      <c r="P41" s="157"/>
-      <c r="Q41" s="159"/>
+      <c r="O41" s="264"/>
+      <c r="P41" s="184"/>
+      <c r="Q41" s="186"/>
       <c r="R41" s="150"/>
     </row>
     <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="134"/>
-      <c r="B42" s="194"/>
-      <c r="C42" s="194"/>
-      <c r="D42" s="211"/>
-      <c r="E42" s="212"/>
+      <c r="B42" s="157"/>
+      <c r="C42" s="157"/>
+      <c r="D42" s="182"/>
+      <c r="E42" s="183"/>
       <c r="F42" s="139"/>
       <c r="G42" s="129"/>
       <c r="H42" s="129"/>
       <c r="I42" s="129"/>
       <c r="J42" s="129"/>
       <c r="K42" s="129"/>
-      <c r="L42" s="200"/>
+      <c r="L42" s="204"/>
       <c r="M42" s="147" t="str">
         <f t="shared" ref="M42" si="31">IF(ISBLANK(A42),"",A42)</f>
         <v/>
       </c>
-      <c r="N42" s="215" t="str">
+      <c r="N42" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O42" s="216"/>
-      <c r="P42" s="157"/>
-      <c r="Q42" s="159"/>
+      <c r="O42" s="262"/>
+      <c r="P42" s="184"/>
+      <c r="Q42" s="186"/>
       <c r="R42" s="149"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4132,54 +4182,54 @@
         <f t="shared" ref="A43" si="32">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="195"/>
-      <c r="C43" s="195"/>
-      <c r="D43" s="209"/>
-      <c r="E43" s="210"/>
+      <c r="B43" s="158"/>
+      <c r="C43" s="158"/>
+      <c r="D43" s="180"/>
+      <c r="E43" s="181"/>
       <c r="F43" s="141"/>
       <c r="G43" s="127"/>
       <c r="H43" s="127"/>
       <c r="I43" s="127"/>
       <c r="J43" s="127"/>
       <c r="K43" s="128"/>
-      <c r="L43" s="200"/>
+      <c r="L43" s="204"/>
       <c r="M43" s="148" t="str">
         <f t="shared" ref="M43" si="33">A43</f>
         <v/>
       </c>
-      <c r="N43" s="213" t="str">
+      <c r="N43" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O43" s="214"/>
-      <c r="P43" s="157"/>
-      <c r="Q43" s="159"/>
+      <c r="O43" s="264"/>
+      <c r="P43" s="184"/>
+      <c r="Q43" s="186"/>
       <c r="R43" s="150"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="134"/>
-      <c r="B44" s="194"/>
-      <c r="C44" s="194"/>
-      <c r="D44" s="211"/>
-      <c r="E44" s="212"/>
+      <c r="B44" s="157"/>
+      <c r="C44" s="157"/>
+      <c r="D44" s="182"/>
+      <c r="E44" s="183"/>
       <c r="F44" s="139"/>
       <c r="G44" s="129"/>
       <c r="H44" s="129"/>
       <c r="I44" s="129"/>
       <c r="J44" s="129"/>
       <c r="K44" s="129"/>
-      <c r="L44" s="200"/>
+      <c r="L44" s="204"/>
       <c r="M44" s="147" t="str">
         <f t="shared" ref="M44" si="34">IF(ISBLANK(A44),"",A44)</f>
         <v/>
       </c>
-      <c r="N44" s="215" t="str">
+      <c r="N44" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O44" s="216"/>
-      <c r="P44" s="157"/>
-      <c r="Q44" s="159"/>
+      <c r="O44" s="262"/>
+      <c r="P44" s="184"/>
+      <c r="Q44" s="186"/>
       <c r="R44" s="149"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4187,54 +4237,54 @@
         <f t="shared" ref="A45" si="35">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="195"/>
-      <c r="C45" s="195"/>
-      <c r="D45" s="209"/>
-      <c r="E45" s="210"/>
+      <c r="B45" s="158"/>
+      <c r="C45" s="158"/>
+      <c r="D45" s="180"/>
+      <c r="E45" s="181"/>
       <c r="F45" s="141"/>
       <c r="G45" s="127"/>
       <c r="H45" s="127"/>
       <c r="I45" s="127"/>
       <c r="J45" s="127"/>
       <c r="K45" s="128"/>
-      <c r="L45" s="200"/>
+      <c r="L45" s="204"/>
       <c r="M45" s="148" t="str">
         <f t="shared" ref="M45" si="36">A45</f>
         <v/>
       </c>
-      <c r="N45" s="213" t="str">
+      <c r="N45" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O45" s="214"/>
-      <c r="P45" s="157"/>
-      <c r="Q45" s="159"/>
+      <c r="O45" s="264"/>
+      <c r="P45" s="184"/>
+      <c r="Q45" s="186"/>
       <c r="R45" s="150"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="134"/>
-      <c r="B46" s="194"/>
-      <c r="C46" s="194"/>
-      <c r="D46" s="211"/>
-      <c r="E46" s="212"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="157"/>
+      <c r="D46" s="182"/>
+      <c r="E46" s="183"/>
       <c r="F46" s="139"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
       <c r="I46" s="129"/>
       <c r="J46" s="129"/>
       <c r="K46" s="129"/>
-      <c r="L46" s="200"/>
+      <c r="L46" s="204"/>
       <c r="M46" s="147" t="str">
         <f t="shared" ref="M46" si="37">IF(ISBLANK(A46),"",A46)</f>
         <v/>
       </c>
-      <c r="N46" s="215" t="str">
+      <c r="N46" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O46" s="216"/>
-      <c r="P46" s="157"/>
-      <c r="Q46" s="159"/>
+      <c r="O46" s="262"/>
+      <c r="P46" s="184"/>
+      <c r="Q46" s="186"/>
       <c r="R46" s="149"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4242,54 +4292,54 @@
         <f t="shared" ref="A47" si="38">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="195"/>
-      <c r="C47" s="195"/>
-      <c r="D47" s="209"/>
-      <c r="E47" s="210"/>
+      <c r="B47" s="158"/>
+      <c r="C47" s="158"/>
+      <c r="D47" s="180"/>
+      <c r="E47" s="181"/>
       <c r="F47" s="141"/>
       <c r="G47" s="127"/>
       <c r="H47" s="127"/>
       <c r="I47" s="127"/>
       <c r="J47" s="127"/>
       <c r="K47" s="128"/>
-      <c r="L47" s="200"/>
+      <c r="L47" s="204"/>
       <c r="M47" s="148" t="str">
         <f t="shared" ref="M47" si="39">A47</f>
         <v/>
       </c>
-      <c r="N47" s="213" t="str">
+      <c r="N47" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O47" s="214"/>
-      <c r="P47" s="157"/>
-      <c r="Q47" s="159"/>
+      <c r="O47" s="264"/>
+      <c r="P47" s="184"/>
+      <c r="Q47" s="186"/>
       <c r="R47" s="150"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="134"/>
-      <c r="B48" s="194"/>
-      <c r="C48" s="194"/>
-      <c r="D48" s="211"/>
-      <c r="E48" s="212"/>
+      <c r="B48" s="157"/>
+      <c r="C48" s="157"/>
+      <c r="D48" s="182"/>
+      <c r="E48" s="183"/>
       <c r="F48" s="139"/>
       <c r="G48" s="129"/>
       <c r="H48" s="129"/>
       <c r="I48" s="129"/>
       <c r="J48" s="129"/>
       <c r="K48" s="129"/>
-      <c r="L48" s="200"/>
+      <c r="L48" s="204"/>
       <c r="M48" s="147" t="str">
         <f t="shared" ref="M48" si="40">IF(ISBLANK(A48),"",A48)</f>
         <v/>
       </c>
-      <c r="N48" s="215" t="str">
+      <c r="N48" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O48" s="216"/>
-      <c r="P48" s="157"/>
-      <c r="Q48" s="159"/>
+      <c r="O48" s="262"/>
+      <c r="P48" s="184"/>
+      <c r="Q48" s="186"/>
       <c r="R48" s="149"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4297,54 +4347,54 @@
         <f t="shared" ref="A49" si="41">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="195"/>
-      <c r="C49" s="195"/>
-      <c r="D49" s="209"/>
-      <c r="E49" s="210"/>
+      <c r="B49" s="158"/>
+      <c r="C49" s="158"/>
+      <c r="D49" s="180"/>
+      <c r="E49" s="181"/>
       <c r="F49" s="141"/>
       <c r="G49" s="127"/>
       <c r="H49" s="127"/>
       <c r="I49" s="127"/>
       <c r="J49" s="127"/>
       <c r="K49" s="128"/>
-      <c r="L49" s="200"/>
+      <c r="L49" s="204"/>
       <c r="M49" s="148" t="str">
         <f t="shared" ref="M49" si="42">A49</f>
         <v/>
       </c>
-      <c r="N49" s="213" t="str">
+      <c r="N49" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O49" s="214"/>
-      <c r="P49" s="157"/>
-      <c r="Q49" s="159"/>
+      <c r="O49" s="264"/>
+      <c r="P49" s="184"/>
+      <c r="Q49" s="186"/>
       <c r="R49" s="150"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134"/>
-      <c r="B50" s="194"/>
-      <c r="C50" s="194"/>
-      <c r="D50" s="211"/>
-      <c r="E50" s="212"/>
+      <c r="B50" s="157"/>
+      <c r="C50" s="157"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="183"/>
       <c r="F50" s="139"/>
       <c r="G50" s="129"/>
       <c r="H50" s="129"/>
       <c r="I50" s="129"/>
       <c r="J50" s="129"/>
       <c r="K50" s="129"/>
-      <c r="L50" s="200"/>
+      <c r="L50" s="204"/>
       <c r="M50" s="147" t="str">
         <f t="shared" ref="M50" si="43">IF(ISBLANK(A50),"",A50)</f>
         <v/>
       </c>
-      <c r="N50" s="215" t="str">
+      <c r="N50" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O50" s="216"/>
-      <c r="P50" s="157"/>
-      <c r="Q50" s="159"/>
+      <c r="O50" s="262"/>
+      <c r="P50" s="184"/>
+      <c r="Q50" s="186"/>
       <c r="R50" s="149"/>
     </row>
     <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4352,54 +4402,54 @@
         <f t="shared" ref="A51" si="44">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="195"/>
-      <c r="C51" s="195"/>
-      <c r="D51" s="209"/>
-      <c r="E51" s="210"/>
+      <c r="B51" s="158"/>
+      <c r="C51" s="158"/>
+      <c r="D51" s="180"/>
+      <c r="E51" s="181"/>
       <c r="F51" s="141"/>
       <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127"/>
       <c r="J51" s="127"/>
       <c r="K51" s="128"/>
-      <c r="L51" s="200"/>
+      <c r="L51" s="204"/>
       <c r="M51" s="148" t="str">
         <f t="shared" ref="M51" si="45">A51</f>
         <v/>
       </c>
-      <c r="N51" s="213" t="str">
+      <c r="N51" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O51" s="214"/>
-      <c r="P51" s="157"/>
-      <c r="Q51" s="159"/>
+      <c r="O51" s="264"/>
+      <c r="P51" s="184"/>
+      <c r="Q51" s="186"/>
       <c r="R51" s="150"/>
     </row>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="134"/>
-      <c r="B52" s="194"/>
-      <c r="C52" s="194"/>
-      <c r="D52" s="211"/>
-      <c r="E52" s="212"/>
+      <c r="B52" s="157"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="183"/>
       <c r="F52" s="139"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
       <c r="I52" s="129"/>
       <c r="J52" s="129"/>
       <c r="K52" s="129"/>
-      <c r="L52" s="200"/>
+      <c r="L52" s="204"/>
       <c r="M52" s="147" t="str">
         <f t="shared" ref="M52" si="46">IF(ISBLANK(A52),"",A52)</f>
         <v/>
       </c>
-      <c r="N52" s="215" t="str">
+      <c r="N52" s="261" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O52" s="216"/>
-      <c r="P52" s="157"/>
-      <c r="Q52" s="159"/>
+      <c r="O52" s="262"/>
+      <c r="P52" s="184"/>
+      <c r="Q52" s="186"/>
       <c r="R52" s="149"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4407,28 +4457,28 @@
         <f t="shared" ref="A53" si="47">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B53" s="195"/>
-      <c r="C53" s="195"/>
-      <c r="D53" s="209"/>
-      <c r="E53" s="210"/>
+      <c r="B53" s="158"/>
+      <c r="C53" s="158"/>
+      <c r="D53" s="180"/>
+      <c r="E53" s="181"/>
       <c r="F53" s="141"/>
       <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127"/>
       <c r="J53" s="127"/>
       <c r="K53" s="128"/>
-      <c r="L53" s="201"/>
+      <c r="L53" s="205"/>
       <c r="M53" s="148" t="str">
         <f t="shared" ref="M53" si="48">A53</f>
         <v/>
       </c>
-      <c r="N53" s="213" t="str">
+      <c r="N53" s="263" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O53" s="214"/>
-      <c r="P53" s="158"/>
-      <c r="Q53" s="160"/>
+      <c r="O53" s="264"/>
+      <c r="P53" s="185"/>
+      <c r="Q53" s="187"/>
       <c r="R53" s="150"/>
     </row>
     <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4543,8 +4593,8 @@
         <f>SUM(G55:K55)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="218"/>
-      <c r="H58" s="218"/>
+      <c r="G58" s="214"/>
+      <c r="H58" s="214"/>
       <c r="I58" s="49" t="s">
         <v>29</v>
       </c>
@@ -4570,8 +4620,8 @@
         <f>L9</f>
         <v>0</v>
       </c>
-      <c r="G59" s="218"/>
-      <c r="H59" s="218"/>
+      <c r="G59" s="214"/>
+      <c r="H59" s="214"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
@@ -4637,31 +4687,31 @@
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
       <c r="B63" s="57"/>
-      <c r="C63" s="219" t="s">
+      <c r="C63" s="215" t="s">
         <v>35</v>
       </c>
-      <c r="D63" s="219"/>
-      <c r="E63" s="219"/>
-      <c r="F63" s="219"/>
-      <c r="G63" s="219"/>
-      <c r="H63" s="219"/>
-      <c r="I63" s="219"/>
-      <c r="J63" s="219"/>
-      <c r="K63" s="219"/>
+      <c r="D63" s="215"/>
+      <c r="E63" s="215"/>
+      <c r="F63" s="215"/>
+      <c r="G63" s="215"/>
+      <c r="H63" s="215"/>
+      <c r="I63" s="215"/>
+      <c r="J63" s="215"/>
+      <c r="K63" s="215"/>
       <c r="L63" s="3"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
       <c r="B64" s="57"/>
-      <c r="C64" s="219"/>
-      <c r="D64" s="219"/>
-      <c r="E64" s="219"/>
-      <c r="F64" s="219"/>
-      <c r="G64" s="219"/>
-      <c r="H64" s="219"/>
-      <c r="I64" s="219"/>
-      <c r="J64" s="219"/>
-      <c r="K64" s="219"/>
+      <c r="C64" s="215"/>
+      <c r="D64" s="215"/>
+      <c r="E64" s="215"/>
+      <c r="F64" s="215"/>
+      <c r="G64" s="215"/>
+      <c r="H64" s="215"/>
+      <c r="I64" s="215"/>
+      <c r="J64" s="215"/>
+      <c r="K64" s="215"/>
       <c r="L64" s="3"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -4772,14 +4822,14 @@
       <c r="J71" s="60"/>
       <c r="K71" s="60"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="217" t="s">
+      <c r="M71" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="N71" s="217"/>
-      <c r="O71" s="217"/>
-      <c r="P71" s="217"/>
-      <c r="Q71" s="217"/>
-      <c r="R71" s="217"/>
+      <c r="N71" s="213"/>
+      <c r="O71" s="213"/>
+      <c r="P71" s="213"/>
+      <c r="Q71" s="213"/>
+      <c r="R71" s="213"/>
     </row>
     <row r="72" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="50"/>
@@ -4796,14 +4846,14 @@
       <c r="J72" s="60"/>
       <c r="K72" s="60"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="217" t="s">
+      <c r="M72" s="213" t="s">
         <v>88</v>
       </c>
-      <c r="N72" s="217"/>
-      <c r="O72" s="217"/>
-      <c r="P72" s="217"/>
-      <c r="Q72" s="217"/>
-      <c r="R72" s="217"/>
+      <c r="N72" s="213"/>
+      <c r="O72" s="213"/>
+      <c r="P72" s="213"/>
+      <c r="Q72" s="213"/>
+      <c r="R72" s="213"/>
     </row>
     <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
@@ -4822,12 +4872,12 @@
       <c r="J73" s="60"/>
       <c r="K73" s="60"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="221"/>
-      <c r="N73" s="221"/>
-      <c r="O73" s="221"/>
-      <c r="P73" s="221"/>
-      <c r="Q73" s="221"/>
-      <c r="R73" s="221"/>
+      <c r="M73" s="217"/>
+      <c r="N73" s="217"/>
+      <c r="O73" s="217"/>
+      <c r="P73" s="217"/>
+      <c r="Q73" s="217"/>
+      <c r="R73" s="217"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="50"/>
@@ -4853,24 +4903,24 @@
       <c r="E75" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="222">
+      <c r="F75" s="218">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="222"/>
-      <c r="H75" s="222"/>
-      <c r="I75" s="222"/>
-      <c r="J75" s="222"/>
-      <c r="K75" s="222"/>
+      <c r="G75" s="218"/>
+      <c r="H75" s="218"/>
+      <c r="I75" s="218"/>
+      <c r="J75" s="218"/>
+      <c r="K75" s="218"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="223" t="s">
+      <c r="M75" s="219" t="s">
         <v>89</v>
       </c>
-      <c r="N75" s="223"/>
-      <c r="O75" s="223"/>
-      <c r="P75" s="223"/>
-      <c r="Q75" s="223"/>
-      <c r="R75" s="223"/>
+      <c r="N75" s="219"/>
+      <c r="O75" s="219"/>
+      <c r="P75" s="219"/>
+      <c r="Q75" s="219"/>
+      <c r="R75" s="219"/>
     </row>
     <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="50"/>
@@ -4902,14 +4952,14 @@
       <c r="E77" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="224">
+      <c r="F77" s="220">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="224"/>
-      <c r="H77" s="224"/>
-      <c r="I77" s="224"/>
-      <c r="J77" s="224"/>
+      <c r="G77" s="220"/>
+      <c r="H77" s="220"/>
+      <c r="I77" s="220"/>
+      <c r="J77" s="220"/>
       <c r="K77" s="40"/>
       <c r="L77" s="50"/>
       <c r="M77" s="75"/>
@@ -4934,13 +4984,13 @@
       <c r="L78" s="50"/>
       <c r="M78" s="133"/>
       <c r="N78" s="133"/>
-      <c r="O78" s="226" t="str">
+      <c r="O78" s="222" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="P78" s="226"/>
-      <c r="Q78" s="226"/>
-      <c r="R78" s="226"/>
+      <c r="P78" s="222"/>
+      <c r="Q78" s="222"/>
+      <c r="R78" s="222"/>
     </row>
     <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="67"/>
@@ -4962,11 +5012,11 @@
       <c r="M79" s="77"/>
       <c r="N79" s="77"/>
       <c r="O79" s="78"/>
-      <c r="P79" s="225" t="str">
+      <c r="P79" s="221" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="Q79" s="225"/>
+      <c r="Q79" s="221"/>
       <c r="R79" s="79"/>
     </row>
     <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
@@ -5004,13 +5054,13 @@
       <c r="L81" s="50"/>
       <c r="M81" s="78"/>
       <c r="N81" s="78"/>
-      <c r="O81" s="227" t="str">
+      <c r="O81" s="223" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="P81" s="227"/>
-      <c r="Q81" s="227"/>
-      <c r="R81" s="227"/>
+      <c r="P81" s="223"/>
+      <c r="Q81" s="223"/>
+      <c r="R81" s="223"/>
     </row>
     <row r="82" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="50"/>
@@ -5047,12 +5097,12 @@
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="228"/>
-      <c r="N83" s="228"/>
-      <c r="O83" s="228"/>
-      <c r="P83" s="228"/>
-      <c r="Q83" s="228"/>
-      <c r="R83" s="228"/>
+      <c r="M83" s="224"/>
+      <c r="N83" s="224"/>
+      <c r="O83" s="224"/>
+      <c r="P83" s="224"/>
+      <c r="Q83" s="224"/>
+      <c r="R83" s="224"/>
     </row>
     <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="50"/>
@@ -5071,14 +5121,14 @@
       <c r="J84" s="74"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="220" t="s">
+      <c r="M84" s="216" t="s">
         <v>90</v>
       </c>
-      <c r="N84" s="220"/>
-      <c r="O84" s="220"/>
-      <c r="P84" s="220"/>
-      <c r="Q84" s="220"/>
-      <c r="R84" s="220"/>
+      <c r="N84" s="216"/>
+      <c r="O84" s="216"/>
+      <c r="P84" s="216"/>
+      <c r="Q84" s="216"/>
+      <c r="R84" s="216"/>
     </row>
     <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="50"/>
@@ -5093,14 +5143,14 @@
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="220" t="s">
+      <c r="M85" s="216" t="s">
         <v>91</v>
       </c>
-      <c r="N85" s="220"/>
-      <c r="O85" s="220"/>
-      <c r="P85" s="220"/>
-      <c r="Q85" s="220"/>
-      <c r="R85" s="220"/>
+      <c r="N85" s="216"/>
+      <c r="O85" s="216"/>
+      <c r="P85" s="216"/>
+      <c r="Q85" s="216"/>
+      <c r="R85" s="216"/>
     </row>
     <row r="86" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="50"/>
@@ -5119,12 +5169,12 @@
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="229"/>
-      <c r="N86" s="229"/>
-      <c r="O86" s="229"/>
-      <c r="P86" s="229"/>
-      <c r="Q86" s="229"/>
-      <c r="R86" s="229"/>
+      <c r="M86" s="225"/>
+      <c r="N86" s="225"/>
+      <c r="O86" s="225"/>
+      <c r="P86" s="225"/>
+      <c r="Q86" s="225"/>
+      <c r="R86" s="225"/>
     </row>
     <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="50"/>
@@ -5139,12 +5189,12 @@
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="220"/>
-      <c r="N87" s="220"/>
-      <c r="O87" s="220"/>
-      <c r="P87" s="220"/>
-      <c r="Q87" s="220"/>
-      <c r="R87" s="220"/>
+      <c r="M87" s="216"/>
+      <c r="N87" s="216"/>
+      <c r="O87" s="216"/>
+      <c r="P87" s="216"/>
+      <c r="Q87" s="216"/>
+      <c r="R87" s="216"/>
     </row>
     <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50"/>
@@ -5156,21 +5206,21 @@
       <c r="E88" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="244"/>
-      <c r="G88" s="244"/>
-      <c r="H88" s="244"/>
-      <c r="I88" s="244"/>
-      <c r="J88" s="244"/>
+      <c r="F88" s="236"/>
+      <c r="G88" s="236"/>
+      <c r="H88" s="236"/>
+      <c r="I88" s="236"/>
+      <c r="J88" s="236"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="220" t="s">
+      <c r="M88" s="216" t="s">
         <v>92</v>
       </c>
-      <c r="N88" s="220"/>
-      <c r="O88" s="220"/>
-      <c r="P88" s="220"/>
-      <c r="Q88" s="220"/>
-      <c r="R88" s="220"/>
+      <c r="N88" s="216"/>
+      <c r="O88" s="216"/>
+      <c r="P88" s="216"/>
+      <c r="Q88" s="216"/>
+      <c r="R88" s="216"/>
     </row>
     <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="50"/>
@@ -5323,12 +5373,12 @@
       <c r="J95" s="86"/>
       <c r="K95" s="27"/>
       <c r="L95" s="17"/>
-      <c r="M95" s="229"/>
-      <c r="N95" s="229"/>
-      <c r="O95" s="229"/>
-      <c r="P95" s="229"/>
-      <c r="Q95" s="229"/>
-      <c r="R95" s="229"/>
+      <c r="M95" s="225"/>
+      <c r="N95" s="225"/>
+      <c r="O95" s="225"/>
+      <c r="P95" s="225"/>
+      <c r="Q95" s="225"/>
+      <c r="R95" s="225"/>
     </row>
     <row r="96" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
@@ -5345,12 +5395,12 @@
       <c r="J96" s="86"/>
       <c r="K96" s="27"/>
       <c r="L96" s="17"/>
-      <c r="M96" s="229"/>
-      <c r="N96" s="229"/>
-      <c r="O96" s="229"/>
-      <c r="P96" s="229"/>
-      <c r="Q96" s="229"/>
-      <c r="R96" s="229"/>
+      <c r="M96" s="225"/>
+      <c r="N96" s="225"/>
+      <c r="O96" s="225"/>
+      <c r="P96" s="225"/>
+      <c r="Q96" s="225"/>
+      <c r="R96" s="225"/>
     </row>
     <row r="97" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
@@ -5367,12 +5417,12 @@
       <c r="J97" s="86"/>
       <c r="K97" s="27"/>
       <c r="L97" s="17"/>
-      <c r="M97" s="229"/>
-      <c r="N97" s="229"/>
-      <c r="O97" s="229"/>
-      <c r="P97" s="229"/>
-      <c r="Q97" s="229"/>
-      <c r="R97" s="229"/>
+      <c r="M97" s="225"/>
+      <c r="N97" s="225"/>
+      <c r="O97" s="225"/>
+      <c r="P97" s="225"/>
+      <c r="Q97" s="225"/>
+      <c r="R97" s="225"/>
     </row>
     <row r="98" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
@@ -5389,12 +5439,12 @@
       <c r="J98" s="86"/>
       <c r="K98" s="27"/>
       <c r="L98" s="17"/>
-      <c r="M98" s="229"/>
-      <c r="N98" s="229"/>
-      <c r="O98" s="229"/>
-      <c r="P98" s="229"/>
-      <c r="Q98" s="229"/>
-      <c r="R98" s="229"/>
+      <c r="M98" s="225"/>
+      <c r="N98" s="225"/>
+      <c r="O98" s="225"/>
+      <c r="P98" s="225"/>
+      <c r="Q98" s="225"/>
+      <c r="R98" s="225"/>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="64"/>
@@ -5411,12 +5461,12 @@
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
       <c r="L99" s="17"/>
-      <c r="M99" s="220"/>
-      <c r="N99" s="220"/>
-      <c r="O99" s="220"/>
-      <c r="P99" s="220"/>
-      <c r="Q99" s="220"/>
-      <c r="R99" s="220"/>
+      <c r="M99" s="216"/>
+      <c r="N99" s="216"/>
+      <c r="O99" s="216"/>
+      <c r="P99" s="216"/>
+      <c r="Q99" s="216"/>
+      <c r="R99" s="216"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="50"/>
@@ -5721,36 +5771,36 @@
     </row>
     <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="245" t="s">
+      <c r="A124" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="B124" s="246"/>
-      <c r="C124" s="246"/>
-      <c r="D124" s="246"/>
-      <c r="E124" s="246"/>
-      <c r="F124" s="246"/>
-      <c r="G124" s="246"/>
-      <c r="H124" s="246"/>
-      <c r="I124" s="246"/>
-      <c r="J124" s="246"/>
-      <c r="K124" s="246"/>
-      <c r="L124" s="247"/>
+      <c r="B124" s="238"/>
+      <c r="C124" s="238"/>
+      <c r="D124" s="238"/>
+      <c r="E124" s="238"/>
+      <c r="F124" s="238"/>
+      <c r="G124" s="238"/>
+      <c r="H124" s="238"/>
+      <c r="I124" s="238"/>
+      <c r="J124" s="238"/>
+      <c r="K124" s="238"/>
+      <c r="L124" s="239"/>
     </row>
     <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="248" t="s">
+      <c r="A125" s="240" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="249"/>
-      <c r="C125" s="249"/>
-      <c r="D125" s="249"/>
-      <c r="E125" s="249"/>
-      <c r="F125" s="249"/>
-      <c r="G125" s="249"/>
-      <c r="H125" s="249"/>
-      <c r="I125" s="249"/>
-      <c r="J125" s="249"/>
-      <c r="K125" s="249"/>
-      <c r="L125" s="250"/>
+      <c r="B125" s="241"/>
+      <c r="C125" s="241"/>
+      <c r="D125" s="241"/>
+      <c r="E125" s="241"/>
+      <c r="F125" s="241"/>
+      <c r="G125" s="241"/>
+      <c r="H125" s="241"/>
+      <c r="I125" s="241"/>
+      <c r="J125" s="241"/>
+      <c r="K125" s="241"/>
+      <c r="L125" s="242"/>
     </row>
     <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="105" t="s">
@@ -5758,20 +5808,20 @@
       </c>
       <c r="B126" s="106"/>
       <c r="C126" s="106"/>
-      <c r="D126" s="251">
+      <c r="D126" s="243">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="252"/>
-      <c r="F126" s="252"/>
-      <c r="G126" s="252"/>
-      <c r="H126" s="252"/>
-      <c r="I126" s="253"/>
-      <c r="J126" s="254" t="s">
+      <c r="E126" s="244"/>
+      <c r="F126" s="244"/>
+      <c r="G126" s="244"/>
+      <c r="H126" s="244"/>
+      <c r="I126" s="245"/>
+      <c r="J126" s="246" t="s">
         <v>68</v>
       </c>
-      <c r="K126" s="255"/>
-      <c r="L126" s="256"/>
+      <c r="K126" s="247"/>
+      <c r="L126" s="248"/>
     </row>
     <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="107" t="s">
@@ -5807,23 +5857,23 @@
       <c r="A129" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B129" s="234" t="s">
+      <c r="B129" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="235"/>
-      <c r="D129" s="236" t="s">
+      <c r="C129" s="227"/>
+      <c r="D129" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="E129" s="237"/>
-      <c r="F129" s="237"/>
-      <c r="G129" s="237"/>
-      <c r="H129" s="237"/>
-      <c r="I129" s="237"/>
-      <c r="J129" s="238"/>
-      <c r="K129" s="236" t="s">
+      <c r="E129" s="229"/>
+      <c r="F129" s="229"/>
+      <c r="G129" s="229"/>
+      <c r="H129" s="229"/>
+      <c r="I129" s="229"/>
+      <c r="J129" s="230"/>
+      <c r="K129" s="228" t="s">
         <v>73</v>
       </c>
-      <c r="L129" s="237"/>
+      <c r="L129" s="229"/>
     </row>
     <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="121"/>
@@ -5833,15 +5883,15 @@
       <c r="C130" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="D130" s="239"/>
-      <c r="E130" s="240"/>
-      <c r="F130" s="240"/>
-      <c r="G130" s="240"/>
-      <c r="H130" s="240"/>
-      <c r="I130" s="240"/>
-      <c r="J130" s="241"/>
-      <c r="K130" s="242"/>
-      <c r="L130" s="243"/>
+      <c r="D130" s="231"/>
+      <c r="E130" s="232"/>
+      <c r="F130" s="232"/>
+      <c r="G130" s="232"/>
+      <c r="H130" s="232"/>
+      <c r="I130" s="232"/>
+      <c r="J130" s="233"/>
+      <c r="K130" s="234"/>
+      <c r="L130" s="235"/>
     </row>
     <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="124">
@@ -5849,17 +5899,17 @@
       </c>
       <c r="B131" s="124"/>
       <c r="C131" s="125"/>
-      <c r="D131" s="231" t="s">
+      <c r="D131" s="256" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="232"/>
-      <c r="F131" s="232"/>
-      <c r="G131" s="232"/>
-      <c r="H131" s="232"/>
-      <c r="I131" s="232"/>
-      <c r="J131" s="233"/>
-      <c r="K131" s="230"/>
-      <c r="L131" s="230"/>
+      <c r="E131" s="257"/>
+      <c r="F131" s="257"/>
+      <c r="G131" s="257"/>
+      <c r="H131" s="257"/>
+      <c r="I131" s="257"/>
+      <c r="J131" s="258"/>
+      <c r="K131" s="252"/>
+      <c r="L131" s="252"/>
     </row>
     <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="124">
@@ -5867,17 +5917,17 @@
       </c>
       <c r="B132" s="124"/>
       <c r="C132" s="126"/>
-      <c r="D132" s="231" t="s">
+      <c r="D132" s="256" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="232"/>
-      <c r="F132" s="232"/>
-      <c r="G132" s="232"/>
-      <c r="H132" s="232"/>
-      <c r="I132" s="232"/>
-      <c r="J132" s="233"/>
-      <c r="K132" s="230"/>
-      <c r="L132" s="230"/>
+      <c r="E132" s="257"/>
+      <c r="F132" s="257"/>
+      <c r="G132" s="257"/>
+      <c r="H132" s="257"/>
+      <c r="I132" s="257"/>
+      <c r="J132" s="258"/>
+      <c r="K132" s="252"/>
+      <c r="L132" s="252"/>
     </row>
     <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="124">
@@ -5885,17 +5935,17 @@
       </c>
       <c r="B133" s="124"/>
       <c r="C133" s="126"/>
-      <c r="D133" s="231" t="s">
+      <c r="D133" s="256" t="s">
         <v>78</v>
       </c>
-      <c r="E133" s="232"/>
-      <c r="F133" s="232"/>
-      <c r="G133" s="232"/>
-      <c r="H133" s="232"/>
-      <c r="I133" s="232"/>
-      <c r="J133" s="233"/>
-      <c r="K133" s="230"/>
-      <c r="L133" s="230"/>
+      <c r="E133" s="257"/>
+      <c r="F133" s="257"/>
+      <c r="G133" s="257"/>
+      <c r="H133" s="257"/>
+      <c r="I133" s="257"/>
+      <c r="J133" s="258"/>
+      <c r="K133" s="252"/>
+      <c r="L133" s="252"/>
     </row>
     <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="124">
@@ -5903,17 +5953,17 @@
       </c>
       <c r="B134" s="124"/>
       <c r="C134" s="126"/>
-      <c r="D134" s="231" t="s">
+      <c r="D134" s="256" t="s">
         <v>79</v>
       </c>
-      <c r="E134" s="232"/>
-      <c r="F134" s="232"/>
-      <c r="G134" s="232"/>
-      <c r="H134" s="232"/>
-      <c r="I134" s="232"/>
-      <c r="J134" s="233"/>
-      <c r="K134" s="230"/>
-      <c r="L134" s="230"/>
+      <c r="E134" s="257"/>
+      <c r="F134" s="257"/>
+      <c r="G134" s="257"/>
+      <c r="H134" s="257"/>
+      <c r="I134" s="257"/>
+      <c r="J134" s="258"/>
+      <c r="K134" s="252"/>
+      <c r="L134" s="252"/>
     </row>
     <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="124">
@@ -5921,17 +5971,17 @@
       </c>
       <c r="B135" s="124"/>
       <c r="C135" s="126"/>
-      <c r="D135" s="231" t="s">
+      <c r="D135" s="256" t="s">
         <v>80</v>
       </c>
-      <c r="E135" s="232"/>
-      <c r="F135" s="232"/>
-      <c r="G135" s="232"/>
-      <c r="H135" s="232"/>
-      <c r="I135" s="232"/>
-      <c r="J135" s="233"/>
-      <c r="K135" s="230"/>
-      <c r="L135" s="230"/>
+      <c r="E135" s="257"/>
+      <c r="F135" s="257"/>
+      <c r="G135" s="257"/>
+      <c r="H135" s="257"/>
+      <c r="I135" s="257"/>
+      <c r="J135" s="258"/>
+      <c r="K135" s="252"/>
+      <c r="L135" s="252"/>
     </row>
     <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="124">
@@ -5939,17 +5989,17 @@
       </c>
       <c r="B136" s="124"/>
       <c r="C136" s="126"/>
-      <c r="D136" s="231" t="s">
+      <c r="D136" s="256" t="s">
         <v>81</v>
       </c>
-      <c r="E136" s="232"/>
-      <c r="F136" s="232"/>
-      <c r="G136" s="232"/>
-      <c r="H136" s="232"/>
-      <c r="I136" s="232"/>
-      <c r="J136" s="233"/>
-      <c r="K136" s="230"/>
-      <c r="L136" s="230"/>
+      <c r="E136" s="257"/>
+      <c r="F136" s="257"/>
+      <c r="G136" s="257"/>
+      <c r="H136" s="257"/>
+      <c r="I136" s="257"/>
+      <c r="J136" s="258"/>
+      <c r="K136" s="252"/>
+      <c r="L136" s="252"/>
     </row>
     <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="124">
@@ -5957,17 +6007,17 @@
       </c>
       <c r="B137" s="124"/>
       <c r="C137" s="126"/>
-      <c r="D137" s="231" t="s">
+      <c r="D137" s="256" t="s">
         <v>82</v>
       </c>
-      <c r="E137" s="232"/>
-      <c r="F137" s="232"/>
-      <c r="G137" s="232"/>
-      <c r="H137" s="232"/>
-      <c r="I137" s="232"/>
-      <c r="J137" s="233"/>
-      <c r="K137" s="230"/>
-      <c r="L137" s="230"/>
+      <c r="E137" s="257"/>
+      <c r="F137" s="257"/>
+      <c r="G137" s="257"/>
+      <c r="H137" s="257"/>
+      <c r="I137" s="257"/>
+      <c r="J137" s="258"/>
+      <c r="K137" s="252"/>
+      <c r="L137" s="252"/>
     </row>
     <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="124">
@@ -5975,17 +6025,17 @@
       </c>
       <c r="B138" s="124"/>
       <c r="C138" s="126"/>
-      <c r="D138" s="257" t="s">
+      <c r="D138" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="E138" s="258"/>
-      <c r="F138" s="258"/>
-      <c r="G138" s="258"/>
-      <c r="H138" s="258"/>
-      <c r="I138" s="258"/>
-      <c r="J138" s="259"/>
-      <c r="K138" s="263"/>
-      <c r="L138" s="264"/>
+      <c r="E138" s="250"/>
+      <c r="F138" s="250"/>
+      <c r="G138" s="250"/>
+      <c r="H138" s="250"/>
+      <c r="I138" s="250"/>
+      <c r="J138" s="251"/>
+      <c r="K138" s="259"/>
+      <c r="L138" s="260"/>
     </row>
     <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="124">
@@ -5993,17 +6043,17 @@
       </c>
       <c r="B139" s="124"/>
       <c r="C139" s="126"/>
-      <c r="D139" s="257" t="s">
+      <c r="D139" s="249" t="s">
         <v>83</v>
       </c>
-      <c r="E139" s="258"/>
-      <c r="F139" s="258"/>
-      <c r="G139" s="258"/>
-      <c r="H139" s="258"/>
-      <c r="I139" s="258"/>
-      <c r="J139" s="259"/>
-      <c r="K139" s="230"/>
-      <c r="L139" s="230"/>
+      <c r="E139" s="250"/>
+      <c r="F139" s="250"/>
+      <c r="G139" s="250"/>
+      <c r="H139" s="250"/>
+      <c r="I139" s="250"/>
+      <c r="J139" s="251"/>
+      <c r="K139" s="252"/>
+      <c r="L139" s="252"/>
     </row>
     <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="124">
@@ -6011,17 +6061,17 @@
       </c>
       <c r="B140" s="124"/>
       <c r="C140" s="126"/>
-      <c r="D140" s="257" t="s">
+      <c r="D140" s="249" t="s">
         <v>84</v>
       </c>
-      <c r="E140" s="258"/>
-      <c r="F140" s="258"/>
-      <c r="G140" s="258"/>
-      <c r="H140" s="258"/>
-      <c r="I140" s="258"/>
-      <c r="J140" s="259"/>
-      <c r="K140" s="230"/>
-      <c r="L140" s="230"/>
+      <c r="E140" s="250"/>
+      <c r="F140" s="250"/>
+      <c r="G140" s="250"/>
+      <c r="H140" s="250"/>
+      <c r="I140" s="250"/>
+      <c r="J140" s="251"/>
+      <c r="K140" s="252"/>
+      <c r="L140" s="252"/>
     </row>
     <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="124">
@@ -6029,17 +6079,17 @@
       </c>
       <c r="B141" s="124"/>
       <c r="C141" s="126"/>
-      <c r="D141" s="260" t="s">
+      <c r="D141" s="253" t="s">
         <v>85</v>
       </c>
-      <c r="E141" s="261"/>
-      <c r="F141" s="261"/>
-      <c r="G141" s="261"/>
-      <c r="H141" s="261"/>
-      <c r="I141" s="261"/>
-      <c r="J141" s="262"/>
-      <c r="K141" s="230"/>
-      <c r="L141" s="230"/>
+      <c r="E141" s="254"/>
+      <c r="F141" s="254"/>
+      <c r="G141" s="254"/>
+      <c r="H141" s="254"/>
+      <c r="I141" s="254"/>
+      <c r="J141" s="255"/>
+      <c r="K141" s="252"/>
+      <c r="L141" s="252"/>
     </row>
     <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6051,9 +6101,6 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="168">
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="N37:O37"/>
     <mergeCell ref="N38:O38"/>
     <mergeCell ref="N39:O39"/>
     <mergeCell ref="N50:O50"/>
@@ -6065,6 +6112,8 @@
     <mergeCell ref="N47:O47"/>
     <mergeCell ref="N48:O48"/>
     <mergeCell ref="N49:O49"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="D52:E52"/>
@@ -6080,25 +6129,13 @@
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="N37:O37"/>
     <mergeCell ref="D134:J134"/>
     <mergeCell ref="K134:L134"/>
     <mergeCell ref="D135:J135"/>
@@ -6108,6 +6145,9 @@
     <mergeCell ref="D131:J131"/>
     <mergeCell ref="K131:L131"/>
     <mergeCell ref="D132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="K133:L133"/>
     <mergeCell ref="D140:J140"/>
     <mergeCell ref="K140:L140"/>
     <mergeCell ref="D141:J141"/>
@@ -6118,9 +6158,6 @@
     <mergeCell ref="K138:L138"/>
     <mergeCell ref="D139:J139"/>
     <mergeCell ref="K139:L139"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="K133:L133"/>
     <mergeCell ref="B129:C129"/>
     <mergeCell ref="D129:J130"/>
     <mergeCell ref="K129:L130"/>
@@ -6147,13 +6184,9 @@
     <mergeCell ref="M84:R84"/>
     <mergeCell ref="M85:R85"/>
     <mergeCell ref="M86:R86"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="M72:R72"/>
     <mergeCell ref="B40:C41"/>
     <mergeCell ref="B42:C43"/>
@@ -6166,14 +6199,15 @@
     <mergeCell ref="G59:H59"/>
     <mergeCell ref="C63:K64"/>
     <mergeCell ref="M71:R71"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="L20:L53"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N23:O23"/>
     <mergeCell ref="B22:C23"/>
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="B26:C27"/>
@@ -6187,14 +6221,6 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
     <mergeCell ref="P20:P53"/>
     <mergeCell ref="Q20:Q53"/>
     <mergeCell ref="M2:R2"/>
@@ -6203,6 +6229,25 @@
     <mergeCell ref="L15:L17"/>
     <mergeCell ref="M15:M17"/>
     <mergeCell ref="N15:O16"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L20:L53"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B15:C16"/>
@@ -6213,12 +6258,17 @@
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="B20:C21"/>
   </mergeCells>
   <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868F5EF8-9904-40A0-859E-3626D39367A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F482D3F0-4943-427C-BAEF-CE342B8FBC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim" sheetId="92" r:id="rId1"/>
@@ -2045,6 +2045,207 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2053,11 +2254,139 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2109,10 +2438,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2132,331 +2457,6 @@
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3070,25 +3070,25 @@
     <col min="14" max="15" width="7.42578125" style="8" customWidth="1"/>
     <col min="16" max="16" width="28.28515625" style="8" customWidth="1"/>
     <col min="17" max="17" width="30.5703125" style="8" customWidth="1"/>
-    <col min="18" max="18" width="31.85546875" style="8" customWidth="1"/>
+    <col min="18" max="18" width="50.7109375" style="8" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="163"/>
-      <c r="H1" s="163"/>
-      <c r="I1" s="163"/>
-      <c r="J1" s="163"/>
-      <c r="K1" s="163"/>
-      <c r="L1" s="163"/>
+      <c r="B1" s="249"/>
+      <c r="C1" s="249"/>
+      <c r="D1" s="249"/>
+      <c r="E1" s="249"/>
+      <c r="F1" s="249"/>
+      <c r="G1" s="249"/>
+      <c r="H1" s="249"/>
+      <c r="I1" s="249"/>
+      <c r="J1" s="249"/>
+      <c r="K1" s="249"/>
+      <c r="L1" s="249"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
@@ -3096,26 +3096,26 @@
       <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
-      <c r="P2" s="188"/>
-      <c r="Q2" s="188"/>
-      <c r="R2" s="188"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="249"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="229"/>
+      <c r="O2" s="229"/>
+      <c r="P2" s="229"/>
+      <c r="Q2" s="229"/>
+      <c r="R2" s="229"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
@@ -3136,38 +3136,38 @@
       <c r="R3" s="9"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="176" t="s">
+      <c r="A4" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="176"/>
-      <c r="I4" s="176"/>
-      <c r="J4" s="176"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="176"/>
+      <c r="B4" s="261"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="261"/>
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="261"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="261"/>
+      <c r="K4" s="261"/>
+      <c r="L4" s="261"/>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="177"/>
-      <c r="B5" s="177"/>
-      <c r="C5" s="177"/>
-      <c r="D5" s="177"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="177"/>
+      <c r="A5" s="262"/>
+      <c r="B5" s="262"/>
+      <c r="C5" s="262"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3176,20 +3176,20 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="178" t="s">
+      <c r="A6" s="263" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="178"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="178"/>
-      <c r="L6" s="178"/>
+      <c r="B6" s="263"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="263"/>
+      <c r="E6" s="263"/>
+      <c r="F6" s="263"/>
+      <c r="G6" s="263"/>
+      <c r="H6" s="263"/>
+      <c r="I6" s="263"/>
+      <c r="J6" s="263"/>
+      <c r="K6" s="263"/>
+      <c r="L6" s="263"/>
       <c r="O6" s="16"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -3244,9 +3244,9 @@
       <c r="B9" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="179"/>
-      <c r="D9" s="179"/>
-      <c r="E9" s="179"/>
+      <c r="C9" s="264"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="19" t="s">
@@ -3395,41 +3395,41 @@
       <c r="A15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="164" t="s">
+      <c r="B15" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="164"/>
-      <c r="D15" s="166" t="s">
+      <c r="C15" s="250"/>
+      <c r="D15" s="252" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="167"/>
-      <c r="F15" s="167" t="s">
+      <c r="E15" s="253"/>
+      <c r="F15" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="172" t="s">
+      <c r="G15" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="172"/>
-      <c r="I15" s="172"/>
-      <c r="J15" s="172"/>
-      <c r="K15" s="173"/>
-      <c r="L15" s="189" t="s">
+      <c r="H15" s="258"/>
+      <c r="I15" s="258"/>
+      <c r="J15" s="258"/>
+      <c r="K15" s="259"/>
+      <c r="L15" s="230" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="192" t="s">
+      <c r="M15" s="233" t="s">
         <v>59</v>
       </c>
-      <c r="N15" s="195" t="s">
+      <c r="N15" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="196"/>
-      <c r="P15" s="192" t="s">
+      <c r="O15" s="237"/>
+      <c r="P15" s="233" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" s="199" t="s">
+      <c r="Q15" s="240" t="s">
         <v>62</v>
       </c>
-      <c r="R15" s="192" t="s">
+      <c r="R15" s="233" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3437,23 +3437,23 @@
       <c r="A16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="165"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="170"/>
-      <c r="G16" s="174"/>
-      <c r="H16" s="174"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="174"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="190"/>
-      <c r="M16" s="193"/>
-      <c r="N16" s="197"/>
-      <c r="O16" s="198"/>
-      <c r="P16" s="193"/>
-      <c r="Q16" s="200"/>
-      <c r="R16" s="193"/>
+      <c r="B16" s="251"/>
+      <c r="C16" s="251"/>
+      <c r="D16" s="254"/>
+      <c r="E16" s="255"/>
+      <c r="F16" s="256"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="216"/>
+      <c r="I16" s="216"/>
+      <c r="J16" s="216"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="231"/>
+      <c r="M16" s="234"/>
+      <c r="N16" s="238"/>
+      <c r="O16" s="239"/>
+      <c r="P16" s="234"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="234"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
@@ -3471,7 +3471,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="171"/>
+      <c r="F17" s="257"/>
       <c r="G17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3487,39 +3487,39 @@
       <c r="K17" s="37">
         <v>2</v>
       </c>
-      <c r="L17" s="191"/>
-      <c r="M17" s="194"/>
+      <c r="L17" s="232"/>
+      <c r="M17" s="235"/>
       <c r="N17" s="38" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="194"/>
-      <c r="Q17" s="201"/>
-      <c r="R17" s="194"/>
+      <c r="P17" s="235"/>
+      <c r="Q17" s="242"/>
+      <c r="R17" s="235"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
-      <c r="B18" s="174"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="174"/>
-      <c r="E18" s="207"/>
-      <c r="F18" s="211"/>
-      <c r="G18" s="159"/>
-      <c r="H18" s="159">
+      <c r="A18" s="215"/>
+      <c r="B18" s="216"/>
+      <c r="C18" s="216"/>
+      <c r="D18" s="216"/>
+      <c r="E18" s="217"/>
+      <c r="F18" s="221"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="223">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="159"/>
-      <c r="J18" s="159"/>
-      <c r="K18" s="161"/>
-      <c r="L18" s="202" t="s">
+      <c r="I18" s="223"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="247"/>
+      <c r="L18" s="243" t="s">
         <v>107</v>
       </c>
       <c r="M18" s="147"/>
-      <c r="N18" s="261"/>
-      <c r="O18" s="262"/>
+      <c r="N18" s="157"/>
+      <c r="O18" s="158"/>
       <c r="P18" s="151"/>
       <c r="Q18" s="153"/>
       <c r="R18" s="155" t="s">
@@ -3527,49 +3527,49 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="208"/>
-      <c r="B19" s="209"/>
-      <c r="C19" s="209"/>
-      <c r="D19" s="209"/>
-      <c r="E19" s="210"/>
-      <c r="F19" s="212"/>
-      <c r="G19" s="160"/>
-      <c r="H19" s="160"/>
-      <c r="I19" s="160"/>
-      <c r="J19" s="160"/>
-      <c r="K19" s="162"/>
-      <c r="L19" s="203"/>
+      <c r="A19" s="218"/>
+      <c r="B19" s="219"/>
+      <c r="C19" s="219"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="220"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="224"/>
+      <c r="H19" s="224"/>
+      <c r="I19" s="224"/>
+      <c r="J19" s="224"/>
+      <c r="K19" s="248"/>
+      <c r="L19" s="244"/>
       <c r="M19" s="148"/>
-      <c r="N19" s="263"/>
-      <c r="O19" s="264"/>
+      <c r="N19" s="159"/>
+      <c r="O19" s="160"/>
       <c r="P19" s="152"/>
       <c r="Q19" s="154"/>
       <c r="R19" s="156"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="142"/>
-      <c r="B20" s="158"/>
-      <c r="C20" s="158"/>
-      <c r="D20" s="182"/>
-      <c r="E20" s="183"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="212"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="162"/>
       <c r="F20" s="139"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
       <c r="I20" s="129"/>
       <c r="J20" s="129"/>
       <c r="K20" s="129"/>
-      <c r="L20" s="204"/>
+      <c r="L20" s="245"/>
       <c r="M20" s="147" t="str">
         <f>IF(ISBLANK(A20),"",A20)</f>
         <v/>
       </c>
-      <c r="N20" s="261" t="str">
+      <c r="N20" s="157" t="str">
         <f>IF(ISBLANK(D20),"",D20)</f>
         <v/>
       </c>
-      <c r="O20" s="262"/>
-      <c r="P20" s="184"/>
-      <c r="Q20" s="186"/>
+      <c r="O20" s="158"/>
+      <c r="P20" s="225"/>
+      <c r="Q20" s="227"/>
       <c r="R20" s="149"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3577,54 +3577,54 @@
         <f t="shared" ref="A21" si="0">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B21" s="158"/>
-      <c r="C21" s="158"/>
-      <c r="D21" s="180"/>
-      <c r="E21" s="181"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="212"/>
+      <c r="D21" s="163"/>
+      <c r="E21" s="164"/>
       <c r="F21" s="141"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
       <c r="I21" s="127"/>
       <c r="J21" s="127"/>
       <c r="K21" s="128"/>
-      <c r="L21" s="204"/>
+      <c r="L21" s="245"/>
       <c r="M21" s="148" t="str">
         <f>A21</f>
         <v/>
       </c>
-      <c r="N21" s="263" t="str">
+      <c r="N21" s="159" t="str">
         <f>IF(ISBLANK(D21),"",D21)</f>
         <v/>
       </c>
-      <c r="O21" s="264"/>
-      <c r="P21" s="184"/>
-      <c r="Q21" s="186"/>
+      <c r="O21" s="160"/>
+      <c r="P21" s="225"/>
+      <c r="Q21" s="227"/>
       <c r="R21" s="150"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="134"/>
-      <c r="B22" s="157"/>
-      <c r="C22" s="157"/>
-      <c r="D22" s="182"/>
-      <c r="E22" s="183"/>
+      <c r="B22" s="211"/>
+      <c r="C22" s="211"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="162"/>
       <c r="F22" s="139"/>
       <c r="G22" s="129"/>
       <c r="H22" s="129"/>
       <c r="I22" s="129"/>
       <c r="J22" s="129"/>
       <c r="K22" s="129"/>
-      <c r="L22" s="204"/>
+      <c r="L22" s="245"/>
       <c r="M22" s="147" t="str">
         <f t="shared" ref="M22" si="1">IF(ISBLANK(A22),"",A22)</f>
         <v/>
       </c>
-      <c r="N22" s="261" t="str">
+      <c r="N22" s="157" t="str">
         <f t="shared" ref="N22:N53" si="2">IF(ISBLANK(D22),"",D22)</f>
         <v/>
       </c>
-      <c r="O22" s="262"/>
-      <c r="P22" s="184"/>
-      <c r="Q22" s="186"/>
+      <c r="O22" s="158"/>
+      <c r="P22" s="225"/>
+      <c r="Q22" s="227"/>
       <c r="R22" s="149"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3632,54 +3632,54 @@
         <f t="shared" ref="A23:A25" si="3">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="158"/>
-      <c r="C23" s="158"/>
-      <c r="D23" s="180"/>
-      <c r="E23" s="181"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="212"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="164"/>
       <c r="F23" s="141"/>
       <c r="G23" s="127"/>
       <c r="H23" s="127"/>
       <c r="I23" s="127"/>
       <c r="J23" s="127"/>
       <c r="K23" s="128"/>
-      <c r="L23" s="204"/>
+      <c r="L23" s="245"/>
       <c r="M23" s="148" t="str">
         <f t="shared" ref="M23" si="4">A23</f>
         <v/>
       </c>
-      <c r="N23" s="263" t="str">
+      <c r="N23" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O23" s="264"/>
-      <c r="P23" s="184"/>
-      <c r="Q23" s="186"/>
+      <c r="O23" s="160"/>
+      <c r="P23" s="225"/>
+      <c r="Q23" s="227"/>
       <c r="R23" s="150"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="134"/>
-      <c r="B24" s="157"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="182"/>
-      <c r="E24" s="183"/>
+      <c r="B24" s="211"/>
+      <c r="C24" s="211"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="162"/>
       <c r="F24" s="139"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
       <c r="I24" s="129"/>
       <c r="J24" s="129"/>
       <c r="K24" s="129"/>
-      <c r="L24" s="204"/>
+      <c r="L24" s="245"/>
       <c r="M24" s="147" t="str">
         <f t="shared" ref="M24" si="5">IF(ISBLANK(A24),"",A24)</f>
         <v/>
       </c>
-      <c r="N24" s="261" t="str">
+      <c r="N24" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O24" s="262"/>
-      <c r="P24" s="184"/>
-      <c r="Q24" s="186"/>
+      <c r="O24" s="158"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="227"/>
       <c r="R24" s="149"/>
     </row>
     <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3687,54 +3687,54 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="180"/>
-      <c r="E25" s="181"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="212"/>
+      <c r="D25" s="163"/>
+      <c r="E25" s="164"/>
       <c r="F25" s="141"/>
       <c r="G25" s="127"/>
       <c r="H25" s="127"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
       <c r="K25" s="128"/>
-      <c r="L25" s="204"/>
+      <c r="L25" s="245"/>
       <c r="M25" s="148" t="str">
         <f t="shared" ref="M25" si="6">A25</f>
         <v/>
       </c>
-      <c r="N25" s="263" t="str">
+      <c r="N25" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O25" s="264"/>
-      <c r="P25" s="184"/>
-      <c r="Q25" s="186"/>
+      <c r="O25" s="160"/>
+      <c r="P25" s="225"/>
+      <c r="Q25" s="227"/>
       <c r="R25" s="150"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="134"/>
-      <c r="B26" s="157"/>
-      <c r="C26" s="157"/>
-      <c r="D26" s="182"/>
-      <c r="E26" s="183"/>
+      <c r="B26" s="211"/>
+      <c r="C26" s="211"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="162"/>
       <c r="F26" s="139"/>
       <c r="G26" s="129"/>
       <c r="H26" s="129"/>
       <c r="I26" s="129"/>
       <c r="J26" s="129"/>
       <c r="K26" s="129"/>
-      <c r="L26" s="204"/>
+      <c r="L26" s="245"/>
       <c r="M26" s="147" t="str">
         <f t="shared" ref="M26" si="7">IF(ISBLANK(A26),"",A26)</f>
         <v/>
       </c>
-      <c r="N26" s="261" t="str">
+      <c r="N26" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O26" s="262"/>
-      <c r="P26" s="184"/>
-      <c r="Q26" s="186"/>
+      <c r="O26" s="158"/>
+      <c r="P26" s="225"/>
+      <c r="Q26" s="227"/>
       <c r="R26" s="149"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3742,54 +3742,54 @@
         <f t="shared" ref="A27" si="8">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="158"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="180"/>
-      <c r="E27" s="181"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="212"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="164"/>
       <c r="F27" s="141"/>
       <c r="G27" s="127"/>
       <c r="H27" s="127"/>
       <c r="I27" s="127"/>
       <c r="J27" s="127"/>
       <c r="K27" s="128"/>
-      <c r="L27" s="204"/>
+      <c r="L27" s="245"/>
       <c r="M27" s="148" t="str">
         <f t="shared" ref="M27" si="9">A27</f>
         <v/>
       </c>
-      <c r="N27" s="263" t="str">
+      <c r="N27" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O27" s="264"/>
-      <c r="P27" s="184"/>
-      <c r="Q27" s="186"/>
+      <c r="O27" s="160"/>
+      <c r="P27" s="225"/>
+      <c r="Q27" s="227"/>
       <c r="R27" s="150"/>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="135"/>
-      <c r="B28" s="157"/>
-      <c r="C28" s="157"/>
-      <c r="D28" s="182"/>
-      <c r="E28" s="183"/>
+      <c r="B28" s="211"/>
+      <c r="C28" s="211"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="162"/>
       <c r="F28" s="139"/>
       <c r="G28" s="129"/>
       <c r="H28" s="129"/>
       <c r="I28" s="129"/>
       <c r="J28" s="129"/>
       <c r="K28" s="129"/>
-      <c r="L28" s="204"/>
+      <c r="L28" s="245"/>
       <c r="M28" s="147" t="str">
         <f t="shared" ref="M28" si="10">IF(ISBLANK(A28),"",A28)</f>
         <v/>
       </c>
-      <c r="N28" s="261" t="str">
+      <c r="N28" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O28" s="262"/>
-      <c r="P28" s="184"/>
-      <c r="Q28" s="186"/>
+      <c r="O28" s="158"/>
+      <c r="P28" s="225"/>
+      <c r="Q28" s="227"/>
       <c r="R28" s="149"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3797,54 +3797,54 @@
         <f t="shared" ref="A29" si="11">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="158"/>
-      <c r="C29" s="158"/>
-      <c r="D29" s="180"/>
-      <c r="E29" s="181"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="212"/>
+      <c r="D29" s="163"/>
+      <c r="E29" s="164"/>
       <c r="F29" s="141"/>
       <c r="G29" s="127"/>
       <c r="H29" s="127"/>
       <c r="I29" s="127"/>
       <c r="J29" s="129"/>
       <c r="K29" s="128"/>
-      <c r="L29" s="204"/>
+      <c r="L29" s="245"/>
       <c r="M29" s="148" t="str">
         <f t="shared" ref="M29" si="12">A29</f>
         <v/>
       </c>
-      <c r="N29" s="263" t="str">
+      <c r="N29" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O29" s="264"/>
-      <c r="P29" s="184"/>
-      <c r="Q29" s="186"/>
+      <c r="O29" s="160"/>
+      <c r="P29" s="225"/>
+      <c r="Q29" s="227"/>
       <c r="R29" s="150"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="134"/>
-      <c r="B30" s="157"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="182"/>
-      <c r="E30" s="183"/>
+      <c r="B30" s="211"/>
+      <c r="C30" s="211"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="162"/>
       <c r="F30" s="139"/>
       <c r="G30" s="129"/>
       <c r="H30" s="129"/>
       <c r="I30" s="140"/>
       <c r="J30" s="143"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="204"/>
+      <c r="L30" s="245"/>
       <c r="M30" s="147" t="str">
         <f t="shared" ref="M30" si="13">IF(ISBLANK(A30),"",A30)</f>
         <v/>
       </c>
-      <c r="N30" s="261" t="str">
+      <c r="N30" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O30" s="262"/>
-      <c r="P30" s="184"/>
-      <c r="Q30" s="186"/>
+      <c r="O30" s="158"/>
+      <c r="P30" s="225"/>
+      <c r="Q30" s="227"/>
       <c r="R30" s="149"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3852,54 +3852,54 @@
         <f t="shared" ref="A31" si="14">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="158"/>
-      <c r="C31" s="158"/>
-      <c r="D31" s="180"/>
-      <c r="E31" s="181"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="212"/>
+      <c r="D31" s="163"/>
+      <c r="E31" s="164"/>
       <c r="F31" s="141"/>
       <c r="G31" s="127"/>
       <c r="H31" s="127"/>
       <c r="I31" s="127"/>
       <c r="J31" s="127"/>
       <c r="K31" s="128"/>
-      <c r="L31" s="204"/>
+      <c r="L31" s="245"/>
       <c r="M31" s="148" t="str">
         <f t="shared" ref="M31" si="15">A31</f>
         <v/>
       </c>
-      <c r="N31" s="263" t="str">
+      <c r="N31" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O31" s="264"/>
-      <c r="P31" s="184"/>
-      <c r="Q31" s="186"/>
+      <c r="O31" s="160"/>
+      <c r="P31" s="225"/>
+      <c r="Q31" s="227"/>
       <c r="R31" s="150"/>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="134"/>
-      <c r="B32" s="157"/>
-      <c r="C32" s="157"/>
-      <c r="D32" s="182"/>
-      <c r="E32" s="183"/>
+      <c r="B32" s="211"/>
+      <c r="C32" s="211"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="162"/>
       <c r="F32" s="139"/>
       <c r="G32" s="129"/>
       <c r="H32" s="129"/>
       <c r="I32" s="129"/>
       <c r="J32" s="129"/>
       <c r="K32" s="129"/>
-      <c r="L32" s="204"/>
+      <c r="L32" s="245"/>
       <c r="M32" s="147" t="str">
         <f t="shared" ref="M32" si="16">IF(ISBLANK(A32),"",A32)</f>
         <v/>
       </c>
-      <c r="N32" s="261" t="str">
+      <c r="N32" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O32" s="262"/>
-      <c r="P32" s="184"/>
-      <c r="Q32" s="186"/>
+      <c r="O32" s="158"/>
+      <c r="P32" s="225"/>
+      <c r="Q32" s="227"/>
       <c r="R32" s="149"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,54 +3907,54 @@
         <f t="shared" ref="A33" si="17">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="158"/>
-      <c r="C33" s="158"/>
-      <c r="D33" s="180"/>
-      <c r="E33" s="181"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="212"/>
+      <c r="D33" s="163"/>
+      <c r="E33" s="164"/>
       <c r="F33" s="141"/>
       <c r="G33" s="127"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
       <c r="J33" s="127"/>
       <c r="K33" s="128"/>
-      <c r="L33" s="204"/>
+      <c r="L33" s="245"/>
       <c r="M33" s="148" t="str">
         <f t="shared" ref="M33" si="18">A33</f>
         <v/>
       </c>
-      <c r="N33" s="263" t="str">
+      <c r="N33" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O33" s="264"/>
-      <c r="P33" s="184"/>
-      <c r="Q33" s="186"/>
+      <c r="O33" s="160"/>
+      <c r="P33" s="225"/>
+      <c r="Q33" s="227"/>
       <c r="R33" s="150"/>
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="134"/>
-      <c r="B34" s="157"/>
-      <c r="C34" s="157"/>
-      <c r="D34" s="182"/>
-      <c r="E34" s="183"/>
+      <c r="B34" s="211"/>
+      <c r="C34" s="211"/>
+      <c r="D34" s="161"/>
+      <c r="E34" s="162"/>
       <c r="F34" s="139"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
       <c r="I34" s="129"/>
       <c r="J34" s="129"/>
       <c r="K34" s="129"/>
-      <c r="L34" s="204"/>
+      <c r="L34" s="245"/>
       <c r="M34" s="147" t="str">
         <f t="shared" ref="M34" si="19">IF(ISBLANK(A34),"",A34)</f>
         <v/>
       </c>
-      <c r="N34" s="261" t="str">
+      <c r="N34" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O34" s="262"/>
-      <c r="P34" s="184"/>
-      <c r="Q34" s="186"/>
+      <c r="O34" s="158"/>
+      <c r="P34" s="225"/>
+      <c r="Q34" s="227"/>
       <c r="R34" s="149"/>
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3962,54 +3962,54 @@
         <f t="shared" ref="A35" si="20">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="158"/>
-      <c r="C35" s="158"/>
-      <c r="D35" s="180"/>
-      <c r="E35" s="181"/>
+      <c r="B35" s="212"/>
+      <c r="C35" s="212"/>
+      <c r="D35" s="163"/>
+      <c r="E35" s="164"/>
       <c r="F35" s="141"/>
       <c r="G35" s="127"/>
       <c r="H35" s="127"/>
       <c r="I35" s="127"/>
       <c r="J35" s="127"/>
       <c r="K35" s="128"/>
-      <c r="L35" s="204"/>
+      <c r="L35" s="245"/>
       <c r="M35" s="148" t="str">
         <f t="shared" ref="M35" si="21">A35</f>
         <v/>
       </c>
-      <c r="N35" s="263" t="str">
+      <c r="N35" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O35" s="264"/>
-      <c r="P35" s="184"/>
-      <c r="Q35" s="186"/>
+      <c r="O35" s="160"/>
+      <c r="P35" s="225"/>
+      <c r="Q35" s="227"/>
       <c r="R35" s="150"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134"/>
-      <c r="B36" s="157"/>
-      <c r="C36" s="157"/>
-      <c r="D36" s="182"/>
-      <c r="E36" s="183"/>
+      <c r="B36" s="211"/>
+      <c r="C36" s="211"/>
+      <c r="D36" s="161"/>
+      <c r="E36" s="162"/>
       <c r="F36" s="139"/>
       <c r="G36" s="129"/>
       <c r="H36" s="129"/>
       <c r="I36" s="129"/>
       <c r="J36" s="129"/>
       <c r="K36" s="129"/>
-      <c r="L36" s="204"/>
+      <c r="L36" s="245"/>
       <c r="M36" s="147" t="str">
         <f t="shared" ref="M36" si="22">IF(ISBLANK(A36),"",A36)</f>
         <v/>
       </c>
-      <c r="N36" s="261" t="str">
+      <c r="N36" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O36" s="262"/>
-      <c r="P36" s="184"/>
-      <c r="Q36" s="186"/>
+      <c r="O36" s="158"/>
+      <c r="P36" s="225"/>
+      <c r="Q36" s="227"/>
       <c r="R36" s="149"/>
     </row>
     <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4017,54 +4017,54 @@
         <f t="shared" ref="A37" si="23">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="158"/>
-      <c r="C37" s="158"/>
-      <c r="D37" s="180"/>
-      <c r="E37" s="181"/>
+      <c r="B37" s="212"/>
+      <c r="C37" s="212"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="164"/>
       <c r="F37" s="141"/>
       <c r="G37" s="127"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
       <c r="J37" s="127"/>
       <c r="K37" s="128"/>
-      <c r="L37" s="204"/>
+      <c r="L37" s="245"/>
       <c r="M37" s="148" t="str">
         <f t="shared" ref="M37" si="24">A37</f>
         <v/>
       </c>
-      <c r="N37" s="263" t="str">
+      <c r="N37" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O37" s="264"/>
-      <c r="P37" s="184"/>
-      <c r="Q37" s="186"/>
+      <c r="O37" s="160"/>
+      <c r="P37" s="225"/>
+      <c r="Q37" s="227"/>
       <c r="R37" s="150"/>
     </row>
     <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="134"/>
-      <c r="B38" s="157"/>
-      <c r="C38" s="157"/>
-      <c r="D38" s="182"/>
-      <c r="E38" s="183"/>
+      <c r="B38" s="211"/>
+      <c r="C38" s="211"/>
+      <c r="D38" s="161"/>
+      <c r="E38" s="162"/>
       <c r="F38" s="139"/>
       <c r="G38" s="129"/>
       <c r="H38" s="129"/>
       <c r="I38" s="129"/>
       <c r="J38" s="129"/>
       <c r="K38" s="129"/>
-      <c r="L38" s="204"/>
+      <c r="L38" s="245"/>
       <c r="M38" s="147" t="str">
         <f t="shared" ref="M38" si="25">IF(ISBLANK(A38),"",A38)</f>
         <v/>
       </c>
-      <c r="N38" s="261" t="str">
+      <c r="N38" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O38" s="262"/>
-      <c r="P38" s="184"/>
-      <c r="Q38" s="186"/>
+      <c r="O38" s="158"/>
+      <c r="P38" s="225"/>
+      <c r="Q38" s="227"/>
       <c r="R38" s="149"/>
     </row>
     <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4072,54 +4072,54 @@
         <f t="shared" ref="A39" si="26">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="158"/>
-      <c r="C39" s="158"/>
-      <c r="D39" s="180"/>
-      <c r="E39" s="181"/>
+      <c r="B39" s="212"/>
+      <c r="C39" s="212"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="164"/>
       <c r="F39" s="141"/>
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
       <c r="K39" s="128"/>
-      <c r="L39" s="204"/>
+      <c r="L39" s="245"/>
       <c r="M39" s="148" t="str">
         <f t="shared" ref="M39" si="27">A39</f>
         <v/>
       </c>
-      <c r="N39" s="263" t="str">
+      <c r="N39" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O39" s="264"/>
-      <c r="P39" s="184"/>
-      <c r="Q39" s="186"/>
+      <c r="O39" s="160"/>
+      <c r="P39" s="225"/>
+      <c r="Q39" s="227"/>
       <c r="R39" s="150"/>
     </row>
     <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="134"/>
-      <c r="B40" s="157"/>
-      <c r="C40" s="157"/>
-      <c r="D40" s="182"/>
-      <c r="E40" s="183"/>
+      <c r="B40" s="211"/>
+      <c r="C40" s="211"/>
+      <c r="D40" s="161"/>
+      <c r="E40" s="162"/>
       <c r="F40" s="139"/>
       <c r="G40" s="129"/>
       <c r="H40" s="129"/>
       <c r="I40" s="129"/>
       <c r="J40" s="129"/>
       <c r="K40" s="129"/>
-      <c r="L40" s="204"/>
+      <c r="L40" s="245"/>
       <c r="M40" s="147" t="str">
         <f t="shared" ref="M40" si="28">IF(ISBLANK(A40),"",A40)</f>
         <v/>
       </c>
-      <c r="N40" s="261" t="str">
+      <c r="N40" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O40" s="262"/>
-      <c r="P40" s="184"/>
-      <c r="Q40" s="186"/>
+      <c r="O40" s="158"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="227"/>
       <c r="R40" s="149"/>
     </row>
     <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4127,54 +4127,54 @@
         <f t="shared" ref="A41" si="29">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="158"/>
-      <c r="C41" s="158"/>
-      <c r="D41" s="180"/>
-      <c r="E41" s="181"/>
+      <c r="B41" s="212"/>
+      <c r="C41" s="212"/>
+      <c r="D41" s="163"/>
+      <c r="E41" s="164"/>
       <c r="F41" s="141"/>
       <c r="G41" s="127"/>
       <c r="H41" s="127"/>
       <c r="I41" s="127"/>
       <c r="J41" s="127"/>
       <c r="K41" s="128"/>
-      <c r="L41" s="204"/>
+      <c r="L41" s="245"/>
       <c r="M41" s="148" t="str">
         <f t="shared" ref="M41" si="30">A41</f>
         <v/>
       </c>
-      <c r="N41" s="263" t="str">
+      <c r="N41" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O41" s="264"/>
-      <c r="P41" s="184"/>
-      <c r="Q41" s="186"/>
+      <c r="O41" s="160"/>
+      <c r="P41" s="225"/>
+      <c r="Q41" s="227"/>
       <c r="R41" s="150"/>
     </row>
     <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="134"/>
-      <c r="B42" s="157"/>
-      <c r="C42" s="157"/>
-      <c r="D42" s="182"/>
-      <c r="E42" s="183"/>
+      <c r="B42" s="211"/>
+      <c r="C42" s="211"/>
+      <c r="D42" s="161"/>
+      <c r="E42" s="162"/>
       <c r="F42" s="139"/>
       <c r="G42" s="129"/>
       <c r="H42" s="129"/>
       <c r="I42" s="129"/>
       <c r="J42" s="129"/>
       <c r="K42" s="129"/>
-      <c r="L42" s="204"/>
+      <c r="L42" s="245"/>
       <c r="M42" s="147" t="str">
         <f t="shared" ref="M42" si="31">IF(ISBLANK(A42),"",A42)</f>
         <v/>
       </c>
-      <c r="N42" s="261" t="str">
+      <c r="N42" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O42" s="262"/>
-      <c r="P42" s="184"/>
-      <c r="Q42" s="186"/>
+      <c r="O42" s="158"/>
+      <c r="P42" s="225"/>
+      <c r="Q42" s="227"/>
       <c r="R42" s="149"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4182,54 +4182,54 @@
         <f t="shared" ref="A43" si="32">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="158"/>
-      <c r="C43" s="158"/>
-      <c r="D43" s="180"/>
-      <c r="E43" s="181"/>
+      <c r="B43" s="212"/>
+      <c r="C43" s="212"/>
+      <c r="D43" s="163"/>
+      <c r="E43" s="164"/>
       <c r="F43" s="141"/>
       <c r="G43" s="127"/>
       <c r="H43" s="127"/>
       <c r="I43" s="127"/>
       <c r="J43" s="127"/>
       <c r="K43" s="128"/>
-      <c r="L43" s="204"/>
+      <c r="L43" s="245"/>
       <c r="M43" s="148" t="str">
         <f t="shared" ref="M43" si="33">A43</f>
         <v/>
       </c>
-      <c r="N43" s="263" t="str">
+      <c r="N43" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O43" s="264"/>
-      <c r="P43" s="184"/>
-      <c r="Q43" s="186"/>
+      <c r="O43" s="160"/>
+      <c r="P43" s="225"/>
+      <c r="Q43" s="227"/>
       <c r="R43" s="150"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="134"/>
-      <c r="B44" s="157"/>
-      <c r="C44" s="157"/>
-      <c r="D44" s="182"/>
-      <c r="E44" s="183"/>
+      <c r="B44" s="211"/>
+      <c r="C44" s="211"/>
+      <c r="D44" s="161"/>
+      <c r="E44" s="162"/>
       <c r="F44" s="139"/>
       <c r="G44" s="129"/>
       <c r="H44" s="129"/>
       <c r="I44" s="129"/>
       <c r="J44" s="129"/>
       <c r="K44" s="129"/>
-      <c r="L44" s="204"/>
+      <c r="L44" s="245"/>
       <c r="M44" s="147" t="str">
         <f t="shared" ref="M44" si="34">IF(ISBLANK(A44),"",A44)</f>
         <v/>
       </c>
-      <c r="N44" s="261" t="str">
+      <c r="N44" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O44" s="262"/>
-      <c r="P44" s="184"/>
-      <c r="Q44" s="186"/>
+      <c r="O44" s="158"/>
+      <c r="P44" s="225"/>
+      <c r="Q44" s="227"/>
       <c r="R44" s="149"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4237,54 +4237,54 @@
         <f t="shared" ref="A45" si="35">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="158"/>
-      <c r="C45" s="158"/>
-      <c r="D45" s="180"/>
-      <c r="E45" s="181"/>
+      <c r="B45" s="212"/>
+      <c r="C45" s="212"/>
+      <c r="D45" s="163"/>
+      <c r="E45" s="164"/>
       <c r="F45" s="141"/>
       <c r="G45" s="127"/>
       <c r="H45" s="127"/>
       <c r="I45" s="127"/>
       <c r="J45" s="127"/>
       <c r="K45" s="128"/>
-      <c r="L45" s="204"/>
+      <c r="L45" s="245"/>
       <c r="M45" s="148" t="str">
         <f t="shared" ref="M45" si="36">A45</f>
         <v/>
       </c>
-      <c r="N45" s="263" t="str">
+      <c r="N45" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O45" s="264"/>
-      <c r="P45" s="184"/>
-      <c r="Q45" s="186"/>
+      <c r="O45" s="160"/>
+      <c r="P45" s="225"/>
+      <c r="Q45" s="227"/>
       <c r="R45" s="150"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="134"/>
-      <c r="B46" s="157"/>
-      <c r="C46" s="157"/>
-      <c r="D46" s="182"/>
-      <c r="E46" s="183"/>
+      <c r="B46" s="211"/>
+      <c r="C46" s="211"/>
+      <c r="D46" s="161"/>
+      <c r="E46" s="162"/>
       <c r="F46" s="139"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
       <c r="I46" s="129"/>
       <c r="J46" s="129"/>
       <c r="K46" s="129"/>
-      <c r="L46" s="204"/>
+      <c r="L46" s="245"/>
       <c r="M46" s="147" t="str">
         <f t="shared" ref="M46" si="37">IF(ISBLANK(A46),"",A46)</f>
         <v/>
       </c>
-      <c r="N46" s="261" t="str">
+      <c r="N46" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O46" s="262"/>
-      <c r="P46" s="184"/>
-      <c r="Q46" s="186"/>
+      <c r="O46" s="158"/>
+      <c r="P46" s="225"/>
+      <c r="Q46" s="227"/>
       <c r="R46" s="149"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4292,54 +4292,54 @@
         <f t="shared" ref="A47" si="38">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="158"/>
-      <c r="C47" s="158"/>
-      <c r="D47" s="180"/>
-      <c r="E47" s="181"/>
+      <c r="B47" s="212"/>
+      <c r="C47" s="212"/>
+      <c r="D47" s="163"/>
+      <c r="E47" s="164"/>
       <c r="F47" s="141"/>
       <c r="G47" s="127"/>
       <c r="H47" s="127"/>
       <c r="I47" s="127"/>
       <c r="J47" s="127"/>
       <c r="K47" s="128"/>
-      <c r="L47" s="204"/>
+      <c r="L47" s="245"/>
       <c r="M47" s="148" t="str">
         <f t="shared" ref="M47" si="39">A47</f>
         <v/>
       </c>
-      <c r="N47" s="263" t="str">
+      <c r="N47" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O47" s="264"/>
-      <c r="P47" s="184"/>
-      <c r="Q47" s="186"/>
+      <c r="O47" s="160"/>
+      <c r="P47" s="225"/>
+      <c r="Q47" s="227"/>
       <c r="R47" s="150"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="134"/>
-      <c r="B48" s="157"/>
-      <c r="C48" s="157"/>
-      <c r="D48" s="182"/>
-      <c r="E48" s="183"/>
+      <c r="B48" s="211"/>
+      <c r="C48" s="211"/>
+      <c r="D48" s="161"/>
+      <c r="E48" s="162"/>
       <c r="F48" s="139"/>
       <c r="G48" s="129"/>
       <c r="H48" s="129"/>
       <c r="I48" s="129"/>
       <c r="J48" s="129"/>
       <c r="K48" s="129"/>
-      <c r="L48" s="204"/>
+      <c r="L48" s="245"/>
       <c r="M48" s="147" t="str">
         <f t="shared" ref="M48" si="40">IF(ISBLANK(A48),"",A48)</f>
         <v/>
       </c>
-      <c r="N48" s="261" t="str">
+      <c r="N48" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O48" s="262"/>
-      <c r="P48" s="184"/>
-      <c r="Q48" s="186"/>
+      <c r="O48" s="158"/>
+      <c r="P48" s="225"/>
+      <c r="Q48" s="227"/>
       <c r="R48" s="149"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4347,54 +4347,54 @@
         <f t="shared" ref="A49" si="41">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="158"/>
-      <c r="C49" s="158"/>
-      <c r="D49" s="180"/>
-      <c r="E49" s="181"/>
+      <c r="B49" s="212"/>
+      <c r="C49" s="212"/>
+      <c r="D49" s="163"/>
+      <c r="E49" s="164"/>
       <c r="F49" s="141"/>
       <c r="G49" s="127"/>
       <c r="H49" s="127"/>
       <c r="I49" s="127"/>
       <c r="J49" s="127"/>
       <c r="K49" s="128"/>
-      <c r="L49" s="204"/>
+      <c r="L49" s="245"/>
       <c r="M49" s="148" t="str">
         <f t="shared" ref="M49" si="42">A49</f>
         <v/>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O49" s="264"/>
-      <c r="P49" s="184"/>
-      <c r="Q49" s="186"/>
+      <c r="O49" s="160"/>
+      <c r="P49" s="225"/>
+      <c r="Q49" s="227"/>
       <c r="R49" s="150"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134"/>
-      <c r="B50" s="157"/>
-      <c r="C50" s="157"/>
-      <c r="D50" s="182"/>
-      <c r="E50" s="183"/>
+      <c r="B50" s="211"/>
+      <c r="C50" s="211"/>
+      <c r="D50" s="161"/>
+      <c r="E50" s="162"/>
       <c r="F50" s="139"/>
       <c r="G50" s="129"/>
       <c r="H50" s="129"/>
       <c r="I50" s="129"/>
       <c r="J50" s="129"/>
       <c r="K50" s="129"/>
-      <c r="L50" s="204"/>
+      <c r="L50" s="245"/>
       <c r="M50" s="147" t="str">
         <f t="shared" ref="M50" si="43">IF(ISBLANK(A50),"",A50)</f>
         <v/>
       </c>
-      <c r="N50" s="261" t="str">
+      <c r="N50" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O50" s="262"/>
-      <c r="P50" s="184"/>
-      <c r="Q50" s="186"/>
+      <c r="O50" s="158"/>
+      <c r="P50" s="225"/>
+      <c r="Q50" s="227"/>
       <c r="R50" s="149"/>
     </row>
     <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,54 +4402,54 @@
         <f t="shared" ref="A51" si="44">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="158"/>
-      <c r="C51" s="158"/>
-      <c r="D51" s="180"/>
-      <c r="E51" s="181"/>
+      <c r="B51" s="212"/>
+      <c r="C51" s="212"/>
+      <c r="D51" s="163"/>
+      <c r="E51" s="164"/>
       <c r="F51" s="141"/>
       <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127"/>
       <c r="J51" s="127"/>
       <c r="K51" s="128"/>
-      <c r="L51" s="204"/>
+      <c r="L51" s="245"/>
       <c r="M51" s="148" t="str">
         <f t="shared" ref="M51" si="45">A51</f>
         <v/>
       </c>
-      <c r="N51" s="263" t="str">
+      <c r="N51" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O51" s="264"/>
-      <c r="P51" s="184"/>
-      <c r="Q51" s="186"/>
+      <c r="O51" s="160"/>
+      <c r="P51" s="225"/>
+      <c r="Q51" s="227"/>
       <c r="R51" s="150"/>
     </row>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="134"/>
-      <c r="B52" s="157"/>
-      <c r="C52" s="157"/>
-      <c r="D52" s="182"/>
-      <c r="E52" s="183"/>
+      <c r="B52" s="211"/>
+      <c r="C52" s="211"/>
+      <c r="D52" s="161"/>
+      <c r="E52" s="162"/>
       <c r="F52" s="139"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
       <c r="I52" s="129"/>
       <c r="J52" s="129"/>
       <c r="K52" s="129"/>
-      <c r="L52" s="204"/>
+      <c r="L52" s="245"/>
       <c r="M52" s="147" t="str">
         <f t="shared" ref="M52" si="46">IF(ISBLANK(A52),"",A52)</f>
         <v/>
       </c>
-      <c r="N52" s="261" t="str">
+      <c r="N52" s="157" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O52" s="262"/>
-      <c r="P52" s="184"/>
-      <c r="Q52" s="186"/>
+      <c r="O52" s="158"/>
+      <c r="P52" s="225"/>
+      <c r="Q52" s="227"/>
       <c r="R52" s="149"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4457,28 +4457,28 @@
         <f t="shared" ref="A53" si="47">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B53" s="158"/>
-      <c r="C53" s="158"/>
-      <c r="D53" s="180"/>
-      <c r="E53" s="181"/>
+      <c r="B53" s="212"/>
+      <c r="C53" s="212"/>
+      <c r="D53" s="163"/>
+      <c r="E53" s="164"/>
       <c r="F53" s="141"/>
       <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127"/>
       <c r="J53" s="127"/>
       <c r="K53" s="128"/>
-      <c r="L53" s="205"/>
+      <c r="L53" s="246"/>
       <c r="M53" s="148" t="str">
         <f t="shared" ref="M53" si="48">A53</f>
         <v/>
       </c>
-      <c r="N53" s="263" t="str">
+      <c r="N53" s="159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O53" s="264"/>
-      <c r="P53" s="185"/>
-      <c r="Q53" s="187"/>
+      <c r="O53" s="160"/>
+      <c r="P53" s="226"/>
+      <c r="Q53" s="228"/>
       <c r="R53" s="150"/>
     </row>
     <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4593,8 +4593,8 @@
         <f>SUM(G55:K55)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="214"/>
-      <c r="H58" s="214"/>
+      <c r="G58" s="213"/>
+      <c r="H58" s="213"/>
       <c r="I58" s="49" t="s">
         <v>29</v>
       </c>
@@ -4620,8 +4620,8 @@
         <f>L9</f>
         <v>0</v>
       </c>
-      <c r="G59" s="214"/>
-      <c r="H59" s="214"/>
+      <c r="G59" s="213"/>
+      <c r="H59" s="213"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
@@ -4687,31 +4687,31 @@
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
       <c r="B63" s="57"/>
-      <c r="C63" s="215" t="s">
+      <c r="C63" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="D63" s="215"/>
-      <c r="E63" s="215"/>
-      <c r="F63" s="215"/>
-      <c r="G63" s="215"/>
-      <c r="H63" s="215"/>
-      <c r="I63" s="215"/>
-      <c r="J63" s="215"/>
-      <c r="K63" s="215"/>
+      <c r="D63" s="214"/>
+      <c r="E63" s="214"/>
+      <c r="F63" s="214"/>
+      <c r="G63" s="214"/>
+      <c r="H63" s="214"/>
+      <c r="I63" s="214"/>
+      <c r="J63" s="214"/>
+      <c r="K63" s="214"/>
       <c r="L63" s="3"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
       <c r="B64" s="57"/>
-      <c r="C64" s="215"/>
-      <c r="D64" s="215"/>
-      <c r="E64" s="215"/>
-      <c r="F64" s="215"/>
-      <c r="G64" s="215"/>
-      <c r="H64" s="215"/>
-      <c r="I64" s="215"/>
-      <c r="J64" s="215"/>
-      <c r="K64" s="215"/>
+      <c r="C64" s="214"/>
+      <c r="D64" s="214"/>
+      <c r="E64" s="214"/>
+      <c r="F64" s="214"/>
+      <c r="G64" s="214"/>
+      <c r="H64" s="214"/>
+      <c r="I64" s="214"/>
+      <c r="J64" s="214"/>
+      <c r="K64" s="214"/>
       <c r="L64" s="3"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -4822,14 +4822,14 @@
       <c r="J71" s="60"/>
       <c r="K71" s="60"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="213" t="s">
+      <c r="M71" s="210" t="s">
         <v>87</v>
       </c>
-      <c r="N71" s="213"/>
-      <c r="O71" s="213"/>
-      <c r="P71" s="213"/>
-      <c r="Q71" s="213"/>
-      <c r="R71" s="213"/>
+      <c r="N71" s="210"/>
+      <c r="O71" s="210"/>
+      <c r="P71" s="210"/>
+      <c r="Q71" s="210"/>
+      <c r="R71" s="210"/>
     </row>
     <row r="72" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="50"/>
@@ -4846,14 +4846,14 @@
       <c r="J72" s="60"/>
       <c r="K72" s="60"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="213" t="s">
+      <c r="M72" s="210" t="s">
         <v>88</v>
       </c>
-      <c r="N72" s="213"/>
-      <c r="O72" s="213"/>
-      <c r="P72" s="213"/>
-      <c r="Q72" s="213"/>
-      <c r="R72" s="213"/>
+      <c r="N72" s="210"/>
+      <c r="O72" s="210"/>
+      <c r="P72" s="210"/>
+      <c r="Q72" s="210"/>
+      <c r="R72" s="210"/>
     </row>
     <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
@@ -4872,12 +4872,12 @@
       <c r="J73" s="60"/>
       <c r="K73" s="60"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="217"/>
-      <c r="N73" s="217"/>
-      <c r="O73" s="217"/>
-      <c r="P73" s="217"/>
-      <c r="Q73" s="217"/>
-      <c r="R73" s="217"/>
+      <c r="M73" s="202"/>
+      <c r="N73" s="202"/>
+      <c r="O73" s="202"/>
+      <c r="P73" s="202"/>
+      <c r="Q73" s="202"/>
+      <c r="R73" s="202"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="50"/>
@@ -4903,24 +4903,24 @@
       <c r="E75" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="218">
+      <c r="F75" s="203">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="218"/>
-      <c r="H75" s="218"/>
-      <c r="I75" s="218"/>
-      <c r="J75" s="218"/>
-      <c r="K75" s="218"/>
+      <c r="G75" s="203"/>
+      <c r="H75" s="203"/>
+      <c r="I75" s="203"/>
+      <c r="J75" s="203"/>
+      <c r="K75" s="203"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="219" t="s">
+      <c r="M75" s="204" t="s">
         <v>89</v>
       </c>
-      <c r="N75" s="219"/>
-      <c r="O75" s="219"/>
-      <c r="P75" s="219"/>
-      <c r="Q75" s="219"/>
-      <c r="R75" s="219"/>
+      <c r="N75" s="204"/>
+      <c r="O75" s="204"/>
+      <c r="P75" s="204"/>
+      <c r="Q75" s="204"/>
+      <c r="R75" s="204"/>
     </row>
     <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="50"/>
@@ -4952,14 +4952,14 @@
       <c r="E77" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="220">
+      <c r="F77" s="205">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="220"/>
-      <c r="H77" s="220"/>
-      <c r="I77" s="220"/>
-      <c r="J77" s="220"/>
+      <c r="G77" s="205"/>
+      <c r="H77" s="205"/>
+      <c r="I77" s="205"/>
+      <c r="J77" s="205"/>
       <c r="K77" s="40"/>
       <c r="L77" s="50"/>
       <c r="M77" s="75"/>
@@ -4984,13 +4984,13 @@
       <c r="L78" s="50"/>
       <c r="M78" s="133"/>
       <c r="N78" s="133"/>
-      <c r="O78" s="222" t="str">
+      <c r="O78" s="207" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="P78" s="222"/>
-      <c r="Q78" s="222"/>
-      <c r="R78" s="222"/>
+      <c r="P78" s="207"/>
+      <c r="Q78" s="207"/>
+      <c r="R78" s="207"/>
     </row>
     <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="67"/>
@@ -5012,11 +5012,11 @@
       <c r="M79" s="77"/>
       <c r="N79" s="77"/>
       <c r="O79" s="78"/>
-      <c r="P79" s="221" t="str">
+      <c r="P79" s="206" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="Q79" s="221"/>
+      <c r="Q79" s="206"/>
       <c r="R79" s="79"/>
     </row>
     <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
@@ -5054,13 +5054,13 @@
       <c r="L81" s="50"/>
       <c r="M81" s="78"/>
       <c r="N81" s="78"/>
-      <c r="O81" s="223" t="str">
+      <c r="O81" s="208" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="P81" s="223"/>
-      <c r="Q81" s="223"/>
-      <c r="R81" s="223"/>
+      <c r="P81" s="208"/>
+      <c r="Q81" s="208"/>
+      <c r="R81" s="208"/>
     </row>
     <row r="82" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="50"/>
@@ -5097,12 +5097,12 @@
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="224"/>
-      <c r="N83" s="224"/>
-      <c r="O83" s="224"/>
-      <c r="P83" s="224"/>
-      <c r="Q83" s="224"/>
-      <c r="R83" s="224"/>
+      <c r="M83" s="209"/>
+      <c r="N83" s="209"/>
+      <c r="O83" s="209"/>
+      <c r="P83" s="209"/>
+      <c r="Q83" s="209"/>
+      <c r="R83" s="209"/>
     </row>
     <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="50"/>
@@ -5121,14 +5121,14 @@
       <c r="J84" s="74"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="216" t="s">
+      <c r="M84" s="188" t="s">
         <v>90</v>
       </c>
-      <c r="N84" s="216"/>
-      <c r="O84" s="216"/>
-      <c r="P84" s="216"/>
-      <c r="Q84" s="216"/>
-      <c r="R84" s="216"/>
+      <c r="N84" s="188"/>
+      <c r="O84" s="188"/>
+      <c r="P84" s="188"/>
+      <c r="Q84" s="188"/>
+      <c r="R84" s="188"/>
     </row>
     <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="50"/>
@@ -5143,14 +5143,14 @@
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="216" t="s">
+      <c r="M85" s="188" t="s">
         <v>91</v>
       </c>
-      <c r="N85" s="216"/>
-      <c r="O85" s="216"/>
-      <c r="P85" s="216"/>
-      <c r="Q85" s="216"/>
-      <c r="R85" s="216"/>
+      <c r="N85" s="188"/>
+      <c r="O85" s="188"/>
+      <c r="P85" s="188"/>
+      <c r="Q85" s="188"/>
+      <c r="R85" s="188"/>
     </row>
     <row r="86" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="50"/>
@@ -5169,12 +5169,12 @@
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="225"/>
-      <c r="N86" s="225"/>
-      <c r="O86" s="225"/>
-      <c r="P86" s="225"/>
-      <c r="Q86" s="225"/>
-      <c r="R86" s="225"/>
+      <c r="M86" s="189"/>
+      <c r="N86" s="189"/>
+      <c r="O86" s="189"/>
+      <c r="P86" s="189"/>
+      <c r="Q86" s="189"/>
+      <c r="R86" s="189"/>
     </row>
     <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="50"/>
@@ -5189,12 +5189,12 @@
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="216"/>
-      <c r="N87" s="216"/>
-      <c r="O87" s="216"/>
-      <c r="P87" s="216"/>
-      <c r="Q87" s="216"/>
-      <c r="R87" s="216"/>
+      <c r="M87" s="188"/>
+      <c r="N87" s="188"/>
+      <c r="O87" s="188"/>
+      <c r="P87" s="188"/>
+      <c r="Q87" s="188"/>
+      <c r="R87" s="188"/>
     </row>
     <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50"/>
@@ -5206,21 +5206,21 @@
       <c r="E88" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="236"/>
-      <c r="G88" s="236"/>
-      <c r="H88" s="236"/>
-      <c r="I88" s="236"/>
-      <c r="J88" s="236"/>
+      <c r="F88" s="187"/>
+      <c r="G88" s="187"/>
+      <c r="H88" s="187"/>
+      <c r="I88" s="187"/>
+      <c r="J88" s="187"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="216" t="s">
+      <c r="M88" s="188" t="s">
         <v>92</v>
       </c>
-      <c r="N88" s="216"/>
-      <c r="O88" s="216"/>
-      <c r="P88" s="216"/>
-      <c r="Q88" s="216"/>
-      <c r="R88" s="216"/>
+      <c r="N88" s="188"/>
+      <c r="O88" s="188"/>
+      <c r="P88" s="188"/>
+      <c r="Q88" s="188"/>
+      <c r="R88" s="188"/>
     </row>
     <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="50"/>
@@ -5373,12 +5373,12 @@
       <c r="J95" s="86"/>
       <c r="K95" s="27"/>
       <c r="L95" s="17"/>
-      <c r="M95" s="225"/>
-      <c r="N95" s="225"/>
-      <c r="O95" s="225"/>
-      <c r="P95" s="225"/>
-      <c r="Q95" s="225"/>
-      <c r="R95" s="225"/>
+      <c r="M95" s="189"/>
+      <c r="N95" s="189"/>
+      <c r="O95" s="189"/>
+      <c r="P95" s="189"/>
+      <c r="Q95" s="189"/>
+      <c r="R95" s="189"/>
     </row>
     <row r="96" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
@@ -5395,12 +5395,12 @@
       <c r="J96" s="86"/>
       <c r="K96" s="27"/>
       <c r="L96" s="17"/>
-      <c r="M96" s="225"/>
-      <c r="N96" s="225"/>
-      <c r="O96" s="225"/>
-      <c r="P96" s="225"/>
-      <c r="Q96" s="225"/>
-      <c r="R96" s="225"/>
+      <c r="M96" s="189"/>
+      <c r="N96" s="189"/>
+      <c r="O96" s="189"/>
+      <c r="P96" s="189"/>
+      <c r="Q96" s="189"/>
+      <c r="R96" s="189"/>
     </row>
     <row r="97" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
@@ -5417,12 +5417,12 @@
       <c r="J97" s="86"/>
       <c r="K97" s="27"/>
       <c r="L97" s="17"/>
-      <c r="M97" s="225"/>
-      <c r="N97" s="225"/>
-      <c r="O97" s="225"/>
-      <c r="P97" s="225"/>
-      <c r="Q97" s="225"/>
-      <c r="R97" s="225"/>
+      <c r="M97" s="189"/>
+      <c r="N97" s="189"/>
+      <c r="O97" s="189"/>
+      <c r="P97" s="189"/>
+      <c r="Q97" s="189"/>
+      <c r="R97" s="189"/>
     </row>
     <row r="98" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
@@ -5439,12 +5439,12 @@
       <c r="J98" s="86"/>
       <c r="K98" s="27"/>
       <c r="L98" s="17"/>
-      <c r="M98" s="225"/>
-      <c r="N98" s="225"/>
-      <c r="O98" s="225"/>
-      <c r="P98" s="225"/>
-      <c r="Q98" s="225"/>
-      <c r="R98" s="225"/>
+      <c r="M98" s="189"/>
+      <c r="N98" s="189"/>
+      <c r="O98" s="189"/>
+      <c r="P98" s="189"/>
+      <c r="Q98" s="189"/>
+      <c r="R98" s="189"/>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="64"/>
@@ -5461,12 +5461,12 @@
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
       <c r="L99" s="17"/>
-      <c r="M99" s="216"/>
-      <c r="N99" s="216"/>
-      <c r="O99" s="216"/>
-      <c r="P99" s="216"/>
-      <c r="Q99" s="216"/>
-      <c r="R99" s="216"/>
+      <c r="M99" s="188"/>
+      <c r="N99" s="188"/>
+      <c r="O99" s="188"/>
+      <c r="P99" s="188"/>
+      <c r="Q99" s="188"/>
+      <c r="R99" s="188"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="50"/>
@@ -5771,36 +5771,36 @@
     </row>
     <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="237" t="s">
+      <c r="A124" s="190" t="s">
         <v>65</v>
       </c>
-      <c r="B124" s="238"/>
-      <c r="C124" s="238"/>
-      <c r="D124" s="238"/>
-      <c r="E124" s="238"/>
-      <c r="F124" s="238"/>
-      <c r="G124" s="238"/>
-      <c r="H124" s="238"/>
-      <c r="I124" s="238"/>
-      <c r="J124" s="238"/>
-      <c r="K124" s="238"/>
-      <c r="L124" s="239"/>
+      <c r="B124" s="191"/>
+      <c r="C124" s="191"/>
+      <c r="D124" s="191"/>
+      <c r="E124" s="191"/>
+      <c r="F124" s="191"/>
+      <c r="G124" s="191"/>
+      <c r="H124" s="191"/>
+      <c r="I124" s="191"/>
+      <c r="J124" s="191"/>
+      <c r="K124" s="191"/>
+      <c r="L124" s="192"/>
     </row>
     <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="240" t="s">
+      <c r="A125" s="193" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="241"/>
-      <c r="C125" s="241"/>
-      <c r="D125" s="241"/>
-      <c r="E125" s="241"/>
-      <c r="F125" s="241"/>
-      <c r="G125" s="241"/>
-      <c r="H125" s="241"/>
-      <c r="I125" s="241"/>
-      <c r="J125" s="241"/>
-      <c r="K125" s="241"/>
-      <c r="L125" s="242"/>
+      <c r="B125" s="194"/>
+      <c r="C125" s="194"/>
+      <c r="D125" s="194"/>
+      <c r="E125" s="194"/>
+      <c r="F125" s="194"/>
+      <c r="G125" s="194"/>
+      <c r="H125" s="194"/>
+      <c r="I125" s="194"/>
+      <c r="J125" s="194"/>
+      <c r="K125" s="194"/>
+      <c r="L125" s="195"/>
     </row>
     <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="105" t="s">
@@ -5808,20 +5808,20 @@
       </c>
       <c r="B126" s="106"/>
       <c r="C126" s="106"/>
-      <c r="D126" s="243">
+      <c r="D126" s="196">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="244"/>
-      <c r="F126" s="244"/>
-      <c r="G126" s="244"/>
-      <c r="H126" s="244"/>
-      <c r="I126" s="245"/>
-      <c r="J126" s="246" t="s">
+      <c r="E126" s="197"/>
+      <c r="F126" s="197"/>
+      <c r="G126" s="197"/>
+      <c r="H126" s="197"/>
+      <c r="I126" s="198"/>
+      <c r="J126" s="199" t="s">
         <v>68</v>
       </c>
-      <c r="K126" s="247"/>
-      <c r="L126" s="248"/>
+      <c r="K126" s="200"/>
+      <c r="L126" s="201"/>
     </row>
     <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="107" t="s">
@@ -5857,23 +5857,23 @@
       <c r="A129" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B129" s="226" t="s">
+      <c r="B129" s="177" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="227"/>
-      <c r="D129" s="228" t="s">
+      <c r="C129" s="178"/>
+      <c r="D129" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="E129" s="229"/>
-      <c r="F129" s="229"/>
-      <c r="G129" s="229"/>
-      <c r="H129" s="229"/>
-      <c r="I129" s="229"/>
-      <c r="J129" s="230"/>
-      <c r="K129" s="228" t="s">
+      <c r="E129" s="180"/>
+      <c r="F129" s="180"/>
+      <c r="G129" s="180"/>
+      <c r="H129" s="180"/>
+      <c r="I129" s="180"/>
+      <c r="J129" s="181"/>
+      <c r="K129" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="L129" s="229"/>
+      <c r="L129" s="180"/>
     </row>
     <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="121"/>
@@ -5883,15 +5883,15 @@
       <c r="C130" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="D130" s="231"/>
-      <c r="E130" s="232"/>
-      <c r="F130" s="232"/>
-      <c r="G130" s="232"/>
-      <c r="H130" s="232"/>
-      <c r="I130" s="232"/>
-      <c r="J130" s="233"/>
-      <c r="K130" s="234"/>
-      <c r="L130" s="235"/>
+      <c r="D130" s="182"/>
+      <c r="E130" s="183"/>
+      <c r="F130" s="183"/>
+      <c r="G130" s="183"/>
+      <c r="H130" s="183"/>
+      <c r="I130" s="183"/>
+      <c r="J130" s="184"/>
+      <c r="K130" s="185"/>
+      <c r="L130" s="186"/>
     </row>
     <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="124">
@@ -5899,17 +5899,17 @@
       </c>
       <c r="B131" s="124"/>
       <c r="C131" s="125"/>
-      <c r="D131" s="256" t="s">
+      <c r="D131" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="257"/>
-      <c r="F131" s="257"/>
-      <c r="G131" s="257"/>
-      <c r="H131" s="257"/>
-      <c r="I131" s="257"/>
-      <c r="J131" s="258"/>
-      <c r="K131" s="252"/>
-      <c r="L131" s="252"/>
+      <c r="E131" s="166"/>
+      <c r="F131" s="166"/>
+      <c r="G131" s="166"/>
+      <c r="H131" s="166"/>
+      <c r="I131" s="166"/>
+      <c r="J131" s="167"/>
+      <c r="K131" s="168"/>
+      <c r="L131" s="168"/>
     </row>
     <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="124">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="B132" s="124"/>
       <c r="C132" s="126"/>
-      <c r="D132" s="256" t="s">
+      <c r="D132" s="165" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="257"/>
-      <c r="F132" s="257"/>
-      <c r="G132" s="257"/>
-      <c r="H132" s="257"/>
-      <c r="I132" s="257"/>
-      <c r="J132" s="258"/>
-      <c r="K132" s="252"/>
-      <c r="L132" s="252"/>
+      <c r="E132" s="166"/>
+      <c r="F132" s="166"/>
+      <c r="G132" s="166"/>
+      <c r="H132" s="166"/>
+      <c r="I132" s="166"/>
+      <c r="J132" s="167"/>
+      <c r="K132" s="168"/>
+      <c r="L132" s="168"/>
     </row>
     <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="124">
@@ -5935,17 +5935,17 @@
       </c>
       <c r="B133" s="124"/>
       <c r="C133" s="126"/>
-      <c r="D133" s="256" t="s">
+      <c r="D133" s="165" t="s">
         <v>78</v>
       </c>
-      <c r="E133" s="257"/>
-      <c r="F133" s="257"/>
-      <c r="G133" s="257"/>
-      <c r="H133" s="257"/>
-      <c r="I133" s="257"/>
-      <c r="J133" s="258"/>
-      <c r="K133" s="252"/>
-      <c r="L133" s="252"/>
+      <c r="E133" s="166"/>
+      <c r="F133" s="166"/>
+      <c r="G133" s="166"/>
+      <c r="H133" s="166"/>
+      <c r="I133" s="166"/>
+      <c r="J133" s="167"/>
+      <c r="K133" s="168"/>
+      <c r="L133" s="168"/>
     </row>
     <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="124">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="B134" s="124"/>
       <c r="C134" s="126"/>
-      <c r="D134" s="256" t="s">
+      <c r="D134" s="165" t="s">
         <v>79</v>
       </c>
-      <c r="E134" s="257"/>
-      <c r="F134" s="257"/>
-      <c r="G134" s="257"/>
-      <c r="H134" s="257"/>
-      <c r="I134" s="257"/>
-      <c r="J134" s="258"/>
-      <c r="K134" s="252"/>
-      <c r="L134" s="252"/>
+      <c r="E134" s="166"/>
+      <c r="F134" s="166"/>
+      <c r="G134" s="166"/>
+      <c r="H134" s="166"/>
+      <c r="I134" s="166"/>
+      <c r="J134" s="167"/>
+      <c r="K134" s="168"/>
+      <c r="L134" s="168"/>
     </row>
     <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="124">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="B135" s="124"/>
       <c r="C135" s="126"/>
-      <c r="D135" s="256" t="s">
+      <c r="D135" s="165" t="s">
         <v>80</v>
       </c>
-      <c r="E135" s="257"/>
-      <c r="F135" s="257"/>
-      <c r="G135" s="257"/>
-      <c r="H135" s="257"/>
-      <c r="I135" s="257"/>
-      <c r="J135" s="258"/>
-      <c r="K135" s="252"/>
-      <c r="L135" s="252"/>
+      <c r="E135" s="166"/>
+      <c r="F135" s="166"/>
+      <c r="G135" s="166"/>
+      <c r="H135" s="166"/>
+      <c r="I135" s="166"/>
+      <c r="J135" s="167"/>
+      <c r="K135" s="168"/>
+      <c r="L135" s="168"/>
     </row>
     <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="124">
@@ -5989,17 +5989,17 @@
       </c>
       <c r="B136" s="124"/>
       <c r="C136" s="126"/>
-      <c r="D136" s="256" t="s">
+      <c r="D136" s="165" t="s">
         <v>81</v>
       </c>
-      <c r="E136" s="257"/>
-      <c r="F136" s="257"/>
-      <c r="G136" s="257"/>
-      <c r="H136" s="257"/>
-      <c r="I136" s="257"/>
-      <c r="J136" s="258"/>
-      <c r="K136" s="252"/>
-      <c r="L136" s="252"/>
+      <c r="E136" s="166"/>
+      <c r="F136" s="166"/>
+      <c r="G136" s="166"/>
+      <c r="H136" s="166"/>
+      <c r="I136" s="166"/>
+      <c r="J136" s="167"/>
+      <c r="K136" s="168"/>
+      <c r="L136" s="168"/>
     </row>
     <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="124">
@@ -6007,17 +6007,17 @@
       </c>
       <c r="B137" s="124"/>
       <c r="C137" s="126"/>
-      <c r="D137" s="256" t="s">
+      <c r="D137" s="165" t="s">
         <v>82</v>
       </c>
-      <c r="E137" s="257"/>
-      <c r="F137" s="257"/>
-      <c r="G137" s="257"/>
-      <c r="H137" s="257"/>
-      <c r="I137" s="257"/>
-      <c r="J137" s="258"/>
-      <c r="K137" s="252"/>
-      <c r="L137" s="252"/>
+      <c r="E137" s="166"/>
+      <c r="F137" s="166"/>
+      <c r="G137" s="166"/>
+      <c r="H137" s="166"/>
+      <c r="I137" s="166"/>
+      <c r="J137" s="167"/>
+      <c r="K137" s="168"/>
+      <c r="L137" s="168"/>
     </row>
     <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="124">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="B138" s="124"/>
       <c r="C138" s="126"/>
-      <c r="D138" s="249" t="s">
+      <c r="D138" s="169" t="s">
         <v>108</v>
       </c>
-      <c r="E138" s="250"/>
-      <c r="F138" s="250"/>
-      <c r="G138" s="250"/>
-      <c r="H138" s="250"/>
-      <c r="I138" s="250"/>
-      <c r="J138" s="251"/>
-      <c r="K138" s="259"/>
-      <c r="L138" s="260"/>
+      <c r="E138" s="170"/>
+      <c r="F138" s="170"/>
+      <c r="G138" s="170"/>
+      <c r="H138" s="170"/>
+      <c r="I138" s="170"/>
+      <c r="J138" s="171"/>
+      <c r="K138" s="175"/>
+      <c r="L138" s="176"/>
     </row>
     <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="124">
@@ -6043,17 +6043,17 @@
       </c>
       <c r="B139" s="124"/>
       <c r="C139" s="126"/>
-      <c r="D139" s="249" t="s">
+      <c r="D139" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="E139" s="250"/>
-      <c r="F139" s="250"/>
-      <c r="G139" s="250"/>
-      <c r="H139" s="250"/>
-      <c r="I139" s="250"/>
-      <c r="J139" s="251"/>
-      <c r="K139" s="252"/>
-      <c r="L139" s="252"/>
+      <c r="E139" s="170"/>
+      <c r="F139" s="170"/>
+      <c r="G139" s="170"/>
+      <c r="H139" s="170"/>
+      <c r="I139" s="170"/>
+      <c r="J139" s="171"/>
+      <c r="K139" s="168"/>
+      <c r="L139" s="168"/>
     </row>
     <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="124">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="B140" s="124"/>
       <c r="C140" s="126"/>
-      <c r="D140" s="249" t="s">
+      <c r="D140" s="169" t="s">
         <v>84</v>
       </c>
-      <c r="E140" s="250"/>
-      <c r="F140" s="250"/>
-      <c r="G140" s="250"/>
-      <c r="H140" s="250"/>
-      <c r="I140" s="250"/>
-      <c r="J140" s="251"/>
-      <c r="K140" s="252"/>
-      <c r="L140" s="252"/>
+      <c r="E140" s="170"/>
+      <c r="F140" s="170"/>
+      <c r="G140" s="170"/>
+      <c r="H140" s="170"/>
+      <c r="I140" s="170"/>
+      <c r="J140" s="171"/>
+      <c r="K140" s="168"/>
+      <c r="L140" s="168"/>
     </row>
     <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="124">
@@ -6079,17 +6079,17 @@
       </c>
       <c r="B141" s="124"/>
       <c r="C141" s="126"/>
-      <c r="D141" s="253" t="s">
+      <c r="D141" s="172" t="s">
         <v>85</v>
       </c>
-      <c r="E141" s="254"/>
-      <c r="F141" s="254"/>
-      <c r="G141" s="254"/>
-      <c r="H141" s="254"/>
-      <c r="I141" s="254"/>
-      <c r="J141" s="255"/>
-      <c r="K141" s="252"/>
-      <c r="L141" s="252"/>
+      <c r="E141" s="173"/>
+      <c r="F141" s="173"/>
+      <c r="G141" s="173"/>
+      <c r="H141" s="173"/>
+      <c r="I141" s="173"/>
+      <c r="J141" s="174"/>
+      <c r="K141" s="168"/>
+      <c r="L141" s="168"/>
     </row>
     <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6101,17 +6101,139 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="168">
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:K16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="P20:P53"/>
+    <mergeCell ref="Q20:Q53"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L20:L53"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M72:R72"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="B52:C53"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C63:K64"/>
+    <mergeCell ref="M71:R71"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="M87:R87"/>
+    <mergeCell ref="M73:R73"/>
+    <mergeCell ref="F75:K75"/>
+    <mergeCell ref="M75:R75"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="O78:R78"/>
+    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="M83:R83"/>
+    <mergeCell ref="M84:R84"/>
+    <mergeCell ref="M85:R85"/>
+    <mergeCell ref="M86:R86"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:J130"/>
+    <mergeCell ref="K129:L130"/>
+    <mergeCell ref="F88:J88"/>
+    <mergeCell ref="M88:R88"/>
+    <mergeCell ref="M95:R95"/>
+    <mergeCell ref="M96:R96"/>
+    <mergeCell ref="M97:R97"/>
+    <mergeCell ref="M98:R98"/>
+    <mergeCell ref="M99:R99"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="D126:I126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="D140:J140"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="D141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="D139:J139"/>
+    <mergeCell ref="K139:L139"/>
+    <mergeCell ref="D134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="D136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="K133:L133"/>
     <mergeCell ref="N28:O28"/>
     <mergeCell ref="N29:O29"/>
     <mergeCell ref="D50:E50"/>
@@ -6136,148 +6258,29 @@
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="N36:O36"/>
     <mergeCell ref="N37:O37"/>
-    <mergeCell ref="D134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="D136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="D140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="D141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="D139:J139"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:J130"/>
-    <mergeCell ref="K129:L130"/>
-    <mergeCell ref="F88:J88"/>
-    <mergeCell ref="M88:R88"/>
-    <mergeCell ref="M95:R95"/>
-    <mergeCell ref="M96:R96"/>
-    <mergeCell ref="M97:R97"/>
-    <mergeCell ref="M98:R98"/>
-    <mergeCell ref="M99:R99"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="M87:R87"/>
-    <mergeCell ref="M73:R73"/>
-    <mergeCell ref="F75:K75"/>
-    <mergeCell ref="M75:R75"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="O78:R78"/>
-    <mergeCell ref="O81:R81"/>
-    <mergeCell ref="M83:R83"/>
-    <mergeCell ref="M84:R84"/>
-    <mergeCell ref="M85:R85"/>
-    <mergeCell ref="M86:R86"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M72:R72"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="B52:C53"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="C63:K64"/>
-    <mergeCell ref="M71:R71"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="P20:P53"/>
-    <mergeCell ref="Q20:Q53"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="L20:L53"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:K16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="N49:O49"/>
   </mergeCells>
   <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="75" fitToWidth="2" fitToHeight="3" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="71" fitToWidth="2" fitToHeight="3" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="64" max="18" man="1"/>
     <brk id="120" max="18" man="1"/>
   </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="12" max="142" man="1"/>
+  </colBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/OTTimetableApp/Template/ot_template.xlsx
+++ b/OTTimetableApp/Template/ot_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\OTTimetableApp\OTTimetableApp\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F482D3F0-4943-427C-BAEF-CE342B8FBC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D92BD7-C01F-4352-A75C-0601029AA0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2045,17 +2045,101 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="173" fontId="7" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2065,28 +2149,265 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2101,6 +2422,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2113,349 +2438,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3069,26 +3069,26 @@
     <col min="13" max="13" width="13.140625" style="8" customWidth="1"/>
     <col min="14" max="15" width="7.42578125" style="8" customWidth="1"/>
     <col min="16" max="16" width="28.28515625" style="8" customWidth="1"/>
-    <col min="17" max="17" width="30.5703125" style="8" customWidth="1"/>
-    <col min="18" max="18" width="50.7109375" style="8" customWidth="1"/>
+    <col min="17" max="17" width="26.7109375" style="8" customWidth="1"/>
+    <col min="18" max="18" width="52.7109375" style="8" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="249"/>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
-      <c r="F1" s="249"/>
-      <c r="G1" s="249"/>
-      <c r="H1" s="249"/>
-      <c r="I1" s="249"/>
-      <c r="J1" s="249"/>
-      <c r="K1" s="249"/>
-      <c r="L1" s="249"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
+      <c r="L1" s="163"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
@@ -3096,26 +3096,26 @@
       <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="249"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="229"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="188"/>
+      <c r="N2" s="188"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="188"/>
+      <c r="Q2" s="188"/>
+      <c r="R2" s="188"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
@@ -3136,38 +3136,38 @@
       <c r="R3" s="9"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="261"/>
-      <c r="C4" s="261"/>
-      <c r="D4" s="261"/>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="261"/>
-      <c r="I4" s="261"/>
-      <c r="J4" s="261"/>
-      <c r="K4" s="261"/>
-      <c r="L4" s="261"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="262"/>
-      <c r="B5" s="262"/>
-      <c r="C5" s="262"/>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="A5" s="177"/>
+      <c r="B5" s="177"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="177"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3176,20 +3176,20 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="263" t="s">
+      <c r="A6" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="263"/>
-      <c r="C6" s="263"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="263"/>
-      <c r="F6" s="263"/>
-      <c r="G6" s="263"/>
-      <c r="H6" s="263"/>
-      <c r="I6" s="263"/>
-      <c r="J6" s="263"/>
-      <c r="K6" s="263"/>
-      <c r="L6" s="263"/>
+      <c r="B6" s="178"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="178"/>
+      <c r="L6" s="178"/>
       <c r="O6" s="16"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -3244,9 +3244,9 @@
       <c r="B9" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="264"/>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
+      <c r="C9" s="179"/>
+      <c r="D9" s="179"/>
+      <c r="E9" s="179"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="19" t="s">
@@ -3395,41 +3395,41 @@
       <c r="A15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="250" t="s">
+      <c r="B15" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="250"/>
-      <c r="D15" s="252" t="s">
+      <c r="C15" s="164"/>
+      <c r="D15" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="253"/>
-      <c r="F15" s="253" t="s">
+      <c r="E15" s="167"/>
+      <c r="F15" s="167" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="258" t="s">
+      <c r="G15" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="258"/>
-      <c r="I15" s="258"/>
-      <c r="J15" s="258"/>
-      <c r="K15" s="259"/>
-      <c r="L15" s="230" t="s">
+      <c r="H15" s="172"/>
+      <c r="I15" s="172"/>
+      <c r="J15" s="172"/>
+      <c r="K15" s="173"/>
+      <c r="L15" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="233" t="s">
+      <c r="M15" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="N15" s="236" t="s">
+      <c r="N15" s="195" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="237"/>
-      <c r="P15" s="233" t="s">
+      <c r="O15" s="196"/>
+      <c r="P15" s="192" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" s="240" t="s">
+      <c r="Q15" s="199" t="s">
         <v>62</v>
       </c>
-      <c r="R15" s="233" t="s">
+      <c r="R15" s="192" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3437,23 +3437,23 @@
       <c r="A16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="251"/>
-      <c r="C16" s="251"/>
-      <c r="D16" s="254"/>
-      <c r="E16" s="255"/>
-      <c r="F16" s="256"/>
-      <c r="G16" s="216"/>
-      <c r="H16" s="216"/>
-      <c r="I16" s="216"/>
-      <c r="J16" s="216"/>
-      <c r="K16" s="260"/>
-      <c r="L16" s="231"/>
-      <c r="M16" s="234"/>
-      <c r="N16" s="238"/>
-      <c r="O16" s="239"/>
-      <c r="P16" s="234"/>
-      <c r="Q16" s="241"/>
-      <c r="R16" s="234"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="170"/>
+      <c r="G16" s="174"/>
+      <c r="H16" s="174"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="174"/>
+      <c r="K16" s="175"/>
+      <c r="L16" s="190"/>
+      <c r="M16" s="193"/>
+      <c r="N16" s="197"/>
+      <c r="O16" s="198"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="200"/>
+      <c r="R16" s="193"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
@@ -3471,7 +3471,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="257"/>
+      <c r="F17" s="171"/>
       <c r="G17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3487,39 +3487,39 @@
       <c r="K17" s="37">
         <v>2</v>
       </c>
-      <c r="L17" s="232"/>
-      <c r="M17" s="235"/>
+      <c r="L17" s="191"/>
+      <c r="M17" s="194"/>
       <c r="N17" s="38" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="235"/>
-      <c r="Q17" s="242"/>
-      <c r="R17" s="235"/>
+      <c r="P17" s="194"/>
+      <c r="Q17" s="201"/>
+      <c r="R17" s="194"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="215"/>
-      <c r="B18" s="216"/>
-      <c r="C18" s="216"/>
-      <c r="D18" s="216"/>
-      <c r="E18" s="217"/>
-      <c r="F18" s="221"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="223">
+      <c r="A18" s="210"/>
+      <c r="B18" s="174"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="174"/>
+      <c r="E18" s="211"/>
+      <c r="F18" s="215"/>
+      <c r="G18" s="159"/>
+      <c r="H18" s="159">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="223"/>
-      <c r="J18" s="223"/>
-      <c r="K18" s="247"/>
-      <c r="L18" s="243" t="s">
+      <c r="I18" s="159"/>
+      <c r="J18" s="159"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="202" t="s">
         <v>107</v>
       </c>
       <c r="M18" s="147"/>
-      <c r="N18" s="157"/>
-      <c r="O18" s="158"/>
+      <c r="N18" s="206"/>
+      <c r="O18" s="207"/>
       <c r="P18" s="151"/>
       <c r="Q18" s="153"/>
       <c r="R18" s="155" t="s">
@@ -3527,49 +3527,49 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="218"/>
-      <c r="B19" s="219"/>
-      <c r="C19" s="219"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="220"/>
-      <c r="F19" s="222"/>
-      <c r="G19" s="224"/>
-      <c r="H19" s="224"/>
-      <c r="I19" s="224"/>
-      <c r="J19" s="224"/>
-      <c r="K19" s="248"/>
-      <c r="L19" s="244"/>
+      <c r="A19" s="212"/>
+      <c r="B19" s="213"/>
+      <c r="C19" s="213"/>
+      <c r="D19" s="213"/>
+      <c r="E19" s="214"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
+      <c r="J19" s="160"/>
+      <c r="K19" s="162"/>
+      <c r="L19" s="203"/>
       <c r="M19" s="148"/>
-      <c r="N19" s="159"/>
-      <c r="O19" s="160"/>
+      <c r="N19" s="208"/>
+      <c r="O19" s="209"/>
       <c r="P19" s="152"/>
       <c r="Q19" s="154"/>
       <c r="R19" s="156"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="142"/>
-      <c r="B20" s="212"/>
-      <c r="C20" s="212"/>
-      <c r="D20" s="161"/>
-      <c r="E20" s="162"/>
+      <c r="B20" s="158"/>
+      <c r="C20" s="158"/>
+      <c r="D20" s="182"/>
+      <c r="E20" s="183"/>
       <c r="F20" s="139"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
       <c r="I20" s="129"/>
       <c r="J20" s="129"/>
       <c r="K20" s="129"/>
-      <c r="L20" s="245"/>
+      <c r="L20" s="204"/>
       <c r="M20" s="147" t="str">
         <f>IF(ISBLANK(A20),"",A20)</f>
         <v/>
       </c>
-      <c r="N20" s="157" t="str">
+      <c r="N20" s="206" t="str">
         <f>IF(ISBLANK(D20),"",D20)</f>
         <v/>
       </c>
-      <c r="O20" s="158"/>
-      <c r="P20" s="225"/>
-      <c r="Q20" s="227"/>
+      <c r="O20" s="207"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="186"/>
       <c r="R20" s="149"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3577,54 +3577,54 @@
         <f t="shared" ref="A21" si="0">IF(A20="","",UPPER(TEXT(A20,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B21" s="212"/>
-      <c r="C21" s="212"/>
-      <c r="D21" s="163"/>
-      <c r="E21" s="164"/>
+      <c r="B21" s="158"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="180"/>
+      <c r="E21" s="181"/>
       <c r="F21" s="141"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
       <c r="I21" s="127"/>
       <c r="J21" s="127"/>
       <c r="K21" s="128"/>
-      <c r="L21" s="245"/>
+      <c r="L21" s="204"/>
       <c r="M21" s="148" t="str">
         <f>A21</f>
         <v/>
       </c>
-      <c r="N21" s="159" t="str">
+      <c r="N21" s="208" t="str">
         <f>IF(ISBLANK(D21),"",D21)</f>
         <v/>
       </c>
-      <c r="O21" s="160"/>
-      <c r="P21" s="225"/>
-      <c r="Q21" s="227"/>
+      <c r="O21" s="209"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="186"/>
       <c r="R21" s="150"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="134"/>
-      <c r="B22" s="211"/>
-      <c r="C22" s="211"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="162"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="183"/>
       <c r="F22" s="139"/>
       <c r="G22" s="129"/>
       <c r="H22" s="129"/>
       <c r="I22" s="129"/>
       <c r="J22" s="129"/>
       <c r="K22" s="129"/>
-      <c r="L22" s="245"/>
+      <c r="L22" s="204"/>
       <c r="M22" s="147" t="str">
         <f t="shared" ref="M22" si="1">IF(ISBLANK(A22),"",A22)</f>
         <v/>
       </c>
-      <c r="N22" s="157" t="str">
+      <c r="N22" s="206" t="str">
         <f t="shared" ref="N22:N53" si="2">IF(ISBLANK(D22),"",D22)</f>
         <v/>
       </c>
-      <c r="O22" s="158"/>
-      <c r="P22" s="225"/>
-      <c r="Q22" s="227"/>
+      <c r="O22" s="207"/>
+      <c r="P22" s="184"/>
+      <c r="Q22" s="186"/>
       <c r="R22" s="149"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3632,54 +3632,54 @@
         <f t="shared" ref="A23:A25" si="3">IF(A22="","",UPPER(TEXT(A22,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B23" s="212"/>
-      <c r="C23" s="212"/>
-      <c r="D23" s="163"/>
-      <c r="E23" s="164"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="180"/>
+      <c r="E23" s="181"/>
       <c r="F23" s="141"/>
       <c r="G23" s="127"/>
       <c r="H23" s="127"/>
       <c r="I23" s="127"/>
       <c r="J23" s="127"/>
       <c r="K23" s="128"/>
-      <c r="L23" s="245"/>
+      <c r="L23" s="204"/>
       <c r="M23" s="148" t="str">
         <f t="shared" ref="M23" si="4">A23</f>
         <v/>
       </c>
-      <c r="N23" s="159" t="str">
+      <c r="N23" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O23" s="160"/>
-      <c r="P23" s="225"/>
-      <c r="Q23" s="227"/>
+      <c r="O23" s="209"/>
+      <c r="P23" s="184"/>
+      <c r="Q23" s="186"/>
       <c r="R23" s="150"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="134"/>
-      <c r="B24" s="211"/>
-      <c r="C24" s="211"/>
-      <c r="D24" s="161"/>
-      <c r="E24" s="162"/>
+      <c r="B24" s="157"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="183"/>
       <c r="F24" s="139"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
       <c r="I24" s="129"/>
       <c r="J24" s="129"/>
       <c r="K24" s="129"/>
-      <c r="L24" s="245"/>
+      <c r="L24" s="204"/>
       <c r="M24" s="147" t="str">
         <f t="shared" ref="M24" si="5">IF(ISBLANK(A24),"",A24)</f>
         <v/>
       </c>
-      <c r="N24" s="157" t="str">
+      <c r="N24" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O24" s="158"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="227"/>
+      <c r="O24" s="207"/>
+      <c r="P24" s="184"/>
+      <c r="Q24" s="186"/>
       <c r="R24" s="149"/>
     </row>
     <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3687,54 +3687,54 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B25" s="212"/>
-      <c r="C25" s="212"/>
-      <c r="D25" s="163"/>
-      <c r="E25" s="164"/>
+      <c r="B25" s="158"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="180"/>
+      <c r="E25" s="181"/>
       <c r="F25" s="141"/>
       <c r="G25" s="127"/>
       <c r="H25" s="127"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
       <c r="K25" s="128"/>
-      <c r="L25" s="245"/>
+      <c r="L25" s="204"/>
       <c r="M25" s="148" t="str">
         <f t="shared" ref="M25" si="6">A25</f>
         <v/>
       </c>
-      <c r="N25" s="159" t="str">
+      <c r="N25" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O25" s="160"/>
-      <c r="P25" s="225"/>
-      <c r="Q25" s="227"/>
+      <c r="O25" s="209"/>
+      <c r="P25" s="184"/>
+      <c r="Q25" s="186"/>
       <c r="R25" s="150"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="134"/>
-      <c r="B26" s="211"/>
-      <c r="C26" s="211"/>
-      <c r="D26" s="161"/>
-      <c r="E26" s="162"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="157"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="183"/>
       <c r="F26" s="139"/>
       <c r="G26" s="129"/>
       <c r="H26" s="129"/>
       <c r="I26" s="129"/>
       <c r="J26" s="129"/>
       <c r="K26" s="129"/>
-      <c r="L26" s="245"/>
+      <c r="L26" s="204"/>
       <c r="M26" s="147" t="str">
         <f t="shared" ref="M26" si="7">IF(ISBLANK(A26),"",A26)</f>
         <v/>
       </c>
-      <c r="N26" s="157" t="str">
+      <c r="N26" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O26" s="158"/>
-      <c r="P26" s="225"/>
-      <c r="Q26" s="227"/>
+      <c r="O26" s="207"/>
+      <c r="P26" s="184"/>
+      <c r="Q26" s="186"/>
       <c r="R26" s="149"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3742,54 +3742,54 @@
         <f t="shared" ref="A27" si="8">IF(A26="","",UPPER(TEXT(A26,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B27" s="212"/>
-      <c r="C27" s="212"/>
-      <c r="D27" s="163"/>
-      <c r="E27" s="164"/>
+      <c r="B27" s="158"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="180"/>
+      <c r="E27" s="181"/>
       <c r="F27" s="141"/>
       <c r="G27" s="127"/>
       <c r="H27" s="127"/>
       <c r="I27" s="127"/>
       <c r="J27" s="127"/>
       <c r="K27" s="128"/>
-      <c r="L27" s="245"/>
+      <c r="L27" s="204"/>
       <c r="M27" s="148" t="str">
         <f t="shared" ref="M27" si="9">A27</f>
         <v/>
       </c>
-      <c r="N27" s="159" t="str">
+      <c r="N27" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O27" s="160"/>
-      <c r="P27" s="225"/>
-      <c r="Q27" s="227"/>
+      <c r="O27" s="209"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="186"/>
       <c r="R27" s="150"/>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="135"/>
-      <c r="B28" s="211"/>
-      <c r="C28" s="211"/>
-      <c r="D28" s="161"/>
-      <c r="E28" s="162"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="182"/>
+      <c r="E28" s="183"/>
       <c r="F28" s="139"/>
       <c r="G28" s="129"/>
       <c r="H28" s="129"/>
       <c r="I28" s="129"/>
       <c r="J28" s="129"/>
       <c r="K28" s="129"/>
-      <c r="L28" s="245"/>
+      <c r="L28" s="204"/>
       <c r="M28" s="147" t="str">
         <f t="shared" ref="M28" si="10">IF(ISBLANK(A28),"",A28)</f>
         <v/>
       </c>
-      <c r="N28" s="157" t="str">
+      <c r="N28" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O28" s="158"/>
-      <c r="P28" s="225"/>
-      <c r="Q28" s="227"/>
+      <c r="O28" s="207"/>
+      <c r="P28" s="184"/>
+      <c r="Q28" s="186"/>
       <c r="R28" s="149"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3797,54 +3797,54 @@
         <f t="shared" ref="A29" si="11">IF(A28="","",UPPER(TEXT(A28,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B29" s="212"/>
-      <c r="C29" s="212"/>
-      <c r="D29" s="163"/>
-      <c r="E29" s="164"/>
+      <c r="B29" s="158"/>
+      <c r="C29" s="158"/>
+      <c r="D29" s="180"/>
+      <c r="E29" s="181"/>
       <c r="F29" s="141"/>
       <c r="G29" s="127"/>
       <c r="H29" s="127"/>
       <c r="I29" s="127"/>
       <c r="J29" s="129"/>
       <c r="K29" s="128"/>
-      <c r="L29" s="245"/>
+      <c r="L29" s="204"/>
       <c r="M29" s="148" t="str">
         <f t="shared" ref="M29" si="12">A29</f>
         <v/>
       </c>
-      <c r="N29" s="159" t="str">
+      <c r="N29" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O29" s="160"/>
-      <c r="P29" s="225"/>
-      <c r="Q29" s="227"/>
+      <c r="O29" s="209"/>
+      <c r="P29" s="184"/>
+      <c r="Q29" s="186"/>
       <c r="R29" s="150"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="134"/>
-      <c r="B30" s="211"/>
-      <c r="C30" s="211"/>
-      <c r="D30" s="161"/>
-      <c r="E30" s="162"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="182"/>
+      <c r="E30" s="183"/>
       <c r="F30" s="139"/>
       <c r="G30" s="129"/>
       <c r="H30" s="129"/>
       <c r="I30" s="140"/>
       <c r="J30" s="143"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="245"/>
+      <c r="L30" s="204"/>
       <c r="M30" s="147" t="str">
         <f t="shared" ref="M30" si="13">IF(ISBLANK(A30),"",A30)</f>
         <v/>
       </c>
-      <c r="N30" s="157" t="str">
+      <c r="N30" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O30" s="158"/>
-      <c r="P30" s="225"/>
-      <c r="Q30" s="227"/>
+      <c r="O30" s="207"/>
+      <c r="P30" s="184"/>
+      <c r="Q30" s="186"/>
       <c r="R30" s="149"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3852,54 +3852,54 @@
         <f t="shared" ref="A31" si="14">IF(A30="","",UPPER(TEXT(A30,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B31" s="212"/>
-      <c r="C31" s="212"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="164"/>
+      <c r="B31" s="158"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="180"/>
+      <c r="E31" s="181"/>
       <c r="F31" s="141"/>
       <c r="G31" s="127"/>
       <c r="H31" s="127"/>
       <c r="I31" s="127"/>
       <c r="J31" s="127"/>
       <c r="K31" s="128"/>
-      <c r="L31" s="245"/>
+      <c r="L31" s="204"/>
       <c r="M31" s="148" t="str">
         <f t="shared" ref="M31" si="15">A31</f>
         <v/>
       </c>
-      <c r="N31" s="159" t="str">
+      <c r="N31" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O31" s="160"/>
-      <c r="P31" s="225"/>
-      <c r="Q31" s="227"/>
+      <c r="O31" s="209"/>
+      <c r="P31" s="184"/>
+      <c r="Q31" s="186"/>
       <c r="R31" s="150"/>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="134"/>
-      <c r="B32" s="211"/>
-      <c r="C32" s="211"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="162"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="157"/>
+      <c r="D32" s="182"/>
+      <c r="E32" s="183"/>
       <c r="F32" s="139"/>
       <c r="G32" s="129"/>
       <c r="H32" s="129"/>
       <c r="I32" s="129"/>
       <c r="J32" s="129"/>
       <c r="K32" s="129"/>
-      <c r="L32" s="245"/>
+      <c r="L32" s="204"/>
       <c r="M32" s="147" t="str">
         <f t="shared" ref="M32" si="16">IF(ISBLANK(A32),"",A32)</f>
         <v/>
       </c>
-      <c r="N32" s="157" t="str">
+      <c r="N32" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O32" s="158"/>
-      <c r="P32" s="225"/>
-      <c r="Q32" s="227"/>
+      <c r="O32" s="207"/>
+      <c r="P32" s="184"/>
+      <c r="Q32" s="186"/>
       <c r="R32" s="149"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,54 +3907,54 @@
         <f t="shared" ref="A33" si="17">IF(A32="","",UPPER(TEXT(A32,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B33" s="212"/>
-      <c r="C33" s="212"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="164"/>
+      <c r="B33" s="158"/>
+      <c r="C33" s="158"/>
+      <c r="D33" s="180"/>
+      <c r="E33" s="181"/>
       <c r="F33" s="141"/>
       <c r="G33" s="127"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
       <c r="J33" s="127"/>
       <c r="K33" s="128"/>
-      <c r="L33" s="245"/>
+      <c r="L33" s="204"/>
       <c r="M33" s="148" t="str">
         <f t="shared" ref="M33" si="18">A33</f>
         <v/>
       </c>
-      <c r="N33" s="159" t="str">
+      <c r="N33" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O33" s="160"/>
-      <c r="P33" s="225"/>
-      <c r="Q33" s="227"/>
+      <c r="O33" s="209"/>
+      <c r="P33" s="184"/>
+      <c r="Q33" s="186"/>
       <c r="R33" s="150"/>
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="134"/>
-      <c r="B34" s="211"/>
-      <c r="C34" s="211"/>
-      <c r="D34" s="161"/>
-      <c r="E34" s="162"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="183"/>
       <c r="F34" s="139"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
       <c r="I34" s="129"/>
       <c r="J34" s="129"/>
       <c r="K34" s="129"/>
-      <c r="L34" s="245"/>
+      <c r="L34" s="204"/>
       <c r="M34" s="147" t="str">
         <f t="shared" ref="M34" si="19">IF(ISBLANK(A34),"",A34)</f>
         <v/>
       </c>
-      <c r="N34" s="157" t="str">
+      <c r="N34" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O34" s="158"/>
-      <c r="P34" s="225"/>
-      <c r="Q34" s="227"/>
+      <c r="O34" s="207"/>
+      <c r="P34" s="184"/>
+      <c r="Q34" s="186"/>
       <c r="R34" s="149"/>
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3962,54 +3962,54 @@
         <f t="shared" ref="A35" si="20">IF(A34="","",UPPER(TEXT(A34,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B35" s="212"/>
-      <c r="C35" s="212"/>
-      <c r="D35" s="163"/>
-      <c r="E35" s="164"/>
+      <c r="B35" s="158"/>
+      <c r="C35" s="158"/>
+      <c r="D35" s="180"/>
+      <c r="E35" s="181"/>
       <c r="F35" s="141"/>
       <c r="G35" s="127"/>
       <c r="H35" s="127"/>
       <c r="I35" s="127"/>
       <c r="J35" s="127"/>
       <c r="K35" s="128"/>
-      <c r="L35" s="245"/>
+      <c r="L35" s="204"/>
       <c r="M35" s="148" t="str">
         <f t="shared" ref="M35" si="21">A35</f>
         <v/>
       </c>
-      <c r="N35" s="159" t="str">
+      <c r="N35" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O35" s="160"/>
-      <c r="P35" s="225"/>
-      <c r="Q35" s="227"/>
+      <c r="O35" s="209"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="186"/>
       <c r="R35" s="150"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134"/>
-      <c r="B36" s="211"/>
-      <c r="C36" s="211"/>
-      <c r="D36" s="161"/>
-      <c r="E36" s="162"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="157"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="183"/>
       <c r="F36" s="139"/>
       <c r="G36" s="129"/>
       <c r="H36" s="129"/>
       <c r="I36" s="129"/>
       <c r="J36" s="129"/>
       <c r="K36" s="129"/>
-      <c r="L36" s="245"/>
+      <c r="L36" s="204"/>
       <c r="M36" s="147" t="str">
         <f t="shared" ref="M36" si="22">IF(ISBLANK(A36),"",A36)</f>
         <v/>
       </c>
-      <c r="N36" s="157" t="str">
+      <c r="N36" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O36" s="158"/>
-      <c r="P36" s="225"/>
-      <c r="Q36" s="227"/>
+      <c r="O36" s="207"/>
+      <c r="P36" s="184"/>
+      <c r="Q36" s="186"/>
       <c r="R36" s="149"/>
     </row>
     <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4017,54 +4017,54 @@
         <f t="shared" ref="A37" si="23">IF(A36="","",UPPER(TEXT(A36,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B37" s="212"/>
-      <c r="C37" s="212"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="164"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="158"/>
+      <c r="D37" s="180"/>
+      <c r="E37" s="181"/>
       <c r="F37" s="141"/>
       <c r="G37" s="127"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
       <c r="J37" s="127"/>
       <c r="K37" s="128"/>
-      <c r="L37" s="245"/>
+      <c r="L37" s="204"/>
       <c r="M37" s="148" t="str">
         <f t="shared" ref="M37" si="24">A37</f>
         <v/>
       </c>
-      <c r="N37" s="159" t="str">
+      <c r="N37" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O37" s="160"/>
-      <c r="P37" s="225"/>
-      <c r="Q37" s="227"/>
+      <c r="O37" s="209"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="186"/>
       <c r="R37" s="150"/>
     </row>
     <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="134"/>
-      <c r="B38" s="211"/>
-      <c r="C38" s="211"/>
-      <c r="D38" s="161"/>
-      <c r="E38" s="162"/>
+      <c r="B38" s="157"/>
+      <c r="C38" s="157"/>
+      <c r="D38" s="182"/>
+      <c r="E38" s="183"/>
       <c r="F38" s="139"/>
       <c r="G38" s="129"/>
       <c r="H38" s="129"/>
       <c r="I38" s="129"/>
       <c r="J38" s="129"/>
       <c r="K38" s="129"/>
-      <c r="L38" s="245"/>
+      <c r="L38" s="204"/>
       <c r="M38" s="147" t="str">
         <f t="shared" ref="M38" si="25">IF(ISBLANK(A38),"",A38)</f>
         <v/>
       </c>
-      <c r="N38" s="157" t="str">
+      <c r="N38" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O38" s="158"/>
-      <c r="P38" s="225"/>
-      <c r="Q38" s="227"/>
+      <c r="O38" s="207"/>
+      <c r="P38" s="184"/>
+      <c r="Q38" s="186"/>
       <c r="R38" s="149"/>
     </row>
     <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4072,54 +4072,54 @@
         <f t="shared" ref="A39" si="26">IF(A38="","",UPPER(TEXT(A38,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B39" s="212"/>
-      <c r="C39" s="212"/>
-      <c r="D39" s="163"/>
-      <c r="E39" s="164"/>
+      <c r="B39" s="158"/>
+      <c r="C39" s="158"/>
+      <c r="D39" s="180"/>
+      <c r="E39" s="181"/>
       <c r="F39" s="141"/>
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
       <c r="K39" s="128"/>
-      <c r="L39" s="245"/>
+      <c r="L39" s="204"/>
       <c r="M39" s="148" t="str">
         <f t="shared" ref="M39" si="27">A39</f>
         <v/>
       </c>
-      <c r="N39" s="159" t="str">
+      <c r="N39" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O39" s="160"/>
-      <c r="P39" s="225"/>
-      <c r="Q39" s="227"/>
+      <c r="O39" s="209"/>
+      <c r="P39" s="184"/>
+      <c r="Q39" s="186"/>
       <c r="R39" s="150"/>
     </row>
     <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="134"/>
-      <c r="B40" s="211"/>
-      <c r="C40" s="211"/>
-      <c r="D40" s="161"/>
-      <c r="E40" s="162"/>
+      <c r="B40" s="157"/>
+      <c r="C40" s="157"/>
+      <c r="D40" s="182"/>
+      <c r="E40" s="183"/>
       <c r="F40" s="139"/>
       <c r="G40" s="129"/>
       <c r="H40" s="129"/>
       <c r="I40" s="129"/>
       <c r="J40" s="129"/>
       <c r="K40" s="129"/>
-      <c r="L40" s="245"/>
+      <c r="L40" s="204"/>
       <c r="M40" s="147" t="str">
         <f t="shared" ref="M40" si="28">IF(ISBLANK(A40),"",A40)</f>
         <v/>
       </c>
-      <c r="N40" s="157" t="str">
+      <c r="N40" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O40" s="158"/>
-      <c r="P40" s="225"/>
-      <c r="Q40" s="227"/>
+      <c r="O40" s="207"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="186"/>
       <c r="R40" s="149"/>
     </row>
     <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4127,54 +4127,54 @@
         <f t="shared" ref="A41" si="29">IF(A40="","",UPPER(TEXT(A40,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B41" s="212"/>
-      <c r="C41" s="212"/>
-      <c r="D41" s="163"/>
-      <c r="E41" s="164"/>
+      <c r="B41" s="158"/>
+      <c r="C41" s="158"/>
+      <c r="D41" s="180"/>
+      <c r="E41" s="181"/>
       <c r="F41" s="141"/>
       <c r="G41" s="127"/>
       <c r="H41" s="127"/>
       <c r="I41" s="127"/>
       <c r="J41" s="127"/>
       <c r="K41" s="128"/>
-      <c r="L41" s="245"/>
+      <c r="L41" s="204"/>
       <c r="M41" s="148" t="str">
         <f t="shared" ref="M41" si="30">A41</f>
         <v/>
       </c>
-      <c r="N41" s="159" t="str">
+      <c r="N41" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O41" s="160"/>
-      <c r="P41" s="225"/>
-      <c r="Q41" s="227"/>
+      <c r="O41" s="209"/>
+      <c r="P41" s="184"/>
+      <c r="Q41" s="186"/>
       <c r="R41" s="150"/>
     </row>
     <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="134"/>
-      <c r="B42" s="211"/>
-      <c r="C42" s="211"/>
-      <c r="D42" s="161"/>
-      <c r="E42" s="162"/>
+      <c r="B42" s="157"/>
+      <c r="C42" s="157"/>
+      <c r="D42" s="182"/>
+      <c r="E42" s="183"/>
       <c r="F42" s="139"/>
       <c r="G42" s="129"/>
       <c r="H42" s="129"/>
       <c r="I42" s="129"/>
       <c r="J42" s="129"/>
       <c r="K42" s="129"/>
-      <c r="L42" s="245"/>
+      <c r="L42" s="204"/>
       <c r="M42" s="147" t="str">
         <f t="shared" ref="M42" si="31">IF(ISBLANK(A42),"",A42)</f>
         <v/>
       </c>
-      <c r="N42" s="157" t="str">
+      <c r="N42" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O42" s="158"/>
-      <c r="P42" s="225"/>
-      <c r="Q42" s="227"/>
+      <c r="O42" s="207"/>
+      <c r="P42" s="184"/>
+      <c r="Q42" s="186"/>
       <c r="R42" s="149"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4182,54 +4182,54 @@
         <f t="shared" ref="A43" si="32">IF(A42="","",UPPER(TEXT(A42,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B43" s="212"/>
-      <c r="C43" s="212"/>
-      <c r="D43" s="163"/>
-      <c r="E43" s="164"/>
+      <c r="B43" s="158"/>
+      <c r="C43" s="158"/>
+      <c r="D43" s="180"/>
+      <c r="E43" s="181"/>
       <c r="F43" s="141"/>
       <c r="G43" s="127"/>
       <c r="H43" s="127"/>
       <c r="I43" s="127"/>
       <c r="J43" s="127"/>
       <c r="K43" s="128"/>
-      <c r="L43" s="245"/>
+      <c r="L43" s="204"/>
       <c r="M43" s="148" t="str">
         <f t="shared" ref="M43" si="33">A43</f>
         <v/>
       </c>
-      <c r="N43" s="159" t="str">
+      <c r="N43" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O43" s="160"/>
-      <c r="P43" s="225"/>
-      <c r="Q43" s="227"/>
+      <c r="O43" s="209"/>
+      <c r="P43" s="184"/>
+      <c r="Q43" s="186"/>
       <c r="R43" s="150"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="134"/>
-      <c r="B44" s="211"/>
-      <c r="C44" s="211"/>
-      <c r="D44" s="161"/>
-      <c r="E44" s="162"/>
+      <c r="B44" s="157"/>
+      <c r="C44" s="157"/>
+      <c r="D44" s="182"/>
+      <c r="E44" s="183"/>
       <c r="F44" s="139"/>
       <c r="G44" s="129"/>
       <c r="H44" s="129"/>
       <c r="I44" s="129"/>
       <c r="J44" s="129"/>
       <c r="K44" s="129"/>
-      <c r="L44" s="245"/>
+      <c r="L44" s="204"/>
       <c r="M44" s="147" t="str">
         <f t="shared" ref="M44" si="34">IF(ISBLANK(A44),"",A44)</f>
         <v/>
       </c>
-      <c r="N44" s="157" t="str">
+      <c r="N44" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O44" s="158"/>
-      <c r="P44" s="225"/>
-      <c r="Q44" s="227"/>
+      <c r="O44" s="207"/>
+      <c r="P44" s="184"/>
+      <c r="Q44" s="186"/>
       <c r="R44" s="149"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4237,54 +4237,54 @@
         <f t="shared" ref="A45" si="35">IF(A44="","",UPPER(TEXT(A44,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B45" s="212"/>
-      <c r="C45" s="212"/>
-      <c r="D45" s="163"/>
-      <c r="E45" s="164"/>
+      <c r="B45" s="158"/>
+      <c r="C45" s="158"/>
+      <c r="D45" s="180"/>
+      <c r="E45" s="181"/>
       <c r="F45" s="141"/>
       <c r="G45" s="127"/>
       <c r="H45" s="127"/>
       <c r="I45" s="127"/>
       <c r="J45" s="127"/>
       <c r="K45" s="128"/>
-      <c r="L45" s="245"/>
+      <c r="L45" s="204"/>
       <c r="M45" s="148" t="str">
         <f t="shared" ref="M45" si="36">A45</f>
         <v/>
       </c>
-      <c r="N45" s="159" t="str">
+      <c r="N45" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O45" s="160"/>
-      <c r="P45" s="225"/>
-      <c r="Q45" s="227"/>
+      <c r="O45" s="209"/>
+      <c r="P45" s="184"/>
+      <c r="Q45" s="186"/>
       <c r="R45" s="150"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="134"/>
-      <c r="B46" s="211"/>
-      <c r="C46" s="211"/>
-      <c r="D46" s="161"/>
-      <c r="E46" s="162"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="157"/>
+      <c r="D46" s="182"/>
+      <c r="E46" s="183"/>
       <c r="F46" s="139"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
       <c r="I46" s="129"/>
       <c r="J46" s="129"/>
       <c r="K46" s="129"/>
-      <c r="L46" s="245"/>
+      <c r="L46" s="204"/>
       <c r="M46" s="147" t="str">
         <f t="shared" ref="M46" si="37">IF(ISBLANK(A46),"",A46)</f>
         <v/>
       </c>
-      <c r="N46" s="157" t="str">
+      <c r="N46" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O46" s="158"/>
-      <c r="P46" s="225"/>
-      <c r="Q46" s="227"/>
+      <c r="O46" s="207"/>
+      <c r="P46" s="184"/>
+      <c r="Q46" s="186"/>
       <c r="R46" s="149"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4292,54 +4292,54 @@
         <f t="shared" ref="A47" si="38">IF(A46="","",UPPER(TEXT(A46,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B47" s="212"/>
-      <c r="C47" s="212"/>
-      <c r="D47" s="163"/>
-      <c r="E47" s="164"/>
+      <c r="B47" s="158"/>
+      <c r="C47" s="158"/>
+      <c r="D47" s="180"/>
+      <c r="E47" s="181"/>
       <c r="F47" s="141"/>
       <c r="G47" s="127"/>
       <c r="H47" s="127"/>
       <c r="I47" s="127"/>
       <c r="J47" s="127"/>
       <c r="K47" s="128"/>
-      <c r="L47" s="245"/>
+      <c r="L47" s="204"/>
       <c r="M47" s="148" t="str">
         <f t="shared" ref="M47" si="39">A47</f>
         <v/>
       </c>
-      <c r="N47" s="159" t="str">
+      <c r="N47" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O47" s="160"/>
-      <c r="P47" s="225"/>
-      <c r="Q47" s="227"/>
+      <c r="O47" s="209"/>
+      <c r="P47" s="184"/>
+      <c r="Q47" s="186"/>
       <c r="R47" s="150"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="134"/>
-      <c r="B48" s="211"/>
-      <c r="C48" s="211"/>
-      <c r="D48" s="161"/>
-      <c r="E48" s="162"/>
+      <c r="B48" s="157"/>
+      <c r="C48" s="157"/>
+      <c r="D48" s="182"/>
+      <c r="E48" s="183"/>
       <c r="F48" s="139"/>
       <c r="G48" s="129"/>
       <c r="H48" s="129"/>
       <c r="I48" s="129"/>
       <c r="J48" s="129"/>
       <c r="K48" s="129"/>
-      <c r="L48" s="245"/>
+      <c r="L48" s="204"/>
       <c r="M48" s="147" t="str">
         <f t="shared" ref="M48" si="40">IF(ISBLANK(A48),"",A48)</f>
         <v/>
       </c>
-      <c r="N48" s="157" t="str">
+      <c r="N48" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O48" s="158"/>
-      <c r="P48" s="225"/>
-      <c r="Q48" s="227"/>
+      <c r="O48" s="207"/>
+      <c r="P48" s="184"/>
+      <c r="Q48" s="186"/>
       <c r="R48" s="149"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4347,54 +4347,54 @@
         <f t="shared" ref="A49" si="41">IF(A48="","",UPPER(TEXT(A48,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B49" s="212"/>
-      <c r="C49" s="212"/>
-      <c r="D49" s="163"/>
-      <c r="E49" s="164"/>
+      <c r="B49" s="158"/>
+      <c r="C49" s="158"/>
+      <c r="D49" s="180"/>
+      <c r="E49" s="181"/>
       <c r="F49" s="141"/>
       <c r="G49" s="127"/>
       <c r="H49" s="127"/>
       <c r="I49" s="127"/>
       <c r="J49" s="127"/>
       <c r="K49" s="128"/>
-      <c r="L49" s="245"/>
+      <c r="L49" s="204"/>
       <c r="M49" s="148" t="str">
         <f t="shared" ref="M49" si="42">A49</f>
         <v/>
       </c>
-      <c r="N49" s="159" t="str">
+      <c r="N49" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O49" s="160"/>
-      <c r="P49" s="225"/>
-      <c r="Q49" s="227"/>
+      <c r="O49" s="209"/>
+      <c r="P49" s="184"/>
+      <c r="Q49" s="186"/>
       <c r="R49" s="150"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134"/>
-      <c r="B50" s="211"/>
-      <c r="C50" s="211"/>
-      <c r="D50" s="161"/>
-      <c r="E50" s="162"/>
+      <c r="B50" s="157"/>
+      <c r="C50" s="157"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="183"/>
       <c r="F50" s="139"/>
       <c r="G50" s="129"/>
       <c r="H50" s="129"/>
       <c r="I50" s="129"/>
       <c r="J50" s="129"/>
       <c r="K50" s="129"/>
-      <c r="L50" s="245"/>
+      <c r="L50" s="204"/>
       <c r="M50" s="147" t="str">
         <f t="shared" ref="M50" si="43">IF(ISBLANK(A50),"",A50)</f>
         <v/>
       </c>
-      <c r="N50" s="157" t="str">
+      <c r="N50" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O50" s="158"/>
-      <c r="P50" s="225"/>
-      <c r="Q50" s="227"/>
+      <c r="O50" s="207"/>
+      <c r="P50" s="184"/>
+      <c r="Q50" s="186"/>
       <c r="R50" s="149"/>
     </row>
     <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,54 +4402,54 @@
         <f t="shared" ref="A51" si="44">IF(A50="","",UPPER(TEXT(A50,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B51" s="212"/>
-      <c r="C51" s="212"/>
-      <c r="D51" s="163"/>
-      <c r="E51" s="164"/>
+      <c r="B51" s="158"/>
+      <c r="C51" s="158"/>
+      <c r="D51" s="180"/>
+      <c r="E51" s="181"/>
       <c r="F51" s="141"/>
       <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127"/>
       <c r="J51" s="127"/>
       <c r="K51" s="128"/>
-      <c r="L51" s="245"/>
+      <c r="L51" s="204"/>
       <c r="M51" s="148" t="str">
         <f t="shared" ref="M51" si="45">A51</f>
         <v/>
       </c>
-      <c r="N51" s="159" t="str">
+      <c r="N51" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O51" s="160"/>
-      <c r="P51" s="225"/>
-      <c r="Q51" s="227"/>
+      <c r="O51" s="209"/>
+      <c r="P51" s="184"/>
+      <c r="Q51" s="186"/>
       <c r="R51" s="150"/>
     </row>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="134"/>
-      <c r="B52" s="211"/>
-      <c r="C52" s="211"/>
-      <c r="D52" s="161"/>
-      <c r="E52" s="162"/>
+      <c r="B52" s="157"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="183"/>
       <c r="F52" s="139"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
       <c r="I52" s="129"/>
       <c r="J52" s="129"/>
       <c r="K52" s="129"/>
-      <c r="L52" s="245"/>
+      <c r="L52" s="204"/>
       <c r="M52" s="147" t="str">
         <f t="shared" ref="M52" si="46">IF(ISBLANK(A52),"",A52)</f>
         <v/>
       </c>
-      <c r="N52" s="157" t="str">
+      <c r="N52" s="206" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O52" s="158"/>
-      <c r="P52" s="225"/>
-      <c r="Q52" s="227"/>
+      <c r="O52" s="207"/>
+      <c r="P52" s="184"/>
+      <c r="Q52" s="186"/>
       <c r="R52" s="149"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4457,28 +4457,28 @@
         <f t="shared" ref="A53" si="47">IF(A52="","",UPPER(TEXT(A52,"[$-043E]DDDD")))</f>
         <v/>
       </c>
-      <c r="B53" s="212"/>
-      <c r="C53" s="212"/>
-      <c r="D53" s="163"/>
-      <c r="E53" s="164"/>
+      <c r="B53" s="158"/>
+      <c r="C53" s="158"/>
+      <c r="D53" s="180"/>
+      <c r="E53" s="181"/>
       <c r="F53" s="141"/>
       <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127"/>
       <c r="J53" s="127"/>
       <c r="K53" s="128"/>
-      <c r="L53" s="246"/>
+      <c r="L53" s="205"/>
       <c r="M53" s="148" t="str">
         <f t="shared" ref="M53" si="48">A53</f>
         <v/>
       </c>
-      <c r="N53" s="159" t="str">
+      <c r="N53" s="208" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O53" s="160"/>
-      <c r="P53" s="226"/>
-      <c r="Q53" s="228"/>
+      <c r="O53" s="209"/>
+      <c r="P53" s="185"/>
+      <c r="Q53" s="187"/>
       <c r="R53" s="150"/>
     </row>
     <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4593,8 +4593,8 @@
         <f>SUM(G55:K55)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="213"/>
-      <c r="H58" s="213"/>
+      <c r="G58" s="218"/>
+      <c r="H58" s="218"/>
       <c r="I58" s="49" t="s">
         <v>29</v>
       </c>
@@ -4620,8 +4620,8 @@
         <f>L9</f>
         <v>0</v>
       </c>
-      <c r="G59" s="213"/>
-      <c r="H59" s="213"/>
+      <c r="G59" s="218"/>
+      <c r="H59" s="218"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
@@ -4687,31 +4687,31 @@
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
       <c r="B63" s="57"/>
-      <c r="C63" s="214" t="s">
+      <c r="C63" s="219" t="s">
         <v>35</v>
       </c>
-      <c r="D63" s="214"/>
-      <c r="E63" s="214"/>
-      <c r="F63" s="214"/>
-      <c r="G63" s="214"/>
-      <c r="H63" s="214"/>
-      <c r="I63" s="214"/>
-      <c r="J63" s="214"/>
-      <c r="K63" s="214"/>
+      <c r="D63" s="219"/>
+      <c r="E63" s="219"/>
+      <c r="F63" s="219"/>
+      <c r="G63" s="219"/>
+      <c r="H63" s="219"/>
+      <c r="I63" s="219"/>
+      <c r="J63" s="219"/>
+      <c r="K63" s="219"/>
       <c r="L63" s="3"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
       <c r="B64" s="57"/>
-      <c r="C64" s="214"/>
-      <c r="D64" s="214"/>
-      <c r="E64" s="214"/>
-      <c r="F64" s="214"/>
-      <c r="G64" s="214"/>
-      <c r="H64" s="214"/>
-      <c r="I64" s="214"/>
-      <c r="J64" s="214"/>
-      <c r="K64" s="214"/>
+      <c r="C64" s="219"/>
+      <c r="D64" s="219"/>
+      <c r="E64" s="219"/>
+      <c r="F64" s="219"/>
+      <c r="G64" s="219"/>
+      <c r="H64" s="219"/>
+      <c r="I64" s="219"/>
+      <c r="J64" s="219"/>
+      <c r="K64" s="219"/>
       <c r="L64" s="3"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -4822,14 +4822,14 @@
       <c r="J71" s="60"/>
       <c r="K71" s="60"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="210" t="s">
+      <c r="M71" s="217" t="s">
         <v>87</v>
       </c>
-      <c r="N71" s="210"/>
-      <c r="O71" s="210"/>
-      <c r="P71" s="210"/>
-      <c r="Q71" s="210"/>
-      <c r="R71" s="210"/>
+      <c r="N71" s="217"/>
+      <c r="O71" s="217"/>
+      <c r="P71" s="217"/>
+      <c r="Q71" s="217"/>
+      <c r="R71" s="217"/>
     </row>
     <row r="72" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="50"/>
@@ -4846,14 +4846,14 @@
       <c r="J72" s="60"/>
       <c r="K72" s="60"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="210" t="s">
+      <c r="M72" s="217" t="s">
         <v>88</v>
       </c>
-      <c r="N72" s="210"/>
-      <c r="O72" s="210"/>
-      <c r="P72" s="210"/>
-      <c r="Q72" s="210"/>
-      <c r="R72" s="210"/>
+      <c r="N72" s="217"/>
+      <c r="O72" s="217"/>
+      <c r="P72" s="217"/>
+      <c r="Q72" s="217"/>
+      <c r="R72" s="217"/>
     </row>
     <row r="73" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
@@ -4872,12 +4872,12 @@
       <c r="J73" s="60"/>
       <c r="K73" s="60"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="202"/>
-      <c r="N73" s="202"/>
-      <c r="O73" s="202"/>
-      <c r="P73" s="202"/>
-      <c r="Q73" s="202"/>
-      <c r="R73" s="202"/>
+      <c r="M73" s="221"/>
+      <c r="N73" s="221"/>
+      <c r="O73" s="221"/>
+      <c r="P73" s="221"/>
+      <c r="Q73" s="221"/>
+      <c r="R73" s="221"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="50"/>
@@ -4903,24 +4903,24 @@
       <c r="E75" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="203">
+      <c r="F75" s="222">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="G75" s="203"/>
-      <c r="H75" s="203"/>
-      <c r="I75" s="203"/>
-      <c r="J75" s="203"/>
-      <c r="K75" s="203"/>
+      <c r="G75" s="222"/>
+      <c r="H75" s="222"/>
+      <c r="I75" s="222"/>
+      <c r="J75" s="222"/>
+      <c r="K75" s="222"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="204" t="s">
+      <c r="M75" s="223" t="s">
         <v>89</v>
       </c>
-      <c r="N75" s="204"/>
-      <c r="O75" s="204"/>
-      <c r="P75" s="204"/>
-      <c r="Q75" s="204"/>
-      <c r="R75" s="204"/>
+      <c r="N75" s="223"/>
+      <c r="O75" s="223"/>
+      <c r="P75" s="223"/>
+      <c r="Q75" s="223"/>
+      <c r="R75" s="223"/>
     </row>
     <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="50"/>
@@ -4952,14 +4952,14 @@
       <c r="E77" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="205">
+      <c r="F77" s="224">
         <f>C10</f>
         <v>0</v>
       </c>
-      <c r="G77" s="205"/>
-      <c r="H77" s="205"/>
-      <c r="I77" s="205"/>
-      <c r="J77" s="205"/>
+      <c r="G77" s="224"/>
+      <c r="H77" s="224"/>
+      <c r="I77" s="224"/>
+      <c r="J77" s="224"/>
       <c r="K77" s="40"/>
       <c r="L77" s="50"/>
       <c r="M77" s="75"/>
@@ -4984,13 +4984,13 @@
       <c r="L78" s="50"/>
       <c r="M78" s="133"/>
       <c r="N78" s="133"/>
-      <c r="O78" s="207" t="str">
+      <c r="O78" s="226" t="str">
         <f>"NAMA PEGAWAI :    " &amp; C8</f>
         <v xml:space="preserve">NAMA PEGAWAI :    </v>
       </c>
-      <c r="P78" s="207"/>
-      <c r="Q78" s="207"/>
-      <c r="R78" s="207"/>
+      <c r="P78" s="226"/>
+      <c r="Q78" s="226"/>
+      <c r="R78" s="226"/>
     </row>
     <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="67"/>
@@ -5012,11 +5012,11 @@
       <c r="M79" s="77"/>
       <c r="N79" s="77"/>
       <c r="O79" s="78"/>
-      <c r="P79" s="206" t="str">
+      <c r="P79" s="225" t="str">
         <f>"                      "&amp;C11</f>
         <v xml:space="preserve">                      </v>
       </c>
-      <c r="Q79" s="206"/>
+      <c r="Q79" s="225"/>
       <c r="R79" s="79"/>
     </row>
     <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
@@ -5054,13 +5054,13 @@
       <c r="L81" s="50"/>
       <c r="M81" s="78"/>
       <c r="N81" s="78"/>
-      <c r="O81" s="208" t="str">
+      <c r="O81" s="227" t="str">
         <f>"NO. PEGAWAI :        " &amp; C10</f>
         <v xml:space="preserve">NO. PEGAWAI :        </v>
       </c>
-      <c r="P81" s="208"/>
-      <c r="Q81" s="208"/>
-      <c r="R81" s="208"/>
+      <c r="P81" s="227"/>
+      <c r="Q81" s="227"/>
+      <c r="R81" s="227"/>
     </row>
     <row r="82" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="50"/>
@@ -5097,12 +5097,12 @@
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="209"/>
-      <c r="N83" s="209"/>
-      <c r="O83" s="209"/>
-      <c r="P83" s="209"/>
-      <c r="Q83" s="209"/>
-      <c r="R83" s="209"/>
+      <c r="M83" s="228"/>
+      <c r="N83" s="228"/>
+      <c r="O83" s="228"/>
+      <c r="P83" s="228"/>
+      <c r="Q83" s="228"/>
+      <c r="R83" s="228"/>
     </row>
     <row r="84" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="50"/>
@@ -5121,14 +5121,14 @@
       <c r="J84" s="74"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="188" t="s">
+      <c r="M84" s="220" t="s">
         <v>90</v>
       </c>
-      <c r="N84" s="188"/>
-      <c r="O84" s="188"/>
-      <c r="P84" s="188"/>
-      <c r="Q84" s="188"/>
-      <c r="R84" s="188"/>
+      <c r="N84" s="220"/>
+      <c r="O84" s="220"/>
+      <c r="P84" s="220"/>
+      <c r="Q84" s="220"/>
+      <c r="R84" s="220"/>
     </row>
     <row r="85" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="50"/>
@@ -5143,14 +5143,14 @@
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="188" t="s">
+      <c r="M85" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="N85" s="188"/>
-      <c r="O85" s="188"/>
-      <c r="P85" s="188"/>
-      <c r="Q85" s="188"/>
-      <c r="R85" s="188"/>
+      <c r="N85" s="220"/>
+      <c r="O85" s="220"/>
+      <c r="P85" s="220"/>
+      <c r="Q85" s="220"/>
+      <c r="R85" s="220"/>
     </row>
     <row r="86" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="50"/>
@@ -5169,12 +5169,12 @@
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="189"/>
-      <c r="N86" s="189"/>
-      <c r="O86" s="189"/>
-      <c r="P86" s="189"/>
-      <c r="Q86" s="189"/>
-      <c r="R86" s="189"/>
+      <c r="M86" s="229"/>
+      <c r="N86" s="229"/>
+      <c r="O86" s="229"/>
+      <c r="P86" s="229"/>
+      <c r="Q86" s="229"/>
+      <c r="R86" s="229"/>
     </row>
     <row r="87" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="50"/>
@@ -5189,12 +5189,12 @@
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="188"/>
-      <c r="N87" s="188"/>
-      <c r="O87" s="188"/>
-      <c r="P87" s="188"/>
-      <c r="Q87" s="188"/>
-      <c r="R87" s="188"/>
+      <c r="M87" s="220"/>
+      <c r="N87" s="220"/>
+      <c r="O87" s="220"/>
+      <c r="P87" s="220"/>
+      <c r="Q87" s="220"/>
+      <c r="R87" s="220"/>
     </row>
     <row r="88" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50"/>
@@ -5206,21 +5206,21 @@
       <c r="E88" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="187"/>
-      <c r="G88" s="187"/>
-      <c r="H88" s="187"/>
-      <c r="I88" s="187"/>
-      <c r="J88" s="187"/>
+      <c r="F88" s="240"/>
+      <c r="G88" s="240"/>
+      <c r="H88" s="240"/>
+      <c r="I88" s="240"/>
+      <c r="J88" s="240"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="188" t="s">
+      <c r="M88" s="220" t="s">
         <v>92</v>
       </c>
-      <c r="N88" s="188"/>
-      <c r="O88" s="188"/>
-      <c r="P88" s="188"/>
-      <c r="Q88" s="188"/>
-      <c r="R88" s="188"/>
+      <c r="N88" s="220"/>
+      <c r="O88" s="220"/>
+      <c r="P88" s="220"/>
+      <c r="Q88" s="220"/>
+      <c r="R88" s="220"/>
     </row>
     <row r="89" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="50"/>
@@ -5373,12 +5373,12 @@
       <c r="J95" s="86"/>
       <c r="K95" s="27"/>
       <c r="L95" s="17"/>
-      <c r="M95" s="189"/>
-      <c r="N95" s="189"/>
-      <c r="O95" s="189"/>
-      <c r="P95" s="189"/>
-      <c r="Q95" s="189"/>
-      <c r="R95" s="189"/>
+      <c r="M95" s="229"/>
+      <c r="N95" s="229"/>
+      <c r="O95" s="229"/>
+      <c r="P95" s="229"/>
+      <c r="Q95" s="229"/>
+      <c r="R95" s="229"/>
     </row>
     <row r="96" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
@@ -5395,12 +5395,12 @@
       <c r="J96" s="86"/>
       <c r="K96" s="27"/>
       <c r="L96" s="17"/>
-      <c r="M96" s="189"/>
-      <c r="N96" s="189"/>
-      <c r="O96" s="189"/>
-      <c r="P96" s="189"/>
-      <c r="Q96" s="189"/>
-      <c r="R96" s="189"/>
+      <c r="M96" s="229"/>
+      <c r="N96" s="229"/>
+      <c r="O96" s="229"/>
+      <c r="P96" s="229"/>
+      <c r="Q96" s="229"/>
+      <c r="R96" s="229"/>
     </row>
     <row r="97" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
@@ -5417,12 +5417,12 @@
       <c r="J97" s="86"/>
       <c r="K97" s="27"/>
       <c r="L97" s="17"/>
-      <c r="M97" s="189"/>
-      <c r="N97" s="189"/>
-      <c r="O97" s="189"/>
-      <c r="P97" s="189"/>
-      <c r="Q97" s="189"/>
-      <c r="R97" s="189"/>
+      <c r="M97" s="229"/>
+      <c r="N97" s="229"/>
+      <c r="O97" s="229"/>
+      <c r="P97" s="229"/>
+      <c r="Q97" s="229"/>
+      <c r="R97" s="229"/>
     </row>
     <row r="98" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
@@ -5439,12 +5439,12 @@
       <c r="J98" s="86"/>
       <c r="K98" s="27"/>
       <c r="L98" s="17"/>
-      <c r="M98" s="189"/>
-      <c r="N98" s="189"/>
-      <c r="O98" s="189"/>
-      <c r="P98" s="189"/>
-      <c r="Q98" s="189"/>
-      <c r="R98" s="189"/>
+      <c r="M98" s="229"/>
+      <c r="N98" s="229"/>
+      <c r="O98" s="229"/>
+      <c r="P98" s="229"/>
+      <c r="Q98" s="229"/>
+      <c r="R98" s="229"/>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="64"/>
@@ -5461,12 +5461,12 @@
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
       <c r="L99" s="17"/>
-      <c r="M99" s="188"/>
-      <c r="N99" s="188"/>
-      <c r="O99" s="188"/>
-      <c r="P99" s="188"/>
-      <c r="Q99" s="188"/>
-      <c r="R99" s="188"/>
+      <c r="M99" s="220"/>
+      <c r="N99" s="220"/>
+      <c r="O99" s="220"/>
+      <c r="P99" s="220"/>
+      <c r="Q99" s="220"/>
+      <c r="R99" s="220"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="50"/>
@@ -5771,36 +5771,36 @@
     </row>
     <row r="119" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="190" t="s">
+      <c r="A124" s="241" t="s">
         <v>65</v>
       </c>
-      <c r="B124" s="191"/>
-      <c r="C124" s="191"/>
-      <c r="D124" s="191"/>
-      <c r="E124" s="191"/>
-      <c r="F124" s="191"/>
-      <c r="G124" s="191"/>
-      <c r="H124" s="191"/>
-      <c r="I124" s="191"/>
-      <c r="J124" s="191"/>
-      <c r="K124" s="191"/>
-      <c r="L124" s="192"/>
+      <c r="B124" s="242"/>
+      <c r="C124" s="242"/>
+      <c r="D124" s="242"/>
+      <c r="E124" s="242"/>
+      <c r="F124" s="242"/>
+      <c r="G124" s="242"/>
+      <c r="H124" s="242"/>
+      <c r="I124" s="242"/>
+      <c r="J124" s="242"/>
+      <c r="K124" s="242"/>
+      <c r="L124" s="243"/>
     </row>
     <row r="125" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="193" t="s">
+      <c r="A125" s="244" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="194"/>
-      <c r="C125" s="194"/>
-      <c r="D125" s="194"/>
-      <c r="E125" s="194"/>
-      <c r="F125" s="194"/>
-      <c r="G125" s="194"/>
-      <c r="H125" s="194"/>
-      <c r="I125" s="194"/>
-      <c r="J125" s="194"/>
-      <c r="K125" s="194"/>
-      <c r="L125" s="195"/>
+      <c r="B125" s="245"/>
+      <c r="C125" s="245"/>
+      <c r="D125" s="245"/>
+      <c r="E125" s="245"/>
+      <c r="F125" s="245"/>
+      <c r="G125" s="245"/>
+      <c r="H125" s="245"/>
+      <c r="I125" s="245"/>
+      <c r="J125" s="245"/>
+      <c r="K125" s="245"/>
+      <c r="L125" s="246"/>
     </row>
     <row r="126" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="105" t="s">
@@ -5808,20 +5808,20 @@
       </c>
       <c r="B126" s="106"/>
       <c r="C126" s="106"/>
-      <c r="D126" s="196">
+      <c r="D126" s="247">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="E126" s="197"/>
-      <c r="F126" s="197"/>
-      <c r="G126" s="197"/>
-      <c r="H126" s="197"/>
-      <c r="I126" s="198"/>
-      <c r="J126" s="199" t="s">
+      <c r="E126" s="248"/>
+      <c r="F126" s="248"/>
+      <c r="G126" s="248"/>
+      <c r="H126" s="248"/>
+      <c r="I126" s="249"/>
+      <c r="J126" s="250" t="s">
         <v>68</v>
       </c>
-      <c r="K126" s="200"/>
-      <c r="L126" s="201"/>
+      <c r="K126" s="251"/>
+      <c r="L126" s="252"/>
     </row>
     <row r="127" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="107" t="s">
@@ -5857,23 +5857,23 @@
       <c r="A129" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B129" s="177" t="s">
+      <c r="B129" s="230" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="178"/>
-      <c r="D129" s="179" t="s">
+      <c r="C129" s="231"/>
+      <c r="D129" s="232" t="s">
         <v>72</v>
       </c>
-      <c r="E129" s="180"/>
-      <c r="F129" s="180"/>
-      <c r="G129" s="180"/>
-      <c r="H129" s="180"/>
-      <c r="I129" s="180"/>
-      <c r="J129" s="181"/>
-      <c r="K129" s="179" t="s">
+      <c r="E129" s="233"/>
+      <c r="F129" s="233"/>
+      <c r="G129" s="233"/>
+      <c r="H129" s="233"/>
+      <c r="I129" s="233"/>
+      <c r="J129" s="234"/>
+      <c r="K129" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="L129" s="180"/>
+      <c r="L129" s="233"/>
     </row>
     <row r="130" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="121"/>
@@ -5883,15 +5883,15 @@
       <c r="C130" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="D130" s="182"/>
-      <c r="E130" s="183"/>
-      <c r="F130" s="183"/>
-      <c r="G130" s="183"/>
-      <c r="H130" s="183"/>
-      <c r="I130" s="183"/>
-      <c r="J130" s="184"/>
-      <c r="K130" s="185"/>
-      <c r="L130" s="186"/>
+      <c r="D130" s="235"/>
+      <c r="E130" s="236"/>
+      <c r="F130" s="236"/>
+      <c r="G130" s="236"/>
+      <c r="H130" s="236"/>
+      <c r="I130" s="236"/>
+      <c r="J130" s="237"/>
+      <c r="K130" s="238"/>
+      <c r="L130" s="239"/>
     </row>
     <row r="131" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="124">
@@ -5899,17 +5899,17 @@
       </c>
       <c r="B131" s="124"/>
       <c r="C131" s="125"/>
-      <c r="D131" s="165" t="s">
+      <c r="D131" s="260" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="166"/>
-      <c r="F131" s="166"/>
-      <c r="G131" s="166"/>
-      <c r="H131" s="166"/>
-      <c r="I131" s="166"/>
-      <c r="J131" s="167"/>
-      <c r="K131" s="168"/>
-      <c r="L131" s="168"/>
+      <c r="E131" s="261"/>
+      <c r="F131" s="261"/>
+      <c r="G131" s="261"/>
+      <c r="H131" s="261"/>
+      <c r="I131" s="261"/>
+      <c r="J131" s="262"/>
+      <c r="K131" s="256"/>
+      <c r="L131" s="256"/>
     </row>
     <row r="132" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="124">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="B132" s="124"/>
       <c r="C132" s="126"/>
-      <c r="D132" s="165" t="s">
+      <c r="D132" s="260" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="166"/>
-      <c r="F132" s="166"/>
-      <c r="G132" s="166"/>
-      <c r="H132" s="166"/>
-      <c r="I132" s="166"/>
-      <c r="J132" s="167"/>
-      <c r="K132" s="168"/>
-      <c r="L132" s="168"/>
+      <c r="E132" s="261"/>
+      <c r="F132" s="261"/>
+      <c r="G132" s="261"/>
+      <c r="H132" s="261"/>
+      <c r="I132" s="261"/>
+      <c r="J132" s="262"/>
+      <c r="K132" s="256"/>
+      <c r="L132" s="256"/>
     </row>
     <row r="133" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="124">
@@ -5935,17 +5935,17 @@
       </c>
       <c r="B133" s="124"/>
       <c r="C133" s="126"/>
-      <c r="D133" s="165" t="s">
+      <c r="D133" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="E133" s="166"/>
-      <c r="F133" s="166"/>
-      <c r="G133" s="166"/>
-      <c r="H133" s="166"/>
-      <c r="I133" s="166"/>
-      <c r="J133" s="167"/>
-      <c r="K133" s="168"/>
-      <c r="L133" s="168"/>
+      <c r="E133" s="261"/>
+      <c r="F133" s="261"/>
+      <c r="G133" s="261"/>
+      <c r="H133" s="261"/>
+      <c r="I133" s="261"/>
+      <c r="J133" s="262"/>
+      <c r="K133" s="256"/>
+      <c r="L133" s="256"/>
     </row>
     <row r="134" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="124">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="B134" s="124"/>
       <c r="C134" s="126"/>
-      <c r="D134" s="165" t="s">
+      <c r="D134" s="260" t="s">
         <v>79</v>
       </c>
-      <c r="E134" s="166"/>
-      <c r="F134" s="166"/>
-      <c r="G134" s="166"/>
-      <c r="H134" s="166"/>
-      <c r="I134" s="166"/>
-      <c r="J134" s="167"/>
-      <c r="K134" s="168"/>
-      <c r="L134" s="168"/>
+      <c r="E134" s="261"/>
+      <c r="F134" s="261"/>
+      <c r="G134" s="261"/>
+      <c r="H134" s="261"/>
+      <c r="I134" s="261"/>
+      <c r="J134" s="262"/>
+      <c r="K134" s="256"/>
+      <c r="L134" s="256"/>
     </row>
     <row r="135" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="124">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="B135" s="124"/>
       <c r="C135" s="126"/>
-      <c r="D135" s="165" t="s">
+      <c r="D135" s="260" t="s">
         <v>80</v>
       </c>
-      <c r="E135" s="166"/>
-      <c r="F135" s="166"/>
-      <c r="G135" s="166"/>
-      <c r="H135" s="166"/>
-      <c r="I135" s="166"/>
-      <c r="J135" s="167"/>
-      <c r="K135" s="168"/>
-      <c r="L135" s="168"/>
+      <c r="E135" s="261"/>
+      <c r="F135" s="261"/>
+      <c r="G135" s="261"/>
+      <c r="H135" s="261"/>
+      <c r="I135" s="261"/>
+      <c r="J135" s="262"/>
+      <c r="K135" s="256"/>
+      <c r="L135" s="256"/>
     </row>
     <row r="136" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="124">
@@ -5989,17 +5989,17 @@
       </c>
       <c r="B136" s="124"/>
       <c r="C136" s="126"/>
-      <c r="D136" s="165" t="s">
+      <c r="D136" s="260" t="s">
         <v>81</v>
       </c>
-      <c r="E136" s="166"/>
-      <c r="F136" s="166"/>
-      <c r="G136" s="166"/>
-      <c r="H136" s="166"/>
-      <c r="I136" s="166"/>
-      <c r="J136" s="167"/>
-      <c r="K136" s="168"/>
-      <c r="L136" s="168"/>
+      <c r="E136" s="261"/>
+      <c r="F136" s="261"/>
+      <c r="G136" s="261"/>
+      <c r="H136" s="261"/>
+      <c r="I136" s="261"/>
+      <c r="J136" s="262"/>
+      <c r="K136" s="256"/>
+      <c r="L136" s="256"/>
     </row>
     <row r="137" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="124">
@@ -6007,17 +6007,17 @@
       </c>
       <c r="B137" s="124"/>
       <c r="C137" s="126"/>
-      <c r="D137" s="165" t="s">
+      <c r="D137" s="260" t="s">
         <v>82</v>
       </c>
-      <c r="E137" s="166"/>
-      <c r="F137" s="166"/>
-      <c r="G137" s="166"/>
-      <c r="H137" s="166"/>
-      <c r="I137" s="166"/>
-      <c r="J137" s="167"/>
-      <c r="K137" s="168"/>
-      <c r="L137" s="168"/>
+      <c r="E137" s="261"/>
+      <c r="F137" s="261"/>
+      <c r="G137" s="261"/>
+      <c r="H137" s="261"/>
+      <c r="I137" s="261"/>
+      <c r="J137" s="262"/>
+      <c r="K137" s="256"/>
+      <c r="L137" s="256"/>
     </row>
     <row r="138" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="124">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="B138" s="124"/>
       <c r="C138" s="126"/>
-      <c r="D138" s="169" t="s">
+      <c r="D138" s="253" t="s">
         <v>108</v>
       </c>
-      <c r="E138" s="170"/>
-      <c r="F138" s="170"/>
-      <c r="G138" s="170"/>
-      <c r="H138" s="170"/>
-      <c r="I138" s="170"/>
-      <c r="J138" s="171"/>
-      <c r="K138" s="175"/>
-      <c r="L138" s="176"/>
+      <c r="E138" s="254"/>
+      <c r="F138" s="254"/>
+      <c r="G138" s="254"/>
+      <c r="H138" s="254"/>
+      <c r="I138" s="254"/>
+      <c r="J138" s="255"/>
+      <c r="K138" s="263"/>
+      <c r="L138" s="264"/>
     </row>
     <row r="139" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="124">
@@ -6043,17 +6043,17 @@
       </c>
       <c r="B139" s="124"/>
       <c r="C139" s="126"/>
-      <c r="D139" s="169" t="s">
+      <c r="D139" s="253" t="s">
         <v>83</v>
       </c>
-      <c r="E139" s="170"/>
-      <c r="F139" s="170"/>
-      <c r="G139" s="170"/>
-      <c r="H139" s="170"/>
-      <c r="I139" s="170"/>
-      <c r="J139" s="171"/>
-      <c r="K139" s="168"/>
-      <c r="L139" s="168"/>
+      <c r="E139" s="254"/>
+      <c r="F139" s="254"/>
+      <c r="G139" s="254"/>
+      <c r="H139" s="254"/>
+      <c r="I139" s="254"/>
+      <c r="J139" s="255"/>
+      <c r="K139" s="256"/>
+      <c r="L139" s="256"/>
     </row>
     <row r="140" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="124">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="B140" s="124"/>
       <c r="C140" s="126"/>
-      <c r="D140" s="169" t="s">
+      <c r="D140" s="253" t="s">
         <v>84</v>
       </c>
-      <c r="E140" s="170"/>
-      <c r="F140" s="170"/>
-      <c r="G140" s="170"/>
-      <c r="H140" s="170"/>
-      <c r="I140" s="170"/>
-      <c r="J140" s="171"/>
-      <c r="K140" s="168"/>
-      <c r="L140" s="168"/>
+      <c r="E140" s="254"/>
+      <c r="F140" s="254"/>
+      <c r="G140" s="254"/>
+      <c r="H140" s="254"/>
+      <c r="I140" s="254"/>
+      <c r="J140" s="255"/>
+      <c r="K140" s="256"/>
+      <c r="L140" s="256"/>
     </row>
     <row r="141" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="124">
@@ -6079,17 +6079,17 @@
       </c>
       <c r="B141" s="124"/>
       <c r="C141" s="126"/>
-      <c r="D141" s="172" t="s">
+      <c r="D141" s="257" t="s">
         <v>85</v>
       </c>
-      <c r="E141" s="173"/>
-      <c r="F141" s="173"/>
-      <c r="G141" s="173"/>
-      <c r="H141" s="173"/>
-      <c r="I141" s="173"/>
-      <c r="J141" s="174"/>
-      <c r="K141" s="168"/>
-      <c r="L141" s="168"/>
+      <c r="E141" s="258"/>
+      <c r="F141" s="258"/>
+      <c r="G141" s="258"/>
+      <c r="H141" s="258"/>
+      <c r="I141" s="258"/>
+      <c r="J141" s="259"/>
+      <c r="K141" s="256"/>
+      <c r="L141" s="256"/>
     </row>
     <row r="142" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6101,6 +6101,150 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="168">
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="D134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="D136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="D140:J140"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="D141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="D139:J139"/>
+    <mergeCell ref="K139:L139"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:J130"/>
+    <mergeCell ref="K129:L130"/>
+    <mergeCell ref="F88:J88"/>
+    <mergeCell ref="M88:R88"/>
+    <mergeCell ref="M95:R95"/>
+    <mergeCell ref="M96:R96"/>
+    <mergeCell ref="M97:R97"/>
+    <mergeCell ref="M98:R98"/>
+    <mergeCell ref="M99:R99"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="D126:I126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="M87:R87"/>
+    <mergeCell ref="M73:R73"/>
+    <mergeCell ref="F75:K75"/>
+    <mergeCell ref="M75:R75"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="O78:R78"/>
+    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="M83:R83"/>
+    <mergeCell ref="M84:R84"/>
+    <mergeCell ref="M85:R85"/>
+    <mergeCell ref="M86:R86"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M72:R72"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="B52:C53"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C63:K64"/>
+    <mergeCell ref="M71:R71"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="P20:P53"/>
+    <mergeCell ref="Q20:Q53"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L20:L53"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N27:O27"/>
     <mergeCell ref="B38:C39"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="K18:K19"/>
@@ -6125,155 +6269,11 @@
     <mergeCell ref="B34:C35"/>
     <mergeCell ref="B36:C37"/>
     <mergeCell ref="B20:C21"/>
-    <mergeCell ref="P20:P53"/>
-    <mergeCell ref="Q20:Q53"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="L20:L53"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M72:R72"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="B52:C53"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="C63:K64"/>
-    <mergeCell ref="M71:R71"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="M87:R87"/>
-    <mergeCell ref="M73:R73"/>
-    <mergeCell ref="F75:K75"/>
-    <mergeCell ref="M75:R75"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="O78:R78"/>
-    <mergeCell ref="O81:R81"/>
-    <mergeCell ref="M83:R83"/>
-    <mergeCell ref="M84:R84"/>
-    <mergeCell ref="M85:R85"/>
-    <mergeCell ref="M86:R86"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:J130"/>
-    <mergeCell ref="K129:L130"/>
-    <mergeCell ref="F88:J88"/>
-    <mergeCell ref="M88:R88"/>
-    <mergeCell ref="M95:R95"/>
-    <mergeCell ref="M96:R96"/>
-    <mergeCell ref="M97:R97"/>
-    <mergeCell ref="M98:R98"/>
-    <mergeCell ref="M99:R99"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="D140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="D141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="D139:J139"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="D134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="D136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="N49:O49"/>
   </mergeCells>
   <phoneticPr fontId="40" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="71" fitToWidth="2" fitToHeight="3" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" fitToWidth="2" fitToHeight="3" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="64" max="18" man="1"/>
     <brk id="120" max="18" man="1"/>
